--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="1758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="1759">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,154 +38,154 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469533920288</t>
+    <t xml:space="preserve">0.933469414710999</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927027225494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921873509883881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901902735233307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898037612438202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652415275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835475444794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643546581268</t>
+    <t xml:space="preserve">0.923806250095367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927027106285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873390674591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901902675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898037493228912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835356235504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643606185913</t>
   </si>
   <si>
     <t xml:space="preserve">0.863893926143646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841346383094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653814315796</t>
+    <t xml:space="preserve">0.841346442699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85165399312973</t>
   </si>
   <si>
     <t xml:space="preserve">0.818154752254486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836192607879639</t>
+    <t xml:space="preserve">0.836192727088928</t>
   </si>
   <si>
     <t xml:space="preserve">0.856163442134857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857451796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869692146778107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88644152879715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489830970764</t>
+    <t xml:space="preserve">0.857451856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869692087173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441648006439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489890575409</t>
   </si>
   <si>
     <t xml:space="preserve">0.908344984054565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888374269008636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84327906370163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798899650574</t>
+    <t xml:space="preserve">0.888373911380768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551917552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279123306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798840045929</t>
   </si>
   <si>
     <t xml:space="preserve">0.837481141090393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825240910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432898521423</t>
+    <t xml:space="preserve">0.825240969657898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432838916779</t>
   </si>
   <si>
     <t xml:space="preserve">0.869047701358795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876778244972229</t>
+    <t xml:space="preserve">0.876778364181519</t>
   </si>
   <si>
     <t xml:space="preserve">0.894172132015228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923161923885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142727851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709466934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296681880951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075646877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941200077533722</t>
+    <t xml:space="preserve">0.923161864280701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671492099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142787456512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709586143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296503067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075527667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199839115143</t>
   </si>
   <si>
     <t xml:space="preserve">0.947642147541046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930892467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113621711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412303447723</t>
+    <t xml:space="preserve">0.930892407894135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113562107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412184238434</t>
   </si>
   <si>
     <t xml:space="preserve">0.918008148670197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95408433675766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391648769379</t>
+    <t xml:space="preserve">0.954084098339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391708374023</t>
   </si>
   <si>
     <t xml:space="preserve">0.999179422855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01270806789398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02881348133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0165730714798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365970611572</t>
+    <t xml:space="preserve">1.01270794868469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02881324291229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01657319068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365958690643</t>
   </si>
   <si>
     <t xml:space="preserve">1.00819849967957</t>
@@ -203,19 +203,19 @@
     <t xml:space="preserve">1.02172684669495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464068889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999823808670044</t>
+    <t xml:space="preserve">1.01464056968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237117290497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999823570251465</t>
   </si>
   <si>
     <t xml:space="preserve">1.01141953468323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01206350326538</t>
+    <t xml:space="preserve">1.01206362247467</t>
   </si>
   <si>
     <t xml:space="preserve">1.01786172389984</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">1.02430379390717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01850593090057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02688074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203439712524</t>
+    <t xml:space="preserve">1.01850569248199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0268806219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203451633453</t>
   </si>
   <si>
     <t xml:space="preserve">1.0249480009079</t>
@@ -239,49 +239,49 @@
     <t xml:space="preserve">1.01721751689911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00562143325806</t>
+    <t xml:space="preserve">1.00562167167664</t>
   </si>
   <si>
     <t xml:space="preserve">0.988871872425079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00368881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03525543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02816903591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04040920734406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03396713733673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02945744991302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03010189533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01592910289764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992092907428741</t>
+    <t xml:space="preserve">1.00368893146515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0352555513382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02816915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04040932655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03396701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0294576883316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01592886447906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992093026638031</t>
   </si>
   <si>
     <t xml:space="preserve">1.03332281112671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00948679447174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958387851715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314180850983</t>
+    <t xml:space="preserve">1.00948691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958268642426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995313942432404</t>
   </si>
   <si>
     <t xml:space="preserve">1.0210827589035</t>
@@ -293,31 +293,31 @@
     <t xml:space="preserve">1.07519698143005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06295680999756</t>
+    <t xml:space="preserve">1.06295669078827</t>
   </si>
   <si>
     <t xml:space="preserve">1.05715894699097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07326412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06231272220612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04749572277069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06360101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0616682767868</t>
+    <t xml:space="preserve">1.07326436042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06231260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04749548435211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06360113620758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06166839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.06811058521271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04620718955994</t>
+    <t xml:space="preserve">1.04620707035065</t>
   </si>
   <si>
     <t xml:space="preserve">0.977275967597961</t>
@@ -326,55 +326,55 @@
     <t xml:space="preserve">0.968257069587708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965036153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978564500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522625923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232966899872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517346858978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712280750275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964926719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701484203339</t>
+    <t xml:space="preserve">0.965035915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564560413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522387504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232847690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907712340354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876964867115021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701663017273</t>
   </si>
   <si>
     <t xml:space="preserve">0.895680606365204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929101467132568</t>
+    <t xml:space="preserve">0.929101586341858</t>
   </si>
   <si>
     <t xml:space="preserve">0.935117304325104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939127624034882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048974514008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033256530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915733218193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925090909004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775331497192</t>
+    <t xml:space="preserve">0.939127743244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909049034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033196926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915733098983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925090968608856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775271892548</t>
   </si>
   <si>
     <t xml:space="preserve">0.925759375095367</t>
@@ -386,19 +386,19 @@
     <t xml:space="preserve">0.921080529689789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92709618806839</t>
+    <t xml:space="preserve">0.927096366882324</t>
   </si>
   <si>
     <t xml:space="preserve">0.945143640041351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937122583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955838263034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95316469669342</t>
+    <t xml:space="preserve">0.937122464179993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95583838224411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164577484131</t>
   </si>
   <si>
     <t xml:space="preserve">0.964527666568756</t>
@@ -407,31 +407,31 @@
     <t xml:space="preserve">0.965196073055267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982574939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98391193151474</t>
+    <t xml:space="preserve">0.982575058937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98391181230545</t>
   </si>
   <si>
     <t xml:space="preserve">0.972548842430115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973217129707336</t>
+    <t xml:space="preserve">0.973217248916626</t>
   </si>
   <si>
     <t xml:space="preserve">0.984580218791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99527496099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259302616119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601156234741</t>
+    <t xml:space="preserve">0.987253904342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995274841785431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98925906419754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601275444031</t>
   </si>
   <si>
     <t xml:space="preserve">0.975890815258026</t>
@@ -440,58 +440,58 @@
     <t xml:space="preserve">0.951827764511108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950491011142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485672473907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94113302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501450061798</t>
+    <t xml:space="preserve">0.950490772724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941132962703705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501330852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.965864598751068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985917150974274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927709102631</t>
+    <t xml:space="preserve">0.985917031764984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927470684052</t>
   </si>
   <si>
     <t xml:space="preserve">1.01265382766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02000653743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99193274974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988590598106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996611714363098</t>
+    <t xml:space="preserve">1.02000641822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99193286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988590717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996611833572388</t>
   </si>
   <si>
     <t xml:space="preserve">0.979901254177094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967201232910156</t>
+    <t xml:space="preserve">0.967201352119446</t>
   </si>
   <si>
     <t xml:space="preserve">0.986585438251495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977896094322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885715007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943367481232</t>
+    <t xml:space="preserve">0.977896213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943486690521</t>
   </si>
   <si>
     <t xml:space="preserve">1.02401697635651</t>
@@ -503,25 +503,25 @@
     <t xml:space="preserve">1.00262761116028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206631183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975222408771515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248744487762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0293642282486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05342745780945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05543267726898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07615339756012</t>
+    <t xml:space="preserve">0.969206750392914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975222289562225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248625278473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936434745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05342733860016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05543255805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07615351676941</t>
   </si>
   <si>
     <t xml:space="preserve">1.0895220041275</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">1.09687447547913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07013773918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08751666545868</t>
+    <t xml:space="preserve">1.07013785839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08751654624939</t>
   </si>
   <si>
     <t xml:space="preserve">1.09353256225586</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">1.07749044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479048728943</t>
+    <t xml:space="preserve">1.06479036808014</t>
   </si>
   <si>
     <t xml:space="preserve">1.06278514862061</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06813251972198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05209040641785</t>
+    <t xml:space="preserve">1.06813275814056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05209052562714</t>
   </si>
   <si>
     <t xml:space="preserve">0.957843542098999</t>
@@ -572,34 +572,34 @@
     <t xml:space="preserve">0.946480393409729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935785710811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469954490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780491352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727879524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738437652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94180154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406784534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538343906403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569660663605</t>
+    <t xml:space="preserve">0.93578577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727939128876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738497257233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941801428794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406844139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538165092468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869877815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569779872894</t>
   </si>
   <si>
     <t xml:space="preserve">0.994606554508209</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">0.9979487657547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01332223415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01532757282257</t>
+    <t xml:space="preserve">1.01332235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01532745361328</t>
   </si>
   <si>
     <t xml:space="preserve">1.0159957408905</t>
@@ -620,46 +620,46 @@
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203785419464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04005908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04473805427551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070104122162</t>
+    <t xml:space="preserve">1.03203797340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04005897045135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04473793506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03070116043091</t>
   </si>
   <si>
     <t xml:space="preserve">1.01733267307281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03604829311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874837398529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04941689968109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275893211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05008518695831</t>
+    <t xml:space="preserve">1.036048412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494167804718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275905132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0500853061676</t>
   </si>
   <si>
     <t xml:space="preserve">1.04072737693787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04607462882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0106486082077</t>
+    <t xml:space="preserve">1.04607474803925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02468538284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01064848899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.00530123710632</t>
@@ -671,25 +671,25 @@
     <t xml:space="preserve">1.04273271560669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334856987</t>
+    <t xml:space="preserve">1.02334845066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05610108375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05810630321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484315872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07080614566803</t>
+    <t xml:space="preserve">1.06412196159363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0561009645462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05810618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484303951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07080626487732</t>
   </si>
   <si>
     <t xml:space="preserve">1.0821692943573</t>
@@ -698,28 +698,28 @@
     <t xml:space="preserve">1.06880104541779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07815873622894</t>
+    <t xml:space="preserve">1.07815885543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.08283770084381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08818519115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09620630741119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09954810142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754288196564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628495693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978464603424</t>
+    <t xml:space="preserve">1.0881849527359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09620606899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628483772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978476524353</t>
   </si>
   <si>
     <t xml:space="preserve">1.22120046615601</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">1.22988986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24058437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26665282249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28002107143402</t>
+    <t xml:space="preserve">1.24058449268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2666529417038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28002119064331</t>
   </si>
   <si>
     <t xml:space="preserve">1.28336310386658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29405796527863</t>
+    <t xml:space="preserve">1.29405784606934</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133166790009</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">1.30074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31010031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475270748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007362365723</t>
+    <t xml:space="preserve">1.31010007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007386207581</t>
   </si>
   <si>
     <t xml:space="preserve">1.3114367723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29004740715027</t>
+    <t xml:space="preserve">1.29004752635956</t>
   </si>
   <si>
     <t xml:space="preserve">1.28871059417725</t>
@@ -794,34 +794,34 @@
     <t xml:space="preserve">1.29338943958282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814717292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30341577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349454402924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35421574115753</t>
+    <t xml:space="preserve">1.32814729213715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30341589450836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683669567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35421550273895</t>
   </si>
   <si>
     <t xml:space="preserve">1.37025761604309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37426805496216</t>
+    <t xml:space="preserve">1.37426817417145</t>
   </si>
   <si>
     <t xml:space="preserve">1.364910364151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37961530685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33616828918457</t>
+    <t xml:space="preserve">1.37961542606354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33616816997528</t>
   </si>
   <si>
     <t xml:space="preserve">1.34886801242828</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">1.41036260128021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42105734348297</t>
+    <t xml:space="preserve">1.42105746269226</t>
   </si>
   <si>
     <t xml:space="preserve">1.43175208568573</t>
@@ -848,31 +848,31 @@
     <t xml:space="preserve">1.41303658485413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43442571163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704702377319</t>
+    <t xml:space="preserve">1.43442559242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4170469045639</t>
   </si>
   <si>
     <t xml:space="preserve">1.42239427566528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40902602672577</t>
+    <t xml:space="preserve">1.40902590751648</t>
   </si>
   <si>
     <t xml:space="preserve">1.43977320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44779419898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052049636841</t>
+    <t xml:space="preserve">1.44779407978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052025794983</t>
   </si>
   <si>
     <t xml:space="preserve">1.46784687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46116256713867</t>
+    <t xml:space="preserve">1.46116268634796</t>
   </si>
   <si>
     <t xml:space="preserve">1.47319412231445</t>
@@ -881,37 +881,37 @@
     <t xml:space="preserve">1.46249938011169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46651005744934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4847424030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48336637020111</t>
+    <t xml:space="preserve">1.46650993824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48474252223969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48336625099182</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024641513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47235810756683</t>
+    <t xml:space="preserve">1.47235786914825</t>
   </si>
   <si>
     <t xml:space="preserve">1.4228208065033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44208538532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4063081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3953001499176</t>
+    <t xml:space="preserve">1.44208526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40630841255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39530003070831</t>
   </si>
   <si>
     <t xml:space="preserve">1.39942812919617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40080416202545</t>
+    <t xml:space="preserve">1.40080404281616</t>
   </si>
   <si>
     <t xml:space="preserve">1.40218031406403</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">1.43658113479614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.432452917099</t>
+    <t xml:space="preserve">1.43245315551758</t>
   </si>
   <si>
     <t xml:space="preserve">1.42419683933258</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">1.45997369289398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44621324539185</t>
+    <t xml:space="preserve">1.44621336460114</t>
   </si>
   <si>
     <t xml:space="preserve">1.46685397624969</t>
@@ -953,28 +953,28 @@
     <t xml:space="preserve">1.48199045658112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46960604190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923839092255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125503540039</t>
+    <t xml:space="preserve">1.46960592269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.447589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400698184967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125479698181</t>
   </si>
   <si>
     <t xml:space="preserve">1.49987876415253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50675904750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602350711823</t>
+    <t xml:space="preserve">1.50675892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602338790894</t>
   </si>
   <si>
     <t xml:space="preserve">1.54804003238678</t>
@@ -983,49 +983,49 @@
     <t xml:space="preserve">1.54115974903107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52327132225037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189528942108</t>
+    <t xml:space="preserve">1.52327156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189517021179</t>
   </si>
   <si>
     <t xml:space="preserve">1.54528796672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968902587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831251621246</t>
+    <t xml:space="preserve">1.57968878746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831263542175</t>
   </si>
   <si>
     <t xml:space="preserve">1.57556068897247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57693696022034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56317615509033</t>
+    <t xml:space="preserve">1.57693672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56317639350891</t>
   </si>
   <si>
     <t xml:space="preserve">1.54666388034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55354380607605</t>
+    <t xml:space="preserve">1.55354416370392</t>
   </si>
   <si>
     <t xml:space="preserve">1.56592845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58381712436676</t>
+    <t xml:space="preserve">1.58381700515747</t>
   </si>
   <si>
     <t xml:space="preserve">1.59069716930389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58656883239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58244097232819</t>
+    <t xml:space="preserve">1.58656907081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5824408531189</t>
   </si>
   <si>
     <t xml:space="preserve">1.60996150970459</t>
@@ -1034,52 +1034,52 @@
     <t xml:space="preserve">1.63197815418243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711463451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408960819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583353042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60032951831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978371620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565585613251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180024147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042444705963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427982330322</t>
+    <t xml:space="preserve">1.64711499214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408972740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583364963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5645524263382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978383541107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5356559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180036067963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941630363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427970409393</t>
   </si>
   <si>
     <t xml:space="preserve">1.57005655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868064403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6168417930603</t>
+    <t xml:space="preserve">1.56868040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234604358673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61684155464172</t>
   </si>
   <si>
     <t xml:space="preserve">1.62922608852386</t>
@@ -1088,28 +1088,28 @@
     <t xml:space="preserve">1.61133754253387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59482514858246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66087484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353221893311</t>
+    <t xml:space="preserve">1.59482550621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5728086233139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6182177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509787082672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66087508201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637885570526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940423965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353209972382</t>
   </si>
   <si>
     <t xml:space="preserve">1.69802796840668</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">1.69252383708954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986670017242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62784993648529</t>
+    <t xml:space="preserve">1.64023458957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949892997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986681938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785005569458</t>
   </si>
   <si>
     <t xml:space="preserve">1.6622508764267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67601156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490777492523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105299472809</t>
+    <t xml:space="preserve">1.67601132392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490789413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74894118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105275630951</t>
   </si>
   <si>
     <t xml:space="preserve">1.72004437446594</t>
@@ -1151,37 +1151,37 @@
     <t xml:space="preserve">1.73518085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72830057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76682984828949</t>
+    <t xml:space="preserve">1.72830092906952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618899822235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76682960987091</t>
   </si>
   <si>
     <t xml:space="preserve">1.77233386039734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76545369625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370989322662</t>
+    <t xml:space="preserve">1.76545357704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7737101316452</t>
   </si>
   <si>
     <t xml:space="preserve">1.74068510532379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8204950094223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022204875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747010231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444543361664</t>
+    <t xml:space="preserve">1.82049489021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747022151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444531440735</t>
   </si>
   <si>
     <t xml:space="preserve">1.79159843921661</t>
@@ -1190,22 +1190,22 @@
     <t xml:space="preserve">1.79297435283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76820552349091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75857353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554862499237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967648506165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142064571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169324874878</t>
+    <t xml:space="preserve">1.7682056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7585734128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142040729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169336795807</t>
   </si>
   <si>
     <t xml:space="preserve">1.81499075889587</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">1.80535876750946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031721591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700776100159</t>
+    <t xml:space="preserve">1.75031733512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481308460236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921402454376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700728416443</t>
   </si>
   <si>
     <t xml:space="preserve">1.85351991653442</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">1.86039984226227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88516879081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076797008514</t>
+    <t xml:space="preserve">1.88516855239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076785087585</t>
   </si>
   <si>
     <t xml:space="preserve">1.81361484527588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80123066902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710257053375</t>
+    <t xml:space="preserve">1.80123043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710233211517</t>
   </si>
   <si>
     <t xml:space="preserve">1.7957261800766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82737505435944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564343452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738699913025</t>
+    <t xml:space="preserve">1.82737517356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564391136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573836326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738735675812</t>
   </si>
   <si>
     <t xml:space="preserve">1.63473033905029</t>
@@ -1274,22 +1274,22 @@
     <t xml:space="preserve">1.66913104057312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6801393032074</t>
+    <t xml:space="preserve">1.68013942241669</t>
   </si>
   <si>
     <t xml:space="preserve">1.64298641681671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66500294208527</t>
+    <t xml:space="preserve">1.66500306129456</t>
   </si>
   <si>
     <t xml:space="preserve">1.68701958656311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69114792346954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6333544254303</t>
+    <t xml:space="preserve">1.69114756584167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
   </si>
   <si>
     <t xml:space="preserve">1.67463541030884</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">1.71454036235809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70215582847595</t>
+    <t xml:space="preserve">1.70215606689453</t>
   </si>
   <si>
     <t xml:space="preserve">1.69527578353882</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">1.67876350879669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6526186466217</t>
+    <t xml:space="preserve">1.65261852741241</t>
   </si>
   <si>
     <t xml:space="preserve">1.75306940078735</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">1.74756515026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73930895328522</t>
+    <t xml:space="preserve">1.73930907249451</t>
   </si>
   <si>
     <t xml:space="preserve">1.72417271137238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72692465782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362702846527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289160728455</t>
+    <t xml:space="preserve">1.72692489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362679004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289148807526</t>
   </si>
   <si>
     <t xml:space="preserve">1.71316432952881</t>
@@ -1343,100 +1343,100 @@
     <t xml:space="preserve">1.73380482196808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74206101894379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6883956193924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65399467945099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849042892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757721424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620130062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290355205536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49299871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
+    <t xml:space="preserve">1.74206113815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7599493265152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178829669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839585781097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399491786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849054813385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720944404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757733345032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620118141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134996414185</t>
   </si>
   <si>
     <t xml:space="preserve">1.4764860868454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48611855506897</t>
+    <t xml:space="preserve">1.48611843585968</t>
   </si>
   <si>
     <t xml:space="preserve">1.4751101732254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4572217464447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832505702972</t>
+    <t xml:space="preserve">1.45722162723541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832493782043</t>
   </si>
   <si>
     <t xml:space="preserve">1.51776719093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55079197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542112350464</t>
+    <t xml:space="preserve">1.55079209804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542124271393</t>
   </si>
   <si>
     <t xml:space="preserve">1.56530702114105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54826200008392</t>
+    <t xml:space="preserve">1.54826188087463</t>
   </si>
   <si>
     <t xml:space="preserve">1.52411472797394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121674060822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127373218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837586402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672751903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
+    <t xml:space="preserve">1.5312168598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127385139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837598323822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672739982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55536425113678</t>
   </si>
   <si>
     <t xml:space="preserve">1.56246614456177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59513592720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507893562317</t>
+    <t xml:space="preserve">1.59513604640961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507881641388</t>
   </si>
   <si>
     <t xml:space="preserve">1.60934019088745</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">1.62212383747101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58945417404175</t>
+    <t xml:space="preserve">1.58945441246033</t>
   </si>
   <si>
     <t xml:space="preserve">1.5795111656189</t>
@@ -1454,25 +1454,25 @@
     <t xml:space="preserve">1.60223805904388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60365843772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371566772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63632833957672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348746299744</t>
+    <t xml:space="preserve">1.60365855693817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371554851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63632822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348734378815</t>
   </si>
   <si>
     <t xml:space="preserve">1.62638509273529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61076068878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58803379535675</t>
+    <t xml:space="preserve">1.61076056957245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58803403377533</t>
   </si>
   <si>
     <t xml:space="preserve">1.59229516983032</t>
@@ -1481,43 +1481,43 @@
     <t xml:space="preserve">1.68888413906097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68178176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69882678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013306617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729230880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911198616028</t>
+    <t xml:space="preserve">1.68178188800812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69882702827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013294696808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729207038879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911210536957</t>
   </si>
   <si>
     <t xml:space="preserve">1.66757750511169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67894113063812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752063274384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343023300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928308010101</t>
+    <t xml:space="preserve">1.67894089221954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752039432526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183899879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.643430352211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61928296089172</t>
   </si>
   <si>
     <t xml:space="preserve">1.61786282062531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57667064666748</t>
+    <t xml:space="preserve">1.57667028903961</t>
   </si>
   <si>
     <t xml:space="preserve">1.56388652324677</t>
@@ -1526,34 +1526,34 @@
     <t xml:space="preserve">1.55962562561035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55394351482391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55252313613892</t>
+    <t xml:space="preserve">1.5539436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55252325534821</t>
   </si>
   <si>
     <t xml:space="preserve">1.55110275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51701271533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559233665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871829032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43462789058685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44741201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45735478401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47155904769897</t>
+    <t xml:space="preserve">1.51701259613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559221744537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871817111969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43462800979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44741189479828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45735490322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47155916690826</t>
   </si>
   <si>
     <t xml:space="preserve">1.47013854980469</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">1.47297942638397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5326372385025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58377265930176</t>
+    <t xml:space="preserve">1.53263735771179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58377277851105</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973948955536</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">1.51275134086609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4871838092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47724068164825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144506454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138795375824</t>
+    <t xml:space="preserve">1.48718392848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138819217682</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996757507324</t>
@@ -1592,103 +1592,103 @@
     <t xml:space="preserve">1.49570620059967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41687285900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42184436321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911735057831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065183162689</t>
+    <t xml:space="preserve">1.41687273979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4218442440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065195083618</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426006793976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3522435426712</t>
+    <t xml:space="preserve">1.35224366188049</t>
   </si>
   <si>
     <t xml:space="preserve">1.37994170188904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37070906162262</t>
+    <t xml:space="preserve">1.37070894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573755741119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37923157215118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37212932109833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35579454898834</t>
+    <t xml:space="preserve">1.37923169136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37212944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35579466819763</t>
   </si>
   <si>
     <t xml:space="preserve">1.38633370399475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3643171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39343583583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130520820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35863542556763</t>
+    <t xml:space="preserve">1.36431705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39343571662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130508899689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35863530635834</t>
   </si>
   <si>
     <t xml:space="preserve">1.40906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40124797821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46019577980042</t>
+    <t xml:space="preserve">1.40124821662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46019566059113</t>
   </si>
   <si>
     <t xml:space="preserve">1.45309352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47439992427826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866117954254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593428611755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894637584686</t>
+    <t xml:space="preserve">1.47439980506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866129875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593440532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894661426544</t>
   </si>
   <si>
     <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39556658267975</t>
+    <t xml:space="preserve">1.39556646347046</t>
   </si>
   <si>
     <t xml:space="preserve">1.37568056583405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38704395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37781095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40266847610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38136219978333</t>
+    <t xml:space="preserve">1.3870438337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201533794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37781119346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40266871452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38136231899261</t>
   </si>
   <si>
     <t xml:space="preserve">1.3351982831955</t>
@@ -1697,49 +1697,49 @@
     <t xml:space="preserve">1.36076593399048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940266609192</t>
+    <t xml:space="preserve">1.34940254688263</t>
   </si>
   <si>
     <t xml:space="preserve">1.43178713321686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43320751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468500137329</t>
+    <t xml:space="preserve">1.43320763111115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468523979187</t>
   </si>
   <si>
     <t xml:space="preserve">1.4204238653183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48150193691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48860418796539</t>
+    <t xml:space="preserve">1.48150217533112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985335350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4886040687561</t>
   </si>
   <si>
     <t xml:space="preserve">1.49428582191467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54258024692535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115998744965</t>
+    <t xml:space="preserve">1.54258012771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
     <t xml:space="preserve">1.52553522586823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52979636192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52695560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405785560608</t>
+    <t xml:space="preserve">1.52979648113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52695572376251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405773639679</t>
   </si>
   <si>
     <t xml:space="preserve">1.51133096218109</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">1.50991034507751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48008167743683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49854707717896</t>
+    <t xml:space="preserve">1.48008179664612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49854719638824</t>
   </si>
   <si>
     <t xml:space="preserve">1.50706970691681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48292255401611</t>
+    <t xml:space="preserve">1.4829226732254</t>
   </si>
   <si>
     <t xml:space="preserve">1.48434281349182</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">1.61644232273102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62780570983887</t>
+    <t xml:space="preserve">1.62780559062958</t>
   </si>
   <si>
     <t xml:space="preserve">1.63206708431244</t>
@@ -1784,16 +1784,16 @@
     <t xml:space="preserve">1.62496483325958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59939730167389</t>
+    <t xml:space="preserve">1.59939742088318</t>
   </si>
   <si>
     <t xml:space="preserve">1.62070345878601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502182483673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627122879028</t>
+    <t xml:space="preserve">1.61502194404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627146720886</t>
   </si>
   <si>
     <t xml:space="preserve">1.61218106746674</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">1.51417171955109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50422871112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576331138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303653717041</t>
+    <t xml:space="preserve">1.50422883033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576319217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303641796112</t>
   </si>
   <si>
     <t xml:space="preserve">1.45877528190613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49286532402039</t>
+    <t xml:space="preserve">1.49286544322968</t>
   </si>
   <si>
     <t xml:space="preserve">1.55678451061249</t>
@@ -1823,40 +1823,40 @@
     <t xml:space="preserve">1.57809066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58661329746246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382953166962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916897773743</t>
+    <t xml:space="preserve">1.58661341667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738297700882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916921615601</t>
   </si>
   <si>
     <t xml:space="preserve">1.70450866222382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70166766643524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69061779975891</t>
+    <t xml:space="preserve">1.70166778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6906179189682</t>
   </si>
   <si>
     <t xml:space="preserve">1.69356322288513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69798099994659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294573783875</t>
+    <t xml:space="preserve">1.69798111915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294597625732</t>
   </si>
   <si>
     <t xml:space="preserve">1.68325448036194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68619966506958</t>
+    <t xml:space="preserve">1.68619978427887</t>
   </si>
   <si>
     <t xml:space="preserve">1.7289069890976</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">1.75099718570709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76277828216553</t>
+    <t xml:space="preserve">1.76277840137482</t>
   </si>
   <si>
     <t xml:space="preserve">1.74510633945465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73332500457764</t>
+    <t xml:space="preserve">1.73332536220551</t>
   </si>
   <si>
     <t xml:space="preserve">1.77161407470703</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.77750492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79812204837799</t>
+    <t xml:space="preserve">1.79812216758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.8010675907135</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">1.80401301383972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81137633323669</t>
+    <t xml:space="preserve">1.8113762140274</t>
   </si>
   <si>
     <t xml:space="preserve">1.77455985546112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77603220939636</t>
+    <t xml:space="preserve">1.77603244781494</t>
   </si>
   <si>
     <t xml:space="preserve">1.76719653606415</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">1.74216103553772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70239925384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73921585083008</t>
+    <t xml:space="preserve">1.70239913463593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921573162079</t>
   </si>
   <si>
     <t xml:space="preserve">1.7701416015625</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">1.78486835956573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78928625583649</t>
+    <t xml:space="preserve">1.78928637504578</t>
   </si>
   <si>
     <t xml:space="preserve">1.79664957523346</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">1.79517686367035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79370450973511</t>
+    <t xml:space="preserve">1.79370427131653</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79959511756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254018306732</t>
+    <t xml:space="preserve">1.79959487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254030227661</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308702468872</t>
@@ -1946,46 +1946,46 @@
     <t xml:space="preserve">1.78192293643951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83493912220001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021200656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81873941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168471813202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966540336609</t>
+    <t xml:space="preserve">1.83493888378143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8202121257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81873953342438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82168483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966564178467</t>
   </si>
   <si>
     <t xml:space="preserve">1.84819293022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82904827594757</t>
+    <t xml:space="preserve">1.82904803752899</t>
   </si>
   <si>
     <t xml:space="preserve">1.76425087451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81432139873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990350246429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199334144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8614467382431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91593515872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655264377594</t>
+    <t xml:space="preserve">1.81432151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.809903383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319935798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91593539714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655288219452</t>
   </si>
   <si>
     <t xml:space="preserve">1.93213486671448</t>
@@ -1997,64 +1997,64 @@
     <t xml:space="preserve">1.97042393684387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95569694042206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94244337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96158802509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809623718262</t>
+    <t xml:space="preserve">1.95569741725922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980645179749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9615877866745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809599876404</t>
   </si>
   <si>
     <t xml:space="preserve">1.99693191051483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00724029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.983677983284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987733364105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0057680606842</t>
+    <t xml:space="preserve">2.00724053382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98367774486542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987709522247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576782226562</t>
   </si>
   <si>
     <t xml:space="preserve">1.98073267936707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97189629077911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97631466388702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94391620159149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96895110607147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600592136383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484183311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01754927635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04847526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02049422264099</t>
+    <t xml:space="preserve">1.97189652919769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97631442546844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94391596317291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96895134449005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600615978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484159469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01754903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04847502708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02049446105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.04552984237671</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">2.03227591514587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04111194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03816628456116</t>
+    <t xml:space="preserve">2.04111170768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03816652297974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01018595695496</t>
@@ -2084,37 +2084,37 @@
     <t xml:space="preserve">2.00871300697327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99251413345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02638530731201</t>
+    <t xml:space="preserve">1.99251389503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02638506889343</t>
   </si>
   <si>
     <t xml:space="preserve">2.07940101623535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467413902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0720374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06172871589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03522133827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933049201965</t>
+    <t xml:space="preserve">2.06467437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07203769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03522086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933073043823</t>
   </si>
   <si>
     <t xml:space="preserve">2.06614708900452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676433563232</t>
+    <t xml:space="preserve">2.07645535469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0867645740509</t>
   </si>
   <si>
     <t xml:space="preserve">2.02196717262268</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">2.11032676696777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1368350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10885453224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12652635574341</t>
+    <t xml:space="preserve">2.13683485984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10885429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12652611732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.17659687995911</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">2.19426870346069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2458119392395</t>
+    <t xml:space="preserve">2.24581217765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">2.21341347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20899558067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21783137321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20163178443909</t>
+    <t xml:space="preserve">2.20899534225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2178316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20163202285767</t>
   </si>
   <si>
     <t xml:space="preserve">2.20752263069153</t>
@@ -2195,25 +2195,25 @@
     <t xml:space="preserve">2.17365121841431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23255825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21930360794067</t>
+    <t xml:space="preserve">2.23255801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21930384635925</t>
   </si>
   <si>
     <t xml:space="preserve">2.21635866165161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20310473442078</t>
+    <t xml:space="preserve">2.20310497283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.24728441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28704643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201105117798</t>
+    <t xml:space="preserve">2.2870466709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201128959656</t>
   </si>
   <si>
     <t xml:space="preserve">2.25023007392883</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">2.1147449016571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11621761322021</t>
+    <t xml:space="preserve">2.11621785163879</t>
   </si>
   <si>
     <t xml:space="preserve">2.15303421020508</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">2.13094425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02491235733032</t>
+    <t xml:space="preserve">2.0249125957489</t>
   </si>
   <si>
     <t xml:space="preserve">2.08823704719543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10296368598938</t>
+    <t xml:space="preserve">2.1029634475708</t>
   </si>
   <si>
     <t xml:space="preserve">1.98220527172089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83641159534454</t>
+    <t xml:space="preserve">1.83641135692596</t>
   </si>
   <si>
     <t xml:space="preserve">1.65380120277405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63318383693695</t>
+    <t xml:space="preserve">1.63318407535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724911212921</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">1.42921996116638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35190522670746</t>
+    <t xml:space="preserve">1.35190510749817</t>
   </si>
   <si>
     <t xml:space="preserve">1.35043251514435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30330729484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36442303657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32171559333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31508874893188</t>
+    <t xml:space="preserve">1.30330717563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36442291736603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32171547412872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3150886297226</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565741062164</t>
@@ -2285,28 +2285,28 @@
     <t xml:space="preserve">1.49475359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948011875153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58311331272125</t>
+    <t xml:space="preserve">1.50948023796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58311355113983</t>
   </si>
   <si>
     <t xml:space="preserve">1.65674650669098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55071473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54776930809021</t>
+    <t xml:space="preserve">1.55071485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54776954650879</t>
   </si>
   <si>
     <t xml:space="preserve">1.5359879732132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56249606609344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56102335453033</t>
+    <t xml:space="preserve">1.56249618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56102323532104</t>
   </si>
   <si>
     <t xml:space="preserve">1.55366003513336</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">1.54924213886261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54187893867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58164072036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60225796699524</t>
+    <t xml:space="preserve">1.54187905788422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58164060115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60225808620453</t>
   </si>
   <si>
     <t xml:space="preserve">1.62434804439545</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">1.64643788337708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65527355670929</t>
+    <t xml:space="preserve">1.65527379512787</t>
   </si>
   <si>
     <t xml:space="preserve">1.67589128017426</t>
@@ -2357,73 +2357,73 @@
     <t xml:space="preserve">1.57575011253357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58753132820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5580780506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427716255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5904768705368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784018993378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64202010631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558265686035</t>
+    <t xml:space="preserve">1.58753144741058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55807816982269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427752017975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047675132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59784007072449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64201998710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558253765106</t>
   </si>
   <si>
     <t xml:space="preserve">1.62876582145691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61109375953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6788364648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859848499298</t>
+    <t xml:space="preserve">1.61109399795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67883634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859872341156</t>
   </si>
   <si>
     <t xml:space="preserve">1.76572370529175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75836026668549</t>
+    <t xml:space="preserve">1.75836038589478</t>
   </si>
   <si>
     <t xml:space="preserve">1.7200710773468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7082896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907468318939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70534443855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71123504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756798267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836562156677</t>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821945667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70534455776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71123492717743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756810188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
     <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69781506061554</t>
+    <t xml:space="preserve">1.69781517982483</t>
   </si>
   <si>
     <t xml:space="preserve">1.71161878108978</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">1.72542190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73462438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73769164085388</t>
+    <t xml:space="preserve">1.73462426662445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73769176006317</t>
   </si>
   <si>
     <t xml:space="preserve">1.73002302646637</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">1.68707919120789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68554520606995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327582836151</t>
+    <t xml:space="preserve">1.68554556369781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327558994293</t>
   </si>
   <si>
     <t xml:space="preserve">1.65793871879578</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">1.68401205539703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241641998291</t>
+    <t xml:space="preserve">1.70241618156433</t>
   </si>
   <si>
     <t xml:space="preserve">1.72235441207886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7070175409317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66867470741272</t>
+    <t xml:space="preserve">1.70701742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66867482662201</t>
   </si>
   <si>
     <t xml:space="preserve">1.64566898345947</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">1.65333759784698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.656405210495</t>
+    <t xml:space="preserve">1.65640509128571</t>
   </si>
   <si>
     <t xml:space="preserve">1.6272646188736</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">1.63646697998047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64720284938812</t>
+    <t xml:space="preserve">1.64720273017883</t>
   </si>
   <si>
     <t xml:space="preserve">1.67020845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407382488251</t>
+    <t xml:space="preserve">1.66407370567322</t>
   </si>
   <si>
     <t xml:space="preserve">1.68247818946838</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">1.75609600543976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72695565223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70088255405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72082090377808</t>
+    <t xml:space="preserve">1.72695577144623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70088267326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72082078456879</t>
   </si>
   <si>
     <t xml:space="preserve">1.69321405887604</t>
@@ -2534,34 +2534,34 @@
     <t xml:space="preserve">1.67174208164215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6993488073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787683010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69014668464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008503437042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861281871796</t>
+    <t xml:space="preserve">1.69934892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6778769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69014656543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861269950867</t>
   </si>
   <si>
     <t xml:space="preserve">1.65180385112762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64873647689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62573075294495</t>
+    <t xml:space="preserve">1.64873659610748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62573063373566</t>
   </si>
   <si>
     <t xml:space="preserve">1.61959612369537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659039974213</t>
+    <t xml:space="preserve">1.59659051895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505653381348</t>
@@ -2582,43 +2582,43 @@
     <t xml:space="preserve">1.55057919025421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4999668598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48156225681305</t>
+    <t xml:space="preserve">1.49996674060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48156237602234</t>
   </si>
   <si>
     <t xml:space="preserve">1.4961324930191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50303435325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51990485191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54751169681549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5643824338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53064107894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60425889492035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59198927879333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59965777397156</t>
+    <t xml:space="preserve">1.50303423404694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51990497112274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5475115776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56438255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53064095973969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60425901412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59198915958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59965765476227</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.614994764328</t>
+    <t xml:space="preserve">1.61499488353729</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125340938568</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60272514820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6610062122345</t>
+    <t xml:space="preserve">1.60272526741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66100609302521</t>
   </si>
   <si>
     <t xml:space="preserve">1.74075901508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76069724559784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388792037964</t>
+    <t xml:space="preserve">1.76069736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388803958893</t>
   </si>
   <si>
     <t xml:space="preserve">1.69628131389618</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63033187389374</t>
+    <t xml:space="preserve">1.63033199310303</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889219045639</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">1.6103937625885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61346125602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585453033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63953411579132</t>
+    <t xml:space="preserve">1.61346137523651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585464954376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6395343542099</t>
   </si>
   <si>
     <t xml:space="preserve">1.64260149002075</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">1.65947246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66714096069336</t>
+    <t xml:space="preserve">1.66714119911194</t>
   </si>
   <si>
     <t xml:space="preserve">1.62266337871552</t>
@@ -2690,40 +2690,40 @@
     <t xml:space="preserve">1.55518043041229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56131517887115</t>
+    <t xml:space="preserve">1.55671393871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57051742076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597813129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278691768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60732638835907</t>
+    <t xml:space="preserve">1.57051730155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55978143215179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278703689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60732626914978</t>
   </si>
   <si>
     <t xml:space="preserve">1.63339948654175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192739009857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58432078361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61806225776672</t>
+    <t xml:space="preserve">1.62419712543488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192762851715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58432066440582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61806213855743</t>
   </si>
   <si>
     <t xml:space="preserve">1.64106798171997</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">1.665607213974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67480957508087</t>
+    <t xml:space="preserve">1.67480945587158</t>
   </si>
   <si>
     <t xml:space="preserve">1.71775329113007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517470836639</t>
+    <t xml:space="preserve">1.75762975215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517494678497</t>
   </si>
   <si>
     <t xml:space="preserve">1.81744432449341</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">1.80824208259583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80670833587646</t>
+    <t xml:space="preserve">1.80670857429504</t>
   </si>
   <si>
     <t xml:space="preserve">1.80364108085632</t>
@@ -2765,19 +2765,19 @@
     <t xml:space="preserve">1.82051193714142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78063523769379</t>
+    <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
     <t xml:space="preserve">1.79443871974945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83278155326843</t>
+    <t xml:space="preserve">1.83278179168701</t>
   </si>
   <si>
     <t xml:space="preserve">1.80977582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.829714179039</t>
+    <t xml:space="preserve">1.82971394062042</t>
   </si>
   <si>
     <t xml:space="preserve">1.85885453224182</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">1.83891642093658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82818055152893</t>
+    <t xml:space="preserve">1.82818031311035</t>
   </si>
   <si>
     <t xml:space="preserve">1.86498939990997</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">1.85578715801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86345565319061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965217113495</t>
+    <t xml:space="preserve">1.8634557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965240955353</t>
   </si>
   <si>
     <t xml:space="preserve">1.87112426757812</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">1.90026450157166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100096702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627594947815</t>
+    <t xml:space="preserve">1.91100072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627571105957</t>
   </si>
   <si>
     <t xml:space="preserve">1.95394456386566</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">1.91713547706604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93553984165192</t>
+    <t xml:space="preserve">1.93553996086121</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695004940033</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">1.9600795507431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382078647614</t>
+    <t xml:space="preserve">1.99382054805756</t>
   </si>
   <si>
     <t xml:space="preserve">1.96621406078339</t>
@@ -2852,34 +2852,34 @@
     <t xml:space="preserve">2.00609064102173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00762438774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00915765762329</t>
+    <t xml:space="preserve">2.00762414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375889778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00915789604187</t>
   </si>
   <si>
     <t xml:space="preserve">1.95701193809509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95854556560516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96928191184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97848391532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00302290916443</t>
+    <t xml:space="preserve">1.95854580402374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9692816734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9784836769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00302314758301</t>
   </si>
   <si>
     <t xml:space="preserve">2.01069188117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836013793945</t>
+    <t xml:space="preserve">2.01836037635803</t>
   </si>
   <si>
     <t xml:space="preserve">2.0290961265564</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01682662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01631903648376</t>
+    <t xml:space="preserve">2.01682686805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
     <t xml:space="preserve">1.99563097953796</t>
@@ -2900,19 +2900,19 @@
     <t xml:space="preserve">1.97335124015808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97175979614258</t>
+    <t xml:space="preserve">1.97175967693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.9447056055069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92242586612701</t>
+    <t xml:space="preserve">1.92242610454559</t>
   </si>
   <si>
     <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9144686460495</t>
+    <t xml:space="preserve">1.91446888446808</t>
   </si>
   <si>
     <t xml:space="preserve">1.90332901477814</t>
@@ -2924,22 +2924,22 @@
     <t xml:space="preserve">1.92720007896423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9797168970108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96061968803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95743715763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539402008057</t>
+    <t xml:space="preserve">1.97971665859222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96061992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95743691921234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539425849915</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926532268524</t>
+    <t xml:space="preserve">1.98926508426666</t>
   </si>
   <si>
     <t xml:space="preserve">1.96857678890228</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">2.03223323822021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01950216293335</t>
+    <t xml:space="preserve">2.01950192451477</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">2.02427649497986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06247019767761</t>
+    <t xml:space="preserve">2.06247043609619</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07997584342957</t>
+    <t xml:space="preserve">2.07997608184814</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">2.10543823242188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13726687431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522361755371</t>
+    <t xml:space="preserve">2.13726663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.18819189071655</t>
@@ -3044,22 +3044,22 @@
     <t xml:space="preserve">2.14840650558472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12135219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1165783405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11339545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612652778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363217353821</t>
+    <t xml:space="preserve">2.12135243415833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11657810211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11339569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249230384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363241195679</t>
   </si>
   <si>
     <t xml:space="preserve">2.04178190231323</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04019045829773</t>
+    <t xml:space="preserve">2.04019021987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.09588980674744</t>
@@ -3083,19 +3083,19 @@
     <t xml:space="preserve">1.98767375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01154518127441</t>
+    <t xml:space="preserve">2.01154541969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341755867004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18978333473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023490905762</t>
+    <t xml:space="preserve">2.18341732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18978357315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023467063904</t>
   </si>
   <si>
     <t xml:space="preserve">2.16113805770874</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">2.25343990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29481649398804</t>
+    <t xml:space="preserve">2.29481625556946</t>
   </si>
   <si>
     <t xml:space="preserve">2.23593425750732</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">2.25025701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27571964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27890229225159</t>
+    <t xml:space="preserve">2.27571940422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.22161149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23115992546082</t>
+    <t xml:space="preserve">2.23115968704224</t>
   </si>
   <si>
     <t xml:space="preserve">2.200923204422</t>
@@ -3170,34 +3170,34 @@
     <t xml:space="preserve">2.10702967643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07520151138306</t>
+    <t xml:space="preserve">2.07520174980164</t>
   </si>
   <si>
     <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08634161949158</t>
+    <t xml:space="preserve">2.086341381073</t>
   </si>
   <si>
     <t xml:space="preserve">2.14204072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09748125076294</t>
+    <t xml:space="preserve">2.09748148918152</t>
   </si>
   <si>
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06883597373962</t>
+    <t xml:space="preserve">2.09111571311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06883573532104</t>
   </si>
   <si>
     <t xml:space="preserve">2.01472783088684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02905035018921</t>
+    <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
     <t xml:space="preserve">1.9781254529953</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128623485565</t>
+    <t xml:space="preserve">1.91128599643707</t>
   </si>
   <si>
     <t xml:space="preserve">1.89378046989441</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">1.90651178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87945795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8126186132431</t>
+    <t xml:space="preserve">1.87945771217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261885166168</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">1.83171534538269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82534968852997</t>
+    <t xml:space="preserve">1.82534992694855</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82694101333618</t>
+    <t xml:space="preserve">1.82694125175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444665908813</t>
+    <t xml:space="preserve">1.84444689750671</t>
   </si>
   <si>
     <t xml:space="preserve">1.88423228263855</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">1.98289966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0035879611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94311428070068</t>
+    <t xml:space="preserve">2.00358772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9431140422821</t>
   </si>
   <si>
     <t xml:space="preserve">1.93197441101074</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786638736725</t>
+    <t xml:space="preserve">1.87786626815796</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038320541382</t>
+    <t xml:space="preserve">1.93038296699524</t>
   </si>
   <si>
     <t xml:space="preserve">1.93993139266968</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">1.84285545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71235942840576</t>
+    <t xml:space="preserve">1.71235954761505</t>
   </si>
   <si>
     <t xml:space="preserve">1.64233732223511</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">1.66143441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65984296798706</t>
+    <t xml:space="preserve">1.65984284877777</t>
   </si>
   <si>
     <t xml:space="preserve">1.69007992744446</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">1.6168749332428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483179569244</t>
+    <t xml:space="preserve">1.62483191490173</t>
   </si>
   <si>
     <t xml:space="preserve">1.65506863594055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70758521556854</t>
+    <t xml:space="preserve">1.70758533477783</t>
   </si>
   <si>
     <t xml:space="preserve">1.69644546508789</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68848836421967</t>
+    <t xml:space="preserve">1.68848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435811519623</t>
@@ -3416,16 +3416,16 @@
     <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57151961326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57788527011871</t>
+    <t xml:space="preserve">1.57151973247528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.577885389328</t>
   </si>
   <si>
     <t xml:space="preserve">1.5850465297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58743369579315</t>
+    <t xml:space="preserve">1.58743381500244</t>
   </si>
   <si>
     <t xml:space="preserve">1.54128265380859</t>
@@ -5286,6 +5286,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.68600010871887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66199994087219</t>
   </si>
 </sst>
 </file>
@@ -70260,7 +70263,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6496412037</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>978894</v>
@@ -70281,6 +70284,32 @@
         <v>1757</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493287037</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>827979</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>2.68600010871887</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>2.64199995994568</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>2.68600010871887</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>2.66199994087219</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="1763">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,64 +44,64 @@
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92702716588974</t>
+    <t xml:space="preserve">0.923806071281433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927027225494385</t>
   </si>
   <si>
     <t xml:space="preserve">0.921873509883881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901902735233307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898037552833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652474880219</t>
+    <t xml:space="preserve">0.901902675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898037493228912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652415275574</t>
   </si>
   <si>
     <t xml:space="preserve">0.903835475444794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880643725395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863894164562225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346263885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192667484283</t>
+    <t xml:space="preserve">0.880643665790558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863894045352936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346442699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851653873920441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154633045197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192607879639</t>
   </si>
   <si>
     <t xml:space="preserve">0.856163382530212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857451856136322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869691908359528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441588401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489830970764</t>
+    <t xml:space="preserve">0.857451736927032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691967964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441648006439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489771366119</t>
   </si>
   <si>
     <t xml:space="preserve">0.908344924449921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888374090194702</t>
+    <t xml:space="preserve">0.888374209403992</t>
   </si>
   <si>
     <t xml:space="preserve">0.85551929473877</t>
@@ -113,136 +113,136 @@
     <t xml:space="preserve">0.818798899650574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837480962276459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825240910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432898521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869047820568085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778364181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172132015228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161864280701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671372890472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142847061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709466934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296622276306</t>
+    <t xml:space="preserve">0.837481021881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869047701358795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923161923885345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671432495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142906665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709347724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296741485596</t>
   </si>
   <si>
     <t xml:space="preserve">0.916075468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941200017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947641968727112</t>
+    <t xml:space="preserve">0.941199839115143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642028331757</t>
   </si>
   <si>
     <t xml:space="preserve">0.930892407894135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412303447723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918008089065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954084396362305</t>
+    <t xml:space="preserve">0.934113502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412243843079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008148670197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954084098339081</t>
   </si>
   <si>
     <t xml:space="preserve">0.964391708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999179363250732</t>
+    <t xml:space="preserve">0.999179303646088</t>
   </si>
   <si>
     <t xml:space="preserve">1.01270794868469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02881348133087</t>
+    <t xml:space="preserve">1.02881360054016</t>
   </si>
   <si>
     <t xml:space="preserve">1.01657319068909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02365946769714</t>
+    <t xml:space="preserve">1.02365970611572</t>
   </si>
   <si>
     <t xml:space="preserve">1.00819849967957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00175642967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00497722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755417346954</t>
+    <t xml:space="preserve">1.00175619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497734546661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755429267883</t>
   </si>
   <si>
     <t xml:space="preserve">1.02172684669495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464056968689</t>
+    <t xml:space="preserve">1.01464068889618</t>
   </si>
   <si>
     <t xml:space="preserve">1.02237129211426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999823570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01141965389252</t>
+    <t xml:space="preserve">0.999823689460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01141953468323</t>
   </si>
   <si>
     <t xml:space="preserve">1.01206374168396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01786172389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430379390717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01850593090057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0268806219101</t>
+    <t xml:space="preserve">1.01786160469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430391311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01850581169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02688074111938</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203451633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0249480009079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01721739768982</t>
+    <t xml:space="preserve">1.02494812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0172176361084</t>
   </si>
   <si>
     <t xml:space="preserve">1.00562155246735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988872051239014</t>
+    <t xml:space="preserve">0.988871991634369</t>
   </si>
   <si>
     <t xml:space="preserve">1.00368881225586</t>
@@ -251,43 +251,43 @@
     <t xml:space="preserve">1.03525543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02816915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04040908813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03396701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02945756912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01592886447906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992093026638031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.033322930336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00948703289032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958268642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314121246338</t>
+    <t xml:space="preserve">1.02816891670227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04040920734406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03396713733673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0294576883316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03010165691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01592898368835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992092907428741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03332304954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00948691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958507061005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995314180850983</t>
   </si>
   <si>
     <t xml:space="preserve">1.0210827589035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0494282245636</t>
+    <t xml:space="preserve">1.04942834377289</t>
   </si>
   <si>
     <t xml:space="preserve">1.07519686222076</t>
@@ -296,121 +296,121 @@
     <t xml:space="preserve">1.06295680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05715906620026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07326412200928</t>
+    <t xml:space="preserve">1.05715882778168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07326436042786</t>
   </si>
   <si>
     <t xml:space="preserve">1.06231260299683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04749572277069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06360113620758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06166851520538</t>
+    <t xml:space="preserve">1.0474956035614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06360101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06166839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.06811058521271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04620730876923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977276027202606</t>
+    <t xml:space="preserve">1.04620718955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977276086807251</t>
   </si>
   <si>
     <t xml:space="preserve">0.968256950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965035796165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978564500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522387504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232907295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517168045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712161540985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964867115021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701603412628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680785179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101526737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117423534393</t>
+    <t xml:space="preserve">0.965035915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564381599426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522625923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979233086109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90771222114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87696498632431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701663017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680606365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117304325104</t>
   </si>
   <si>
     <t xml:space="preserve">0.939127802848816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909048914909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033316135406</t>
+    <t xml:space="preserve">0.909049034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033256530762</t>
   </si>
   <si>
     <t xml:space="preserve">0.915733098983765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925090968608856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775271892548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925759375095367</t>
+    <t xml:space="preserve">0.925091087818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775331497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925759434700012</t>
   </si>
   <si>
     <t xml:space="preserve">0.912391126155853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921080589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927096426486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143699645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122523784637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95583838224411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164637088776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527726173401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196132659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982574999332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98391181230545</t>
+    <t xml:space="preserve">0.921080410480499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927096307277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143640041351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122404575348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838263034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527666568756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196073055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982575058937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98391193151474</t>
   </si>
   <si>
     <t xml:space="preserve">0.972548842430115</t>
@@ -422,73 +422,73 @@
     <t xml:space="preserve">0.984580218791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987253725528717</t>
+    <t xml:space="preserve">0.987254023551941</t>
   </si>
   <si>
     <t xml:space="preserve">0.99527496099472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989259243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601275444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890755653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827824115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950490891933441</t>
+    <t xml:space="preserve">0.989259302616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99260151386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890934467316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827764511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950491011142731</t>
   </si>
   <si>
     <t xml:space="preserve">0.948485672473907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941133141517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501569271088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864479541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917031764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927649497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01265382766724</t>
+    <t xml:space="preserve">0.941132962703705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501211643219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864658355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927351474762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01265406608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.02000641822815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991932988166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988590836524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996611773967743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901194572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967201411724091</t>
+    <t xml:space="preserve">0.99193274974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988590717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996611714363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901254177094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201471328735</t>
   </si>
   <si>
     <t xml:space="preserve">0.986585438251495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977896213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885655403137</t>
+    <t xml:space="preserve">0.977896094322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885595798492</t>
   </si>
   <si>
     <t xml:space="preserve">0.995943367481232</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">1.02401685714722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00864338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00262749195099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969206511974335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97522234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248744487762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0293642282486</t>
+    <t xml:space="preserve">1.00864326953888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00262761116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969206631183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975222408771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248625278473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936434745789</t>
   </si>
   <si>
     <t xml:space="preserve">1.05342745780945</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">1.09420084953308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09687471389771</t>
+    <t xml:space="preserve">1.09687459468842</t>
   </si>
   <si>
     <t xml:space="preserve">1.07013785839081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08751666545868</t>
+    <t xml:space="preserve">1.08751654624939</t>
   </si>
   <si>
     <t xml:space="preserve">1.09353256225586</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">1.07749044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479036808014</t>
+    <t xml:space="preserve">1.06479060649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.06278514862061</t>
@@ -557,208 +557,208 @@
     <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06813251972198</t>
+    <t xml:space="preserve">1.06813263893127</t>
   </si>
   <si>
     <t xml:space="preserve">1.05209052562714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957843482494354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953833043575287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480333805084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93578565120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469894886017</t>
+    <t xml:space="preserve">0.957843422889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953833162784576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93578577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469835281372</t>
   </si>
   <si>
     <t xml:space="preserve">0.933780550956726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913728058338165</t>
+    <t xml:space="preserve">0.913727879524231</t>
   </si>
   <si>
     <t xml:space="preserve">0.917738437652588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941801607608795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538224697113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869699001312</t>
+    <t xml:space="preserve">0.94180154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406903743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869639396667</t>
   </si>
   <si>
     <t xml:space="preserve">0.980569779872894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994606494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948467731476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
+    <t xml:space="preserve">0.994606554508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99794864654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332211494446</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01599586009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02869582176208</t>
+    <t xml:space="preserve">1.01599597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0286957025528</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203785419464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04005897045135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04473769664764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070116043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0173327922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.036048412323</t>
+    <t xml:space="preserve">1.04005908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04473805427551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03070104122162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03604829311371</t>
   </si>
   <si>
     <t xml:space="preserve">1.04874837398529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04941701889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275905132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05008518695831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04072737693787</t>
+    <t xml:space="preserve">1.0494167804718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275893211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0500853061676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04072749614716</t>
   </si>
   <si>
     <t xml:space="preserve">1.04607474803925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02468538284302</t>
+    <t xml:space="preserve">1.02468550205231</t>
   </si>
   <si>
     <t xml:space="preserve">1.0106486082077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00530111789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03003263473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04273271560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02334845066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.056769490242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06412196159363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05610108375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05810618400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484315872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07080638408661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08216917514801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06880104541779</t>
+    <t xml:space="preserve">1.00530123710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03003287315369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0427325963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02334856987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05676937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06412208080292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0561009645462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05810630321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484303951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07080626487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0821692943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0688009262085</t>
   </si>
   <si>
     <t xml:space="preserve">1.07815885543823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0828378200531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08818519115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0962061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09954822063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754300117493</t>
+    <t xml:space="preserve">1.08283770084381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0881849527359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09620606899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754288196564</t>
   </si>
   <si>
     <t xml:space="preserve">1.12628495693207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18978464603424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120046615601</t>
+    <t xml:space="preserve">1.18978476524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22120034694672</t>
   </si>
   <si>
     <t xml:space="preserve">1.22988986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24058449268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26665270328522</t>
+    <t xml:space="preserve">1.24058437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26665282249451</t>
   </si>
   <si>
     <t xml:space="preserve">1.28002107143402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28336322307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29405808448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133190631866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932632923126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30074214935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009995937347</t>
+    <t xml:space="preserve">1.28336310386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29405796527863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2713315486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932644844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30074226856232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009984016418</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30007374286652</t>
+    <t xml:space="preserve">1.30007362365723</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143689155579</t>
@@ -770,46 +770,46 @@
     <t xml:space="preserve">1.28871059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29739999771118</t>
+    <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27200019359589</t>
+    <t xml:space="preserve">1.27200031280518</t>
   </si>
   <si>
     <t xml:space="preserve">1.2593001127243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29673171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806852340698</t>
+    <t xml:space="preserve">1.29673159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806840419769</t>
   </si>
   <si>
     <t xml:space="preserve">1.31076848506927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29338955879211</t>
+    <t xml:space="preserve">1.29338943958282</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814729213715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30341601371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683693408966</t>
+    <t xml:space="preserve">1.30341577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683669567108</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349466323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35421562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37025761604309</t>
+    <t xml:space="preserve">1.35421550273895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37025773525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426805496216</t>
@@ -824,31 +824,31 @@
     <t xml:space="preserve">1.33616840839386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34886825084686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39031028747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41036260128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42105734348297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175196647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4504679441452</t>
+    <t xml:space="preserve">1.34886813163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3903101682663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4103627204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42105722427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175208568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046806335449</t>
   </si>
   <si>
     <t xml:space="preserve">1.39966809749603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41303646564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442583084106</t>
+    <t xml:space="preserve">1.41303658485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442571163177</t>
   </si>
   <si>
     <t xml:space="preserve">1.4170469045639</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">1.40902578830719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43977308273315</t>
+    <t xml:space="preserve">1.43977320194244</t>
   </si>
   <si>
     <t xml:space="preserve">1.44779407978058</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">1.47052037715912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46784675121307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116268634796</t>
+    <t xml:space="preserve">1.46784687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">1.47319412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46249938011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46650981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4847424030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48336613178253</t>
+    <t xml:space="preserve">1.46249949932098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650993824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48474252223969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48336637020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024653434753</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">1.44208514690399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40630829334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3953001499176</t>
+    <t xml:space="preserve">1.4063081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39530003070831</t>
   </si>
   <si>
     <t xml:space="preserve">1.39942812919617</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">1.38429188728333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4145644903183</t>
+    <t xml:space="preserve">1.41456437110901</t>
   </si>
   <si>
     <t xml:space="preserve">1.42144465446472</t>
@@ -929,49 +929,49 @@
     <t xml:space="preserve">1.43658113479614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43245303630829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42419672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43107676506042</t>
+    <t xml:space="preserve">1.43245315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42419683933258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.431077003479</t>
   </si>
   <si>
     <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45997357368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44621348381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46685373783112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48199045658112</t>
+    <t xml:space="preserve">1.45997381210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44621324539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46685385704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48199033737183</t>
   </si>
   <si>
     <t xml:space="preserve">1.46960604190826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44758939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923827171326</t>
+    <t xml:space="preserve">1.447589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923815250397</t>
   </si>
   <si>
     <t xml:space="preserve">1.50400686264038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50125479698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50675904750824</t>
+    <t xml:space="preserve">1.50125467777252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987876415253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50675892829895</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602338790894</t>
@@ -980,19 +980,19 @@
     <t xml:space="preserve">1.54804003238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54115986824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52327144145966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189517021179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5452880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57968878746033</t>
+    <t xml:space="preserve">1.54115974903107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52327132225037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54528796672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57968902587891</t>
   </si>
   <si>
     <t xml:space="preserve">1.57831275463104</t>
@@ -1001,46 +1001,46 @@
     <t xml:space="preserve">1.57556068897247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57693672180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56317639350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5466639995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55354404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592845916748</t>
+    <t xml:space="preserve">1.57693684101105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5631765127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54666388034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55354416370392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592833995819</t>
   </si>
   <si>
     <t xml:space="preserve">1.58381688594818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59069728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656895160675</t>
+    <t xml:space="preserve">1.5906970500946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656907081604</t>
   </si>
   <si>
     <t xml:space="preserve">1.58244097232819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60996174812317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63197827339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711451530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408948898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583341121674</t>
+    <t xml:space="preserve">1.60996150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63197815418243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711475372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408960819244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583364963531</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003292798996</t>
@@ -1049,37 +1049,37 @@
     <t xml:space="preserve">1.56455254554749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53978371620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180059909821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427982330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005667686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868052482605</t>
+    <t xml:space="preserve">1.53978383541107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53565585613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180047988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941630363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427970409393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005655765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868028640747</t>
   </si>
   <si>
     <t xml:space="preserve">1.62234604358673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61684167385101</t>
+    <t xml:space="preserve">1.61684155464172</t>
   </si>
   <si>
     <t xml:space="preserve">1.62922620773315</t>
@@ -1088,91 +1088,91 @@
     <t xml:space="preserve">1.61133766174316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59482502937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280886173248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821782588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509787082672</t>
+    <t xml:space="preserve">1.59482538700104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5728086233139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509775161743</t>
   </si>
   <si>
     <t xml:space="preserve">1.66087508201599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66637897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7035323381424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802784919739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252407550812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986681938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66225099563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601132392883</t>
+    <t xml:space="preserve">1.66637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940412044525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353221893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6980277299881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252383708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023458957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949892997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986658096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.627849817276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6622508764267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601144313812</t>
   </si>
   <si>
     <t xml:space="preserve">1.70490789413452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74894154071808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105299472809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004461288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518109321594</t>
+    <t xml:space="preserve">1.7489413022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105275630951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004449367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518073558807</t>
   </si>
   <si>
     <t xml:space="preserve">1.72830080986023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74618923664093</t>
+    <t xml:space="preserve">1.74618899822235</t>
   </si>
   <si>
     <t xml:space="preserve">1.76682984828949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77233374118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545381546021</t>
+    <t xml:space="preserve">1.77233386039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545369625092</t>
   </si>
   <si>
     <t xml:space="preserve">1.77370989322662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74068486690521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8204950094223</t>
+    <t xml:space="preserve">1.7406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049489021301</t>
   </si>
   <si>
     <t xml:space="preserve">1.79022240638733</t>
@@ -1181,73 +1181,73 @@
     <t xml:space="preserve">1.78747010231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444543361664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159820079803</t>
+    <t xml:space="preserve">1.75444531440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159832000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79297411441803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76820576190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75857317447662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554862499237</t>
+    <t xml:space="preserve">1.76820552349091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75857353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554850578308</t>
   </si>
   <si>
     <t xml:space="preserve">1.72967672348022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169348716736</t>
+    <t xml:space="preserve">1.72142064571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169324874878</t>
   </si>
   <si>
     <t xml:space="preserve">1.81499087810516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80535888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031709671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481308460236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921378612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113562107086</t>
+    <t xml:space="preserve">1.80535876750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031733512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481320381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113585948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.8370076417923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85351991653442</t>
+    <t xml:space="preserve">1.853520154953</t>
   </si>
   <si>
     <t xml:space="preserve">1.86040019989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88516867160797</t>
+    <t xml:space="preserve">1.88516855239868</t>
   </si>
   <si>
     <t xml:space="preserve">1.85076797008514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81361496448517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123054981232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710245132446</t>
+    <t xml:space="preserve">1.81361508369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123066902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710233211517</t>
   </si>
   <si>
     <t xml:space="preserve">1.79572641849518</t>
@@ -1256,121 +1256,121 @@
     <t xml:space="preserve">1.82737517356873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68564343452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573848247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738735675812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473010063171</t>
+    <t xml:space="preserve">1.68564355373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573872089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738711833954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63473033905029</t>
   </si>
   <si>
     <t xml:space="preserve">1.68151557445526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66913139820099</t>
+    <t xml:space="preserve">1.66913115978241</t>
   </si>
   <si>
     <t xml:space="preserve">1.6801393032074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64298641681671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500294208527</t>
+    <t xml:space="preserve">1.64298629760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500306129456</t>
   </si>
   <si>
     <t xml:space="preserve">1.68701958656311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69114768505096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463529109955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454048156738</t>
+    <t xml:space="preserve">1.69114744663239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454036235809</t>
   </si>
   <si>
     <t xml:space="preserve">1.70215582847595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69527566432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426728248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876327037811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65261888504028</t>
+    <t xml:space="preserve">1.69527590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426764011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876315116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6526186466217</t>
   </si>
   <si>
     <t xml:space="preserve">1.75306928157806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930895328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417283058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692441940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362690925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289148807526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7131644487381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343693256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7338045835495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206125736237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178829669952</t>
+    <t xml:space="preserve">1.74756503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7393091917038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692465782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362702846527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316409111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343705177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380494117737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74206078052521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994944572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178817749023</t>
   </si>
   <si>
     <t xml:space="preserve">1.6883956193924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6539945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849054813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757733345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620118141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290367126465</t>
+    <t xml:space="preserve">1.65399467945099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720980167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757709503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620130062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290355205536</t>
   </si>
   <si>
     <t xml:space="preserve">1.49299871921539</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">1.4764860868454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48611855506897</t>
+    <t xml:space="preserve">1.48611831665039</t>
   </si>
   <si>
     <t xml:space="preserve">1.4751101732254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45722150802612</t>
+    <t xml:space="preserve">1.4572217464447</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832505702972</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">1.51776731014252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55079209804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542136192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530690193176</t>
+    <t xml:space="preserve">1.55079197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542124271393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530702114105</t>
   </si>
   <si>
     <t xml:space="preserve">1.54826200008392</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">1.52411472797394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121662139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127397060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837598323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672751903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246638298035</t>
+    <t xml:space="preserve">1.5312168598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127385139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837586402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672739982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5553640127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246614456177</t>
   </si>
   <si>
     <t xml:space="preserve">1.59513604640961</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">1.6221239566803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58945417404175</t>
+    <t xml:space="preserve">1.58945405483246</t>
   </si>
   <si>
     <t xml:space="preserve">1.5795111656189</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">1.60223817825317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60365843772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371554851532</t>
+    <t xml:space="preserve">1.60365855693817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371542930603</t>
   </si>
   <si>
     <t xml:space="preserve">1.62922608852386</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">1.63632822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63348746299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638521194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076045036316</t>
+    <t xml:space="preserve">1.63348734378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638509273529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076056957245</t>
   </si>
   <si>
     <t xml:space="preserve">1.58803379535675</t>
@@ -1481,85 +1481,85 @@
     <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6888839006424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68178188800812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69882678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013330459595</t>
+    <t xml:space="preserve">1.68888413906097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68178200721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69882702827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013318538666</t>
   </si>
   <si>
     <t xml:space="preserve">1.71729230880737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64911198616028</t>
+    <t xml:space="preserve">1.64911210536957</t>
   </si>
   <si>
     <t xml:space="preserve">1.66757750511169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67894089221954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752051353455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343023300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6192831993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61786293983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57667052745819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962550640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5539436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55252313613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55110287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51701259613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559233665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871829032898</t>
+    <t xml:space="preserve">1.67894101142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752027511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183911800385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343011379242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61928296089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61786305904388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5766704082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388652324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962538719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55394375324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55252325534821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55110275745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51701271533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559221744537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871817111969</t>
   </si>
   <si>
     <t xml:space="preserve">1.43462800979614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741201400757</t>
+    <t xml:space="preserve">1.44741189479828</t>
   </si>
   <si>
     <t xml:space="preserve">1.45735478401184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47155916690826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47013854980469</t>
+    <t xml:space="preserve">1.47155904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47013866901398</t>
   </si>
   <si>
     <t xml:space="preserve">1.47297942638397</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">1.53263735771179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58377265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973960876465</t>
+    <t xml:space="preserve">1.58377254009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973937034607</t>
   </si>
   <si>
     <t xml:space="preserve">1.51275146007538</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">1.4871838092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47724056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144506454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138795375824</t>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138807296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996757507324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49570631980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41687273979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4218442440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3991174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065207004547</t>
+    <t xml:space="preserve">1.49570620059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41687285900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42184436321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39911758899689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065195083618</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426006793976</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">1.37994170188904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37070906162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573755741119</t>
+    <t xml:space="preserve">1.37070894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3657374382019</t>
   </si>
   <si>
     <t xml:space="preserve">1.37923145294189</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">1.37212944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35579454898834</t>
+    <t xml:space="preserve">1.35579466819763</t>
   </si>
   <si>
     <t xml:space="preserve">1.38633370399475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431694030762</t>
+    <t xml:space="preserve">1.36431705951691</t>
   </si>
   <si>
     <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39130520820618</t>
+    <t xml:space="preserve">1.39130508899689</t>
   </si>
   <si>
     <t xml:space="preserve">1.35863530635834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40906035900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40124821662903</t>
+    <t xml:space="preserve">1.40906047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40124809741974</t>
   </si>
   <si>
     <t xml:space="preserve">1.46019566059113</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">1.47439992427826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47866117954254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593428611755</t>
+    <t xml:space="preserve">1.47866129875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593440532684</t>
   </si>
   <si>
     <t xml:space="preserve">1.42894649505615</t>
@@ -1682,19 +1682,19 @@
     <t xml:space="preserve">1.3870438337326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39201545715332</t>
+    <t xml:space="preserve">1.39201533794403</t>
   </si>
   <si>
     <t xml:space="preserve">1.3778110742569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40266859531403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38136219978333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33519840240479</t>
+    <t xml:space="preserve">1.40266871452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38136231899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351982831955</t>
   </si>
   <si>
     <t xml:space="preserve">1.36076593399048</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">1.34940254688263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320763111115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468523979187</t>
+    <t xml:space="preserve">1.43178725242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468512058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.4204238653183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48150205612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985359191895</t>
+    <t xml:space="preserve">1.48150181770325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985347270966</t>
   </si>
   <si>
     <t xml:space="preserve">1.4886040687561</t>
@@ -1733,40 +1733,40 @@
     <t xml:space="preserve">1.54115998744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52553498744965</t>
+    <t xml:space="preserve">1.52553522586823</t>
   </si>
   <si>
     <t xml:space="preserve">1.52979648113251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52695560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405785560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51133096218109</t>
+    <t xml:space="preserve">1.52695572376251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405773639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5113308429718</t>
   </si>
   <si>
     <t xml:space="preserve">1.50991034507751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48008167743683</t>
+    <t xml:space="preserve">1.48008179664612</t>
   </si>
   <si>
     <t xml:space="preserve">1.49854695796967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48292243480682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48434293270111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50564908981323</t>
+    <t xml:space="preserve">1.50706970691681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48292255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48434281349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50564920902252</t>
   </si>
   <si>
     <t xml:space="preserve">1.53689861297607</t>
@@ -1775,73 +1775,73 @@
     <t xml:space="preserve">1.61644232273102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62780570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206696510315</t>
+    <t xml:space="preserve">1.62780559062958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206708431244</t>
   </si>
   <si>
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496471405029</t>
+    <t xml:space="preserve">1.62496507167816</t>
   </si>
   <si>
     <t xml:space="preserve">1.59939730167389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62070369720459</t>
+    <t xml:space="preserve">1.6207035779953</t>
   </si>
   <si>
     <t xml:space="preserve">1.61502194404602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6462709903717</t>
+    <t xml:space="preserve">1.64627134799957</t>
   </si>
   <si>
     <t xml:space="preserve">1.61218118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5141716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50422871112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4857634305954</t>
+    <t xml:space="preserve">1.51417183876038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50422894954681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576331138611</t>
   </si>
   <si>
     <t xml:space="preserve">1.46303653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45877516269684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49286532402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5567843914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5780907869339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58661329746246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916921615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450878143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166766643524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
+    <t xml:space="preserve">1.45877528190613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49286544322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55678451061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57809066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58661341667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738297700882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916909694672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450842380524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6917245388031</t>
   </si>
   <si>
     <t xml:space="preserve">1.69061779975891</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">1.67294597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68325471878052</t>
+    <t xml:space="preserve">1.68325436115265</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619978427887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72890710830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75099694728851</t>
+    <t xml:space="preserve">1.7289069890976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7509970664978</t>
   </si>
   <si>
     <t xml:space="preserve">1.76277840137482</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">1.74510633945465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73332512378693</t>
+    <t xml:space="preserve">1.73332524299622</t>
   </si>
   <si>
     <t xml:space="preserve">1.77161419391632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77750504016876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812204837799</t>
+    <t xml:space="preserve">1.77750492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812216758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.8010675907135</t>
@@ -1892,55 +1892,55 @@
     <t xml:space="preserve">1.80548548698425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80401277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137645244598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603209018707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76719653606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216103553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239925384521</t>
+    <t xml:space="preserve">1.80401289463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455961704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76719629764557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216091632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239913463593</t>
   </si>
   <si>
     <t xml:space="preserve">1.7392156124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77014136314392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486835956573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928649425507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664957523346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79517698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370427131653</t>
+    <t xml:space="preserve">1.7701416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486812114716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928625583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79517686367035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370450973511</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79959499835968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254018306732</t>
+    <t xml:space="preserve">1.79959487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254030227661</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308690547943</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">1.83493900299072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8202121257782</t>
+    <t xml:space="preserve">1.82021224498749</t>
   </si>
   <si>
     <t xml:space="preserve">1.81873953342438</t>
@@ -1961,37 +1961,37 @@
     <t xml:space="preserve">1.82168483734131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84966552257538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84819269180298</t>
+    <t xml:space="preserve">1.84966564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84819281101227</t>
   </si>
   <si>
     <t xml:space="preserve">1.82904815673828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76425087451935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81432139873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8319935798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91593527793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655264377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213474750519</t>
+    <t xml:space="preserve">1.76425099372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81432151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990326404572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83199346065521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144709587097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91593539714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655288219452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213486671448</t>
   </si>
   <si>
     <t xml:space="preserve">1.95127928256989</t>
@@ -2000,40 +2000,40 @@
     <t xml:space="preserve">1.97042393684387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9424432516098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980669021606</t>
+    <t xml:space="preserve">1.95569717884064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244313240051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980645179749</t>
   </si>
   <si>
     <t xml:space="preserve">1.9615877866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98809587955475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693179130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00724053382874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.983677983284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987721443176</t>
+    <t xml:space="preserve">1.98809599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693167209625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00724077224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98367810249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987733364105</t>
   </si>
   <si>
     <t xml:space="preserve">2.00576758384705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073279857635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97189664840698</t>
+    <t xml:space="preserve">1.98073244094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97189652919769</t>
   </si>
   <si>
     <t xml:space="preserve">1.97631466388702</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">1.97484183311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01754927635193</t>
+    <t xml:space="preserve">2.01754903793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.04847502708435</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">2.02049446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04552960395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03374838829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05436587333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02785754203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227591514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111218452454</t>
+    <t xml:space="preserve">2.04552984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03374862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05436563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02785801887512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227567672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111170768738</t>
   </si>
   <si>
     <t xml:space="preserve">2.03816652297974</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">2.00871300697327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99251413345337</t>
+    <t xml:space="preserve">1.99251389503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.02638530731201</t>
@@ -2096,46 +2096,46 @@
     <t xml:space="preserve">2.07940077781677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467437744141</t>
+    <t xml:space="preserve">2.06467413902283</t>
   </si>
   <si>
     <t xml:space="preserve">2.0720374584198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06172919273376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03522086143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676433563232</t>
+    <t xml:space="preserve">2.06172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03522109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933049201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614708900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645535469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0867645740509</t>
   </si>
   <si>
     <t xml:space="preserve">2.02196717262268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05731081962585</t>
+    <t xml:space="preserve">2.05731105804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.07351040840149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04700231552124</t>
+    <t xml:space="preserve">2.04700207710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.00282263755798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313090324402</t>
+    <t xml:space="preserve">2.01313138008118</t>
   </si>
   <si>
     <t xml:space="preserve">2.01460409164429</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">2.04258441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11179947853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08087372779846</t>
+    <t xml:space="preserve">2.11179971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08087396621704</t>
   </si>
   <si>
     <t xml:space="preserve">2.0749831199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11032700538635</t>
+    <t xml:space="preserve">2.11032676696777</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">2.12652635574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17659664154053</t>
+    <t xml:space="preserve">2.17659687995911</t>
   </si>
   <si>
     <t xml:space="preserve">2.20457744598389</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">2.19426870346069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2458119392395</t>
+    <t xml:space="preserve">2.24581217765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21341347694397</t>
+    <t xml:space="preserve">2.21341323852539</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">2.21783137321472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20163226127625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20752286911011</t>
+    <t xml:space="preserve">2.20163202285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20752263069153</t>
   </si>
   <si>
     <t xml:space="preserve">2.17365121841431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23255801200867</t>
+    <t xml:space="preserve">2.23255825042725</t>
   </si>
   <si>
     <t xml:space="preserve">2.21930384635925</t>
@@ -2210,61 +2210,61 @@
     <t xml:space="preserve">2.20310497283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24728465080261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2870466709137</t>
+    <t xml:space="preserve">2.24728488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28704643249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.26201152801514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25023031234741</t>
+    <t xml:space="preserve">2.25022983551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.1147449016571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11621737480164</t>
+    <t xml:space="preserve">2.11621785163879</t>
   </si>
   <si>
     <t xml:space="preserve">2.1530339717865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13094401359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02491211891174</t>
+    <t xml:space="preserve">2.13094425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0249125957489</t>
   </si>
   <si>
     <t xml:space="preserve">2.08823680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10296368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83641123771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65380132198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63318395614624</t>
+    <t xml:space="preserve">2.1029634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220527172089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83641159534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65380120277405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63318407535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724911212921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42921996116638</t>
+    <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
     <t xml:space="preserve">1.35190510749817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043251514435</t>
+    <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330729484558</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">1.36442291736603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32171547412872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3150886297226</t>
+    <t xml:space="preserve">1.32171559333801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31508874893188</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565741062164</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">1.37767684459686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49475347995758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948011875153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58311331272125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674662590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071485042572</t>
+    <t xml:space="preserve">1.49475359916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948023796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58311343193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674650669098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071473121643</t>
   </si>
   <si>
     <t xml:space="preserve">1.5477694272995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53598821163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249594688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56102323532104</t>
+    <t xml:space="preserve">1.5359879732132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56102335453033</t>
   </si>
   <si>
     <t xml:space="preserve">1.55365991592407</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">1.54187893867493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58164060115814</t>
+    <t xml:space="preserve">1.58164072036743</t>
   </si>
   <si>
     <t xml:space="preserve">1.60225808620453</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">1.61256659030914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61698484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287521362305</t>
+    <t xml:space="preserve">1.61698472499847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287533283234</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643788337708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65527403354645</t>
+    <t xml:space="preserve">1.65527367591858</t>
   </si>
   <si>
     <t xml:space="preserve">1.67589116096497</t>
@@ -2351,94 +2351,94 @@
     <t xml:space="preserve">1.66705513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64349257946014</t>
+    <t xml:space="preserve">1.64349281787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.60520339012146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57575011253357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.587531208992</t>
+    <t xml:space="preserve">1.57574999332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58753144741058</t>
   </si>
   <si>
     <t xml:space="preserve">1.55807816982269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57427752017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047675132751</t>
+    <t xml:space="preserve">1.57427740097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047663211823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59784018993378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64201998710632</t>
+    <t xml:space="preserve">1.64201986789703</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558253765106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62876582145691</t>
+    <t xml:space="preserve">1.6287659406662</t>
   </si>
   <si>
     <t xml:space="preserve">1.61109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67883658409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76572382450104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75836038589478</t>
+    <t xml:space="preserve">1.6788364648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859848499298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76572370529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75836026668549</t>
   </si>
   <si>
     <t xml:space="preserve">1.72007119655609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7082896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907480239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821921825409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70534467697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71123504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756786346436</t>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70534455776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71123492717743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756810188293</t>
   </si>
   <si>
     <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71468591690063</t>
+    <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
     <t xml:space="preserve">1.69781517982483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7116185426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71621954441071</t>
+    <t xml:space="preserve">1.71161866188049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71621966362</t>
   </si>
   <si>
     <t xml:space="preserve">1.69168031215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548367500305</t>
+    <t xml:space="preserve">1.70548355579376</t>
   </si>
   <si>
     <t xml:space="preserve">1.72542202472687</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">1.73769152164459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73002314567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68707931041718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68554556369781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327570915222</t>
+    <t xml:space="preserve">1.73002326488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6870790719986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68554544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327558994293</t>
   </si>
   <si>
     <t xml:space="preserve">1.65793871879578</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">1.68401193618774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235465049744</t>
+    <t xml:space="preserve">1.70241630077362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235441207886</t>
   </si>
   <si>
     <t xml:space="preserve">1.7070175409317</t>
@@ -2486,88 +2486,88 @@
     <t xml:space="preserve">1.64566898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6533374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.656405210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62726449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63646686077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64720261096954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67020833492279</t>
+    <t xml:space="preserve">1.65333771705627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65640497207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6272646188736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63646697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64720284938812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67020857334137</t>
   </si>
   <si>
     <t xml:space="preserve">1.66407382488251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68247807025909</t>
+    <t xml:space="preserve">1.68247818946838</t>
   </si>
   <si>
     <t xml:space="preserve">1.7284893989563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73615777492523</t>
+    <t xml:space="preserve">1.73615765571594</t>
   </si>
   <si>
     <t xml:space="preserve">1.75609612464905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72695565223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70088255405426</t>
+    <t xml:space="preserve">1.72695577144623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70088267326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.72082078456879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69321382045746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094420433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67174220085144</t>
+    <t xml:space="preserve">1.69321393966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094432353973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67174208164215</t>
   </si>
   <si>
     <t xml:space="preserve">1.69934892654419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69014656543732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008503437042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861293792725</t>
+    <t xml:space="preserve">1.67787706851959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69014668464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008479595184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861281871796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65180397033691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64873647689819</t>
+    <t xml:space="preserve">1.64873659610748</t>
   </si>
   <si>
     <t xml:space="preserve">1.62573075294495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61959612369537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59659039974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505653381348</t>
+    <t xml:space="preserve">1.61959600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59659051895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505665302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.58738803863525</t>
@@ -2591,31 +2591,31 @@
     <t xml:space="preserve">1.48156237602234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4961324930191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50303435325623</t>
+    <t xml:space="preserve">1.49613261222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50303423404694</t>
   </si>
   <si>
     <t xml:space="preserve">1.51990497112274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54751181602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56438255310059</t>
+    <t xml:space="preserve">1.54751169681549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
     <t xml:space="preserve">1.53064095973969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60425901412964</t>
+    <t xml:space="preserve">1.60425889492035</t>
   </si>
   <si>
     <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965789318085</t>
+    <t xml:space="preserve">1.59965777397156</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
@@ -2624,31 +2624,31 @@
     <t xml:space="preserve">1.61499488353729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58125329017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57511830329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60272514820099</t>
+    <t xml:space="preserve">1.58125340938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57511842250824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60272526741028</t>
   </si>
   <si>
     <t xml:space="preserve">1.66100609302521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74075901508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069712638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388827800751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628131389618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186573982239</t>
+    <t xml:space="preserve">1.74075889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069724559784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388803958893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6318656206131</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">1.6103937625885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61346125602722</t>
+    <t xml:space="preserve">1.61346137523651</t>
   </si>
   <si>
     <t xml:space="preserve">1.58585453033447</t>
@@ -2675,22 +2675,22 @@
     <t xml:space="preserve">1.6395343542099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64260172843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63493299484253</t>
+    <t xml:space="preserve">1.64260149002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63493323326111</t>
   </si>
   <si>
     <t xml:space="preserve">1.65947246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66714096069336</t>
+    <t xml:space="preserve">1.66714107990265</t>
   </si>
   <si>
     <t xml:space="preserve">1.6226634979248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.555180311203</t>
+    <t xml:space="preserve">1.55518043041229</t>
   </si>
   <si>
     <t xml:space="preserve">1.55671393871307</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56898355484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55978155136108</t>
+    <t xml:space="preserve">1.56898367404938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57051742076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5597813129425</t>
   </si>
   <si>
     <t xml:space="preserve">1.58278703689575</t>
@@ -2717,79 +2717,79 @@
     <t xml:space="preserve">1.63339948654175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419700622559</t>
+    <t xml:space="preserve">1.62419712543488</t>
   </si>
   <si>
     <t xml:space="preserve">1.61192750930786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58432066440582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61806225776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106810092926</t>
+    <t xml:space="preserve">1.58432078361511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61806213855743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106798171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.66560733318329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67480957508087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71775341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75762975215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8174444437027</t>
+    <t xml:space="preserve">1.67480945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71775329113007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517494678497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81744432449341</t>
   </si>
   <si>
     <t xml:space="preserve">1.8082423210144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80670857429504</t>
+    <t xml:space="preserve">1.80670845508575</t>
   </si>
   <si>
     <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903960227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290521144867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82051169872284</t>
+    <t xml:space="preserve">1.79903984069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290533065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82051193714142</t>
   </si>
   <si>
     <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79443895816803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83278155326843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8097757101059</t>
+    <t xml:space="preserve">1.79443848133087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83278167247772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80977582931519</t>
   </si>
   <si>
     <t xml:space="preserve">1.82971405982971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885453224182</t>
+    <t xml:space="preserve">1.85885441303253</t>
   </si>
   <si>
     <t xml:space="preserve">1.83891654014587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82818043231964</t>
+    <t xml:space="preserve">1.82818055152893</t>
   </si>
   <si>
     <t xml:space="preserve">1.86498951911926</t>
@@ -2798,58 +2798,58 @@
     <t xml:space="preserve">1.8557870388031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86345601081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965217113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87112426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89566349983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90179836750031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91866934299469</t>
+    <t xml:space="preserve">1.8634557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87112414836884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89566326141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90179848670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9186692237854</t>
   </si>
   <si>
     <t xml:space="preserve">1.90026450157166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100084781647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627606868744</t>
+    <t xml:space="preserve">1.91100072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627571105957</t>
   </si>
   <si>
     <t xml:space="preserve">1.95394456386566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9156014919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173683643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713559627533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553960323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007907390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382090568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621417999268</t>
+    <t xml:space="preserve">1.91560161113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173647880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553996086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695004940033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007931232452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382054805756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9662139415741</t>
   </si>
   <si>
     <t xml:space="preserve">2.00609064102173</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">2.00762414932251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01375913619995</t>
+    <t xml:space="preserve">2.01375889778137</t>
   </si>
   <si>
     <t xml:space="preserve">2.00915789604187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9570118188858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854544639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9692816734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97848379611969</t>
+    <t xml:space="preserve">1.95701193809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854532718658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96928155422211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9784836769104</t>
   </si>
   <si>
     <t xml:space="preserve">2.00302290916443</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">2.01069164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836037635803</t>
+    <t xml:space="preserve">2.01836013793945</t>
   </si>
   <si>
     <t xml:space="preserve">2.0290961265564</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563109874725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335135936737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.971759557724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94470584392548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92242586612701</t>
+    <t xml:space="preserve">1.99563097953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335124015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97175967693329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9447056055069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92242610454559</t>
   </si>
   <si>
     <t xml:space="preserve">1.91606020927429</t>
@@ -2921,61 +2921,61 @@
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92720031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971677780151</t>
+    <t xml:space="preserve">1.92401731014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92720007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971665859222</t>
   </si>
   <si>
     <t xml:space="preserve">1.96061992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95743727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539413928986</t>
+    <t xml:space="preserve">1.95743691921234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539425849915</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857690811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287732124329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478884935379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449099063873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223347663879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01950240135193</t>
+    <t xml:space="preserve">1.98926508426666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857678890228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287744045258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94788873195648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449110984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01950192451477</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06087851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04337358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04814767837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02427625656128</t>
+    <t xml:space="preserve">2.06087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04337334632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04814743995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02427649497986</t>
   </si>
   <si>
     <t xml:space="preserve">2.06247043609619</t>
@@ -2984,46 +2984,46 @@
     <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07997584342957</t>
+    <t xml:space="preserve">2.07997608184814</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10543847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13726687431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522361755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18819165229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20251441001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17068600654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15158915519714</t>
+    <t xml:space="preserve">2.10543823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13726663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18819189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2025146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1706862449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15158939361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.12453556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1181697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10066413879395</t>
+    <t xml:space="preserve">2.11816954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10066437721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.08315849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07042741775513</t>
+    <t xml:space="preserve">2.07042717933655</t>
   </si>
   <si>
     <t xml:space="preserve">2.10862112045288</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">2.06565308570862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180400848389</t>
+    <t xml:space="preserve">2.11180424690247</t>
   </si>
   <si>
     <t xml:space="preserve">2.14840650558472</t>
@@ -3050,19 +3050,19 @@
     <t xml:space="preserve">2.12135243415833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1165783405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11339545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612652778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363217353821</t>
+    <t xml:space="preserve">2.11657810211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11339569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249230384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363241195679</t>
   </si>
   <si>
     <t xml:space="preserve">2.04178190231323</t>
@@ -3071,58 +3071,58 @@
     <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04019045829773</t>
+    <t xml:space="preserve">2.04019021987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02586793899536</t>
+    <t xml:space="preserve">2.02586770057678</t>
   </si>
   <si>
     <t xml:space="preserve">2.03064203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98767387866974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01154518127441</t>
+    <t xml:space="preserve">1.98767375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01154541969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341779708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18978333473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023490905762</t>
+    <t xml:space="preserve">2.18341732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18978357315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023467063904</t>
   </si>
   <si>
     <t xml:space="preserve">2.16113805770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20569753646851</t>
+    <t xml:space="preserve">2.20569729804993</t>
   </si>
   <si>
     <t xml:space="preserve">2.21842861175537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29163360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27412843704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2534396648407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29481649398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23593401908875</t>
+    <t xml:space="preserve">2.29163384437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27412796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25343990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29481625556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23593425750732</t>
   </si>
   <si>
     <t xml:space="preserve">2.25025701522827</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">2.27571940422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27890229225159</t>
+    <t xml:space="preserve">2.27890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.22161149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23115992546082</t>
+    <t xml:space="preserve">2.23115968704224</t>
   </si>
   <si>
     <t xml:space="preserve">2.200923204422</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10384702682495</t>
+    <t xml:space="preserve">2.10384678840637</t>
   </si>
   <si>
     <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17386913299561</t>
+    <t xml:space="preserve">2.17386937141418</t>
   </si>
   <si>
     <t xml:space="preserve">2.15954637527466</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">2.12771821022034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10702991485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07520151138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07201862335205</t>
+    <t xml:space="preserve">2.10702967643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07520174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
     <t xml:space="preserve">2.086341381073</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">2.14204072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09748125076294</t>
+    <t xml:space="preserve">2.09748148918152</t>
   </si>
   <si>
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06883597373962</t>
+    <t xml:space="preserve">2.09111571311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06883573532104</t>
   </si>
   <si>
     <t xml:space="preserve">2.01472783088684</t>
@@ -3221,34 +3221,34 @@
     <t xml:space="preserve">1.98130810260773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02109336853027</t>
+    <t xml:space="preserve">2.02109360694885</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128623485565</t>
+    <t xml:space="preserve">1.91128599643707</t>
   </si>
   <si>
     <t xml:space="preserve">1.89378046989441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90969491004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00677084922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0019965171814</t>
+    <t xml:space="preserve">1.90969479084015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00677061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
     <t xml:space="preserve">1.90651178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87945795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81261873245239</t>
+    <t xml:space="preserve">1.87945771217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261885166168</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">1.79033887386322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85558664798737</t>
+    <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
     <t xml:space="preserve">1.83330678939819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922087192535</t>
+    <t xml:space="preserve">1.84922075271606</t>
   </si>
   <si>
     <t xml:space="preserve">1.83171534538269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82534980773926</t>
+    <t xml:space="preserve">1.82534992694855</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444665908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423204421997</t>
+    <t xml:space="preserve">1.84444689750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423228263855</t>
   </si>
   <si>
     <t xml:space="preserve">1.8380811214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85240399837494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92879164218903</t>
+    <t xml:space="preserve">1.85240387916565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104927539825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92879152297974</t>
   </si>
   <si>
     <t xml:space="preserve">1.89537191390991</t>
@@ -3308,19 +3308,19 @@
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881374835968</t>
+    <t xml:space="preserve">1.99881398677826</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313638687134</t>
+    <t xml:space="preserve">2.01313662528992</t>
   </si>
   <si>
     <t xml:space="preserve">1.98289966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00358819961548</t>
+    <t xml:space="preserve">2.00358772277832</t>
   </si>
   <si>
     <t xml:space="preserve">1.9431140422821</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">1.93197441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95107138156891</t>
+    <t xml:space="preserve">1.95107126235962</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786650657654</t>
+    <t xml:space="preserve">1.87786626815796</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3344,31 +3344,31 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221125125885</t>
+    <t xml:space="preserve">1.96221137046814</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038332462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993151187897</t>
+    <t xml:space="preserve">1.93038296699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">1.90014612674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91765189170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91924297809601</t>
+    <t xml:space="preserve">1.91765165328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9192430973053</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71235942840576</t>
+    <t xml:space="preserve">1.71235954761505</t>
   </si>
   <si>
     <t xml:space="preserve">1.64233732223511</t>
@@ -3383,34 +3383,34 @@
     <t xml:space="preserve">1.65984284877777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69007980823517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711165428162</t>
+    <t xml:space="preserve">1.69007992744446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711153507233</t>
   </si>
   <si>
     <t xml:space="preserve">1.6168749332428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483179569244</t>
+    <t xml:space="preserve">1.62483191490173</t>
   </si>
   <si>
     <t xml:space="preserve">1.65506863594055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70758521556854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6964453458786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68053138256073</t>
+    <t xml:space="preserve">1.70758533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69644546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68053126335144</t>
   </si>
   <si>
     <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68848824501038</t>
+    <t xml:space="preserve">1.68848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435811519623</t>
@@ -3419,25 +3419,25 @@
     <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57151961326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57788527011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58504664897919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58743369579315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54128277301788</t>
+    <t xml:space="preserve">1.57151973247528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.577885389328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5850465297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58743381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54128265380859</t>
   </si>
   <si>
     <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025032997131</t>
+    <t xml:space="preserve">1.51025021076202</t>
   </si>
   <si>
     <t xml:space="preserve">1.53383469581604</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">1.51446175575256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50266945362091</t>
+    <t xml:space="preserve">1.5026695728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">1.50856566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5136194229126</t>
+    <t xml:space="preserve">1.51361954212189</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54815399646759</t>
+    <t xml:space="preserve">1.5481538772583</t>
   </si>
   <si>
     <t xml:space="preserve">1.48835027217865</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">1.47487342357635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087715148926</t>
+    <t xml:space="preserve">1.49087727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46308124065399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47403120994568</t>
+    <t xml:space="preserve">1.4630811214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47403109073639</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
@@ -3497,13 +3497,13 @@
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171948432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46645045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4571852684021</t>
+    <t xml:space="preserve">1.49171960353851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46645057201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45718502998352</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3990660905838</t>
+    <t xml:space="preserve">1.39906620979309</t>
   </si>
   <si>
     <t xml:space="preserve">1.36200475692749</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178960323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766669750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26177072525024</t>
+    <t xml:space="preserve">1.34178948402405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26177060604095</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">1.20617866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23229014873505</t>
+    <t xml:space="preserve">1.23229002952576</t>
   </si>
   <si>
     <t xml:space="preserve">1.22976315021515</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144769668579</t>
+    <t xml:space="preserve">1.23144781589508</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3569,79 +3569,79 @@
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365166664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20533645153046</t>
+    <t xml:space="preserve">1.20365178585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20533633232117</t>
   </si>
   <si>
     <t xml:space="preserve">1.175013422966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13289821147919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14637506008148</t>
+    <t xml:space="preserve">1.13289833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14637494087219</t>
   </si>
   <si>
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942148208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10594439506531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14300584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16911721229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965551376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16490566730499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13710963726044</t>
+    <t xml:space="preserve">1.11942136287689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1059445142746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1430059671402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16911733150482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965539455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16490578651428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12700212001801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12279045581818</t>
+    <t xml:space="preserve">1.12700223922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12279057502747</t>
   </si>
   <si>
     <t xml:space="preserve">1.08151769638062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10425996780396</t>
+    <t xml:space="preserve">1.10425984859467</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15985190868378</t>
+    <t xml:space="preserve">1.15985202789307</t>
   </si>
   <si>
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553284645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427872657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22470927238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26008605957031</t>
+    <t xml:space="preserve">1.14553272724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427884578705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22470939159393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2600861787796</t>
   </si>
   <si>
     <t xml:space="preserve">1.29462051391602</t>
@@ -3662,28 +3662,28 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829375743866</t>
+    <t xml:space="preserve">1.24829387664795</t>
   </si>
   <si>
     <t xml:space="preserve">1.24492466449738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25334775447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818624019623</t>
+    <t xml:space="preserve">1.25334763526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818612098694</t>
   </si>
   <si>
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325887680054</t>
+    <t xml:space="preserve">1.32325875759125</t>
   </si>
   <si>
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3165203332901</t>
+    <t xml:space="preserve">1.31652045249939</t>
   </si>
   <si>
     <t xml:space="preserve">1.3299971818924</t>
@@ -3692,19 +3692,19 @@
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915496826172</t>
+    <t xml:space="preserve">1.32915484905243</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021269321442</t>
+    <t xml:space="preserve">1.35021257400513</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3535817861557</t>
+    <t xml:space="preserve">1.35358166694641</t>
   </si>
   <si>
     <t xml:space="preserve">1.32747030258179</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33589327335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31062424182892</t>
+    <t xml:space="preserve">1.33589339256287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31062436103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.29546284675598</t>
@@ -3734,16 +3734,16 @@
     <t xml:space="preserve">1.30135893821716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25082075595856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23650169372559</t>
+    <t xml:space="preserve">1.25082087516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2365015745163</t>
   </si>
   <si>
     <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23734390735626</t>
+    <t xml:space="preserve">1.23734378814697</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">1.34263181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37127017974854</t>
+    <t xml:space="preserve">1.37127006053925</t>
   </si>
   <si>
     <t xml:space="preserve">1.36958563327789</t>
@@ -3779,25 +3779,25 @@
     <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46560823917389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4041200876236</t>
+    <t xml:space="preserve">1.4656081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40411996841431</t>
   </si>
   <si>
     <t xml:space="preserve">1.38222014904022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39822387695312</t>
+    <t xml:space="preserve">1.39822375774384</t>
   </si>
   <si>
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43360066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44370818138123</t>
+    <t xml:space="preserve">1.4336005449295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44370830059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">1.44623517990112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232778549194</t>
+    <t xml:space="preserve">1.39232766628265</t>
   </si>
   <si>
     <t xml:space="preserve">1.41843914985657</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727390766144</t>
+    <t xml:space="preserve">1.38727378845215</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
@@ -3836,22 +3836,22 @@
     <t xml:space="preserve">1.39317011833191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37800860404968</t>
+    <t xml:space="preserve">1.37800872325897</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779321193695</t>
+    <t xml:space="preserve">1.35779333114624</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496218204498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3881162405014</t>
+    <t xml:space="preserve">1.40496230125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811612129211</t>
   </si>
   <si>
     <t xml:space="preserve">1.37716627120972</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34515881538391</t>
+    <t xml:space="preserve">1.34515869617462</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">1.41170072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41254305839539</t>
+    <t xml:space="preserve">1.4125429391861</t>
   </si>
   <si>
     <t xml:space="preserve">1.44202363491058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45634281635284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42686212062836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4470773935318</t>
+    <t xml:space="preserve">1.45634269714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42686223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44707751274109</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
@@ -3911,25 +3911,25 @@
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60711514949799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61132657527924</t>
+    <t xml:space="preserve">1.6071150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61132669448853</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57426536083221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5852153301239</t>
+    <t xml:space="preserve">1.57426524162292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521521091461</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942675590515</t>
+    <t xml:space="preserve">1.58942663669586</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037672519684</t>
@@ -3947,10 +3947,10 @@
     <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62396109104156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59953439235687</t>
+    <t xml:space="preserve">1.62396121025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59953451156616</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3962,19 +3962,19 @@
     <t xml:space="preserve">1.61806511878967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61048436164856</t>
+    <t xml:space="preserve">1.61048424243927</t>
   </si>
   <si>
     <t xml:space="preserve">1.64249193668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66186487674713</t>
+    <t xml:space="preserve">1.66186499595642</t>
   </si>
   <si>
     <t xml:space="preserve">1.62227654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58774209022522</t>
+    <t xml:space="preserve">1.58774220943451</t>
   </si>
   <si>
     <t xml:space="preserve">1.62480342388153</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5776344537735</t>
+    <t xml:space="preserve">1.57763457298279</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">1.58353054523468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57089602947235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57594990730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58437299728394</t>
+    <t xml:space="preserve">1.57089614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57595002651215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58437287807465</t>
   </si>
   <si>
     <t xml:space="preserve">1.58184599876404</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">1.57173836231232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59026908874512</t>
+    <t xml:space="preserve">1.59026896953583</t>
   </si>
   <si>
     <t xml:space="preserve">1.5801614522934</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53087472915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5210268497467</t>
+    <t xml:space="preserve">1.5308746099472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52102696895599</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357881069183</t>
+    <t xml:space="preserve">1.47357869148254</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4950647354126</t>
+    <t xml:space="preserve">1.49506461620331</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4091,52 +4091,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192223072052</t>
+    <t xml:space="preserve">1.52192211151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070395469666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308514118195</t>
+    <t xml:space="preserve">1.61144697666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070407390594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308526039124</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786604881287</t>
+    <t xml:space="preserve">1.60786592960358</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039935588837</t>
+    <t xml:space="preserve">1.62039947509766</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801816940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773210525513</t>
+    <t xml:space="preserve">1.59801828861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773198604584</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937038898468</t>
+    <t xml:space="preserve">1.56937026977539</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502802371979</t>
+    <t xml:space="preserve">1.6150279045105</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.582799077034</t>
+    <t xml:space="preserve">1.58279895782471</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769527435303</t>
+    <t xml:space="preserve">1.67769539356232</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575251102448</t>
+    <t xml:space="preserve">1.68575263023376</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66426658630371</t>
+    <t xml:space="preserve">1.664266705513</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977210044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887671947479</t>
+    <t xml:space="preserve">1.71977198123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843829631805</t>
+    <t xml:space="preserve">1.68843841552734</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4226,16 +4226,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159933567047</t>
+    <t xml:space="preserve">1.60159921646118</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340803623199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399869918823</t>
+    <t xml:space="preserve">1.54340815544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4256,25 +4256,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234223842621</t>
+    <t xml:space="preserve">1.61234211921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112408161163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350526809692</t>
+    <t xml:space="preserve">1.63024723529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112420082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350538730621</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74573421478271</t>
+    <t xml:space="preserve">1.745734333992</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201934337616</t>
+    <t xml:space="preserve">1.69201922416687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4304,10 +4304,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691565990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7940776348114</t>
+    <t xml:space="preserve">1.78691577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79407751560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525907993317</t>
+    <t xml:space="preserve">1.83525896072388</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272553443909</t>
+    <t xml:space="preserve">1.82272565364838</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558197498322</t>
+    <t xml:space="preserve">1.75558185577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76453447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857235908508</t>
+    <t xml:space="preserve">1.7645343542099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857223987579</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723843574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859065532684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874277591705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009499549866</t>
+    <t xml:space="preserve">1.70723855495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859053611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874289512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009487628937</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740921020508</t>
+    <t xml:space="preserve">1.63740909099579</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6409900188446</t>
+    <t xml:space="preserve">1.63919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64099013805389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693395614624</t>
+    <t xml:space="preserve">1.72693407535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041789054871</t>
+    <t xml:space="preserve">1.56041777133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458948135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609382152557</t>
+    <t xml:space="preserve">1.58458960056305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609394073486</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205617427826</t>
+    <t xml:space="preserve">1.57205605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278078079224</t>
+    <t xml:space="preserve">1.64278066158295</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4529,10 +4529,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754315376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129473686218</t>
+    <t xml:space="preserve">1.68754303455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129461765289</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708631515503</t>
+    <t xml:space="preserve">1.71708619594574</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274383068085</t>
+    <t xml:space="preserve">1.76274394989014</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602051734924</t>
+    <t xml:space="preserve">1.78602039813995</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -5298,6 +5298,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.68799996376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71000003814697</t>
   </si>
 </sst>
 </file>
@@ -70350,7 +70353,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6494444444</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>874384</v>
@@ -70371,6 +70374,32 @@
         <v>1761</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493634259</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>801728</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>2.66199994087219</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1762</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="1765">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469235897064</t>
+    <t xml:space="preserve">0.933469414710999</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
@@ -47,160 +47,160 @@
     <t xml:space="preserve">0.923806130886078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92702704668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921873450279236</t>
+    <t xml:space="preserve">0.927027225494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873569488525</t>
   </si>
   <si>
     <t xml:space="preserve">0.901902794837952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898037612438202</t>
+    <t xml:space="preserve">0.898037493228912</t>
   </si>
   <si>
     <t xml:space="preserve">0.918652415275574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903835356235504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643665790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893926143646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346502304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653933525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154633045197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192727088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163322925568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869691967964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441648006439</t>
+    <t xml:space="preserve">0.903835535049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643546581268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346442699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851653873920441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192667484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163442134857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451975345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869692027568817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88644152879715</t>
   </si>
   <si>
     <t xml:space="preserve">0.875489830970764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90834504365921</t>
+    <t xml:space="preserve">0.908344805240631</t>
   </si>
   <si>
     <t xml:space="preserve">0.888374149799347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855519235134125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279182910919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798899650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481141090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825240969657898</t>
+    <t xml:space="preserve">0.85551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279123306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481081485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241029262543</t>
   </si>
   <si>
     <t xml:space="preserve">0.848432719707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869047522544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172072410583</t>
+    <t xml:space="preserve">0.86904776096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778364181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
   </si>
   <si>
     <t xml:space="preserve">0.923161864280701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927671492099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94570928812027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075646877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941199898719788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947641909122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892467498779</t>
+    <t xml:space="preserve">0.927671551704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142906665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709586143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296622276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075587272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642028331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892646312714</t>
   </si>
   <si>
     <t xml:space="preserve">0.934113681316376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906412243843079</t>
+    <t xml:space="preserve">0.906412184238434</t>
   </si>
   <si>
     <t xml:space="preserve">0.918008148670197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954084396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179363250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01270794868469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02881336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01657330989838</t>
+    <t xml:space="preserve">0.95408433675766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391827583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179542064667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01270806789398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02881348133087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01657319068909</t>
   </si>
   <si>
     <t xml:space="preserve">1.02365970611572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00819849967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00497734546661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755429267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02172696590424</t>
+    <t xml:space="preserve">1.00819826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175631046295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497722625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02172708511353</t>
   </si>
   <si>
     <t xml:space="preserve">1.01464068889618</t>
@@ -215,94 +215,94 @@
     <t xml:space="preserve">1.01141953468323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01206374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01786160469055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430379390717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01850581169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02688074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203451633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0249480009079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01721739768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00562143325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988871932029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368881225586</t>
+    <t xml:space="preserve">1.01206362247467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01786184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430391311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01850593090057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0268806219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203439712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02494812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01721751689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00562167167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368893146515</t>
   </si>
   <si>
     <t xml:space="preserve">1.03525543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02816915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04040932655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03396701812744</t>
+    <t xml:space="preserve">1.02816927433014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04040920734406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03396713733673</t>
   </si>
   <si>
     <t xml:space="preserve">1.02945756912231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01592910289764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992092907428741</t>
+    <t xml:space="preserve">1.03010153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01592898368835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992093026638031</t>
   </si>
   <si>
     <t xml:space="preserve">1.03332281112671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00948691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958387851715</t>
+    <t xml:space="preserve">1.00948679447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958268642426</t>
   </si>
   <si>
     <t xml:space="preserve">0.995314121246338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0210827589035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04942810535431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519686222076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295669078827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05715894699097</t>
+    <t xml:space="preserve">1.02108287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519698143005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05715882778168</t>
   </si>
   <si>
     <t xml:space="preserve">1.07326424121857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06231272220612</t>
+    <t xml:space="preserve">1.06231248378754</t>
   </si>
   <si>
     <t xml:space="preserve">1.04749572277069</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">1.06360113620758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06166851520538</t>
+    <t xml:space="preserve">1.06166839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.06811046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04620730876923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977276027202606</t>
+    <t xml:space="preserve">1.04620718955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977275967597961</t>
   </si>
   <si>
     <t xml:space="preserve">0.968257069587708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965036034584045</t>
+    <t xml:space="preserve">0.96503609418869</t>
   </si>
   <si>
     <t xml:space="preserve">0.978564381599426</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.962522506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979232907295227</t>
+    <t xml:space="preserve">0.979232847690582</t>
   </si>
   <si>
     <t xml:space="preserve">0.960517168045044</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">0.876964867115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903701543807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101407527924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117304325104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127802848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048855304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033018112183</t>
+    <t xml:space="preserve">0.903701484203339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680487155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101347923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117363929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127624034882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048974514008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033256530762</t>
   </si>
   <si>
     <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925091087818146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775271892548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925759494304657</t>
+    <t xml:space="preserve">0.925090968608856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775331497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925759255886078</t>
   </si>
   <si>
     <t xml:space="preserve">0.912391066551208</t>
@@ -386,55 +386,55 @@
     <t xml:space="preserve">0.921080529689789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927096307277679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143461227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955838143825531</t>
+    <t xml:space="preserve">0.92709618806839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143580436707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122523784637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838322639465</t>
   </si>
   <si>
     <t xml:space="preserve">0.953164517879486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964527606964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196132659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982575118541718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911693096161</t>
+    <t xml:space="preserve">0.964527666568756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196192264557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982574999332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911752700806</t>
   </si>
   <si>
     <t xml:space="preserve">0.972548842430115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973217129707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580218791962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99527496099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99260139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890755653381</t>
+    <t xml:space="preserve">0.973217189311981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580338001251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253963947296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995275139808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989259421825409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601215839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890934467316</t>
   </si>
   <si>
     <t xml:space="preserve">0.951827883720398</t>
@@ -443,109 +443,109 @@
     <t xml:space="preserve">0.950490951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948485612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941133081912994</t>
+    <t xml:space="preserve">0.948485553264618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941132962703705</t>
   </si>
   <si>
     <t xml:space="preserve">0.954501330852509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965864479541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917150974274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927530288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01265394687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02000641822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932988166809</t>
+    <t xml:space="preserve">0.965864598751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917031764984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927411079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01265382766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02000653743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99193286895752</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996611654758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96720153093338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986585557460785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977896094322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885655403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943248271942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00864315032959</t>
+    <t xml:space="preserve">0.996611833572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901254177094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98658549785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977896153926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885774612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943367481232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401697635651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00864326953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.00262761116028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206631183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97522234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248625278473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0293642282486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05342745780945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05543267726898</t>
+    <t xml:space="preserve">0.969206750392914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97522246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936446666718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05342733860016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05543255805969</t>
   </si>
   <si>
     <t xml:space="preserve">1.07615351676941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08952188491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420096874237</t>
+    <t xml:space="preserve">1.0895220041275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420073032379</t>
   </si>
   <si>
     <t xml:space="preserve">1.09687459468842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07013785839081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08751666545868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09353244304657</t>
+    <t xml:space="preserve">1.07013773918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08751678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479048728943</t>
+    <t xml:space="preserve">1.06479036808014</t>
   </si>
   <si>
     <t xml:space="preserve">1.06278514862061</t>
@@ -557,58 +557,58 @@
     <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06813251972198</t>
+    <t xml:space="preserve">1.06813263893127</t>
   </si>
   <si>
     <t xml:space="preserve">1.05209064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957843482494354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953832924365997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480631828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935785710811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469894886017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780372142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727879524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738378047943</t>
+    <t xml:space="preserve">0.957843542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953833162784576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935785889625549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469954490662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780550956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727819919586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738556861877</t>
   </si>
   <si>
     <t xml:space="preserve">0.941801488399506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918406784534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538105487823</t>
+    <t xml:space="preserve">0.918406963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538284301758</t>
   </si>
   <si>
     <t xml:space="preserve">0.967869818210602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980569660663605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948706150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
+    <t xml:space="preserve">0.98056972026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99794864654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332235336304</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532745361328</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">1.01599586009979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02869582176208</t>
+    <t xml:space="preserve">1.02869594097137</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203797340393</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">1.04005897045135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04473781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070116043091</t>
+    <t xml:space="preserve">1.04473793506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0307012796402</t>
   </si>
   <si>
     <t xml:space="preserve">1.01733267307281</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">1.04874849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04941689968109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275905132294</t>
+    <t xml:space="preserve">1.0494167804718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275893211365</t>
   </si>
   <si>
     <t xml:space="preserve">1.0500853061676</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">1.04072749614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02468538284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0106486082077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530099868774</t>
+    <t xml:space="preserve">1.04607474803925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02468550205231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01064848899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530123710632</t>
   </si>
   <si>
     <t xml:space="preserve">1.03003263473511</t>
@@ -671,25 +671,25 @@
     <t xml:space="preserve">1.04273271560669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334856987</t>
+    <t xml:space="preserve">1.02334845066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412208080292</t>
+    <t xml:space="preserve">1.06412196159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.0561009645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810618400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484303951263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07080638408661</t>
+    <t xml:space="preserve">1.05810630321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484315872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07080626487732</t>
   </si>
   <si>
     <t xml:space="preserve">1.0821692943573</t>
@@ -698,22 +698,22 @@
     <t xml:space="preserve">1.0688009262085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07815885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08283770084381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08818507194519</t>
+    <t xml:space="preserve">1.07815873622894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0828378200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08818519115448</t>
   </si>
   <si>
     <t xml:space="preserve">1.09620606899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09954822063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754300117493</t>
+    <t xml:space="preserve">1.09954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754288196564</t>
   </si>
   <si>
     <t xml:space="preserve">1.12628495693207</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">1.18978464603424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22120034694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988998889923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24058425426483</t>
+    <t xml:space="preserve">1.22120046615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988975048065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24058437347412</t>
   </si>
   <si>
     <t xml:space="preserve">1.26665282249451</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">1.28002107143402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28336298465729</t>
+    <t xml:space="preserve">1.28336322307587</t>
   </si>
   <si>
     <t xml:space="preserve">1.29405796527863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27133166790009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932668685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30074203014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009995937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475270748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007374286652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3114367723465</t>
+    <t xml:space="preserve">1.27133178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932656764984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30074214935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31010019779205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007386207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31143701076508</t>
   </si>
   <si>
     <t xml:space="preserve">1.29004740715027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28871059417725</t>
+    <t xml:space="preserve">1.28871071338654</t>
   </si>
   <si>
     <t xml:space="preserve">1.29739999771118</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">1.27200019359589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2593001127243</t>
+    <t xml:space="preserve">1.25930023193359</t>
   </si>
   <si>
     <t xml:space="preserve">1.29673171043396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29806840419769</t>
+    <t xml:space="preserve">1.29806864261627</t>
   </si>
   <si>
     <t xml:space="preserve">1.31076836585999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2933896780014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814717292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30341589450836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349478244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35421562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3702574968338</t>
+    <t xml:space="preserve">1.29338955879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814729213715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30341577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683669567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349454402924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35421574115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37025773525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426817417145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.364910364151</t>
+    <t xml:space="preserve">1.36491048336029</t>
   </si>
   <si>
     <t xml:space="preserve">1.37961542606354</t>
@@ -827,19 +827,19 @@
     <t xml:space="preserve">1.34886825084686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3903101682663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4103627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42105722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175196647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45046806335449</t>
+    <t xml:space="preserve">1.39031004905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42105734348297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175208568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046782493591</t>
   </si>
   <si>
     <t xml:space="preserve">1.39966809749603</t>
@@ -848,43 +848,43 @@
     <t xml:space="preserve">1.41303646564484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43442571163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4170469045639</t>
+    <t xml:space="preserve">1.4344254732132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704678535461</t>
   </si>
   <si>
     <t xml:space="preserve">1.42239427566528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40902614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43977320194244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44779419898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052049636841</t>
+    <t xml:space="preserve">1.40902590751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43977332115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44779407978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4705206155777</t>
   </si>
   <si>
     <t xml:space="preserve">1.46784687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46116244792938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319400310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249914169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46650981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48474228382111</t>
+    <t xml:space="preserve">1.46116268634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319388389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249938011169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650993824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
     <t xml:space="preserve">1.48336625099182</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">1.40630829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39530026912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39942824840546</t>
+    <t xml:space="preserve">1.3953001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39942800998688</t>
   </si>
   <si>
     <t xml:space="preserve">1.40080428123474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40218019485474</t>
+    <t xml:space="preserve">1.40218031406403</t>
   </si>
   <si>
     <t xml:space="preserve">1.38429188728333</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">1.41456460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42144477367401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43658113479614</t>
+    <t xml:space="preserve">1.42144465446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43658125400543</t>
   </si>
   <si>
     <t xml:space="preserve">1.43245303630829</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45997381210327</t>
+    <t xml:space="preserve">1.45997369289398</t>
   </si>
   <si>
     <t xml:space="preserve">1.44621348381042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46685373783112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48199033737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46960592269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758951663971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923839092255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400686264038</t>
+    <t xml:space="preserve">1.46685397624969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48199045658112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46960604190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923815250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400698184967</t>
   </si>
   <si>
     <t xml:space="preserve">1.50125479698181</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">1.49987876415253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50675904750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602350711823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54803991317749</t>
+    <t xml:space="preserve">1.50675892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602362632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54804003238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115974903107</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">1.57968902587891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57831263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556056976318</t>
+    <t xml:space="preserve">1.57831275463104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556080818176</t>
   </si>
   <si>
     <t xml:space="preserve">1.57693672180176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5631765127182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54666388034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55354392528534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592857837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381688594818</t>
+    <t xml:space="preserve">1.56317639350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5466639995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55354416370392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381712436676</t>
   </si>
   <si>
     <t xml:space="preserve">1.59069716930389</t>
@@ -1031,67 +1031,67 @@
     <t xml:space="preserve">1.60996162891388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63197803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711451530457</t>
+    <t xml:space="preserve">1.63197815418243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711463451385</t>
   </si>
   <si>
     <t xml:space="preserve">1.61408960819244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6058337688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6003292798996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455254554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978383541107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565585613251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
+    <t xml:space="preserve">1.60583353042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032951831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5645524263382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978371620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53565549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
   </si>
   <si>
     <t xml:space="preserve">1.56180036067963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941606521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427958488464</t>
+    <t xml:space="preserve">1.56042432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941618442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427970409393</t>
   </si>
   <si>
     <t xml:space="preserve">1.57005655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868040561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61684167385101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133778095245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280850410461</t>
+    <t xml:space="preserve">1.56868052482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234604358673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6168417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482514858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5728086233139</t>
   </si>
   <si>
     <t xml:space="preserve">1.61821782588959</t>
@@ -1109,106 +1109,106 @@
     <t xml:space="preserve">1.69940388202667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70353245735168</t>
+    <t xml:space="preserve">1.70353221893311</t>
   </si>
   <si>
     <t xml:space="preserve">1.69802784919739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69252359867096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023435115814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949904918671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986681938171</t>
+    <t xml:space="preserve">1.69252383708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949892997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986670017242</t>
   </si>
   <si>
     <t xml:space="preserve">1.62785005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6622508764267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601132392883</t>
+    <t xml:space="preserve">1.66225099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601144313812</t>
   </si>
   <si>
     <t xml:space="preserve">1.7049081325531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74894118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105275630951</t>
+    <t xml:space="preserve">1.7489413022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7310528755188</t>
   </si>
   <si>
     <t xml:space="preserve">1.72004449367523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73518109321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830092906952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618899822235</t>
+    <t xml:space="preserve">1.73518097400665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830080986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618887901306</t>
   </si>
   <si>
     <t xml:space="preserve">1.7668297290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77233397960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545369625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77371001243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74068486690521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82049512863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022228717804</t>
+    <t xml:space="preserve">1.77233386039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545357704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77370977401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8204950094223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022252559662</t>
   </si>
   <si>
     <t xml:space="preserve">1.78747010231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444543361664</t>
+    <t xml:space="preserve">1.75444531440735</t>
   </si>
   <si>
     <t xml:space="preserve">1.79159820079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79297435283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76820540428162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7585734128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554886341095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142064571381</t>
+    <t xml:space="preserve">1.79297423362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76820576190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75857329368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554862499237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967684268951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142052650452</t>
   </si>
   <si>
     <t xml:space="preserve">1.75169336795807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81499063968658</t>
+    <t xml:space="preserve">1.81499075889587</t>
   </si>
   <si>
     <t xml:space="preserve">1.80535864830017</t>
@@ -1217,61 +1217,61 @@
     <t xml:space="preserve">1.75031709671021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74481308460236</t>
+    <t xml:space="preserve">1.74481332302094</t>
   </si>
   <si>
     <t xml:space="preserve">1.77921378612518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84113597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700752258301</t>
+    <t xml:space="preserve">1.84113574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8370076417923</t>
   </si>
   <si>
     <t xml:space="preserve">1.85351991653442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86039996147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516879081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361496448517</t>
+    <t xml:space="preserve">1.86039984226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516867160797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076797008514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361484527588</t>
   </si>
   <si>
     <t xml:space="preserve">1.80123043060303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79710257053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79572629928589</t>
+    <t xml:space="preserve">1.79710245132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572641849518</t>
   </si>
   <si>
     <t xml:space="preserve">1.82737517356873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68564355373383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573848247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738711833954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151557445526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66913115978241</t>
+    <t xml:space="preserve">1.68564343452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.634730219841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6815150976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66913104057312</t>
   </si>
   <si>
     <t xml:space="preserve">1.68013942241669</t>
@@ -1286,91 +1286,91 @@
     <t xml:space="preserve">1.6870197057724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69114744663239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6333544254303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463552951813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215618610382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527590274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426752090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876350879669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65261840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306928157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756503105164</t>
+    <t xml:space="preserve">1.69114768505096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335406780243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426740169525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876327037811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65261876583099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306940078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756526947021</t>
   </si>
   <si>
     <t xml:space="preserve">1.73930895328522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72417283058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692477703094</t>
+    <t xml:space="preserve">1.7241724729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692489624023</t>
   </si>
   <si>
     <t xml:space="preserve">1.66362690925598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68289172649384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7131644487381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343705177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380482196808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206113815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7599493265152</t>
+    <t xml:space="preserve">1.68289160728455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316421031952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343693256378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380470275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7420608997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994956493378</t>
   </si>
   <si>
     <t xml:space="preserve">1.71178817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68839585781097</t>
+    <t xml:space="preserve">1.6883956193924</t>
   </si>
   <si>
     <t xml:space="preserve">1.6539945602417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64849078655243</t>
+    <t xml:space="preserve">1.64849066734314</t>
   </si>
   <si>
     <t xml:space="preserve">1.60720956325531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59757733345032</t>
+    <t xml:space="preserve">1.59757721424103</t>
   </si>
   <si>
     <t xml:space="preserve">1.59620118141174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53290367126465</t>
+    <t xml:space="preserve">1.53290355205536</t>
   </si>
   <si>
     <t xml:space="preserve">1.4929986000061</t>
@@ -1382,28 +1382,28 @@
     <t xml:space="preserve">1.46134984493256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4764860868454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4861181974411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4751101732254</t>
+    <t xml:space="preserve">1.47648584842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611843585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511005401611</t>
   </si>
   <si>
     <t xml:space="preserve">1.45722162723541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42832481861115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542124271393</t>
+    <t xml:space="preserve">1.42832493782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776719093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079221725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542112350464</t>
   </si>
   <si>
     <t xml:space="preserve">1.56530690193176</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">1.52411460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121697902679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127373218536</t>
+    <t xml:space="preserve">1.53121674060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127408981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.52837598323822</t>
@@ -1430,100 +1430,100 @@
     <t xml:space="preserve">1.55536413192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56246614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513580799103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507881641388</t>
+    <t xml:space="preserve">1.56246638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513592720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507893562317</t>
   </si>
   <si>
     <t xml:space="preserve">1.60934019088745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6221239566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5795111656189</t>
+    <t xml:space="preserve">1.62212407588959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945405483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951140403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.60223805904388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60365831851959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371554851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922608852386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63632798194885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348734378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638509273529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076045036316</t>
+    <t xml:space="preserve">1.60365843772888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371542930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922585010529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63632822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348746299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076056957245</t>
   </si>
   <si>
     <t xml:space="preserve">1.58803391456604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59229505062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68888413906097</t>
+    <t xml:space="preserve">1.59229516983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68888401985168</t>
   </si>
   <si>
     <t xml:space="preserve">1.68178188800812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013318538666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729230880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911210536957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757750511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894101142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752051353455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183911800385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343011379242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928296089172</t>
+    <t xml:space="preserve">1.69882690906525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013330459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729254722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911198616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757762432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894089221954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752039432526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183899879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343023300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61928308010101</t>
   </si>
   <si>
     <t xml:space="preserve">1.61786293983459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5766704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388652324677</t>
+    <t xml:space="preserve">1.57667052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388676166534</t>
   </si>
   <si>
     <t xml:space="preserve">1.55962550640106</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">1.5539436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55252313613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55110287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51701247692108</t>
+    <t xml:space="preserve">1.5525233745575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55110275745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51701259613037</t>
   </si>
   <si>
     <t xml:space="preserve">1.51559233665466</t>
@@ -1547,49 +1547,49 @@
     <t xml:space="preserve">1.46871829032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43462800979614</t>
+    <t xml:space="preserve">1.43462812900543</t>
   </si>
   <si>
     <t xml:space="preserve">1.44741189479828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45735490322113</t>
+    <t xml:space="preserve">1.45735478401184</t>
   </si>
   <si>
     <t xml:space="preserve">1.47155916690826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47013854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47297954559326</t>
+    <t xml:space="preserve">1.47013866901398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47297942638397</t>
   </si>
   <si>
     <t xml:space="preserve">1.53263735771179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58377254009247</t>
+    <t xml:space="preserve">1.58377265930176</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973948955536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51275134086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48718392848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47724068164825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144518375397</t>
+    <t xml:space="preserve">1.51275157928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4871838092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.50138807296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996757507324</t>
+    <t xml:space="preserve">1.49996745586395</t>
   </si>
   <si>
     <t xml:space="preserve">1.49570631980896</t>
@@ -1604,25 +1604,25 @@
     <t xml:space="preserve">1.3991174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065207004547</t>
+    <t xml:space="preserve">1.38065195083618</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426006793976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3522435426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994170188904</t>
+    <t xml:space="preserve">1.35224366188049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994182109833</t>
   </si>
   <si>
     <t xml:space="preserve">1.37070906162262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36573755741119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37923157215118</t>
+    <t xml:space="preserve">1.3657374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37923145294189</t>
   </si>
   <si>
     <t xml:space="preserve">1.37212944030762</t>
@@ -1631,34 +1631,34 @@
     <t xml:space="preserve">1.35579454898834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38633370399475</t>
+    <t xml:space="preserve">1.38633358478546</t>
   </si>
   <si>
     <t xml:space="preserve">1.36431705951691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39343595504761</t>
+    <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130520820618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35863542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40906047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40124833583832</t>
+    <t xml:space="preserve">1.35863530635834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40906035900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40124821662903</t>
   </si>
   <si>
     <t xml:space="preserve">1.46019577980042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45309364795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439980506897</t>
+    <t xml:space="preserve">1.45309352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439992427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866117954254</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39556658267975</t>
+    <t xml:space="preserve">1.39556646347046</t>
   </si>
   <si>
     <t xml:space="preserve">1.37568044662476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3870438337326</t>
+    <t xml:space="preserve">1.38704371452332</t>
   </si>
   <si>
     <t xml:space="preserve">1.39201533794403</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">1.3778110742569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40266859531403</t>
+    <t xml:space="preserve">1.40266847610474</t>
   </si>
   <si>
     <t xml:space="preserve">1.38136231899261</t>
@@ -1709,31 +1709,31 @@
     <t xml:space="preserve">1.43320751190186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42468512058258</t>
+    <t xml:space="preserve">1.42468523979187</t>
   </si>
   <si>
     <t xml:space="preserve">1.4204238653183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48150193691254</t>
+    <t xml:space="preserve">1.48150205612183</t>
   </si>
   <si>
     <t xml:space="preserve">1.51985347270966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48860418796539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428606033325</t>
+    <t xml:space="preserve">1.4886040687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428582191467</t>
   </si>
   <si>
     <t xml:space="preserve">1.54258024692535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54115986824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52553498744965</t>
+    <t xml:space="preserve">1.54115998744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.52979648113251</t>
@@ -1745,67 +1745,67 @@
     <t xml:space="preserve">1.53405773639679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51133096218109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50991034507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008179664612</t>
+    <t xml:space="preserve">1.5113308429718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5099104642868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48008155822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.49854695796967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706970691681</t>
+    <t xml:space="preserve">1.50706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.48292243480682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48434293270111</t>
+    <t xml:space="preserve">1.48434281349182</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564897060394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689849376678</t>
+    <t xml:space="preserve">1.53689861297607</t>
   </si>
   <si>
     <t xml:space="preserve">1.61644244194031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62780570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206720352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6008175611496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62496507167816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939730167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6207035779953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61502194404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627122879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218106746674</t>
+    <t xml:space="preserve">1.62780559062958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206708431244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60081768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62496483325958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939742088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62070369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61502170562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627110958099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218094825745</t>
   </si>
   <si>
     <t xml:space="preserve">1.51417171955109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50422883033752</t>
+    <t xml:space="preserve">1.50422871112823</t>
   </si>
   <si>
     <t xml:space="preserve">1.48576331138611</t>
@@ -1817,64 +1817,64 @@
     <t xml:space="preserve">1.45877516269684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49286556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5567843914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57809090614319</t>
+    <t xml:space="preserve">1.49286544322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55678451061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5780907869339</t>
   </si>
   <si>
     <t xml:space="preserve">1.58661329746246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5738297700882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916921615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450866222382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166790485382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6917245388031</t>
+    <t xml:space="preserve">1.57382965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6391693353653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450878143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172465801239</t>
   </si>
   <si>
     <t xml:space="preserve">1.6906179189682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69356298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69798111915588</t>
+    <t xml:space="preserve">1.69356310367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69798123836517</t>
   </si>
   <si>
     <t xml:space="preserve">1.67294585704803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68325459957123</t>
+    <t xml:space="preserve">1.68325448036194</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7289069890976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75099718570709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277840137482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74510610103607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73332524299622</t>
+    <t xml:space="preserve">1.72890710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75099694728851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277852058411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74510633945465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73332512378693</t>
   </si>
   <si>
     <t xml:space="preserve">1.77161419391632</t>
@@ -1886,40 +1886,40 @@
     <t xml:space="preserve">1.79812216758728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80106794834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80548548698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401289463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137609481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603232860565</t>
+    <t xml:space="preserve">1.80106770992279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80548536777496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455961704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603220939636</t>
   </si>
   <si>
     <t xml:space="preserve">1.76719641685486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74216115474701</t>
+    <t xml:space="preserve">1.74216103553772</t>
   </si>
   <si>
     <t xml:space="preserve">1.70239913463593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7392156124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7701416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486847877502</t>
+    <t xml:space="preserve">1.73921573162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77014148235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486835956573</t>
   </si>
   <si>
     <t xml:space="preserve">1.78928637504578</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">1.79664957523346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79517686367035</t>
+    <t xml:space="preserve">1.79517674446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.79370427131653</t>
@@ -1943,19 +1943,19 @@
     <t xml:space="preserve">1.80254030227661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77308702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192293643951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493888378143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021200656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81873953342438</t>
+    <t xml:space="preserve">1.77308714389801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192317485809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493876457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021224498749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8187392950058</t>
   </si>
   <si>
     <t xml:space="preserve">1.82168483734131</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">1.84819281101227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82904803752899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425099372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81432139873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.809903383255</t>
+    <t xml:space="preserve">1.82904827594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425111293793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81432151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990362167358</t>
   </si>
   <si>
     <t xml:space="preserve">1.8319935798645</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">1.86144685745239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91593527793884</t>
+    <t xml:space="preserve">1.91593551635742</t>
   </si>
   <si>
     <t xml:space="preserve">1.93655288219452</t>
@@ -1994,19 +1994,19 @@
     <t xml:space="preserve">1.93213474750519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95127904415131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042429447174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9424432516098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980657100677</t>
+    <t xml:space="preserve">1.95127952098846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042393684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569705963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244301319122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980669021606</t>
   </si>
   <si>
     <t xml:space="preserve">1.9615877866745</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">1.99693179130554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00724077224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98367774486542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987745285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00576782226562</t>
+    <t xml:space="preserve">2.00724053382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.983677983284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987721443176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576758384705</t>
   </si>
   <si>
     <t xml:space="preserve">1.98073256015778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97189652919769</t>
+    <t xml:space="preserve">1.97189664840698</t>
   </si>
   <si>
     <t xml:space="preserve">1.97631466388702</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">1.94391596317291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96895134449005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600615978241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484159469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01754903793335</t>
+    <t xml:space="preserve">1.96895110607147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600568294525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484183311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01754927635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04847502708435</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">2.02049422264099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04552960395813</t>
+    <t xml:space="preserve">2.04552984237671</t>
   </si>
   <si>
     <t xml:space="preserve">2.03374838829041</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">2.04111194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03816628456116</t>
+    <t xml:space="preserve">2.03816604614258</t>
   </si>
   <si>
     <t xml:space="preserve">2.01018595695496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00871300697327</t>
+    <t xml:space="preserve">2.00871324539185</t>
   </si>
   <si>
     <t xml:space="preserve">1.99251389503479</t>
@@ -2093,40 +2093,40 @@
     <t xml:space="preserve">2.02638506889343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07940053939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07203769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06172895431519</t>
+    <t xml:space="preserve">2.07940077781677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467413902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0720374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06172919273376</t>
   </si>
   <si>
     <t xml:space="preserve">2.03522109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02933073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614708900452</t>
+    <t xml:space="preserve">2.02933049201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614685058594</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645583152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0867645740509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02196717262268</t>
+    <t xml:space="preserve">2.08676433563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02196741104126</t>
   </si>
   <si>
     <t xml:space="preserve">2.05731081962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07351040840149</t>
+    <t xml:space="preserve">2.07351016998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.04700231552124</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">2.00282263755798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0131311416626</t>
+    <t xml:space="preserve">2.01313090324402</t>
   </si>
   <si>
     <t xml:space="preserve">2.01460385322571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04258441925049</t>
+    <t xml:space="preserve">2.04258418083191</t>
   </si>
   <si>
     <t xml:space="preserve">2.11179947853088</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">2.0749831199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11032700538635</t>
+    <t xml:space="preserve">2.11032676696777</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
@@ -2162,40 +2162,40 @@
     <t xml:space="preserve">2.10885429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12652611732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17659687995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20457768440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19426894187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24581217765808</t>
+    <t xml:space="preserve">2.12652635574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17659664154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20457720756531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19426870346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2458119392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21341347694397</t>
+    <t xml:space="preserve">2.21341371536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899558067322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21783137321472</t>
+    <t xml:space="preserve">2.2178316116333</t>
   </si>
   <si>
     <t xml:space="preserve">2.20163226127625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20752239227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17365145683289</t>
+    <t xml:space="preserve">2.20752263069153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17365121841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.23255825042725</t>
@@ -2204,55 +2204,55 @@
     <t xml:space="preserve">2.21930384635925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21635890007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20310497283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24728465080261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2870466709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201152801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25022983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11474466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11621761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15303421020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13094449043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0249125957489</t>
+    <t xml:space="preserve">2.21635866165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20310473442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24728488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28704643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201105117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25023007392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1147449016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11621737480164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1530339717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13094401359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02491235733032</t>
   </si>
   <si>
     <t xml:space="preserve">2.08823704719543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1029634475708</t>
+    <t xml:space="preserve">2.10296368598938</t>
   </si>
   <si>
     <t xml:space="preserve">1.9822051525116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83641159534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65380120277405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63318407535553</t>
+    <t xml:space="preserve">1.83641147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65380132198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63318395614624</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724899291992</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">1.35190510749817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043251514435</t>
+    <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330729484558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36442303657532</t>
+    <t xml:space="preserve">1.36442291736603</t>
   </si>
   <si>
     <t xml:space="preserve">1.32171559333801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31508874893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40565741062164</t>
+    <t xml:space="preserve">1.3150886297226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40565729141235</t>
   </si>
   <si>
     <t xml:space="preserve">1.37767684459686</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">1.50948011875153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58311343193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674650669098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071473121643</t>
+    <t xml:space="preserve">1.58311331272125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674638748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071485042572</t>
   </si>
   <si>
     <t xml:space="preserve">1.5477694272995</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">1.53598809242249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56249606609344</t>
+    <t xml:space="preserve">1.56249594688416</t>
   </si>
   <si>
     <t xml:space="preserve">1.56102323532104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55365991592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5492422580719</t>
+    <t xml:space="preserve">1.55366003513336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54187881946564</t>
@@ -2324,52 +2324,52 @@
     <t xml:space="preserve">1.58164072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60225820541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434804439545</t>
+    <t xml:space="preserve">1.60225808620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434792518616</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61698484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287509441376</t>
+    <t xml:space="preserve">1.61698472499847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287521362305</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643800258636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65527367591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67589128017426</t>
+    <t xml:space="preserve">1.65527391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67589116096497</t>
   </si>
   <si>
     <t xml:space="preserve">1.66705513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64349269866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520327091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57574999332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58753132820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55807793140411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427740097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047651290894</t>
+    <t xml:space="preserve">1.64349246025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520339012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57575011253357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.587531208992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5580780506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427752017975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047663211823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59784007072449</t>
@@ -2378,34 +2378,34 @@
     <t xml:space="preserve">1.64201998710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66558253765106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62876570224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61109399795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67883622646332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859860420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76572382450104</t>
+    <t xml:space="preserve">1.66558241844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62876582145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61109387874603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67883634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859848499298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76572370529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.75836038589478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7200710773468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7082896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6390745639801</t>
+    <t xml:space="preserve">1.72007119655609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63907468318939</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821933746338</t>
@@ -2414,55 +2414,55 @@
     <t xml:space="preserve">1.70534443855286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71123480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756810188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836574077606</t>
+    <t xml:space="preserve">1.71123504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836585998535</t>
   </si>
   <si>
     <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69781517982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71161878108978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71621966362</t>
+    <t xml:space="preserve">1.69781529903412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71161842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71621942520142</t>
   </si>
   <si>
     <t xml:space="preserve">1.69168031215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548355579376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72542190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73462426662445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73769176006317</t>
+    <t xml:space="preserve">1.70548367500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72542178630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73462414741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73769152164459</t>
   </si>
   <si>
     <t xml:space="preserve">1.73002302646637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68707919120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68554556369781</t>
+    <t xml:space="preserve">1.68707942962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68554544448853</t>
   </si>
   <si>
     <t xml:space="preserve">1.67327570915222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793859958649</t>
+    <t xml:space="preserve">1.65793871879578</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487134456635</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">1.68401193618774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241630077362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235453128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70701730251312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66867482662201</t>
+    <t xml:space="preserve">1.70241641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235465049744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70701742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66867470741272</t>
   </si>
   <si>
     <t xml:space="preserve">1.64566898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65333771705627</t>
+    <t xml:space="preserve">1.6533374786377</t>
   </si>
   <si>
     <t xml:space="preserve">1.65640509128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6272646188736</t>
+    <t xml:space="preserve">1.62726449966431</t>
   </si>
   <si>
     <t xml:space="preserve">1.63646686077118</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">1.64720273017883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67020845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407370567322</t>
+    <t xml:space="preserve">1.67020833492279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407382488251</t>
   </si>
   <si>
     <t xml:space="preserve">1.68247818946838</t>
@@ -2516,28 +2516,28 @@
     <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75609600543976</t>
+    <t xml:space="preserve">1.75609612464905</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088267326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72082078456879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69321405887604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094420433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67174208164215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69934904575348</t>
+    <t xml:space="preserve">1.70088255405426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7208206653595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69321393966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094432353973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67174220085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69934892654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778769493103</t>
@@ -2546,25 +2546,25 @@
     <t xml:space="preserve">1.69014656543732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71008491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861281871796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65180397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64873659610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62573063373566</t>
+    <t xml:space="preserve">1.71008503437042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861305713654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6518040895462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64873647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62573075294495</t>
   </si>
   <si>
     <t xml:space="preserve">1.61959612369537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659051895142</t>
+    <t xml:space="preserve">1.59659039974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505665302277</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">1.54904544353485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5505793094635</t>
+    <t xml:space="preserve">1.55057919025421</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996674060822</t>
@@ -2600,22 +2600,22 @@
     <t xml:space="preserve">1.51990497112274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54751169681549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56438255310059</t>
+    <t xml:space="preserve">1.54751181602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
     <t xml:space="preserve">1.53064095973969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60425889492035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59198915958405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59965765476227</t>
+    <t xml:space="preserve">1.60425901412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59198927879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59965789318085</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">1.66100597381592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74075901508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069736480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388803958893</t>
+    <t xml:space="preserve">1.74075889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069724559784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388827800751</t>
   </si>
   <si>
     <t xml:space="preserve">1.69628131389618</t>
@@ -2651,40 +2651,40 @@
     <t xml:space="preserve">1.63186573982239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62879848480225</t>
+    <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
     <t xml:space="preserve">1.63033199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5889219045639</t>
+    <t xml:space="preserve">1.58892178535461</t>
   </si>
   <si>
     <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61039364337921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346125602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585464954376</t>
+    <t xml:space="preserve">1.6103937625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346113681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585453033447</t>
   </si>
   <si>
     <t xml:space="preserve">1.6395343542099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64260149002075</t>
+    <t xml:space="preserve">1.64260184764862</t>
   </si>
   <si>
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947234630585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66714119911194</t>
+    <t xml:space="preserve">1.65947246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66714096069336</t>
   </si>
   <si>
     <t xml:space="preserve">1.62266337871552</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56898367404938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57051742076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55978155136108</t>
+    <t xml:space="preserve">1.56898355484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57051753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55978143215179</t>
   </si>
   <si>
     <t xml:space="preserve">1.58278703689575</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">1.60732626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63339936733246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62419724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192762851715</t>
+    <t xml:space="preserve">1.63339948654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62419712543488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192750930786</t>
   </si>
   <si>
     <t xml:space="preserve">1.58432066440582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806225776672</t>
+    <t xml:space="preserve">1.61806237697601</t>
   </si>
   <si>
     <t xml:space="preserve">1.64106810092926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.665607213974</t>
+    <t xml:space="preserve">1.66560733318329</t>
   </si>
   <si>
     <t xml:space="preserve">1.67480957508087</t>
@@ -2741,34 +2741,34 @@
     <t xml:space="preserve">1.71775329113007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517494678497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81744432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824208259583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670857429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80364120006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903972148895</t>
+    <t xml:space="preserve">1.75762963294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8174444437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082423210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80364084243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903960227966</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290521144867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82051193714142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78063547611237</t>
+    <t xml:space="preserve">1.82051169872284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
     <t xml:space="preserve">1.79443871974945</t>
@@ -2786,28 +2786,28 @@
     <t xml:space="preserve">1.85885453224182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83891642093658</t>
+    <t xml:space="preserve">1.83891630172729</t>
   </si>
   <si>
     <t xml:space="preserve">1.82818043231964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86498939990997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85578715801239</t>
+    <t xml:space="preserve">1.86498928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85578727722168</t>
   </si>
   <si>
     <t xml:space="preserve">1.8634557723999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84965240955353</t>
+    <t xml:space="preserve">1.84965217113495</t>
   </si>
   <si>
     <t xml:space="preserve">1.87112426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89566338062286</t>
+    <t xml:space="preserve">1.89566349983215</t>
   </si>
   <si>
     <t xml:space="preserve">1.90179836750031</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">1.91866934299469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90026462078094</t>
+    <t xml:space="preserve">1.90026473999023</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100060939789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94627583026886</t>
+    <t xml:space="preserve">1.94627606868744</t>
   </si>
   <si>
     <t xml:space="preserve">1.95394456386566</t>
@@ -2831,22 +2831,22 @@
     <t xml:space="preserve">1.9156014919281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92173659801483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713547706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9355400800705</t>
+    <t xml:space="preserve">1.92173683643341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713559627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553984165192</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695016860962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9600795507431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382066726685</t>
+    <t xml:space="preserve">1.96007907390594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382090568542</t>
   </si>
   <si>
     <t xml:space="preserve">1.96621417999268</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">2.00762414932251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01375865936279</t>
+    <t xml:space="preserve">2.01375913619995</t>
   </si>
   <si>
     <t xml:space="preserve">2.00915789604187</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">1.9570118188858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95854568481445</t>
+    <t xml:space="preserve">1.95854544639587</t>
   </si>
   <si>
     <t xml:space="preserve">1.9692816734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97848379611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00302314758301</t>
+    <t xml:space="preserve">1.97848355770111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00302290916443</t>
   </si>
   <si>
     <t xml:space="preserve">2.01069164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836037635803</t>
+    <t xml:space="preserve">2.01836013793945</t>
   </si>
   <si>
     <t xml:space="preserve">2.0290961265564</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563086032867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335112094879</t>
+    <t xml:space="preserve">1.99563109874725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335135936737</t>
   </si>
   <si>
     <t xml:space="preserve">1.971759557724</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92242610454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91606044769287</t>
+    <t xml:space="preserve">1.92242586612701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401719093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92720007896423</t>
+    <t xml:space="preserve">1.92401742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92720031738281</t>
   </si>
   <si>
     <t xml:space="preserve">1.97971677780151</t>
@@ -2933,25 +2933,25 @@
     <t xml:space="preserve">1.96061992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95743703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539425849915</t>
+    <t xml:space="preserve">1.95743727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539413928986</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926520347595</t>
+    <t xml:space="preserve">1.98926544189453</t>
   </si>
   <si>
     <t xml:space="preserve">1.96857690811157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91287755966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94788873195648</t>
+    <t xml:space="preserve">1.91287732124329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478884935379</t>
   </si>
   <si>
     <t xml:space="preserve">1.98449099063873</t>
@@ -2960,19 +2960,19 @@
     <t xml:space="preserve">2.03223347663879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01950192451477</t>
+    <t xml:space="preserve">2.01950240135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06087875366211</t>
+    <t xml:space="preserve">2.06087851524353</t>
   </si>
   <si>
     <t xml:space="preserve">2.04337358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04814743995667</t>
+    <t xml:space="preserve">2.04814767837524</t>
   </si>
   <si>
     <t xml:space="preserve">2.02427625656128</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07997608184814</t>
+    <t xml:space="preserve">2.07997584342957</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">2.10543847084045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13726663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522385597229</t>
+    <t xml:space="preserve">2.13726687431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522361755371</t>
   </si>
   <si>
     <t xml:space="preserve">2.18819165229797</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">2.17068600654602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15158939361572</t>
+    <t xml:space="preserve">2.15158915519714</t>
   </si>
   <si>
     <t xml:space="preserve">2.12453556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11816954612732</t>
+    <t xml:space="preserve">2.1181697845459</t>
   </si>
   <si>
     <t xml:space="preserve">2.10066413879395</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">2.10862112045288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08952403068542</t>
+    <t xml:space="preserve">2.089524269104</t>
   </si>
   <si>
     <t xml:space="preserve">2.0847499370575</t>
@@ -3053,16 +3053,16 @@
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249230384827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363241195679</t>
+    <t xml:space="preserve">2.11339545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249254226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612652778625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363217353821</t>
   </si>
   <si>
     <t xml:space="preserve">2.04178190231323</t>
@@ -3071,40 +3071,40 @@
     <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09589004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02586770057678</t>
+    <t xml:space="preserve">2.04019045829773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09588980674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02586793899536</t>
   </si>
   <si>
     <t xml:space="preserve">2.03064203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98767364025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01154541969299</t>
+    <t xml:space="preserve">1.98767387866974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01154518127441</t>
   </si>
   <si>
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341755867004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18978357315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023467063904</t>
+    <t xml:space="preserve">2.18341779708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18978333473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023490905762</t>
   </si>
   <si>
     <t xml:space="preserve">2.16113805770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20569729804993</t>
+    <t xml:space="preserve">2.20569753646851</t>
   </si>
   <si>
     <t xml:space="preserve">2.21842861175537</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">2.29163360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27412819862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25343990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29481625556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23593425750732</t>
+    <t xml:space="preserve">2.27412843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2534396648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29481649398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23593401908875</t>
   </si>
   <si>
     <t xml:space="preserve">2.25025701522827</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">2.27571940422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27890253067017</t>
+    <t xml:space="preserve">2.27890229225159</t>
   </si>
   <si>
     <t xml:space="preserve">2.22161149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23115968704224</t>
+    <t xml:space="preserve">2.23115992546082</t>
   </si>
   <si>
     <t xml:space="preserve">2.200923204422</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">2.19296598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19774055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10384678840637</t>
+    <t xml:space="preserve">2.19774031639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10384702682495</t>
   </si>
   <si>
     <t xml:space="preserve">2.15795493125916</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">2.12930965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12771844863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10702967643738</t>
+    <t xml:space="preserve">2.12771821022034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10702991485596</t>
   </si>
   <si>
     <t xml:space="preserve">2.07520151138306</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">2.07201862335205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08634114265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14204096794128</t>
+    <t xml:space="preserve">2.086341381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14204072952271</t>
   </si>
   <si>
     <t xml:space="preserve">2.09748125076294</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111571311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06883573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01472806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02905082702637</t>
+    <t xml:space="preserve">2.09111595153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06883597373962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01472783088684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
     <t xml:space="preserve">1.9781254529953</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">2.11976099014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03541612625122</t>
+    <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
     <t xml:space="preserve">1.98130810260773</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128599643707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8937805891037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969467163086</t>
+    <t xml:space="preserve">1.91128623485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89378046989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969491004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">1.90651178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87945771217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81261885166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79193043708801</t>
+    <t xml:space="preserve">1.87945795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261873245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.7553277015686</t>
@@ -3260,67 +3260,67 @@
     <t xml:space="preserve">1.79033887386322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85558676719666</t>
+    <t xml:space="preserve">1.85558664798737</t>
   </si>
   <si>
     <t xml:space="preserve">1.83330678939819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922075271606</t>
+    <t xml:space="preserve">1.84922087192535</t>
   </si>
   <si>
     <t xml:space="preserve">1.83171534538269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82534992694855</t>
+    <t xml:space="preserve">1.82534980773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82694137096405</t>
+    <t xml:space="preserve">1.82694125175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444689750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423216342926</t>
+    <t xml:space="preserve">1.84444665908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423204421997</t>
   </si>
   <si>
     <t xml:space="preserve">1.8380811214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85240387916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104927539825</t>
+    <t xml:space="preserve">1.85240399837494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104915618896</t>
   </si>
   <si>
     <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89537179470062</t>
+    <t xml:space="preserve">1.89537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881398677826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01791095733643</t>
+    <t xml:space="preserve">1.99881374835968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01791071891785</t>
   </si>
   <si>
     <t xml:space="preserve">2.01313638687134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9828999042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0035879611969</t>
+    <t xml:space="preserve">1.98289966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00358819961548</t>
   </si>
   <si>
     <t xml:space="preserve">1.9431140422821</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786626815796</t>
+    <t xml:space="preserve">1.87786650657654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221148967743</t>
+    <t xml:space="preserve">1.96221125125885</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038308620453</t>
+    <t xml:space="preserve">1.93038332462311</t>
   </si>
   <si>
     <t xml:space="preserve">1.93993151187897</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">1.90014612674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91765165328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91924321651459</t>
+    <t xml:space="preserve">1.91765189170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91924297809601</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71235954761505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6423374414444</t>
+    <t xml:space="preserve">1.71235942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64233732223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">1.6168749332428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483191490173</t>
+    <t xml:space="preserve">1.62483179569244</t>
   </si>
   <si>
     <t xml:space="preserve">1.65506863594055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70758533477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69644546508789</t>
+    <t xml:space="preserve">1.70758521556854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6964453458786</t>
   </si>
   <si>
     <t xml:space="preserve">1.68053138256073</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68848836421967</t>
+    <t xml:space="preserve">1.68848824501038</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435811519623</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57151973247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.577885389328</t>
+    <t xml:space="preserve">1.57151961326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57788527011871</t>
   </si>
   <si>
     <t xml:space="preserve">1.58504664897919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58743381500244</t>
+    <t xml:space="preserve">1.58743369579315</t>
   </si>
   <si>
     <t xml:space="preserve">1.54128277301788</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025021076202</t>
+    <t xml:space="preserve">1.51025032997131</t>
   </si>
   <si>
     <t xml:space="preserve">1.53383469581604</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446163654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5026695728302</t>
+    <t xml:space="preserve">1.51446175575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50266945362091</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
@@ -3485,25 +3485,25 @@
     <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47403109073639</t>
+    <t xml:space="preserve">1.47403120994568</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48498106002808</t>
+    <t xml:space="preserve">1.48498117923737</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171960353851</t>
+    <t xml:space="preserve">1.49171948432922</t>
   </si>
   <si>
     <t xml:space="preserve">1.46645045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45718514919281</t>
+    <t xml:space="preserve">1.4571852684021</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">1.3990660905838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3620046377182</t>
+    <t xml:space="preserve">1.36200475692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">1.34178960323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26177060604095</t>
+    <t xml:space="preserve">1.26766669750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26177072525024</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144781589508</t>
+    <t xml:space="preserve">1.23144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">1.20365166664124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20533633232117</t>
+    <t xml:space="preserve">1.20533645153046</t>
   </si>
   <si>
     <t xml:space="preserve">1.175013422966</t>
@@ -3587,22 +3587,22 @@
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942136287689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1059445142746</t>
+    <t xml:space="preserve">1.11942148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10594439506531</t>
   </si>
   <si>
     <t xml:space="preserve">1.14300584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16911733150482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965539455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16490578651428</t>
+    <t xml:space="preserve">1.16911721229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965551376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16490566730499</t>
   </si>
   <si>
     <t xml:space="preserve">1.13710963726044</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">1.11352527141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12700223922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12279057502747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0815178155899</t>
+    <t xml:space="preserve">1.12700212001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12279045581818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08151769638062</t>
   </si>
   <si>
     <t xml:space="preserve">1.10425996780396</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553272724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427884578705</t>
+    <t xml:space="preserve">1.14553284645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427872657776</t>
   </si>
   <si>
     <t xml:space="preserve">1.22470927238464</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24492454528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25334763526917</t>
+    <t xml:space="preserve">1.24829375743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24492466449738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25334775447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818624019623</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31652045249939</t>
+    <t xml:space="preserve">1.3165203332901</t>
   </si>
   <si>
     <t xml:space="preserve">1.3299971818924</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35358166694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32747042179108</t>
+    <t xml:space="preserve">1.3535817861557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32747030258179</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33589339256287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31062436103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29546272754669</t>
+    <t xml:space="preserve">1.33589327335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31062424182892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29546284675598</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135893821716</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2365015745163</t>
+    <t xml:space="preserve">1.23650169372559</t>
   </si>
   <si>
     <t xml:space="preserve">1.25503218173981</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039032936096</t>
+    <t xml:space="preserve">1.21039021015167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4656081199646</t>
+    <t xml:space="preserve">1.46560823917389</t>
   </si>
   <si>
     <t xml:space="preserve">1.4041200876236</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">1.43360066413879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44370830059052</t>
+    <t xml:space="preserve">1.44370818138123</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42265057563782</t>
+    <t xml:space="preserve">1.42265069484711</t>
   </si>
   <si>
     <t xml:space="preserve">1.44623517990112</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770457267761</t>
+    <t xml:space="preserve">1.42770445346832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727378845215</t>
+    <t xml:space="preserve">1.38727390766144</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37716639041901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431648254395</t>
+    <t xml:space="preserve">1.37716627120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
     <t xml:space="preserve">1.34515881538391</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230890750885</t>
+    <t xml:space="preserve">1.31230878829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">1.53888845443726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5666846036911</t>
+    <t xml:space="preserve">1.56668448448181</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
@@ -3914,28 +3914,28 @@
     <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61132669448853</t>
+    <t xml:space="preserve">1.61132657527924</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57426524162292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521521091461</t>
+    <t xml:space="preserve">1.57426536083221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5852153301239</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942663669586</t>
+    <t xml:space="preserve">1.58942675590515</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784960746765</t>
+    <t xml:space="preserve">1.59784972667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">1.64754557609558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65007269382477</t>
+    <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
     <t xml:space="preserve">1.62396109104156</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">1.62227654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58774220943451</t>
+    <t xml:space="preserve">1.58774209022522</t>
   </si>
   <si>
     <t xml:space="preserve">1.62480342388153</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57763457298279</t>
+    <t xml:space="preserve">1.5776344537735</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353066444397</t>
+    <t xml:space="preserve">1.58353054523468</t>
   </si>
   <si>
     <t xml:space="preserve">1.57089602947235</t>
@@ -5304,6 +5304,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.75799989700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73799991607666</t>
   </si>
 </sst>
 </file>
@@ -70434,7 +70437,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.650150463</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>1984873</v>
@@ -70455,6 +70458,32 @@
         <v>1763</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493865741</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>3080419</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>2.74200010299683</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>2.7720000743866</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>2.73799991607666</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="1766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="1767">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806071281433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92702704668045</t>
+    <t xml:space="preserve">0.923806250095367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92702728509903</t>
   </si>
   <si>
     <t xml:space="preserve">0.921873509883881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901902735233307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898037552833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652355670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835356235504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643665790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346323490143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154633045197</t>
+    <t xml:space="preserve">0.901902616024017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898037374019623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652415275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835415840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643486976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863894045352936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346442699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851653873920441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154811859131</t>
   </si>
   <si>
     <t xml:space="preserve">0.836192607879639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856163322925568</t>
+    <t xml:space="preserve">0.856163382530212</t>
   </si>
   <si>
     <t xml:space="preserve">0.857451796531677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869691908359528</t>
+    <t xml:space="preserve">0.869692087173462</t>
   </si>
   <si>
     <t xml:space="preserve">0.886441588401794</t>
@@ -101,49 +101,49 @@
     <t xml:space="preserve">0.908344805240631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888374209403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551905632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279123306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798899650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481141090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825240969657898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432838916779</t>
+    <t xml:space="preserve">0.888374090194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279182910919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798959255219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481200695038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241029262543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432719707489</t>
   </si>
   <si>
     <t xml:space="preserve">0.869047701358795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876778304576874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172132015228</t>
+    <t xml:space="preserve">0.876778244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
   </si>
   <si>
     <t xml:space="preserve">0.923161864280701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927671372890472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142847061157</t>
+    <t xml:space="preserve">0.927671432495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914143025875092</t>
   </si>
   <si>
     <t xml:space="preserve">0.945709466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919296622276306</t>
+    <t xml:space="preserve">0.919296681880951</t>
   </si>
   <si>
     <t xml:space="preserve">0.916075587272644</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">0.941200017929077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947641968727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892646312714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412184238434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918008208274841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954084277153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391589164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179363250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01270806789398</t>
+    <t xml:space="preserve">0.947642147541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892407894135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113442897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008267879486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954084396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391648769379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179482460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01270794868469</t>
   </si>
   <si>
     <t xml:space="preserve">1.02881324291229</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">1.02365958690643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00819861888885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175642967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00497722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755417346954</t>
+    <t xml:space="preserve">1.00819849967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175607204437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497734546661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755429267883</t>
   </si>
   <si>
     <t xml:space="preserve">1.02172696590424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464056968689</t>
+    <t xml:space="preserve">1.01464068889618</t>
   </si>
   <si>
     <t xml:space="preserve">1.02237129211426</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">0.999823570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01141953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206362247467</t>
+    <t xml:space="preserve">1.01141965389252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206374168396</t>
   </si>
   <si>
     <t xml:space="preserve">1.01786172389984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02430367469788</t>
+    <t xml:space="preserve">1.02430391311646</t>
   </si>
   <si>
     <t xml:space="preserve">1.01850581169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0268806219101</t>
+    <t xml:space="preserve">1.02688074111938</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203439712524</t>
@@ -239,22 +239,22 @@
     <t xml:space="preserve">1.01721739768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00562167167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988871932029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368905067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0352555513382</t>
+    <t xml:space="preserve">1.00562143325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988871872425079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03525567054749</t>
   </si>
   <si>
     <t xml:space="preserve">1.02816927433014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04040920734406</t>
+    <t xml:space="preserve">1.04040932655334</t>
   </si>
   <si>
     <t xml:space="preserve">1.03396713733673</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">1.03010177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01592886447906</t>
+    <t xml:space="preserve">1.01592922210693</t>
   </si>
   <si>
     <t xml:space="preserve">0.992093026638031</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">0.995958268642426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995314061641693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0210827589035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04942810535431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519686222076</t>
+    <t xml:space="preserve">0.995314240455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02108287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519698143005</t>
   </si>
   <si>
     <t xml:space="preserve">1.06295669078827</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">1.06231272220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04749572277069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06360113620758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06166839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06811034679413</t>
+    <t xml:space="preserve">1.0474956035614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.063600897789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0616682767868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06811058521271</t>
   </si>
   <si>
     <t xml:space="preserve">1.04620718955994</t>
@@ -323,52 +323,52 @@
     <t xml:space="preserve">0.977276027202606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968257129192352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965035915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978564500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522387504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232907295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517287254333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712161540985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964867115021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701722621918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680665969849</t>
+    <t xml:space="preserve">0.968257009983063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965035855770111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564560413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522327899933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517048835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90771210193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87696498632431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701663017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680546760559</t>
   </si>
   <si>
     <t xml:space="preserve">0.929101526737213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935117423534393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127802848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909049034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033316135406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915733218193054</t>
+    <t xml:space="preserve">0.935117363929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127743244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048914909363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033196926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
     <t xml:space="preserve">0.925090968608856</t>
@@ -377,109 +377,109 @@
     <t xml:space="preserve">0.931775271892548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925759375095367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912391126155853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921080589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927096426486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143818855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122523784637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95583838224411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164637088776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527726173401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196192264557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982574999332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98391181230545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972548723220825</t>
+    <t xml:space="preserve">0.925759315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912391066551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921080529689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92709618806839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143640041351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122583389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95316469669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527785778046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196013450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982574939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97254866361618</t>
   </si>
   <si>
     <t xml:space="preserve">0.973217129707336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984580338001251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987253963947296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99527496099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601275444031</t>
+    <t xml:space="preserve">0.984580218791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253904342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995275020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98925918340683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601215839386</t>
   </si>
   <si>
     <t xml:space="preserve">0.975890874862671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951827824115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950490891933441</t>
+    <t xml:space="preserve">0.951827764511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950491011142731</t>
   </si>
   <si>
     <t xml:space="preserve">0.948485672473907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941133141517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501450061798</t>
+    <t xml:space="preserve">0.94113302230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501330852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.965864598751068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985917031764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927530288696</t>
+    <t xml:space="preserve">0.985917210578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927589893341</t>
   </si>
   <si>
     <t xml:space="preserve">1.01265382766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02000641822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99193286895752</t>
+    <t xml:space="preserve">1.02000653743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99193274974823</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996611773967743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901194572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967201173305511</t>
+    <t xml:space="preserve">0.996611833572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901373386383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201411724091</t>
   </si>
   <si>
     <t xml:space="preserve">0.986585438251495</t>
@@ -488,52 +488,52 @@
     <t xml:space="preserve">0.977896094322205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973885655403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943248271942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401697635651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00864315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00262761116028</t>
+    <t xml:space="preserve">0.973885595798492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943367481232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401673793793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00864326953888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0026273727417</t>
   </si>
   <si>
     <t xml:space="preserve">0.969206631183624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97522246837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248625278473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02936410903931</t>
+    <t xml:space="preserve">0.975222408771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248804092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936434745789</t>
   </si>
   <si>
     <t xml:space="preserve">1.05342733860016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05543255805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07615351676941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08952212333679</t>
+    <t xml:space="preserve">1.05543279647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0761536359787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0895220041275</t>
   </si>
   <si>
     <t xml:space="preserve">1.09420084953308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09687459468842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07013785839081</t>
+    <t xml:space="preserve">1.09687447547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07013773918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.08751666545868</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">1.09353244304657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749056816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06479036808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06278502941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04741156101227</t>
+    <t xml:space="preserve">1.07749032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06479060649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06278538703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04741168022156</t>
   </si>
   <si>
     <t xml:space="preserve">1.06077992916107</t>
@@ -560,73 +560,73 @@
     <t xml:space="preserve">1.06813251972198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05209052562714</t>
+    <t xml:space="preserve">1.05209040641785</t>
   </si>
   <si>
     <t xml:space="preserve">0.957843482494354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953833043575287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480453014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935785710811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469894886017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738556861877</t>
+    <t xml:space="preserve">0.953832983970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935785591602325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780372142792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727760314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738318443298</t>
   </si>
   <si>
     <t xml:space="preserve">0.941801488399506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918406963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538224697113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869579792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569899082184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948467731476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01532733440399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01599586009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02869582176208</t>
+    <t xml:space="preserve">0.918406844139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538165092468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869818210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98056972026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606554508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948527336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01532757282257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01599597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02869606018066</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203797340393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04005897045135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04473769664764</t>
+    <t xml:space="preserve">1.04005885124207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04473781585693</t>
   </si>
   <si>
     <t xml:space="preserve">1.03070116043091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">1.0173327922821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.036048412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0494167804718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275917053223</t>
+    <t xml:space="preserve">1.03604853153229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874861240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04941689968109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275893211365</t>
   </si>
   <si>
     <t xml:space="preserve">1.05008518695831</t>
@@ -659,40 +659,40 @@
     <t xml:space="preserve">1.02468526363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0106486082077</t>
+    <t xml:space="preserve">1.01064836978912</t>
   </si>
   <si>
     <t xml:space="preserve">1.00530111789703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03003251552582</t>
+    <t xml:space="preserve">1.03003263473511</t>
   </si>
   <si>
     <t xml:space="preserve">1.04273271560669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334856987</t>
+    <t xml:space="preserve">1.02334845066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412208080292</t>
+    <t xml:space="preserve">1.06412196159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.0561009645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810618400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484315872192</t>
+    <t xml:space="preserve">1.05810630321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484303951263</t>
   </si>
   <si>
     <t xml:space="preserve">1.07080626487732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0821692943573</t>
+    <t xml:space="preserve">1.08216941356659</t>
   </si>
   <si>
     <t xml:space="preserve">1.06880104541779</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">1.0828378200531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08818531036377</t>
+    <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
     <t xml:space="preserve">1.0962061882019</t>
@@ -719,19 +719,19 @@
     <t xml:space="preserve">1.12628495693207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18978476524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120034694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988975048065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24058437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26665282249451</t>
+    <t xml:space="preserve">1.18978464603424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22120046615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24058449268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26665270328522</t>
   </si>
   <si>
     <t xml:space="preserve">1.28002119064331</t>
@@ -743,70 +743,70 @@
     <t xml:space="preserve">1.29405796527863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932644844055</t>
+    <t xml:space="preserve">1.27133166790009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932656764984</t>
   </si>
   <si>
     <t xml:space="preserve">1.30074226856232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31009995937347</t>
+    <t xml:space="preserve">1.31010007858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475258827209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30007386207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31143701076508</t>
+    <t xml:space="preserve">1.30007374286652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31143689155579</t>
   </si>
   <si>
     <t xml:space="preserve">1.29004752635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28871059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29739999771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28937911987305</t>
+    <t xml:space="preserve">1.28871047496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29740011692047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28937900066376</t>
   </si>
   <si>
     <t xml:space="preserve">1.27200019359589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2593001127243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29673159122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806852340698</t>
+    <t xml:space="preserve">1.25930023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29673171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806840419769</t>
   </si>
   <si>
     <t xml:space="preserve">1.31076848506927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2933896780014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814717292786</t>
+    <t xml:space="preserve">1.29338932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814729213715</t>
   </si>
   <si>
     <t xml:space="preserve">1.30341601371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33683681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349454402924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35421550273895</t>
+    <t xml:space="preserve">1.33683669567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349478244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35421574115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.3702574968338</t>
@@ -818,52 +818,52 @@
     <t xml:space="preserve">1.364910364151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37961554527283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33616828918457</t>
+    <t xml:space="preserve">1.37961542606354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33616816997528</t>
   </si>
   <si>
     <t xml:space="preserve">1.34886813163757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39031004905701</t>
+    <t xml:space="preserve">1.3903101682663</t>
   </si>
   <si>
     <t xml:space="preserve">1.4103627204895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42105722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175196647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4504679441452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39966809749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303634643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442571163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704666614532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42239427566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40902590751648</t>
+    <t xml:space="preserve">1.42105734348297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046806335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303646564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442583084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704678535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42239439487457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40902602672577</t>
   </si>
   <si>
     <t xml:space="preserve">1.43977320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44779407978058</t>
+    <t xml:space="preserve">1.44779396057129</t>
   </si>
   <si>
     <t xml:space="preserve">1.4705206155777</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">1.46116268634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47319388389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4624992609024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46650993824005</t>
+    <t xml:space="preserve">1.47319400310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249938011169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650981903076</t>
   </si>
   <si>
     <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48336625099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49024653434753</t>
+    <t xml:space="preserve">1.4833664894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49024629592896</t>
   </si>
   <si>
     <t xml:space="preserve">1.47235822677612</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">1.4228208065033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44208514690399</t>
+    <t xml:space="preserve">1.44208526611328</t>
   </si>
   <si>
     <t xml:space="preserve">1.40630829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39530026912689</t>
+    <t xml:space="preserve">1.3953001499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.39942800998688</t>
@@ -914,70 +914,70 @@
     <t xml:space="preserve">1.40080428123474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40218019485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38429188728333</t>
+    <t xml:space="preserve">1.40218031406403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38429176807404</t>
   </si>
   <si>
     <t xml:space="preserve">1.4145644903183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42144477367401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43658137321472</t>
+    <t xml:space="preserve">1.42144465446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43658125400543</t>
   </si>
   <si>
     <t xml:space="preserve">1.43245303630829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42419683933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43107688426971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483721256256</t>
+    <t xml:space="preserve">1.424196600914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.431077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
     <t xml:space="preserve">1.45997357368469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44621360301971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46685373783112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48199033737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46960592269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758951663971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923827171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5012549161911</t>
+    <t xml:space="preserve">1.44621348381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46685385704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48199021816254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46960604190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923839092255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125467777252</t>
   </si>
   <si>
     <t xml:space="preserve">1.49987888336182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50675904750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602350711823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54804003238678</t>
+    <t xml:space="preserve">1.50675892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602338790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54803991317749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115986824036</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">1.52327144145966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52189517021179</t>
+    <t xml:space="preserve">1.52189528942108</t>
   </si>
   <si>
     <t xml:space="preserve">1.54528796672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968878746033</t>
+    <t xml:space="preserve">1.57968890666962</t>
   </si>
   <si>
     <t xml:space="preserve">1.57831275463104</t>
@@ -1004,487 +1004,490 @@
     <t xml:space="preserve">1.57693684101105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56317639350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5466639995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55354416370392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592845916748</t>
+    <t xml:space="preserve">1.56317627429962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54666376113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55354404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592869758606</t>
   </si>
   <si>
     <t xml:space="preserve">1.58381688594818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59069728851318</t>
+    <t xml:space="preserve">1.59069716930389</t>
   </si>
   <si>
     <t xml:space="preserve">1.58656895160675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5824408531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60996174812317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63197815418243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711463451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408960819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583353042603</t>
+    <t xml:space="preserve">1.58244073390961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60996162891388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63197839260101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711475372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408984661102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6058337688446</t>
   </si>
   <si>
     <t xml:space="preserve">1.6003292798996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56455254554749</t>
+    <t xml:space="preserve">1.5645524263382</t>
   </si>
   <si>
     <t xml:space="preserve">1.53978371620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53565573692322</t>
+    <t xml:space="preserve">1.53565561771393</t>
   </si>
   <si>
     <t xml:space="preserve">1.54391193389893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56180059909821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427982330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005667686462</t>
+    <t xml:space="preserve">1.56180047988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941642284393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427958488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005655765533</t>
   </si>
   <si>
     <t xml:space="preserve">1.56868052482605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62234604358673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61684155464172</t>
+    <t xml:space="preserve">1.62234592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6168417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57280874252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509787082672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66087472438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353221893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6980277299881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949857234955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986670017242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785005569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66225099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601144313812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490801334381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74894118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105251789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004461288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518073558807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830080986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7668297290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233409881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545357704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77370953559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74068510532379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8204950094223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022228717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747010231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444519519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159820079803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7929744720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7682056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75857329368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554838657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967660427094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142040729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535876750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031721591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481320381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113585948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700776100159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85351991653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86039996147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516867160797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076797008514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361472606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123066902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710245132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957261800766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82737517356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564367294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738711833954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151545524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66913104057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68013942241669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64298641681671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500306129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701958656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114768505096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463529109955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7145402431488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426740169525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6787633895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6526186466217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306951999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930895328522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417271137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692465782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362726688385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289160728455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343705177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380482196808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74206101894379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839573860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399491786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720956325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5975775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620118141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290355205536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49299871921539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134984493256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47648620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511041164398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45722186565399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832505702972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079209804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530690193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5482622385025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52411472797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5312168598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127385139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672751903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55536413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246626377106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513580799103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507881641388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934019088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62212383747101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951128482819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223805904388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6036581993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5937157869339</t>
   </si>
   <si>
     <t xml:space="preserve">1.62922608852386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61133754253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482514858246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280886173248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821782588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509799003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6608749628067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637885570526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940388202667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802784919739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023435115814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949881076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986681938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6622508764267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601132392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490789413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105275630951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004449367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518097400665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830080986023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618923664093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7668297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233374118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77371001243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7406849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8204950094223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022240638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747010231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444531440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159820079803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79297411441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76820576190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7585734128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169336795807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499087810516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031721591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481308460236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921378612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113574028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700740337372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85351991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86040019989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516891002655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361496448517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8012307882309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79572641849518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737493515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738735675812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6801393032074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500306129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68701958656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114756584167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335430622101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215582847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426740169525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6787633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65261876583099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306928157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930895328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692453861237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362702846527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289148807526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343693256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7420608997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839573860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6539945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849054813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757721424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620118141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290355205536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49299871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034158229828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4764860868454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611855506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4751101732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45722150802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832493782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776719093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079209804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542124271393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530690193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54826200008392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52411472797394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121674060822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127408981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837586402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672739982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246638298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513592720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934019088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6221239566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57951128482819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223805904388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60365855693817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371554851532</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.63632822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63348734378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638521194458</t>
+    <t xml:space="preserve">1.63348746299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638533115387</t>
   </si>
   <si>
     <t xml:space="preserve">1.61076045036316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58803391456604</t>
+    <t xml:space="preserve">1.58803379535675</t>
   </si>
   <si>
     <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6888839006424</t>
+    <t xml:space="preserve">1.68888378143311</t>
   </si>
   <si>
     <t xml:space="preserve">1.68178176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882690906525</t>
+    <t xml:space="preserve">1.69882667064667</t>
   </si>
   <si>
     <t xml:space="preserve">1.72013318538666</t>
@@ -1493,31 +1496,31 @@
     <t xml:space="preserve">1.71729242801666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64911186695099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757762432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894089221954</t>
+    <t xml:space="preserve">1.64911210536957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894124984741</t>
   </si>
   <si>
     <t xml:space="preserve">1.67752063274384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67183899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343023300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6192831993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61786293983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5766704082489</t>
+    <t xml:space="preserve">1.67183887958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.643430352211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61928331851959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61786270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667052745819</t>
   </si>
   <si>
     <t xml:space="preserve">1.56388664245605</t>
@@ -1529,7 +1532,7 @@
     <t xml:space="preserve">1.55394351482391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55252313613892</t>
+    <t xml:space="preserve">1.55252325534821</t>
   </si>
   <si>
     <t xml:space="preserve">1.55110287666321</t>
@@ -1538,25 +1541,25 @@
     <t xml:space="preserve">1.51701247692108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559233665466</t>
+    <t xml:space="preserve">1.51559221744537</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871829032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43462800979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44741189479828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45735466480255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47155916690826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47013866901398</t>
+    <t xml:space="preserve">1.43462812900543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44741201400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45735490322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47155904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4701384305954</t>
   </si>
   <si>
     <t xml:space="preserve">1.47297942638397</t>
@@ -1565,13 +1568,13 @@
     <t xml:space="preserve">1.53263735771179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58377265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973948955536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275134086609</t>
+    <t xml:space="preserve">1.58377254009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973925113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275146007538</t>
   </si>
   <si>
     <t xml:space="preserve">1.48718369007111</t>
@@ -1580,49 +1583,49 @@
     <t xml:space="preserve">1.47724068164825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49144494533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138783454895</t>
+    <t xml:space="preserve">1.49144506454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138795375824</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996745586395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49570643901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41687262058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4218442440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911758899689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065207004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426018714905</t>
+    <t xml:space="preserve">1.49570620059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41687273979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42184436321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39911735057831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065183162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426006793976</t>
   </si>
   <si>
     <t xml:space="preserve">1.3522435426712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37994170188904</t>
+    <t xml:space="preserve">1.37994182109833</t>
   </si>
   <si>
     <t xml:space="preserve">1.37070894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36573755741119</t>
+    <t xml:space="preserve">1.3657374382019</t>
   </si>
   <si>
     <t xml:space="preserve">1.37923157215118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37212944030762</t>
+    <t xml:space="preserve">1.37212932109833</t>
   </si>
   <si>
     <t xml:space="preserve">1.35579454898834</t>
@@ -1631,49 +1634,49 @@
     <t xml:space="preserve">1.38633370399475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431694030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39343583583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130520820618</t>
+    <t xml:space="preserve">1.36431705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39343571662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130508899689</t>
   </si>
   <si>
     <t xml:space="preserve">1.35863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40906023979187</t>
+    <t xml:space="preserve">1.40906059741974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40124809741974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46019566059113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45309352874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439980506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866117954254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593440532684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894649505615</t>
+    <t xml:space="preserve">1.46019577980042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45309364795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439992427826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866129875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593428611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894637584686</t>
   </si>
   <si>
     <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39556634426117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568032741547</t>
+    <t xml:space="preserve">1.39556646347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568056583405</t>
   </si>
   <si>
     <t xml:space="preserve">1.3870438337326</t>
@@ -1682,61 +1685,58 @@
     <t xml:space="preserve">1.39201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3778110742569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40266859531403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38136208057404</t>
+    <t xml:space="preserve">1.37781119346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40266847610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38136219978333</t>
   </si>
   <si>
     <t xml:space="preserve">1.33519840240479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36076593399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320763111115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468523979187</t>
+    <t xml:space="preserve">1.36076605319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940254688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43178725242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468512058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.4204238653183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48150205612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985371112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4886040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428606033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258024692535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115998744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52553498744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52979636192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52695560455322</t>
+    <t xml:space="preserve">1.48150193691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985347270966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48860418796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428582191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258036613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52553534507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5297966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52695572376251</t>
   </si>
   <si>
     <t xml:space="preserve">1.53405785560608</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">1.51133096218109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5099104642868</t>
+    <t xml:space="preserve">1.50991034507751</t>
   </si>
   <si>
     <t xml:space="preserve">1.48008167743683</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">1.4829226732254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48434293270111</t>
+    <t xml:space="preserve">1.48434257507324</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689873218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61644232273102</t>
+    <t xml:space="preserve">1.53689861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61644220352173</t>
   </si>
   <si>
     <t xml:space="preserve">1.62780582904816</t>
@@ -1787,79 +1787,79 @@
     <t xml:space="preserve">1.59939730167389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62070369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61502194404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627110958099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218118667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5141716003418</t>
+    <t xml:space="preserve">1.62070345878601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61502182483673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627122879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218106746674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51417171955109</t>
   </si>
   <si>
     <t xml:space="preserve">1.50422871112823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48576331138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303641796112</t>
+    <t xml:space="preserve">1.48576319217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303653717041</t>
   </si>
   <si>
     <t xml:space="preserve">1.45877516269684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49286544322968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5567843914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5780907869339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58661329746246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916921615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450854301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166778564453</t>
+    <t xml:space="preserve">1.49286532402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55678451061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57809066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58661341667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738297700882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916909694672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7045089006424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166754722595</t>
   </si>
   <si>
     <t xml:space="preserve">1.69172465801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69061779975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69356310367584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69798111915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325471878052</t>
+    <t xml:space="preserve">1.69061756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69356322288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69798099994659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294585704803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325448036194</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619978427887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72890710830688</t>
+    <t xml:space="preserve">1.72890722751617</t>
   </si>
   <si>
     <t xml:space="preserve">1.75099694728851</t>
@@ -1868,19 +1868,19 @@
     <t xml:space="preserve">1.76277840137482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74510633945465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73332512378693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161419391632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750504016876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812204837799</t>
+    <t xml:space="preserve">1.74510622024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73332500457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812216758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.8010675907135</t>
@@ -1892,157 +1892,157 @@
     <t xml:space="preserve">1.80401277542114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81137645244598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603209018707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76719653606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216103553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239925384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7392156124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77014136314392</t>
+    <t xml:space="preserve">1.81137633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603232860565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76719641685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216091632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239913463593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921597003937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77014172077179</t>
   </si>
   <si>
     <t xml:space="preserve">1.78486835956573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78928649425507</t>
+    <t xml:space="preserve">1.78928637504578</t>
   </si>
   <si>
     <t xml:space="preserve">1.79664957523346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79517698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370427131653</t>
+    <t xml:space="preserve">1.79517686367035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370439052582</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79959499835968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254018306732</t>
+    <t xml:space="preserve">1.79959511756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254030227661</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78192281723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493900299072</t>
+    <t xml:space="preserve">1.78192293643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493912220001</t>
   </si>
   <si>
     <t xml:space="preserve">1.8202121257782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81873953342438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966552257538</t>
+    <t xml:space="preserve">1.81873965263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82168471813202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966564178467</t>
   </si>
   <si>
     <t xml:space="preserve">1.84819269180298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82904815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425087451935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81432139873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8319935798645</t>
+    <t xml:space="preserve">1.82904827594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425099372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81432163715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990374088287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83199322223663</t>
   </si>
   <si>
     <t xml:space="preserve">1.86144685745239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91593527793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655264377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213474750519</t>
+    <t xml:space="preserve">1.91593539714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655276298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213486671448</t>
   </si>
   <si>
     <t xml:space="preserve">1.95127928256989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97042393684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9424432516098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9615877866745</t>
+    <t xml:space="preserve">1.97042417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569717884064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244337081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980657100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158802509308</t>
   </si>
   <si>
     <t xml:space="preserve">1.98809587955475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99693179130554</t>
+    <t xml:space="preserve">1.99693191051483</t>
   </si>
   <si>
     <t xml:space="preserve">2.00724053382874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.983677983284</t>
+    <t xml:space="preserve">1.98367774486542</t>
   </si>
   <si>
     <t xml:space="preserve">1.99987721443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00576758384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98073279857635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97189664840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97631466388702</t>
+    <t xml:space="preserve">2.0057680606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98073256015778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9718964099884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97631478309631</t>
   </si>
   <si>
     <t xml:space="preserve">1.94391596317291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96895134449005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600592136383</t>
+    <t xml:space="preserve">1.96895122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600604057312</t>
   </si>
   <si>
     <t xml:space="preserve">1.97484183311462</t>
@@ -2051,76 +2051,76 @@
     <t xml:space="preserve">2.01754927635193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04847502708435</t>
+    <t xml:space="preserve">2.04847526550293</t>
   </si>
   <si>
     <t xml:space="preserve">2.02049446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04552960395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03374838829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05436587333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02785754203796</t>
+    <t xml:space="preserve">2.04552984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03374814987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05436563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02785778045654</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227591514587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04111218452454</t>
+    <t xml:space="preserve">2.04111194610596</t>
   </si>
   <si>
     <t xml:space="preserve">2.03816652297974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01018595695496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00871300697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99251413345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02638530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07940077781677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0720374584198</t>
+    <t xml:space="preserve">2.01018571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00871276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99251401424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02638506889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07940053939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467413902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07203769683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.06172919273376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03522086143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614685058594</t>
+    <t xml:space="preserve">2.03522109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614708900452</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645583152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08676433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02196717262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05731081962585</t>
+    <t xml:space="preserve">2.0867645740509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02196741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05731105804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.07351040840149</t>
@@ -2132,31 +2132,31 @@
     <t xml:space="preserve">2.00282263755798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313090324402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01460409164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11179947853088</t>
+    <t xml:space="preserve">2.0131311416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01460385322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04258418083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11179971694946</t>
   </si>
   <si>
     <t xml:space="preserve">2.08087372779846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749831199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11032700538635</t>
+    <t xml:space="preserve">2.07498288154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11032676696777</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10885429382324</t>
+    <t xml:space="preserve">2.10885453224182</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652635574341</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">2.17659664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19426870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2458119392395</t>
+    <t xml:space="preserve">2.20457768440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19426894187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24581170082092</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
@@ -2192,76 +2192,76 @@
     <t xml:space="preserve">2.20752286911011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17365121841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23255801200867</t>
+    <t xml:space="preserve">2.17365145683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23255825042725</t>
   </si>
   <si>
     <t xml:space="preserve">2.21930384635925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21635890007019</t>
+    <t xml:space="preserve">2.21635866165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.20310497283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24728465080261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2870466709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201152801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25023031234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1147449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11621737480164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1530339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13094401359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02491211891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08823680877686</t>
+    <t xml:space="preserve">2.24728441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28704643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201128959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25023007392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11474466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11621761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15303421020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13094449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0249125957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08823704719543</t>
   </si>
   <si>
     <t xml:space="preserve">2.10296368598938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83641123771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65380132198334</t>
+    <t xml:space="preserve">1.98220503330231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83641135692596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65380108356476</t>
   </si>
   <si>
     <t xml:space="preserve">1.63318395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724911212921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42921996116638</t>
+    <t xml:space="preserve">1.38724899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
     <t xml:space="preserve">1.35190510749817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043251514435</t>
+    <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330729484558</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">1.36442291736603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32171547412872</t>
+    <t xml:space="preserve">1.32171559333801</t>
   </si>
   <si>
     <t xml:space="preserve">1.3150886297226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40565741062164</t>
+    <t xml:space="preserve">1.40565729141235</t>
   </si>
   <si>
     <t xml:space="preserve">1.37767684459686</t>
@@ -2294,61 +2294,61 @@
     <t xml:space="preserve">1.65674662590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55071485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477694272995</t>
+    <t xml:space="preserve">1.55071461200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54776930809021</t>
   </si>
   <si>
     <t xml:space="preserve">1.53598821163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56249594688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56102323532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55365991592407</t>
+    <t xml:space="preserve">1.56249606609344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56102335453033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55366003513336</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54187893867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58164060115814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60225808620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434792518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256659030914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61698484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64643788337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65527403354645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67589116096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66705513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349257946014</t>
+    <t xml:space="preserve">1.54187881946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58164083957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60225796699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434804439545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256670951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61698472499847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287533283234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64643800258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65527379512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67589128017426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66705501079559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349269866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.60520339012146</t>
@@ -2357,40 +2357,40 @@
     <t xml:space="preserve">1.57575011253357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.587531208992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55807816982269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427752017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047675132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784018993378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64201998710632</t>
+    <t xml:space="preserve">1.58753144741058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5580780506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427728176117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5904768705368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59784007072449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64201986789703</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558253765106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62876582145691</t>
+    <t xml:space="preserve">1.62876570224762</t>
   </si>
   <si>
     <t xml:space="preserve">1.61109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67883658409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76572382450104</t>
+    <t xml:space="preserve">1.6788364648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859848499298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76572358608246</t>
   </si>
   <si>
     <t xml:space="preserve">1.75836038589478</t>
@@ -2402,49 +2402,49 @@
     <t xml:space="preserve">1.7082896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63907480239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821921825409</t>
+    <t xml:space="preserve">1.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821933746338</t>
   </si>
   <si>
     <t xml:space="preserve">1.70534467697144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71123504638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756786346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836574077606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71468591690063</t>
+    <t xml:space="preserve">1.71123492717743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756798267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836562156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
     <t xml:space="preserve">1.69781517982483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7116185426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71621954441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69168031215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70548367500305</t>
+    <t xml:space="preserve">1.71161866188049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71621966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69168043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70548355579376</t>
   </si>
   <si>
     <t xml:space="preserve">1.72542202472687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73462426662445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73769152164459</t>
+    <t xml:space="preserve">1.73462414741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73769176006317</t>
   </si>
   <si>
     <t xml:space="preserve">1.73002314567566</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">1.68707931041718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68554556369781</t>
+    <t xml:space="preserve">1.68554520606995</t>
   </si>
   <si>
     <t xml:space="preserve">1.67327570915222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793871879578</t>
+    <t xml:space="preserve">1.65793859958649</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487134456635</t>
@@ -2471,37 +2471,37 @@
     <t xml:space="preserve">1.70241641998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72235465049744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7070175409317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66867482662201</t>
+    <t xml:space="preserve">1.72235441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70701742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66867470741272</t>
   </si>
   <si>
     <t xml:space="preserve">1.64566898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6533374786377</t>
+    <t xml:space="preserve">1.65333771705627</t>
   </si>
   <si>
     <t xml:space="preserve">1.656405210495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62726449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63646686077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64720261096954</t>
+    <t xml:space="preserve">1.6272646188736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63646697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64720296859741</t>
   </si>
   <si>
     <t xml:space="preserve">1.67020833492279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407382488251</t>
+    <t xml:space="preserve">1.66407370567322</t>
   </si>
   <si>
     <t xml:space="preserve">1.68247807025909</t>
@@ -2510,46 +2510,46 @@
     <t xml:space="preserve">1.7284893989563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73615777492523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75609612464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72695565223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70088255405426</t>
+    <t xml:space="preserve">1.73615765571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75609600543976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72695577144623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70088267326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.72082078456879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69321382045746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094420433044</t>
+    <t xml:space="preserve">1.69321405887604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094432353973</t>
   </si>
   <si>
     <t xml:space="preserve">1.67174220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69934892654419</t>
+    <t xml:space="preserve">1.6993488073349</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69014656543732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008503437042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65180397033691</t>
+    <t xml:space="preserve">1.69014668464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008479595184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861281871796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65180385112762</t>
   </si>
   <si>
     <t xml:space="preserve">1.64873647689819</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">1.58738803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57971954345703</t>
+    <t xml:space="preserve">1.57971966266632</t>
   </si>
   <si>
     <t xml:space="preserve">1.57358479499817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54904544353485</t>
+    <t xml:space="preserve">1.54904556274414</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057919025421</t>
@@ -2591,64 +2591,64 @@
     <t xml:space="preserve">1.4961324930191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50303435325623</t>
+    <t xml:space="preserve">1.50303423404694</t>
   </si>
   <si>
     <t xml:space="preserve">1.51990497112274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54751181602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56438255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53064095973969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60425901412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59198927879333</t>
+    <t xml:space="preserve">1.5475115776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5643824338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53064107894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60425889492035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59198939800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.59965789318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60119152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61499488353729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58125329017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57511830329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60272514820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66100609302521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74075901508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069712638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388827800751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628131389618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186573982239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62879836559296</t>
+    <t xml:space="preserve">1.60119163990021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.614994764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58125340938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57511842250824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6610062122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74075889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069700717926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388815879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628119468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6318656206131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62879848480225</t>
   </si>
   <si>
     <t xml:space="preserve">1.63033187389374</t>
@@ -2666,16 +2666,16 @@
     <t xml:space="preserve">1.61346125602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58585453033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6395343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64260172843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63493299484253</t>
+    <t xml:space="preserve">1.58585464954376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63953411579132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64260160923004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
     <t xml:space="preserve">1.65947246551514</t>
@@ -2684,28 +2684,28 @@
     <t xml:space="preserve">1.66714096069336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6226634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.555180311203</t>
+    <t xml:space="preserve">1.62266337871552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55518043041229</t>
   </si>
   <si>
     <t xml:space="preserve">1.55671393871307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56131505966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56898355484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55978155136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278703689575</t>
+    <t xml:space="preserve">1.56131517887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56898367404938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57051742076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5597813129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278691768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.60732626914978</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">1.63339948654175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192750930786</t>
+    <t xml:space="preserve">1.62419712543488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192739009857</t>
   </si>
   <si>
     <t xml:space="preserve">1.58432066440582</t>
@@ -2726,49 +2726,49 @@
     <t xml:space="preserve">1.61806225776672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64106810092926</t>
+    <t xml:space="preserve">1.64106798171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.66560733318329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67480957508087</t>
+    <t xml:space="preserve">1.67480945587158</t>
   </si>
   <si>
     <t xml:space="preserve">1.71775341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75762975215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8174444437027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8082423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670857429504</t>
+    <t xml:space="preserve">1.75762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517470836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81744432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80824208259583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670845508575</t>
   </si>
   <si>
     <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903960227966</t>
+    <t xml:space="preserve">1.79903995990753</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290521144867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82051169872284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78063535690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79443895816803</t>
+    <t xml:space="preserve">1.82051181793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78063547611237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79443871974945</t>
   </si>
   <si>
     <t xml:space="preserve">1.83278155326843</t>
@@ -2780,112 +2780,112 @@
     <t xml:space="preserve">1.82971405982971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885453224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891654014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818043231964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498951911926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8557870388031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345601081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965217113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87112426757812</t>
+    <t xml:space="preserve">1.85885465145111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891630172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498939990997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85578715801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8634557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87112414836884</t>
   </si>
   <si>
     <t xml:space="preserve">1.89566349983215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90179836750031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91866934299469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90026450157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91100084781647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627606868744</t>
+    <t xml:space="preserve">1.90179848670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91866910457611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90026473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100096702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627594947815</t>
   </si>
   <si>
     <t xml:space="preserve">1.95394456386566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9156014919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173683643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713559627533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553960323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007907390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382090568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621417999268</t>
+    <t xml:space="preserve">1.91560161113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713547706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553996086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695004940033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007931232452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382078647614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9662139415741</t>
   </si>
   <si>
     <t xml:space="preserve">2.00609064102173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00762414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375913619995</t>
+    <t xml:space="preserve">2.00762391090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375889778137</t>
   </si>
   <si>
     <t xml:space="preserve">2.00915789604187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9570118188858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854544639587</t>
+    <t xml:space="preserve">1.95701193809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854556560516</t>
   </si>
   <si>
     <t xml:space="preserve">1.9692816734314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97848379611969</t>
+    <t xml:space="preserve">1.97848391532898</t>
   </si>
   <si>
     <t xml:space="preserve">2.00302290916443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01069164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01836037635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0290961265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03369760513306</t>
+    <t xml:space="preserve">2.01069188117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01835989952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02909588813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
     <t xml:space="preserve">2.01682662963867</t>
@@ -2894,13 +2894,13 @@
     <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563109874725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335135936737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.971759557724</t>
+    <t xml:space="preserve">1.99563097953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335124015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97175967693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.94470584392548</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">1.92242586612701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91606020927429</t>
+    <t xml:space="preserve">1.91606044769287</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2918,64 +2918,64 @@
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92720031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971677780151</t>
+    <t xml:space="preserve">1.9240175485611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92720007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9797168970108</t>
   </si>
   <si>
     <t xml:space="preserve">1.96061992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95743727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539413928986</t>
+    <t xml:space="preserve">1.95743715763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539425849915</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857690811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287732124329</t>
+    <t xml:space="preserve">1.98926532268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857702732086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287744045258</t>
   </si>
   <si>
     <t xml:space="preserve">1.9478884935379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449099063873</t>
+    <t xml:space="preserve">1.98449110984802</t>
   </si>
   <si>
     <t xml:space="preserve">2.03223347663879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01950240135193</t>
+    <t xml:space="preserve">2.01950216293335</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06087851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04337358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04814767837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02427625656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06247043609619</t>
+    <t xml:space="preserve">2.06087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04337334632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04814743995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02427649497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06247019767761</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724452972412</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">2.10543847084045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13726687431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522361755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18819165229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20251441001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17068600654602</t>
+    <t xml:space="preserve">2.13726663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18819189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2025146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1706862449646</t>
   </si>
   <si>
     <t xml:space="preserve">2.15158915519714</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">2.12453556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1181697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08315849304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07042741775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10862112045288</t>
+    <t xml:space="preserve">2.11816954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10066437721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08315873146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07042717933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10862135887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.089524269104</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">2.0847499370575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08793306350708</t>
+    <t xml:space="preserve">2.0879328250885</t>
   </si>
   <si>
     <t xml:space="preserve">2.06565308570862</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249254226685</t>
+    <t xml:space="preserve">2.11339569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249230384827</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612652778625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363217353821</t>
+    <t xml:space="preserve">2.14363241195679</t>
   </si>
   <si>
     <t xml:space="preserve">2.04178190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05928754806519</t>
+    <t xml:space="preserve">2.05928730964661</t>
   </si>
   <si>
     <t xml:space="preserve">2.04019045829773</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02586793899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03064203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98767387866974</t>
+    <t xml:space="preserve">2.02586770057678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03064179420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98767399787903</t>
   </si>
   <si>
     <t xml:space="preserve">2.01154518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15477204322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18341779708862</t>
+    <t xml:space="preserve">2.15477228164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18341732025146</t>
   </si>
   <si>
     <t xml:space="preserve">2.18978333473206</t>
@@ -3098,37 +3098,37 @@
     <t xml:space="preserve">2.18023490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16113805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20569753646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21842861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29163360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27412843704224</t>
+    <t xml:space="preserve">2.16113781929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20569729804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21842885017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29163384437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27412796020508</t>
   </si>
   <si>
     <t xml:space="preserve">2.2534396648407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29481649398804</t>
+    <t xml:space="preserve">2.29481625556946</t>
   </si>
   <si>
     <t xml:space="preserve">2.23593401908875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25025701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27571940422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27890229225159</t>
+    <t xml:space="preserve">2.25025677680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27571964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.22161149978638</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">2.200923204422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17546057701111</t>
+    <t xml:space="preserve">2.17546033859253</t>
   </si>
   <si>
     <t xml:space="preserve">2.19296598434448</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10384702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15795493125916</t>
+    <t xml:space="preserve">2.10384678840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15795516967773</t>
   </si>
   <si>
     <t xml:space="preserve">2.17386913299561</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">2.12771821022034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10702991485596</t>
+    <t xml:space="preserve">2.10702967643738</t>
   </si>
   <si>
     <t xml:space="preserve">2.07520151138306</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">2.086341381073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14204072952271</t>
+    <t xml:space="preserve">2.14204096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.09748125076294</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111595153809</t>
+    <t xml:space="preserve">2.09111571311951</t>
   </si>
   <si>
     <t xml:space="preserve">2.06883597373962</t>
@@ -3200,55 +3200,55 @@
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9781254529953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97016847133636</t>
+    <t xml:space="preserve">1.97812521457672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97016823291779</t>
   </si>
   <si>
     <t xml:space="preserve">2.03700757026672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11976099014282</t>
+    <t xml:space="preserve">2.1197612285614</t>
   </si>
   <si>
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130810260773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02109336853027</t>
+    <t xml:space="preserve">1.98130834102631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02109360694885</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128623485565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89378046989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969491004944</t>
+    <t xml:space="preserve">1.91128599643707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89378070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969467163086</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0019965171814</t>
+    <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
     <t xml:space="preserve">1.90651178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87945795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81261873245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79193031787872</t>
+    <t xml:space="preserve">1.87945783138275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8126186132431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.7553277015686</t>
@@ -3257,13 +3257,13 @@
     <t xml:space="preserve">1.79033887386322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85558664798737</t>
+    <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
     <t xml:space="preserve">1.83330678939819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922087192535</t>
+    <t xml:space="preserve">1.84922099113464</t>
   </si>
   <si>
     <t xml:space="preserve">1.83171534538269</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">1.82534980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8110271692276</t>
+    <t xml:space="preserve">1.81102728843689</t>
   </si>
   <si>
     <t xml:space="preserve">1.82694125175476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012402057648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444665908813</t>
+    <t xml:space="preserve">1.83012413978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444677829742</t>
   </si>
   <si>
     <t xml:space="preserve">1.88423204421997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8380811214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240399837494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92879164218903</t>
+    <t xml:space="preserve">1.83808100223541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240387916565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104927539825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92879152297974</t>
   </si>
   <si>
     <t xml:space="preserve">1.89537191390991</t>
@@ -3305,34 +3305,34 @@
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881374835968</t>
+    <t xml:space="preserve">1.99881386756897</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313638687134</t>
+    <t xml:space="preserve">2.01313662528992</t>
   </si>
   <si>
     <t xml:space="preserve">1.98289966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00358819961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9431140422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95107138156891</t>
+    <t xml:space="preserve">2.0035879611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94311439990997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197453022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9510715007782</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786650657654</t>
+    <t xml:space="preserve">1.87786626815796</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3341,34 +3341,34 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221125125885</t>
+    <t xml:space="preserve">1.96221137046814</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038332462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993151187897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90014612674713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91765189170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91924297809601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71235942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64233732223511</t>
+    <t xml:space="preserve">1.93038320541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993139266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90014636516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91765165328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9192430973053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285533428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71235954761505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6423374414444</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
@@ -3380,52 +3380,52 @@
     <t xml:space="preserve">1.65984284877777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69007980823517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711165428162</t>
+    <t xml:space="preserve">1.69007992744446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711153507233</t>
   </si>
   <si>
     <t xml:space="preserve">1.6168749332428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483179569244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65506863594055</t>
+    <t xml:space="preserve">1.62483191490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65506875514984</t>
   </si>
   <si>
     <t xml:space="preserve">1.70758521556854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6964453458786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68053138256073</t>
+    <t xml:space="preserve">1.69644546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68053126335144</t>
   </si>
   <si>
     <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68848824501038</t>
+    <t xml:space="preserve">1.68848836421967</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435811519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58345520496368</t>
+    <t xml:space="preserve">1.58345532417297</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57788527011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58504664897919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58743369579315</t>
+    <t xml:space="preserve">1.577885389328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5850465297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58743381500244</t>
   </si>
   <si>
     <t xml:space="preserve">1.54128277301788</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025032997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53383469581604</t>
+    <t xml:space="preserve">1.51025021076202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53383481502533</t>
   </si>
   <si>
     <t xml:space="preserve">1.54731154441833</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">1.50688099861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51698863506317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50856566429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5136194229126</t>
+    <t xml:space="preserve">1.51698851585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50856554508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51361954212189</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">1.54815399646759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48835027217865</t>
+    <t xml:space="preserve">1.48835039138794</t>
   </si>
   <si>
     <t xml:space="preserve">1.47487342357635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087715148926</t>
+    <t xml:space="preserve">1.49087727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
@@ -3482,28 +3482,28 @@
     <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47403120994568</t>
+    <t xml:space="preserve">1.47403109073639</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48498117923737</t>
+    <t xml:space="preserve">1.48498106002808</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171948432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46645045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4571852684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41591215133667</t>
+    <t xml:space="preserve">1.49171960353851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46645057201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45718502998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41591227054596</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201238155365</t>
@@ -3512,40 +3512,40 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3990660905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200475692749</t>
+    <t xml:space="preserve">1.39906620979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200487613678</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178960323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766669750214</t>
+    <t xml:space="preserve">1.34178948402405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
     <t xml:space="preserve">1.26177072525024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27777445316315</t>
+    <t xml:space="preserve">1.27777433395386</t>
   </si>
   <si>
     <t xml:space="preserve">1.22892081737518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20617866516113</t>
+    <t xml:space="preserve">1.20617878437042</t>
   </si>
   <si>
     <t xml:space="preserve">1.23229014873505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22976315021515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29209363460541</t>
+    <t xml:space="preserve">1.22976326942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2920937538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.31988966464996</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144769668579</t>
+    <t xml:space="preserve">1.23144781589508</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365166664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20533645153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.175013422966</t>
+    <t xml:space="preserve">1.20365178585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20533633232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17501330375671</t>
   </si>
   <si>
     <t xml:space="preserve">1.13289821147919</t>
@@ -3584,10 +3584,10 @@
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942148208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10594439506531</t>
+    <t xml:space="preserve">1.11942136287689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1059445142746</t>
   </si>
   <si>
     <t xml:space="preserve">1.14300584793091</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">1.21965551376343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16490566730499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13710963726044</t>
+    <t xml:space="preserve">1.16490578651428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">1.12700212001801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12279045581818</t>
+    <t xml:space="preserve">1.12279057502747</t>
   </si>
   <si>
     <t xml:space="preserve">1.08151769638062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10425996780396</t>
+    <t xml:space="preserve">1.10425984859467</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553284645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427872657776</t>
+    <t xml:space="preserve">1.14553272724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427884578705</t>
   </si>
   <si>
     <t xml:space="preserve">1.22470927238464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26008605957031</t>
+    <t xml:space="preserve">1.2600861787796</t>
   </si>
   <si>
     <t xml:space="preserve">1.29462051391602</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">1.28367066383362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26682448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26935148239136</t>
+    <t xml:space="preserve">1.26682436466217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26935136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.28030133247375</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829375743866</t>
+    <t xml:space="preserve">1.24829387664795</t>
   </si>
   <si>
     <t xml:space="preserve">1.24492466449738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25334775447845</t>
+    <t xml:space="preserve">1.25334763526917</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818624019623</t>
@@ -3674,28 +3674,28 @@
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31567811965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3165203332901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3299971818924</t>
+    <t xml:space="preserve">1.32325875759125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31567823886871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31652045249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32999730110168</t>
   </si>
   <si>
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915496826172</t>
+    <t xml:space="preserve">1.32915484905243</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021269321442</t>
+    <t xml:space="preserve">1.35021257400513</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">1.367058634758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32662808895111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33589327335358</t>
+    <t xml:space="preserve">1.32662796974182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33589339256287</t>
   </si>
   <si>
     <t xml:space="preserve">1.31062424182892</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">1.29546284675598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30135893821716</t>
+    <t xml:space="preserve">1.30135881900787</t>
   </si>
   <si>
     <t xml:space="preserve">1.25082075595856</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23734390735626</t>
+    <t xml:space="preserve">1.23734378814697</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">1.2895667552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842027187347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34263181686401</t>
+    <t xml:space="preserve">1.33842039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34263169765472</t>
   </si>
   <si>
     <t xml:space="preserve">1.37127017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36958563327789</t>
+    <t xml:space="preserve">1.3695855140686</t>
   </si>
   <si>
     <t xml:space="preserve">1.43865430355072</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">1.44539284706116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46560823917389</t>
+    <t xml:space="preserve">1.46139657497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4656081199646</t>
   </si>
   <si>
     <t xml:space="preserve">1.4041200876236</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43360066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44370818138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39653921127319</t>
+    <t xml:space="preserve">1.4336005449295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44370830059052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39653933048248</t>
   </si>
   <si>
     <t xml:space="preserve">1.42265069484711</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">1.39148533344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38474702835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38727390766144</t>
+    <t xml:space="preserve">1.38474690914154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38727378845215</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39317011833191</t>
+    <t xml:space="preserve">1.39316999912262</t>
   </si>
   <si>
     <t xml:space="preserve">1.37800860404968</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779321193695</t>
+    <t xml:space="preserve">1.35779333114624</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496218204498</t>
+    <t xml:space="preserve">1.40496230125427</t>
   </si>
   <si>
     <t xml:space="preserve">1.3881162405014</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34515881538391</t>
+    <t xml:space="preserve">1.34515869617462</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230878829956</t>
+    <t xml:space="preserve">1.31230890750885</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">1.45634281635284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42686212062836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4470773935318</t>
+    <t xml:space="preserve">1.42686223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44707751274109</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">1.48329651355743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47655808925629</t>
+    <t xml:space="preserve">1.476557970047</t>
   </si>
   <si>
     <t xml:space="preserve">1.53888845443726</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60711514949799</t>
+    <t xml:space="preserve">1.6071150302887</t>
   </si>
   <si>
     <t xml:space="preserve">1.61132657527924</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.57426536083221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5852153301239</t>
+    <t xml:space="preserve">1.58521521091461</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784972667694</t>
+    <t xml:space="preserve">1.59784984588623</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62396109104156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59953439235687</t>
+    <t xml:space="preserve">1.62396121025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59953451156616</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">1.64249193668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66186487674713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62227654457092</t>
+    <t xml:space="preserve">1.66186499595642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62227666378021</t>
   </si>
   <si>
     <t xml:space="preserve">1.58774209022522</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">1.62480342388153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61385345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795736312866</t>
+    <t xml:space="preserve">1.61385357379913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795748233795</t>
   </si>
   <si>
     <t xml:space="preserve">1.58100366592407</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5776344537735</t>
+    <t xml:space="preserve">1.57763457298279</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">1.57089602947235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57594990730286</t>
+    <t xml:space="preserve">1.57595002651215</t>
   </si>
   <si>
     <t xml:space="preserve">1.58437299728394</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">1.58184599876404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57173836231232</t>
+    <t xml:space="preserve">1.57173848152161</t>
   </si>
   <si>
     <t xml:space="preserve">1.59026908874512</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53087472915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5210268497467</t>
+    <t xml:space="preserve">1.5308746099472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52102696895599</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357881069183</t>
+    <t xml:space="preserve">1.47357869148254</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4950647354126</t>
+    <t xml:space="preserve">1.49506461620331</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4088,52 +4088,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192223072052</t>
+    <t xml:space="preserve">1.52192211151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070395469666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308514118195</t>
+    <t xml:space="preserve">1.61144697666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070407390594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308526039124</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786604881287</t>
+    <t xml:space="preserve">1.60786592960358</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039935588837</t>
+    <t xml:space="preserve">1.62039947509766</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801816940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773210525513</t>
+    <t xml:space="preserve">1.59801828861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773198604584</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937038898468</t>
+    <t xml:space="preserve">1.56937026977539</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502802371979</t>
+    <t xml:space="preserve">1.6150279045105</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.582799077034</t>
+    <t xml:space="preserve">1.58279895782471</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769527435303</t>
+    <t xml:space="preserve">1.67769539356232</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575251102448</t>
+    <t xml:space="preserve">1.68575263023376</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66426658630371</t>
+    <t xml:space="preserve">1.664266705513</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977210044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887671947479</t>
+    <t xml:space="preserve">1.71977198123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843829631805</t>
+    <t xml:space="preserve">1.68843841552734</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159933567047</t>
+    <t xml:space="preserve">1.60159921646118</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340803623199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399869918823</t>
+    <t xml:space="preserve">1.54340815544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234223842621</t>
+    <t xml:space="preserve">1.61234211921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112408161163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350526809692</t>
+    <t xml:space="preserve">1.63024723529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112420082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350538730621</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74573421478271</t>
+    <t xml:space="preserve">1.745734333992</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201934337616</t>
+    <t xml:space="preserve">1.69201922416687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691565990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7940776348114</t>
+    <t xml:space="preserve">1.78691577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79407751560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525907993317</t>
+    <t xml:space="preserve">1.83525896072388</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272553443909</t>
+    <t xml:space="preserve">1.82272565364838</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558197498322</t>
+    <t xml:space="preserve">1.75558185577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76453447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857235908508</t>
+    <t xml:space="preserve">1.7645343542099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857223987579</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4409,16 +4409,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723843574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859065532684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874277591705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009499549866</t>
+    <t xml:space="preserve">1.70723855495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859053611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874289512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009487628937</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740921020508</t>
+    <t xml:space="preserve">1.63740909099579</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6409900188446</t>
+    <t xml:space="preserve">1.63919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64099013805389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693395614624</t>
+    <t xml:space="preserve">1.72693407535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041789054871</t>
+    <t xml:space="preserve">1.56041777133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458948135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609382152557</t>
+    <t xml:space="preserve">1.58458960056305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609394073486</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205617427826</t>
+    <t xml:space="preserve">1.57205605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278078079224</t>
+    <t xml:space="preserve">1.64278066158295</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754315376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129473686218</t>
+    <t xml:space="preserve">1.68754303455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129461765289</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708631515503</t>
+    <t xml:space="preserve">1.71708619594574</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274383068085</t>
+    <t xml:space="preserve">1.76274394989014</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602051734924</t>
+    <t xml:space="preserve">1.78602039813995</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -5310,6 +5310,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.73000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72399997711182</t>
   </si>
 </sst>
 </file>
@@ -22514,7 +22517,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G649" t="s">
-        <v>356</v>
+        <v>482</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22540,7 +22543,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G650" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22566,7 +22569,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G651" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22592,7 +22595,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22618,7 +22621,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G653" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22644,7 +22647,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G654" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22670,7 +22673,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G655" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22696,7 +22699,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G656" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22722,7 +22725,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G657" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22748,7 +22751,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G658" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22774,7 +22777,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G659" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22800,7 +22803,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G660" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22826,7 +22829,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G661" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22852,7 +22855,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G662" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22878,7 +22881,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G663" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22904,7 +22907,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22930,7 +22933,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G665" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22956,7 +22959,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G666" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22982,7 +22985,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G667" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23008,7 +23011,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G668" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23034,7 +23037,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23060,7 +23063,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G670" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23086,7 +23089,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G671" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23112,7 +23115,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G672" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23138,7 +23141,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G673" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23190,7 +23193,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G675" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23216,7 +23219,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G676" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23268,7 +23271,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G678" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23294,7 +23297,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G679" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23320,7 +23323,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G680" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23346,7 +23349,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23372,7 +23375,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G682" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23398,7 +23401,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G683" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23424,7 +23427,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G684" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23450,7 +23453,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G685" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23476,7 +23479,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G686" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23502,7 +23505,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G687" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23554,7 +23557,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23606,7 +23609,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G691" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23710,7 +23713,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G695" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23736,7 +23739,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23762,7 +23765,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G697" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23788,7 +23791,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G698" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23814,7 +23817,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23840,7 +23843,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G700" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23866,7 +23869,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G701" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23892,7 +23895,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G702" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23918,7 +23921,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G703" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23944,7 +23947,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23970,7 +23973,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23996,7 +23999,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G706" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -24022,7 +24025,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G707" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24048,7 +24051,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G708" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -24074,7 +24077,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G709" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -24100,7 +24103,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G710" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24126,7 +24129,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G711" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24152,7 +24155,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G712" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24178,7 +24181,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G713" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24204,7 +24207,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G714" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24230,7 +24233,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G715" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24256,7 +24259,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G716" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24282,7 +24285,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G717" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24308,7 +24311,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G718" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24334,7 +24337,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G719" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24360,7 +24363,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G720" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24386,7 +24389,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G721" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24412,7 +24415,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G722" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24438,7 +24441,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G723" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24464,7 +24467,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G724" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24490,7 +24493,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G725" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24516,7 +24519,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G726" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24542,7 +24545,7 @@
         <v>1.97300004959106</v>
       </c>
       <c r="G727" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24568,7 +24571,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G728" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24594,7 +24597,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G729" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24620,7 +24623,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G730" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24646,7 +24649,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24672,7 +24675,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G732" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24698,7 +24701,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G733" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24724,7 +24727,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24750,7 +24753,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G735" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24776,7 +24779,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G736" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24802,7 +24805,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G737" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24828,7 +24831,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G738" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24854,7 +24857,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G739" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24880,7 +24883,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G740" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24906,7 +24909,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G741" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24932,7 +24935,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G742" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24958,7 +24961,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24984,7 +24987,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G744" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -25010,7 +25013,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -25036,7 +25039,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G746" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -25062,7 +25065,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G747" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -25088,7 +25091,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -25114,7 +25117,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G749" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -25140,7 +25143,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -25166,7 +25169,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G751" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25192,7 +25195,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G752" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25218,7 +25221,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G753" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25244,7 +25247,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G754" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25270,7 +25273,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25296,7 +25299,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G756" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25322,7 +25325,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G757" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25348,7 +25351,7 @@
         <v>2</v>
       </c>
       <c r="G758" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25374,7 +25377,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G759" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25400,7 +25403,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G760" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25426,7 +25429,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25452,7 +25455,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G762" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25478,7 +25481,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G763" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25504,7 +25507,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G764" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25556,7 +25559,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G766" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25582,7 +25585,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G767" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25608,7 +25611,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>571</v>
+        <v>322</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25660,7 +25663,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G770" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25738,7 +25741,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>571</v>
+        <v>322</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25894,7 +25897,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26076,7 +26079,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G786" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -26102,7 +26105,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G787" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26180,7 +26183,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G790" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26310,7 +26313,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26388,7 +26391,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G798" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26492,7 +26495,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G802" t="s">
-        <v>571</v>
+        <v>322</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26544,7 +26547,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G804" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26570,7 +26573,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G805" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26596,7 +26599,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26622,7 +26625,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G807" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26648,7 +26651,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G808" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26726,7 +26729,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G811" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26778,7 +26781,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G813" t="s">
-        <v>356</v>
+        <v>482</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26804,7 +26807,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26908,7 +26911,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G818" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26960,7 +26963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G820" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27038,7 +27041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -27168,7 +27171,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27272,7 +27275,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27532,7 +27535,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G842" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27558,7 +27561,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G843" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27584,7 +27587,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G844" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27610,7 +27613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27662,7 +27665,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G847" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27818,7 +27821,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G853" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27948,7 +27951,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G858" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28026,7 +28029,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G861" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28078,7 +28081,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G863" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28156,7 +28159,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G866" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28260,7 +28263,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G870" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28312,7 +28315,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28364,7 +28367,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G874" t="s">
-        <v>356</v>
+        <v>482</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28390,7 +28393,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G875" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28468,7 +28471,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G878" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28494,7 +28497,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G879" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28598,7 +28601,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G883" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -70544,7 +70547,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6493634259</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>833882</v>
@@ -70565,6 +70568,32 @@
         <v>1765</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912384259</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>524771</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>2.74200010299683</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>2.74200010299683</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>2.72399997711182</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1766</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806250095367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92702728509903</t>
+    <t xml:space="preserve">0.923806130886078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927027225494385</t>
   </si>
   <si>
     <t xml:space="preserve">0.921873509883881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901902616024017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898037374019623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652415275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835415840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643486976624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863894045352936</t>
+    <t xml:space="preserve">0.901902675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898037672042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652355670929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835535049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643665790558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893985748291</t>
   </si>
   <si>
     <t xml:space="preserve">0.841346442699432</t>
@@ -77,55 +77,55 @@
     <t xml:space="preserve">0.851653873920441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818154811859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192607879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163382530212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869692087173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441588401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489830970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344805240631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374090194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279182910919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798959255219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481200695038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825241029262543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432719707489</t>
+    <t xml:space="preserve">0.818154633045197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192786693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163322925568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691908359528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441648006439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374149799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84327906370163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798840045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481141090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432898521423</t>
   </si>
   <si>
     <t xml:space="preserve">0.869047701358795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876778244972229</t>
+    <t xml:space="preserve">0.876778364181519</t>
   </si>
   <si>
     <t xml:space="preserve">0.894172191619873</t>
@@ -134,46 +134,46 @@
     <t xml:space="preserve">0.923161864280701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927671432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914143025875092</t>
+    <t xml:space="preserve">0.927671492099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142847061157</t>
   </si>
   <si>
     <t xml:space="preserve">0.945709466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919296681880951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075587272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941200017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947642147541046</t>
+    <t xml:space="preserve">0.91929680109024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199719905853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642087936401</t>
   </si>
   <si>
     <t xml:space="preserve">0.930892407894135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934113442897797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918008267879486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954084396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391648769379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179482460022</t>
+    <t xml:space="preserve">0.934113562107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412303447723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918007910251617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954084098339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391767978668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179363250732</t>
   </si>
   <si>
     <t xml:space="preserve">1.01270794868469</t>
@@ -182,40 +182,40 @@
     <t xml:space="preserve">1.02881324291229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01657330989838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365958690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00819849967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175607204437</t>
+    <t xml:space="preserve">1.01657319068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00819873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175619125366</t>
   </si>
   <si>
     <t xml:space="preserve">1.00497734546661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00755429267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02172696590424</t>
+    <t xml:space="preserve">1.00755417346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02172708511353</t>
   </si>
   <si>
     <t xml:space="preserve">1.01464068889618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02237129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999823570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01141965389252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206374168396</t>
+    <t xml:space="preserve">1.02237117290497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999823689460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01141953468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206362247467</t>
   </si>
   <si>
     <t xml:space="preserve">1.01786172389984</t>
@@ -227,88 +227,88 @@
     <t xml:space="preserve">1.01850581169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02688074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203439712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02494812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01721739768982</t>
+    <t xml:space="preserve">1.0268806219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203451633453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0249480009079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01721751689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.00562143325806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988871872425079</t>
+    <t xml:space="preserve">0.988871932029724</t>
   </si>
   <si>
     <t xml:space="preserve">1.00368881225586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03525567054749</t>
+    <t xml:space="preserve">1.0352555513382</t>
   </si>
   <si>
     <t xml:space="preserve">1.02816927433014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04040932655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03396713733673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02945756912231</t>
+    <t xml:space="preserve">1.04040920734406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03396725654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02945744991302</t>
   </si>
   <si>
     <t xml:space="preserve">1.03010177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01592922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992093026638031</t>
+    <t xml:space="preserve">1.01592898368835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992093145847321</t>
   </si>
   <si>
     <t xml:space="preserve">1.03332281112671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00948679447174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958268642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314240455627</t>
+    <t xml:space="preserve">1.00948691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958387851715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995314002037048</t>
   </si>
   <si>
     <t xml:space="preserve">1.02108287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0494282245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519698143005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295669078827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05715894699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07326412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06231272220612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0474956035614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.063600897789</t>
+    <t xml:space="preserve">1.04942834377289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519710063934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05715882778168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07326436042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06231260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04749572277069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06360113620758</t>
   </si>
   <si>
     <t xml:space="preserve">1.0616682767868</t>
@@ -320,31 +320,31 @@
     <t xml:space="preserve">1.04620718955994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977276027202606</t>
+    <t xml:space="preserve">0.977276086807251</t>
   </si>
   <si>
     <t xml:space="preserve">0.968257009983063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965035855770111</t>
+    <t xml:space="preserve">0.965035915374756</t>
   </si>
   <si>
     <t xml:space="preserve">0.978564560413361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962522327899933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517048835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90771210193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87696498632431</t>
+    <t xml:space="preserve">0.962522566318512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232847690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517227649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90771222114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876964867115021</t>
   </si>
   <si>
     <t xml:space="preserve">0.903701663017273</t>
@@ -353,70 +353,70 @@
     <t xml:space="preserve">0.895680546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929101526737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117363929749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127743244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048914909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033196926117</t>
+    <t xml:space="preserve">0.929101586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127683639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048974514008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033316135406</t>
   </si>
   <si>
     <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925090968608856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775271892548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925759315490723</t>
+    <t xml:space="preserve">0.925091028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775331497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925759434700012</t>
   </si>
   <si>
     <t xml:space="preserve">0.912391066551208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921080529689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92709618806839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143640041351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955838203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95316469669342</t>
+    <t xml:space="preserve">0.921080350875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927096366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143699645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122464179993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838322639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164577484131</t>
   </si>
   <si>
     <t xml:space="preserve">0.964527785778046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965196013450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982574939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97254866361618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217129707336</t>
+    <t xml:space="preserve">0.965196192264557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982575237751007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98391181230545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972548723220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217248916626</t>
   </si>
   <si>
     <t xml:space="preserve">0.984580218791962</t>
@@ -425,40 +425,40 @@
     <t xml:space="preserve">0.987253904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995275020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98925918340683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601215839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827764511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950491011142731</t>
+    <t xml:space="preserve">0.995274841785431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989259243011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827883720398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950490891933441</t>
   </si>
   <si>
     <t xml:space="preserve">0.948485672473907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94113302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501330852509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864598751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917210578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927589893341</t>
+    <t xml:space="preserve">0.94113290309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501450061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864479541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927530288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.01265382766724</t>
@@ -467,49 +467,49 @@
     <t xml:space="preserve">1.02000653743744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99193274974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988590717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996611833572388</t>
+    <t xml:space="preserve">0.991932988166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988590598106384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996611893177032</t>
   </si>
   <si>
     <t xml:space="preserve">0.979901373386383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967201411724091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986585438251495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977896094322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885595798492</t>
+    <t xml:space="preserve">0.967201292514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98658549785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977896153926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885536193848</t>
   </si>
   <si>
     <t xml:space="preserve">0.995943367481232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02401673793793</t>
+    <t xml:space="preserve">1.02401697635651</t>
   </si>
   <si>
     <t xml:space="preserve">1.00864326953888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0026273727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969206631183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975222408771515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248804092407</t>
+    <t xml:space="preserve">1.00262749195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969206690788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975222229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248744487762</t>
   </si>
   <si>
     <t xml:space="preserve">1.02936434745789</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">1.05342733860016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05543279647827</t>
+    <t xml:space="preserve">1.05543267726898</t>
   </si>
   <si>
     <t xml:space="preserve">1.0761536359787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0895220041275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420084953308</t>
+    <t xml:space="preserve">1.08952212333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420096874237</t>
   </si>
   <si>
     <t xml:space="preserve">1.09687447547913</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">1.07013773918152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08751666545868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09353244304657</t>
+    <t xml:space="preserve">1.08751678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749032974243</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">1.06479060649872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06278538703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04741168022156</t>
+    <t xml:space="preserve">1.06278514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04741156101227</t>
   </si>
   <si>
     <t xml:space="preserve">1.06077992916107</t>
@@ -560,55 +560,55 @@
     <t xml:space="preserve">1.06813251972198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05209040641785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957843482494354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953832983970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480393409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935785591602325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780372142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727760314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738318443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941801488399506</t>
+    <t xml:space="preserve">1.05209064483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957843542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953833222389221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480333805084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935785710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469954490662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727939128876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738437652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941801428794861</t>
   </si>
   <si>
     <t xml:space="preserve">0.918406844139099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968538165092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869818210602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98056972026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948527336121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332235336304</t>
+    <t xml:space="preserve">0.968538284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869639396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569779872894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606673717499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948586940765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332223415375</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532757282257</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">1.01599597930908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02869606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203797340393</t>
+    <t xml:space="preserve">1.02869582176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203809261322</t>
   </si>
   <si>
     <t xml:space="preserve">1.04005885124207</t>
@@ -629,46 +629,46 @@
     <t xml:space="preserve">1.04473781585693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03070116043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0173327922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03604853153229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874861240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04941689968109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275893211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05008518695831</t>
+    <t xml:space="preserve">1.03070104122162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01733291149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03604865074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494167804718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275905132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0500853061676</t>
   </si>
   <si>
     <t xml:space="preserve">1.04072749614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04607474803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01064836978912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530111789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03003263473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04273271560669</t>
+    <t xml:space="preserve">1.04607486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02468550205231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0106486082077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530123710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03003251552582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0427325963974</t>
   </si>
   <si>
     <t xml:space="preserve">1.02334845066071</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412196159363</t>
+    <t xml:space="preserve">1.06412220001221</t>
   </si>
   <si>
     <t xml:space="preserve">1.0561009645462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810630321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484303951263</t>
+    <t xml:space="preserve">1.05810618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484315872192</t>
   </si>
   <si>
     <t xml:space="preserve">1.07080626487732</t>
@@ -695,43 +695,43 @@
     <t xml:space="preserve">1.08216941356659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06880104541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07815885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0828378200531</t>
+    <t xml:space="preserve">1.0688009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07815897464752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08283793926239</t>
   </si>
   <si>
     <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0962061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09954822063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754300117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628495693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978464603424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120046615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988986968994</t>
+    <t xml:space="preserve">1.09620606899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754288196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628483772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22120034694672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988963127136</t>
   </si>
   <si>
     <t xml:space="preserve">1.24058449268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26665270328522</t>
+    <t xml:space="preserve">1.26665282249451</t>
   </si>
   <si>
     <t xml:space="preserve">1.28002119064331</t>
@@ -740,136 +740,136 @@
     <t xml:space="preserve">1.28336322307587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29405796527863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133166790009</t>
+    <t xml:space="preserve">1.29405808448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133178710938</t>
   </si>
   <si>
     <t xml:space="preserve">1.26932656764984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30074226856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31010007858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475258827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007374286652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31143689155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29004752635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28871047496796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29740011692047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28937900066376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27200019359589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25930023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29673171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806840419769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31076848506927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29338932037354</t>
+    <t xml:space="preserve">1.30074238777161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009995937347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475270748138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007386207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3114367723465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29004740715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28871071338654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29739999771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28937911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2720000743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2593001127243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29673159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31076812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29338943958282</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814729213715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30341601371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683669567108</t>
+    <t xml:space="preserve">1.30341589450836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683657646179</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349478244781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35421574115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3702574968338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426817417145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.364910364151</t>
+    <t xml:space="preserve">1.35421562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37025773525238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426805496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36491012573242</t>
   </si>
   <si>
     <t xml:space="preserve">1.37961542606354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33616816997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34886813163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3903101682663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4103627204895</t>
+    <t xml:space="preserve">1.33616840839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34886825084686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39031004905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036260128021</t>
   </si>
   <si>
     <t xml:space="preserve">1.42105734348297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45046806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39966821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303646564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442583084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704678535461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42239439487457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40902602672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43977320194244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44779396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4705206155777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46784663200378</t>
+    <t xml:space="preserve">1.43175196647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4504679441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39966809749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303658485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442559242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4170469045639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42239427566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40902590751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43977344036102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44779407978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052049636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46784687042236</t>
   </si>
   <si>
     <t xml:space="preserve">1.46116268634796</t>
@@ -887,19 +887,19 @@
     <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4833664894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49024629592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47235822677612</t>
+    <t xml:space="preserve">1.48336613178253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49024653434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47235810756683</t>
   </si>
   <si>
     <t xml:space="preserve">1.4228208065033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44208526611328</t>
+    <t xml:space="preserve">1.44208538532257</t>
   </si>
   <si>
     <t xml:space="preserve">1.40630829334259</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">1.3953001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39942800998688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40080428123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40218031406403</t>
+    <t xml:space="preserve">1.39942824840546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40080416202545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40218043327332</t>
   </si>
   <si>
     <t xml:space="preserve">1.38429176807404</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">1.4145644903183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42144465446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43658125400543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43245303630829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.424196600914</t>
+    <t xml:space="preserve">1.42144477367401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43658113479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43245315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42419672012329</t>
   </si>
   <si>
     <t xml:space="preserve">1.431077003479</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45997357368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44621348381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46685385704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48199021816254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46960604190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923839092255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400710105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125467777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987888336182</t>
+    <t xml:space="preserve">1.45997369289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44621336460114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46685397624969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48199033737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46960580348969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758951663971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400698184967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125479698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987876415253</t>
   </si>
   <si>
     <t xml:space="preserve">1.50675892829895</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">1.52602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54803991317749</t>
+    <t xml:space="preserve">1.54804003238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52327144145966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189528942108</t>
+    <t xml:space="preserve">1.52327120304108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189517021179</t>
   </si>
   <si>
     <t xml:space="preserve">1.54528796672821</t>
@@ -995,34 +995,34 @@
     <t xml:space="preserve">1.57968890666962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57831275463104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556068897247</t>
+    <t xml:space="preserve">1.57831263542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556080818176</t>
   </si>
   <si>
     <t xml:space="preserve">1.57693684101105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56317627429962</t>
+    <t xml:space="preserve">1.5631765127182</t>
   </si>
   <si>
     <t xml:space="preserve">1.54666376113892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55354404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592869758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381688594818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069716930389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656895160675</t>
+    <t xml:space="preserve">1.55354416370392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592857837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381700515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5906970500946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656907081604</t>
   </si>
   <si>
     <t xml:space="preserve">1.58244073390961</t>
@@ -1031,97 +1031,97 @@
     <t xml:space="preserve">1.60996162891388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63197839260101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408984661102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6058337688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6003292798996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5645524263382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978371620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565561771393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180047988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941642284393</t>
+    <t xml:space="preserve">1.63197815418243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711463451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408972740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583341121674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455218791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978359699249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53565573692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180059909821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941618442535</t>
   </si>
   <si>
     <t xml:space="preserve">1.53427958488464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57005655765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868052482605</t>
+    <t xml:space="preserve">1.57005667686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868028640747</t>
   </si>
   <si>
     <t xml:space="preserve">1.62234592437744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6168417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509787082672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66087472438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940376281738</t>
+    <t xml:space="preserve">1.61684167385101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133778095245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482514858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5728086233139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6182177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6250981092453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6608749628067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637885570526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940400123596</t>
   </si>
   <si>
     <t xml:space="preserve">1.70353221893311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6980277299881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949857234955</t>
+    <t xml:space="preserve">1.69802784919739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252383708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023435115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949881076813</t>
   </si>
   <si>
     <t xml:space="preserve">1.64986670017242</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">1.62785005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66225099563599</t>
+    <t xml:space="preserve">1.6622508764267</t>
   </si>
   <si>
     <t xml:space="preserve">1.67601144313812</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">1.74894118309021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73105251789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004461288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518073558807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830080986023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618923664093</t>
+    <t xml:space="preserve">1.73105299472809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004437446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518097400665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618911743164</t>
   </si>
   <si>
     <t xml:space="preserve">1.7668297290802</t>
@@ -1163,43 +1163,43 @@
     <t xml:space="preserve">1.77233409881592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76545357704163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370953559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74068510532379</t>
+    <t xml:space="preserve">1.76545381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77371001243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7406849861145</t>
   </si>
   <si>
     <t xml:space="preserve">1.8204950094223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79022228717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747010231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444519519806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159820079803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7929744720459</t>
+    <t xml:space="preserve">1.79022240638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747045993805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444531440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297423362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.7682056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75857329368591</t>
+    <t xml:space="preserve">1.75857353210449</t>
   </si>
   <si>
     <t xml:space="preserve">1.72554838657379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72967660427094</t>
+    <t xml:space="preserve">1.72967648506165</t>
   </si>
   <si>
     <t xml:space="preserve">1.72142040729523</t>
@@ -1211,91 +1211,91 @@
     <t xml:space="preserve">1.81499099731445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80535876750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031721591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481320381165</t>
+    <t xml:space="preserve">1.80535864830017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031733512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481308460236</t>
   </si>
   <si>
     <t xml:space="preserve">1.77921390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84113585948944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700776100159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85351991653442</t>
+    <t xml:space="preserve">1.84113562107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700740337372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85352003574371</t>
   </si>
   <si>
     <t xml:space="preserve">1.86039996147156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88516867160797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076797008514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361472606659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123066902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957261800766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737517356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738711833954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66913104057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68013942241669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298641681671</t>
+    <t xml:space="preserve">1.88516879081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076785087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123054981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710257053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82737505435944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564355373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573848247528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63473033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151557445526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801393032074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64298665523529</t>
   </si>
   <si>
     <t xml:space="preserve">1.66500306129456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68701958656311</t>
+    <t xml:space="preserve">1.68701934814453</t>
   </si>
   <si>
     <t xml:space="preserve">1.69114768505096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63335418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463529109955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7145402431488</t>
+    <t xml:space="preserve">1.63335454463959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463552951813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454036235809</t>
   </si>
   <si>
     <t xml:space="preserve">1.70215582847595</t>
@@ -1304,67 +1304,67 @@
     <t xml:space="preserve">1.69527590274811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68426740169525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6787633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6526186466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306951999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930895328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417271137238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692465782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362726688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289160728455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343705177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380482196808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206101894379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839573860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65399491786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849066734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5975775718689</t>
+    <t xml:space="preserve">1.68426764011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876350879669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65261876583099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306928157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7241724729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692477703094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362690925598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289172649384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316421031952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343693256378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380470275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74206113815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994944572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178805828094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399467945099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849054813385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720944404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757721424103</t>
   </si>
   <si>
     <t xml:space="preserve">1.59620118141174</t>
@@ -1373,184 +1373,181 @@
     <t xml:space="preserve">1.53290355205536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49299871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47648620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47511041164398</t>
+    <t xml:space="preserve">1.4929986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4503413438797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134972572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4764860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611855506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511005401611</t>
   </si>
   <si>
     <t xml:space="preserve">1.45722186565399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42832505702972</t>
+    <t xml:space="preserve">1.42832493782043</t>
   </si>
   <si>
     <t xml:space="preserve">1.51776742935181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55079209804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542112350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530690193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5482622385025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52411472797394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5312168598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127385139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837610244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672751903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246626377106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513580799103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507881641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934019088745</t>
+    <t xml:space="preserve">1.55079197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542124271393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530702114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54826188087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52411460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121662139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127373218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837598323822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55536425113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513604640961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507893562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934031009674</t>
   </si>
   <si>
     <t xml:space="preserve">1.62212383747101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58945417404175</t>
+    <t xml:space="preserve">1.58945429325104</t>
   </si>
   <si>
     <t xml:space="preserve">1.57951128482819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60223805904388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6036581993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5937157869339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922608852386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63632822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348746299744</t>
+    <t xml:space="preserve">1.60223817825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60365855693817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371554851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63632833957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348722457886</t>
   </si>
   <si>
     <t xml:space="preserve">1.62638533115387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61076045036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58803379535675</t>
+    <t xml:space="preserve">1.61076056957245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58803391456604</t>
   </si>
   <si>
     <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68888378143311</t>
+    <t xml:space="preserve">1.6888839006424</t>
   </si>
   <si>
     <t xml:space="preserve">1.68178176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882667064667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013318538666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729242801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911210536957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894124984741</t>
+    <t xml:space="preserve">1.69882690906525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013306617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729230880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757750511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894101142883</t>
   </si>
   <si>
     <t xml:space="preserve">1.67752063274384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67183887958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.643430352211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928331851959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61786270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57667052745819</t>
+    <t xml:space="preserve">1.67183899879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343023300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61928296089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61786282062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667064666748</t>
   </si>
   <si>
     <t xml:space="preserve">1.56388664245605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962550640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55394351482391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55252325534821</t>
+    <t xml:space="preserve">1.55962538719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5539436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5525233745575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55110287666321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51701247692108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559221744537</t>
+    <t xml:space="preserve">1.51701259613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559245586395</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871829032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43462812900543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44741201400757</t>
+    <t xml:space="preserve">1.43462789058685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44741189479828</t>
   </si>
   <si>
     <t xml:space="preserve">1.45735490322113</t>
@@ -1559,61 +1556,61 @@
     <t xml:space="preserve">1.47155904769897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4701384305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47297942638397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53263735771179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58377254009247</t>
+    <t xml:space="preserve">1.47013866901398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47297954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5326372385025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58377242088318</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973925113678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51275146007538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48718369007111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47724068164825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144506454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138795375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49996745586395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49570620059967</t>
+    <t xml:space="preserve">1.51275157928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4871838092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138807296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49996757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49570631980896</t>
   </si>
   <si>
     <t xml:space="preserve">1.41687273979187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42184436321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911735057831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065183162689</t>
+    <t xml:space="preserve">1.4218442440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065195083618</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426006793976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3522435426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994182109833</t>
+    <t xml:space="preserve">1.35224342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994158267975</t>
   </si>
   <si>
     <t xml:space="preserve">1.37070894241333</t>
@@ -1622,37 +1619,37 @@
     <t xml:space="preserve">1.3657374382019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37923157215118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37212932109833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35579454898834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38633370399475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36431705951691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39343571662903</t>
+    <t xml:space="preserve">1.37923145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37212955951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35579442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38633346557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3643171787262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130508899689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35863542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40906059741974</t>
+    <t xml:space="preserve">1.35863530635834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40906035900116</t>
   </si>
   <si>
     <t xml:space="preserve">1.40124809741974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46019577980042</t>
+    <t xml:space="preserve">1.46019554138184</t>
   </si>
   <si>
     <t xml:space="preserve">1.45309364795685</t>
@@ -1661,7 +1658,7 @@
     <t xml:space="preserve">1.47439992427826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47866129875183</t>
+    <t xml:space="preserve">1.47866117954254</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593428611755</t>
@@ -1676,19 +1673,19 @@
     <t xml:space="preserve">1.39556646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37568056583405</t>
+    <t xml:space="preserve">1.37568044662476</t>
   </si>
   <si>
     <t xml:space="preserve">1.3870438337326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39201545715332</t>
+    <t xml:space="preserve">1.39201533794403</t>
   </si>
   <si>
     <t xml:space="preserve">1.37781119346619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40266847610474</t>
+    <t xml:space="preserve">1.40266859531403</t>
   </si>
   <si>
     <t xml:space="preserve">1.38136219978333</t>
@@ -1697,16 +1694,16 @@
     <t xml:space="preserve">1.33519840240479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36076605319977</t>
+    <t xml:space="preserve">1.36076593399048</t>
   </si>
   <si>
     <t xml:space="preserve">1.34940254688263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43178725242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320751190186</t>
+    <t xml:space="preserve">1.43178713321686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320739269257</t>
   </si>
   <si>
     <t xml:space="preserve">1.42468512058258</t>
@@ -1715,28 +1712,31 @@
     <t xml:space="preserve">1.4204238653183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48150193691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985347270966</t>
+    <t xml:space="preserve">1.48150205612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985359191895</t>
   </si>
   <si>
     <t xml:space="preserve">1.48860418796539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49428582191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258036613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52553534507751</t>
+    <t xml:space="preserve">1.49428594112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258024692535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115998744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.5297966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52695572376251</t>
+    <t xml:space="preserve">1.52695560455322</t>
   </si>
   <si>
     <t xml:space="preserve">1.53405785560608</t>
@@ -1748,43 +1748,43 @@
     <t xml:space="preserve">1.50991034507751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48008167743683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49854707717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4829226732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48434257507324</t>
+    <t xml:space="preserve">1.48008155822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49854695796967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50706970691681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48292243480682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48434269428253</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689861297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61644220352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780582904816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206696510315</t>
+    <t xml:space="preserve">1.53689873218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61644232273102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206708431244</t>
   </si>
   <si>
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496483325958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939730167389</t>
+    <t xml:space="preserve">1.62496495246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939742088318</t>
   </si>
   <si>
     <t xml:space="preserve">1.62070345878601</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.61502182483673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64627122879028</t>
+    <t xml:space="preserve">1.64627110958099</t>
   </si>
   <si>
     <t xml:space="preserve">1.61218106746674</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">1.51417171955109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50422871112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576319217682</t>
+    <t xml:space="preserve">1.50422894954681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576331138611</t>
   </si>
   <si>
     <t xml:space="preserve">1.46303653717041</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">1.58661341667175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5738297700882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916909694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7045089006424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166754722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69061756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69356322288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69798099994659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294585704803</t>
+    <t xml:space="preserve">1.57382953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916921615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450854301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166766643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69061779975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69356298446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69798123836517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294609546661</t>
   </si>
   <si>
     <t xml:space="preserve">1.68325448036194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68619978427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72890722751617</t>
+    <t xml:space="preserve">1.68619990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72890710830688</t>
   </si>
   <si>
     <t xml:space="preserve">1.75099694728851</t>
@@ -1868,76 +1868,76 @@
     <t xml:space="preserve">1.76277840137482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74510622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73332500457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812216758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8010675907135</t>
+    <t xml:space="preserve">1.74510610103607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73332536220551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161431312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750504016876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812204837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80106782913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.80548548698425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80401277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137633323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455997467041</t>
+    <t xml:space="preserve">1.80401289463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8113762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455973625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603232860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76719641685486</t>
+    <t xml:space="preserve">1.76719653606415</t>
   </si>
   <si>
     <t xml:space="preserve">1.74216091632843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70239913463593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73921597003937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77014172077179</t>
+    <t xml:space="preserve">1.70239901542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7701416015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78486835956573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78928637504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664957523346</t>
+    <t xml:space="preserve">1.78928625583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664981365204</t>
   </si>
   <si>
     <t xml:space="preserve">1.79517686367035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79370439052582</t>
+    <t xml:space="preserve">1.79370427131653</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79959511756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254030227661</t>
+    <t xml:space="preserve">1.79959499835968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254018306732</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308690547943</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">1.78192293643951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83493912220001</t>
+    <t xml:space="preserve">1.83493900299072</t>
   </si>
   <si>
     <t xml:space="preserve">1.8202121257782</t>
@@ -1955,46 +1955,46 @@
     <t xml:space="preserve">1.81873965263367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82168471813202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84819269180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82904827594757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425099372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81432163715363</t>
+    <t xml:space="preserve">1.82168459892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966540336609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84819293022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82904815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425087451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81432151794434</t>
   </si>
   <si>
     <t xml:space="preserve">1.80990374088287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83199322223663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144685745239</t>
+    <t xml:space="preserve">1.83199334144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144709587097</t>
   </si>
   <si>
     <t xml:space="preserve">1.91593539714813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655276298523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127928256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042417526245</t>
+    <t xml:space="preserve">1.93655264377594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213474750519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127952098846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042381763458</t>
   </si>
   <si>
     <t xml:space="preserve">1.95569717884064</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">1.94244337081909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94980657100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96158802509308</t>
+    <t xml:space="preserve">1.94980669021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9615877866745</t>
   </si>
   <si>
     <t xml:space="preserve">1.98809587955475</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">2.00724053382874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98367774486542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987721443176</t>
+    <t xml:space="preserve">1.98367786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987733364105</t>
   </si>
   <si>
     <t xml:space="preserve">2.0057680606842</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">1.96895122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96600604057312</t>
+    <t xml:space="preserve">1.96600592136383</t>
   </si>
   <si>
     <t xml:space="preserve">1.97484183311462</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">2.01754927635193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04847526550293</t>
+    <t xml:space="preserve">2.04847502708435</t>
   </si>
   <si>
     <t xml:space="preserve">2.02049446105957</t>
@@ -2063,34 +2063,34 @@
     <t xml:space="preserve">2.03374814987183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05436563491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02785778045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227591514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03816652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01018571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00871276855469</t>
+    <t xml:space="preserve">2.05436587333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02785801887512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227567672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111170768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03816628456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01018595695496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00871300697327</t>
   </si>
   <si>
     <t xml:space="preserve">1.99251401424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02638506889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07940053939819</t>
+    <t xml:space="preserve">2.02638530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07940101623535</t>
   </si>
   <si>
     <t xml:space="preserve">2.06467413902283</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">2.07203769683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06172919273376</t>
+    <t xml:space="preserve">2.06172895431519</t>
   </si>
   <si>
     <t xml:space="preserve">2.03522109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02933025360107</t>
+    <t xml:space="preserve">2.02933073043823</t>
   </si>
   <si>
     <t xml:space="preserve">2.06614708900452</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">2.07645583152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0867645740509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02196741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05731105804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07351040840149</t>
+    <t xml:space="preserve">2.08676409721375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02196717262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05731081962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07351016998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.04700231552124</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">2.0131311416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01460385322571</t>
+    <t xml:space="preserve">2.01460409164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.04258418083191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11179971694946</t>
+    <t xml:space="preserve">2.11179947853088</t>
   </si>
   <si>
     <t xml:space="preserve">2.08087372779846</t>
@@ -2153,31 +2153,31 @@
     <t xml:space="preserve">2.11032676696777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13683485984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10885453224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12652635574341</t>
+    <t xml:space="preserve">2.13683462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10885429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12652659416199</t>
   </si>
   <si>
     <t xml:space="preserve">2.17659664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457768440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19426894187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24581170082092</t>
+    <t xml:space="preserve">2.20457744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19426870346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24581217765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21341347694397</t>
+    <t xml:space="preserve">2.21341323852539</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
@@ -2186,40 +2186,40 @@
     <t xml:space="preserve">2.21783137321472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20163226127625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20752286911011</t>
+    <t xml:space="preserve">2.20163202285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20752263069153</t>
   </si>
   <si>
     <t xml:space="preserve">2.17365145683289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23255825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21930384635925</t>
+    <t xml:space="preserve">2.23255801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21930432319641</t>
   </si>
   <si>
     <t xml:space="preserve">2.21635866165161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20310497283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24728441238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28704643249512</t>
+    <t xml:space="preserve">2.20310473442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24728488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2870466709137</t>
   </si>
   <si>
     <t xml:space="preserve">2.26201128959656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25023007392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11474466323853</t>
+    <t xml:space="preserve">2.25022959709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11474514007568</t>
   </si>
   <si>
     <t xml:space="preserve">2.11621761322021</t>
@@ -2228,58 +2228,58 @@
     <t xml:space="preserve">2.15303421020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13094449043274</t>
+    <t xml:space="preserve">2.13094425201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.0249125957489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08823704719543</t>
+    <t xml:space="preserve">2.08823680877686</t>
   </si>
   <si>
     <t xml:space="preserve">2.10296368598938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220503330231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83641135692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65380108356476</t>
+    <t xml:space="preserve">1.9822051525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83641159534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65380120277405</t>
   </si>
   <si>
     <t xml:space="preserve">1.63318395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724899291992</t>
+    <t xml:space="preserve">1.38724911212921</t>
   </si>
   <si>
     <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35190510749817</t>
+    <t xml:space="preserve">1.35190522670746</t>
   </si>
   <si>
     <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30330729484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36442291736603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32171559333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3150886297226</t>
+    <t xml:space="preserve">1.30330717563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36442279815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32171547412872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31508874893188</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565729141235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37767684459686</t>
+    <t xml:space="preserve">1.37767672538757</t>
   </si>
   <si>
     <t xml:space="preserve">1.49475347995758</t>
@@ -2288,28 +2288,28 @@
     <t xml:space="preserve">1.50948011875153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58311331272125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674662590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071461200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54776930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53598821163177</t>
+    <t xml:space="preserve">1.58311343193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674638748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5477694272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53598809242249</t>
   </si>
   <si>
     <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56102335453033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55366003513336</t>
+    <t xml:space="preserve">1.56102323532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55365991592407</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
@@ -2318,55 +2318,55 @@
     <t xml:space="preserve">1.54187881946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58164083957672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60225796699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434804439545</t>
+    <t xml:space="preserve">1.58164072036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60225808620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434816360474</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61698472499847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287533283234</t>
+    <t xml:space="preserve">1.61698460578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287521362305</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643800258636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65527379512787</t>
+    <t xml:space="preserve">1.65527367591858</t>
   </si>
   <si>
     <t xml:space="preserve">1.67589128017426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66705501079559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349269866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520339012146</t>
+    <t xml:space="preserve">1.66705513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349257946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">1.57575011253357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58753144741058</t>
+    <t xml:space="preserve">1.587531208992</t>
   </si>
   <si>
     <t xml:space="preserve">1.5580780506134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57427728176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5904768705368</t>
+    <t xml:space="preserve">1.57427740097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047675132751</t>
   </si>
   <si>
     <t xml:space="preserve">1.59784007072449</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">1.64201986789703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66558253765106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62876570224762</t>
+    <t xml:space="preserve">1.66558241844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6287659406662</t>
   </si>
   <si>
     <t xml:space="preserve">1.61109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6788364648819</t>
+    <t xml:space="preserve">1.67883622646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.71859848499298</t>
@@ -2393,34 +2393,34 @@
     <t xml:space="preserve">1.76572358608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75836038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72007119655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7082896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6390745639801</t>
+    <t xml:space="preserve">1.75836062431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7200710773468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63907468318939</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70534467697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71123492717743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756798267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836562156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71468603610992</t>
+    <t xml:space="preserve">1.70534443855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7112352848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756810188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836574077606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71468591690063</t>
   </si>
   <si>
     <t xml:space="preserve">1.69781517982483</t>
@@ -2429,70 +2429,70 @@
     <t xml:space="preserve">1.71161866188049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71621966362</t>
+    <t xml:space="preserve">1.71621954441071</t>
   </si>
   <si>
     <t xml:space="preserve">1.69168043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548355579376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72542202472687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73462414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73769176006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73002314567566</t>
+    <t xml:space="preserve">1.70548367500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72542178630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73462426662445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73769164085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73002302646637</t>
   </si>
   <si>
     <t xml:space="preserve">1.68707931041718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68554520606995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327570915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65793859958649</t>
+    <t xml:space="preserve">1.68554544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327582836151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65793871879578</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487134456635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68401193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70241641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70701742172241</t>
+    <t xml:space="preserve">1.68401181697845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70241630077362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235453128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7070175409317</t>
   </si>
   <si>
     <t xml:space="preserve">1.66867470741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64566898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65333771705627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.656405210495</t>
+    <t xml:space="preserve">1.64566910266876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65333759784698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65640509128571</t>
   </si>
   <si>
     <t xml:space="preserve">1.6272646188736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63646697998047</t>
+    <t xml:space="preserve">1.63646686077118</t>
   </si>
   <si>
     <t xml:space="preserve">1.64720296859741</t>
@@ -2501,25 +2501,25 @@
     <t xml:space="preserve">1.67020833492279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407370567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68247807025909</t>
+    <t xml:space="preserve">1.66407346725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68247818946838</t>
   </si>
   <si>
     <t xml:space="preserve">1.7284893989563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73615765571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75609600543976</t>
+    <t xml:space="preserve">1.73615777492523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75609588623047</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088267326355</t>
+    <t xml:space="preserve">1.70088255405426</t>
   </si>
   <si>
     <t xml:space="preserve">1.72082078456879</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">1.67174220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6993488073349</t>
+    <t xml:space="preserve">1.69934892654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69014668464661</t>
+    <t xml:space="preserve">1.69014656543732</t>
   </si>
   <si>
     <t xml:space="preserve">1.71008479595184</t>
@@ -2549,43 +2549,43 @@
     <t xml:space="preserve">1.68861281871796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65180385112762</t>
+    <t xml:space="preserve">1.6518040895462</t>
   </si>
   <si>
     <t xml:space="preserve">1.64873647689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62573075294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61959612369537</t>
+    <t xml:space="preserve">1.62573087215424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61959600448608</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659039974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505653381348</t>
+    <t xml:space="preserve">1.59505665302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.58738803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57971966266632</t>
+    <t xml:space="preserve">1.57971954345703</t>
   </si>
   <si>
     <t xml:space="preserve">1.57358479499817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54904556274414</t>
+    <t xml:space="preserve">1.54904544353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057919025421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996674060822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48156237602234</t>
+    <t xml:space="preserve">1.49996662139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48156249523163</t>
   </si>
   <si>
     <t xml:space="preserve">1.4961324930191</t>
@@ -2594,61 +2594,61 @@
     <t xml:space="preserve">1.50303423404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51990497112274</t>
+    <t xml:space="preserve">1.51990485191345</t>
   </si>
   <si>
     <t xml:space="preserve">1.5475115776062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5643824338913</t>
+    <t xml:space="preserve">1.56438255310059</t>
   </si>
   <si>
     <t xml:space="preserve">1.53064107894897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60425889492035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59198939800262</t>
+    <t xml:space="preserve">1.60425901412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
     <t xml:space="preserve">1.59965789318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60119163990021</t>
+    <t xml:space="preserve">1.60119152069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.614994764328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58125340938568</t>
+    <t xml:space="preserve">1.58125329017639</t>
   </si>
   <si>
     <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6027250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6610062122345</t>
+    <t xml:space="preserve">1.60272514820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66100609302521</t>
   </si>
   <si>
     <t xml:space="preserve">1.74075889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76069700717926</t>
+    <t xml:space="preserve">1.76069724559784</t>
   </si>
   <si>
     <t xml:space="preserve">1.72388815879822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69628119468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6318656206131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62879848480225</t>
+    <t xml:space="preserve">1.69628131389618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186585903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
     <t xml:space="preserve">1.63033187389374</t>
@@ -2657,52 +2657,52 @@
     <t xml:space="preserve">1.5889219045639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60886013507843</t>
+    <t xml:space="preserve">1.60886001586914</t>
   </si>
   <si>
     <t xml:space="preserve">1.6103937625885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61346125602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585464954376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63953411579132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64260160923004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63493311405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65947246551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66714096069336</t>
+    <t xml:space="preserve">1.61346137523651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585441112518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63953423500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64260172843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63493299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65947234630585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66714107990265</t>
   </si>
   <si>
     <t xml:space="preserve">1.62266337871552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55518043041229</t>
+    <t xml:space="preserve">1.555180311203</t>
   </si>
   <si>
     <t xml:space="preserve">1.55671393871307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56131517887115</t>
+    <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57051742076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597813129425</t>
+    <t xml:space="preserve">1.57051753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55978143215179</t>
   </si>
   <si>
     <t xml:space="preserve">1.58278691768646</t>
@@ -2714,73 +2714,73 @@
     <t xml:space="preserve">1.63339948654175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419712543488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192739009857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58432066440582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61806225776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66560733318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71775341033936</t>
+    <t xml:space="preserve">1.62419724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192750930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58432078361511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61806237697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106810092926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.665607213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67480957508087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71775329113007</t>
   </si>
   <si>
     <t xml:space="preserve">1.75762987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80517470836639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81744432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824208259583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670845508575</t>
+    <t xml:space="preserve">1.80517494678497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8174444437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082423210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670821666718</t>
   </si>
   <si>
     <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903995990753</t>
+    <t xml:space="preserve">1.79903984069824</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290521144867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82051181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78063547611237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79443871974945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83278155326843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8097757101059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82971405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85885465145111</t>
+    <t xml:space="preserve">1.82051205635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78063535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79443883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83278167247772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80977594852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82971394062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85885453224182</t>
   </si>
   <si>
     <t xml:space="preserve">1.83891630172729</t>
@@ -2795,64 +2795,64 @@
     <t xml:space="preserve">1.85578715801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8634557723999</t>
+    <t xml:space="preserve">1.86345589160919</t>
   </si>
   <si>
     <t xml:space="preserve">1.84965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87112414836884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89566349983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90179848670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91866910457611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90026473999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91100096702576</t>
+    <t xml:space="preserve">1.8711245059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89566338062286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90179860591888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91866934299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90026462078094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100072860718</t>
   </si>
   <si>
     <t xml:space="preserve">1.94627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95394456386566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91560161113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713547706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553996086121</t>
+    <t xml:space="preserve">1.95394444465637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9156014919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173683643341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713535785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553984165192</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695004940033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96007931232452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382078647614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9662139415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00609064102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762391090393</t>
+    <t xml:space="preserve">1.96007943153381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382054805756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621382236481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00609040260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762438774109</t>
   </si>
   <si>
     <t xml:space="preserve">2.01375889778137</t>
@@ -2861,31 +2861,31 @@
     <t xml:space="preserve">2.00915789604187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95701193809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854556560516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9692816734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97848391532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00302290916443</t>
+    <t xml:space="preserve">1.95701217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854544639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96928155422211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97848355770111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00302314758301</t>
   </si>
   <si>
     <t xml:space="preserve">2.01069188117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01835989952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02909588813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03369736671448</t>
+    <t xml:space="preserve">2.01836037635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0290961265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0336971282959</t>
   </si>
   <si>
     <t xml:space="preserve">2.01682662963867</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563097953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335124015808</t>
+    <t xml:space="preserve">1.99563086032867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335135936737</t>
   </si>
   <si>
     <t xml:space="preserve">1.97175967693329</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92242586612701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91606044769287</t>
+    <t xml:space="preserve">1.9224259853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.916060090065</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2918,13 +2918,13 @@
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9240175485611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92720007896423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9797168970108</t>
+    <t xml:space="preserve">1.92401742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92719995975494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971653938293</t>
   </si>
   <si>
     <t xml:space="preserve">1.96061992645264</t>
@@ -2939,22 +2939,22 @@
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926532268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857702732086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287744045258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478884935379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449110984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223347663879</t>
+    <t xml:space="preserve">1.98926520347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857678890228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287767887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94788837432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449099063873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223323822021</t>
   </si>
   <si>
     <t xml:space="preserve">2.01950216293335</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">2.04337334632874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04814743995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02427649497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06247019767761</t>
+    <t xml:space="preserve">2.04814720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02427625656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06247043609619</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07997584342957</t>
+    <t xml:space="preserve">2.07997560501099</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10543847084045</t>
+    <t xml:space="preserve">2.10543823242188</t>
   </si>
   <si>
     <t xml:space="preserve">2.13726663589478</t>
@@ -2999,34 +2999,34 @@
     <t xml:space="preserve">2.18819189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2025146484375</t>
+    <t xml:space="preserve">2.20251441001892</t>
   </si>
   <si>
     <t xml:space="preserve">2.1706862449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15158915519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12453556060791</t>
+    <t xml:space="preserve">2.15158939361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12453532218933</t>
   </si>
   <si>
     <t xml:space="preserve">2.11816954612732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10066437721252</t>
+    <t xml:space="preserve">2.10066413879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.08315873146057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07042717933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10862135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.089524269104</t>
+    <t xml:space="preserve">2.07042741775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10862112045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08952403068542</t>
   </si>
   <si>
     <t xml:space="preserve">2.0847499370575</t>
@@ -3041,22 +3041,22 @@
     <t xml:space="preserve">2.11180400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14840650558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12135243415833</t>
+    <t xml:space="preserve">2.14840626716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12135219573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339569091797</t>
+    <t xml:space="preserve">2.11339545249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.13249230384827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612652778625</t>
+    <t xml:space="preserve">2.12612676620483</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363241195679</t>
@@ -3065,37 +3065,37 @@
     <t xml:space="preserve">2.04178190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05928730964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04019045829773</t>
+    <t xml:space="preserve">2.05928754806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04019021987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02586770057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03064179420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98767399787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01154518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15477228164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18341732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18978333473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023490905762</t>
+    <t xml:space="preserve">2.02586793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03064227104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98767364025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01154494285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15477204322815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18341755867004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18978309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023467063904</t>
   </si>
   <si>
     <t xml:space="preserve">2.16113781929016</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">2.20569729804993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21842885017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29163384437561</t>
+    <t xml:space="preserve">2.21842861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29163360595703</t>
   </si>
   <si>
     <t xml:space="preserve">2.27412796020508</t>
@@ -3116,43 +3116,43 @@
     <t xml:space="preserve">2.2534396648407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29481625556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23593401908875</t>
+    <t xml:space="preserve">2.29481649398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23593425750732</t>
   </si>
   <si>
     <t xml:space="preserve">2.25025677680969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27571964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27890253067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22161149978638</t>
+    <t xml:space="preserve">2.27571940422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27890229225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2216112613678</t>
   </si>
   <si>
     <t xml:space="preserve">2.23115992546082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.200923204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17546033859253</t>
+    <t xml:space="preserve">2.20092296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17546057701111</t>
   </si>
   <si>
     <t xml:space="preserve">2.19296598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19774031639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10384678840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15795516967773</t>
+    <t xml:space="preserve">2.19774055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10384702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
     <t xml:space="preserve">2.17386913299561</t>
@@ -3167,46 +3167,46 @@
     <t xml:space="preserve">2.12771821022034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10702967643738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07520151138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07201862335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.086341381073</t>
+    <t xml:space="preserve">2.10702991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07520174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07201886177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08634161949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.14204096794128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09748125076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09907269477844</t>
+    <t xml:space="preserve">2.09748101234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09907293319702</t>
   </si>
   <si>
     <t xml:space="preserve">2.09111571311951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06883597373962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01472783088684</t>
+    <t xml:space="preserve">2.06883549690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.014728307724</t>
   </si>
   <si>
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97812521457672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97016823291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03700757026672</t>
+    <t xml:space="preserve">1.97812557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97016847133636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03700733184814</t>
   </si>
   <si>
     <t xml:space="preserve">2.1197612285614</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130834102631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02109360694885</t>
+    <t xml:space="preserve">1.98130822181702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02109336853027</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380257606506</t>
@@ -3227,10 +3227,10 @@
     <t xml:space="preserve">1.91128599643707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89378070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969467163086</t>
+    <t xml:space="preserve">1.89378094673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969491004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
@@ -3239,64 +3239,64 @@
     <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90651178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945783138275</t>
+    <t xml:space="preserve">1.90651154518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945771217346</t>
   </si>
   <si>
     <t xml:space="preserve">1.8126186132431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7553277015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79033887386322</t>
+    <t xml:space="preserve">1.79193031787872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75532782077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79033863544464</t>
   </si>
   <si>
     <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83330678939819</t>
+    <t xml:space="preserve">1.83330690860748</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83171534538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81102728843689</t>
+    <t xml:space="preserve">1.83171546459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534992694855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81102705001831</t>
   </si>
   <si>
     <t xml:space="preserve">1.82694125175476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012413978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444677829742</t>
+    <t xml:space="preserve">1.83012402057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444689750671</t>
   </si>
   <si>
     <t xml:space="preserve">1.88423204421997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83808100223541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240387916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104927539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92879152297974</t>
+    <t xml:space="preserve">1.83808088302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240375995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104939460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
     <t xml:space="preserve">1.89537191390991</t>
@@ -3305,34 +3305,34 @@
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881386756897</t>
+    <t xml:space="preserve">1.99881398677826</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313662528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98289966583252</t>
+    <t xml:space="preserve">2.01313638687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98289978504181</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035879611969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94311439990997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197453022003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9510715007782</t>
+    <t xml:space="preserve">1.94311416149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107126235962</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786626815796</t>
+    <t xml:space="preserve">1.87786650657654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3341,43 +3341,43 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9526629447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93038320541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993139266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90014636516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91765165328979</t>
+    <t xml:space="preserve">1.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95266270637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93038308620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993151187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90014612674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91765177249908</t>
   </si>
   <si>
     <t xml:space="preserve">1.9192430973053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84285533428192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71235954761505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6423374414444</t>
+    <t xml:space="preserve">1.84285521507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71235942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64233732223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66143441200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65984284877777</t>
+    <t xml:space="preserve">1.66143429279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65984296798706</t>
   </si>
   <si>
     <t xml:space="preserve">1.69007992744446</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">1.64711153507233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6168749332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483191490173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65506875514984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70758521556854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69644546508789</t>
+    <t xml:space="preserve">1.61687481403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483179569244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65506863594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70758533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6964453458786</t>
   </si>
   <si>
     <t xml:space="preserve">1.68053126335144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65825164318085</t>
+    <t xml:space="preserve">1.65825176239014</t>
   </si>
   <si>
     <t xml:space="preserve">1.68848836421967</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">1.56435811519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58345532417297</t>
+    <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.577885389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5850465297699</t>
+    <t xml:space="preserve">1.57788527011871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58504641056061</t>
   </si>
   <si>
     <t xml:space="preserve">1.58743381500244</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">1.51025021076202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53383481502533</t>
+    <t xml:space="preserve">1.53383469581604</t>
   </si>
   <si>
     <t xml:space="preserve">1.54731154441833</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">1.50688099861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51698851585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50856554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51361954212189</t>
+    <t xml:space="preserve">1.51698863506317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50856566429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5136194229126</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">1.54815399646759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48835039138794</t>
+    <t xml:space="preserve">1.48835027217865</t>
   </si>
   <si>
     <t xml:space="preserve">1.47487342357635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087727069855</t>
+    <t xml:space="preserve">1.49087715148926</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
@@ -3482,28 +3482,28 @@
     <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47403109073639</t>
+    <t xml:space="preserve">1.47403120994568</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48498106002808</t>
+    <t xml:space="preserve">1.48498117923737</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171960353851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46645057201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45718502998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41591227054596</t>
+    <t xml:space="preserve">1.49171948432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46645045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4571852684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41591215133667</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201238155365</t>
@@ -3512,40 +3512,40 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39906620979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200487613678</t>
+    <t xml:space="preserve">1.3990660905838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200475692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178948402405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766681671143</t>
+    <t xml:space="preserve">1.34178960323334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766669750214</t>
   </si>
   <si>
     <t xml:space="preserve">1.26177072525024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27777433395386</t>
+    <t xml:space="preserve">1.27777445316315</t>
   </si>
   <si>
     <t xml:space="preserve">1.22892081737518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20617878437042</t>
+    <t xml:space="preserve">1.20617866516113</t>
   </si>
   <si>
     <t xml:space="preserve">1.23229014873505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22976326942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2920937538147</t>
+    <t xml:space="preserve">1.22976315021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29209363460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.31988966464996</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144781589508</t>
+    <t xml:space="preserve">1.23144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365178585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20533633232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17501330375671</t>
+    <t xml:space="preserve">1.20365166664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20533645153046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.175013422966</t>
   </si>
   <si>
     <t xml:space="preserve">1.13289821147919</t>
@@ -3584,10 +3584,10 @@
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942136287689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1059445142746</t>
+    <t xml:space="preserve">1.11942148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10594439506531</t>
   </si>
   <si>
     <t xml:space="preserve">1.14300584793091</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">1.21965551376343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16490578651428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13710975646973</t>
+    <t xml:space="preserve">1.16490566730499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13710963726044</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">1.12700212001801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12279057502747</t>
+    <t xml:space="preserve">1.12279045581818</t>
   </si>
   <si>
     <t xml:space="preserve">1.08151769638062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10425984859467</t>
+    <t xml:space="preserve">1.10425996780396</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553272724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427884578705</t>
+    <t xml:space="preserve">1.14553284645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427872657776</t>
   </si>
   <si>
     <t xml:space="preserve">1.22470927238464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2600861787796</t>
+    <t xml:space="preserve">1.26008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">1.29462051391602</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">1.28367066383362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26682436466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26935136318207</t>
+    <t xml:space="preserve">1.26682448387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26935148239136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28030133247375</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829387664795</t>
+    <t xml:space="preserve">1.24829375743866</t>
   </si>
   <si>
     <t xml:space="preserve">1.24492466449738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25334763526917</t>
+    <t xml:space="preserve">1.25334775447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818624019623</t>
@@ -3674,28 +3674,28 @@
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325875759125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31567823886871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31652045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32999730110168</t>
+    <t xml:space="preserve">1.32325887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31567811965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3165203332901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3299971818924</t>
   </si>
   <si>
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915484905243</t>
+    <t xml:space="preserve">1.32915496826172</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021257400513</t>
+    <t xml:space="preserve">1.35021269321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">1.367058634758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32662796974182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33589339256287</t>
+    <t xml:space="preserve">1.32662808895111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33589327335358</t>
   </si>
   <si>
     <t xml:space="preserve">1.31062424182892</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">1.29546284675598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30135881900787</t>
+    <t xml:space="preserve">1.30135893821716</t>
   </si>
   <si>
     <t xml:space="preserve">1.25082075595856</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23734378814697</t>
+    <t xml:space="preserve">1.23734390735626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">1.2895667552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34263169765472</t>
+    <t xml:space="preserve">1.33842027187347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34263181686401</t>
   </si>
   <si>
     <t xml:space="preserve">1.37127017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3695855140686</t>
+    <t xml:space="preserve">1.36958563327789</t>
   </si>
   <si>
     <t xml:space="preserve">1.43865430355072</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">1.44539284706116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139657497406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4656081199646</t>
+    <t xml:space="preserve">1.46139669418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46560823917389</t>
   </si>
   <si>
     <t xml:space="preserve">1.4041200876236</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4336005449295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44370830059052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39653933048248</t>
+    <t xml:space="preserve">1.43360066413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44370818138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
     <t xml:space="preserve">1.42265069484711</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">1.39148533344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38474690914154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38727378845215</t>
+    <t xml:space="preserve">1.38474702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38727390766144</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39316999912262</t>
+    <t xml:space="preserve">1.39317011833191</t>
   </si>
   <si>
     <t xml:space="preserve">1.37800860404968</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779333114624</t>
+    <t xml:space="preserve">1.35779321193695</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496230125427</t>
+    <t xml:space="preserve">1.40496218204498</t>
   </si>
   <si>
     <t xml:space="preserve">1.3881162405014</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34515869617462</t>
+    <t xml:space="preserve">1.34515881538391</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230890750885</t>
+    <t xml:space="preserve">1.31230878829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">1.45634281635284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42686223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707751274109</t>
+    <t xml:space="preserve">1.42686212062836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4470773935318</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">1.48329651355743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.476557970047</t>
+    <t xml:space="preserve">1.47655808925629</t>
   </si>
   <si>
     <t xml:space="preserve">1.53888845443726</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6071150302887</t>
+    <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
     <t xml:space="preserve">1.61132657527924</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.57426536083221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521521091461</t>
+    <t xml:space="preserve">1.5852153301239</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784984588623</t>
+    <t xml:space="preserve">1.59784972667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62396121025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59953451156616</t>
+    <t xml:space="preserve">1.62396109104156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59953439235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">1.64249193668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66186499595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62227666378021</t>
+    <t xml:space="preserve">1.66186487674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62227654457092</t>
   </si>
   <si>
     <t xml:space="preserve">1.58774209022522</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">1.62480342388153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61385357379913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795748233795</t>
+    <t xml:space="preserve">1.61385345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795736312866</t>
   </si>
   <si>
     <t xml:space="preserve">1.58100366592407</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57763457298279</t>
+    <t xml:space="preserve">1.5776344537735</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">1.57089602947235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57595002651215</t>
+    <t xml:space="preserve">1.57594990730286</t>
   </si>
   <si>
     <t xml:space="preserve">1.58437299728394</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">1.58184599876404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57173848152161</t>
+    <t xml:space="preserve">1.57173836231232</t>
   </si>
   <si>
     <t xml:space="preserve">1.59026908874512</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5308746099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52102696895599</t>
+    <t xml:space="preserve">1.53087472915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5210268497467</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357869148254</t>
+    <t xml:space="preserve">1.47357881069183</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506461620331</t>
+    <t xml:space="preserve">1.4950647354126</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4088,52 +4088,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192211151123</t>
+    <t xml:space="preserve">1.52192223072052</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070407390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308526039124</t>
+    <t xml:space="preserve">1.61144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070395469666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308514118195</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786592960358</t>
+    <t xml:space="preserve">1.60786604881287</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039947509766</t>
+    <t xml:space="preserve">1.62039935588837</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801828861237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773198604584</t>
+    <t xml:space="preserve">1.59801816940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773210525513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937026977539</t>
+    <t xml:space="preserve">1.56937038898468</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6150279045105</t>
+    <t xml:space="preserve">1.61502802371979</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58279895782471</t>
+    <t xml:space="preserve">1.582799077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769539356232</t>
+    <t xml:space="preserve">1.67769527435303</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575263023376</t>
+    <t xml:space="preserve">1.68575251102448</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.664266705513</t>
+    <t xml:space="preserve">1.66426658630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977198123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887683868408</t>
+    <t xml:space="preserve">1.71977210044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887671947479</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843841552734</t>
+    <t xml:space="preserve">1.68843829631805</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159921646118</t>
+    <t xml:space="preserve">1.60159933567047</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340815544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399881839752</t>
+    <t xml:space="preserve">1.54340803623199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234211921692</t>
+    <t xml:space="preserve">1.61234223842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024723529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112420082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350538730621</t>
+    <t xml:space="preserve">1.63024711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112408161163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350526809692</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.745734333992</t>
+    <t xml:space="preserve">1.74573421478271</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201922416687</t>
+    <t xml:space="preserve">1.69201934337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79407751560211</t>
+    <t xml:space="preserve">1.78691565990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7940776348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525896072388</t>
+    <t xml:space="preserve">1.83525907993317</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272565364838</t>
+    <t xml:space="preserve">1.82272553443909</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558185577393</t>
+    <t xml:space="preserve">1.75558197498322</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7645343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857223987579</t>
+    <t xml:space="preserve">1.76453447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857235908508</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4409,16 +4409,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723855495453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859053611755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009487628937</t>
+    <t xml:space="preserve">1.70723843574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859065532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009499549866</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740909099579</t>
+    <t xml:space="preserve">1.63740921020508</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64099013805389</t>
+    <t xml:space="preserve">1.63919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6409900188446</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693407535553</t>
+    <t xml:space="preserve">1.72693395614624</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041777133942</t>
+    <t xml:space="preserve">1.56041789054871</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458960056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609394073486</t>
+    <t xml:space="preserve">1.58458948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609382152557</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205605506897</t>
+    <t xml:space="preserve">1.57205617427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278066158295</t>
+    <t xml:space="preserve">1.64278078079224</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754303455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129461765289</t>
+    <t xml:space="preserve">1.68754315376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129473686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708619594574</t>
+    <t xml:space="preserve">1.71708631515503</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274394989014</t>
+    <t xml:space="preserve">1.76274383068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602039813995</t>
+    <t xml:space="preserve">1.78602051734924</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -22517,7 +22517,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G649" t="s">
-        <v>482</v>
+        <v>356</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22543,7 +22543,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G650" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22569,7 +22569,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G651" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22595,7 +22595,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22621,7 +22621,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G653" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22647,7 +22647,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G654" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22673,7 +22673,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G655" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22699,7 +22699,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G656" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22725,7 +22725,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G657" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22751,7 +22751,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G658" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22777,7 +22777,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G659" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22803,7 +22803,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G660" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22829,7 +22829,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G661" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22855,7 +22855,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G662" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22881,7 +22881,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G663" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22907,7 +22907,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22933,7 +22933,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G665" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22959,7 +22959,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G666" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22985,7 +22985,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G667" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23011,7 +23011,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G668" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23037,7 +23037,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23063,7 +23063,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G670" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23089,7 +23089,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G671" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23115,7 +23115,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G672" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23141,7 +23141,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G673" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23193,7 +23193,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G675" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23219,7 +23219,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G676" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23271,7 +23271,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G678" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23297,7 +23297,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G679" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23323,7 +23323,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G680" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23349,7 +23349,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23375,7 +23375,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G682" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23401,7 +23401,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G683" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23427,7 +23427,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G684" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23453,7 +23453,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G685" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23479,7 +23479,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G686" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23505,7 +23505,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G687" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23557,7 +23557,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23609,7 +23609,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G691" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23713,7 +23713,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G695" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23739,7 +23739,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23765,7 +23765,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G697" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23791,7 +23791,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G698" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23817,7 +23817,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23843,7 +23843,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G700" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23869,7 +23869,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G701" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23895,7 +23895,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G702" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23921,7 +23921,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G703" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23947,7 +23947,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23973,7 +23973,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23999,7 +23999,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G706" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -24025,7 +24025,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G707" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24051,7 +24051,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G708" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -24077,7 +24077,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G709" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -24103,7 +24103,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G710" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24129,7 +24129,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G711" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24155,7 +24155,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G712" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24181,7 +24181,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G713" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24207,7 +24207,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G714" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24233,7 +24233,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G715" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24259,7 +24259,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G716" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24285,7 +24285,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G717" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24311,7 +24311,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G718" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24337,7 +24337,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G719" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24363,7 +24363,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G720" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24389,7 +24389,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G721" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24415,7 +24415,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G722" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24441,7 +24441,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G723" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24467,7 +24467,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G724" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24493,7 +24493,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G725" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24519,7 +24519,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G726" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24545,7 +24545,7 @@
         <v>1.97300004959106</v>
       </c>
       <c r="G727" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24571,7 +24571,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G728" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24597,7 +24597,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G729" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24623,7 +24623,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G730" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24649,7 +24649,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24675,7 +24675,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G732" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24701,7 +24701,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G733" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24727,7 +24727,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24753,7 +24753,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G735" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24779,7 +24779,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G736" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24805,7 +24805,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G737" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24831,7 +24831,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G738" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24857,7 +24857,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G739" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24883,7 +24883,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G740" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24909,7 +24909,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G741" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24935,7 +24935,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G742" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24961,7 +24961,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24987,7 +24987,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G744" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -25013,7 +25013,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -25039,7 +25039,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G746" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -25065,7 +25065,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G747" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -25091,7 +25091,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -25117,7 +25117,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G749" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -25143,7 +25143,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -25169,7 +25169,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G751" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25195,7 +25195,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G752" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25221,7 +25221,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G753" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25247,7 +25247,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G754" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25273,7 +25273,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25299,7 +25299,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G756" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25325,7 +25325,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G757" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25351,7 +25351,7 @@
         <v>2</v>
       </c>
       <c r="G758" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25377,7 +25377,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G759" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25403,7 +25403,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G760" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25429,7 +25429,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25455,7 +25455,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G762" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25481,7 +25481,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G763" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25507,7 +25507,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G764" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25559,7 +25559,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G766" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25585,7 +25585,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G767" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25611,7 +25611,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>322</v>
+        <v>571</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25663,7 +25663,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G770" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25741,7 +25741,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>322</v>
+        <v>571</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25897,7 +25897,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26079,7 +26079,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G786" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -26105,7 +26105,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G787" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26183,7 +26183,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G790" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26313,7 +26313,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26391,7 +26391,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G798" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26495,7 +26495,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G802" t="s">
-        <v>322</v>
+        <v>571</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26547,7 +26547,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G804" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26573,7 +26573,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G805" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26599,7 +26599,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26625,7 +26625,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G807" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26651,7 +26651,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G808" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26729,7 +26729,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G811" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26781,7 +26781,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G813" t="s">
-        <v>482</v>
+        <v>356</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26807,7 +26807,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26911,7 +26911,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G818" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26963,7 +26963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G820" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27041,7 +27041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -27171,7 +27171,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27275,7 +27275,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27535,7 +27535,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G842" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27561,7 +27561,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G843" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27587,7 +27587,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G844" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27613,7 +27613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27665,7 +27665,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G847" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27821,7 +27821,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G853" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27951,7 +27951,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G858" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28029,7 +28029,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G861" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28081,7 +28081,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G863" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28159,7 +28159,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G866" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28263,7 +28263,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G870" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28315,7 +28315,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28367,7 +28367,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G874" t="s">
-        <v>482</v>
+        <v>356</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28393,7 +28393,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G875" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28471,7 +28471,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G878" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28497,7 +28497,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G879" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28601,7 +28601,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G883" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -70573,7 +70573,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912384259</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>524771</v>
@@ -70594,6 +70594,32 @@
         <v>1766</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.69125</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>492505</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>2.73600006103516</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>2.69400000572205</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>2.7279999256134</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>2.72399997711182</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1766</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="1768">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,139 +38,139 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469414710999</t>
+    <t xml:space="preserve">0.933469355106354</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806130886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927027225494385</t>
+    <t xml:space="preserve">0.923806190490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92702716588974</t>
   </si>
   <si>
     <t xml:space="preserve">0.921873509883881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901902675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898037672042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652355670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835535049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643665790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346442699432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653873920441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154633045197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163322925568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451856136322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869691908359528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441648006439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374149799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551905632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84327906370163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798840045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481141090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825241088867188</t>
+    <t xml:space="preserve">0.901902794837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898037552833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652474880219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835356235504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643606185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893926143646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346502304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851654052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192727088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451796531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441767215729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489890575409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344924449921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374090194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551917552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279004096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798899650574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481021881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241208076477</t>
   </si>
   <si>
     <t xml:space="preserve">0.848432898521423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869047701358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778364181519</t>
+    <t xml:space="preserve">0.869047582149506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778304576874</t>
   </si>
   <si>
     <t xml:space="preserve">0.894172191619873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923161864280701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671492099762</t>
+    <t xml:space="preserve">0.923161745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671432495117</t>
   </si>
   <si>
     <t xml:space="preserve">0.914142847061157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945709466934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91929680109024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075468063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941199719905853</t>
+    <t xml:space="preserve">0.945709645748138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296622276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075587272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199958324432</t>
   </si>
   <si>
     <t xml:space="preserve">0.947642087936401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930892407894135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412303447723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918007910251617</t>
+    <t xml:space="preserve">0.930892527103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412243843079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008029460907</t>
   </si>
   <si>
     <t xml:space="preserve">0.954084098339081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964391767978668</t>
+    <t xml:space="preserve">0.964391648769379</t>
   </si>
   <si>
     <t xml:space="preserve">0.999179363250732</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">1.01270794868469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02881324291229</t>
+    <t xml:space="preserve">1.02881336212158</t>
   </si>
   <si>
     <t xml:space="preserve">1.01657319068909</t>
@@ -188,109 +188,109 @@
     <t xml:space="preserve">1.02365970611572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00819873809814</t>
+    <t xml:space="preserve">1.00819849967957</t>
   </si>
   <si>
     <t xml:space="preserve">1.00175619125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00497734546661</t>
+    <t xml:space="preserve">1.00497722625732</t>
   </si>
   <si>
     <t xml:space="preserve">1.00755417346954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02172708511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01464068889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237117290497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999823689460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01141953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206362247467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01786172389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430391311646</t>
+    <t xml:space="preserve">1.02172696590424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01464056968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999823451042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01141941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206386089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01786148548126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430379390717</t>
   </si>
   <si>
     <t xml:space="preserve">1.01850581169128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0268806219101</t>
+    <t xml:space="preserve">1.02688074111938</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203451633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0249480009079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01721751689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00562143325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988871932029724</t>
+    <t xml:space="preserve">1.02494812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0172176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00562167167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988871991634369</t>
   </si>
   <si>
     <t xml:space="preserve">1.00368881225586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0352555513382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02816927433014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04040920734406</t>
+    <t xml:space="preserve">1.03525567054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02816903591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04040944576263</t>
   </si>
   <si>
     <t xml:space="preserve">1.03396725654602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02945744991302</t>
+    <t xml:space="preserve">1.0294576883316</t>
   </si>
   <si>
     <t xml:space="preserve">1.03010177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01592898368835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992093145847321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03332281112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00948691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958387851715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314002037048</t>
+    <t xml:space="preserve">1.01592922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992093026638031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03332269191742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00948679447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958268642426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995314061641693</t>
   </si>
   <si>
     <t xml:space="preserve">1.02108287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04942834377289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519710063934</t>
+    <t xml:space="preserve">1.0494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519686222076</t>
   </si>
   <si>
     <t xml:space="preserve">1.06295680999756</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">1.07326436042786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06231260299683</t>
+    <t xml:space="preserve">1.06231284141541</t>
   </si>
   <si>
     <t xml:space="preserve">1.04749572277069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06360113620758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0616682767868</t>
+    <t xml:space="preserve">1.06360101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06166839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.06811058521271</t>
@@ -320,76 +320,76 @@
     <t xml:space="preserve">1.04620718955994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977276086807251</t>
+    <t xml:space="preserve">0.977276146411896</t>
   </si>
   <si>
     <t xml:space="preserve">0.968257009983063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965035915374756</t>
+    <t xml:space="preserve">0.965035855770111</t>
   </si>
   <si>
     <t xml:space="preserve">0.978564560413361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962522566318512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232847690582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517227649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90771222114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964867115021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701663017273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680546760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101586341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117244720459</t>
+    <t xml:space="preserve">0.962522447109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232907295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517287254333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90771210193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876964926719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701722621918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680725574493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101645946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117363929749</t>
   </si>
   <si>
     <t xml:space="preserve">0.939127683639526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909048974514008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033316135406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915733158588409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925091028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775331497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925759434700012</t>
+    <t xml:space="preserve">0.909049034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033256530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915733218193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925091147422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775271892548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925759315490723</t>
   </si>
   <si>
     <t xml:space="preserve">0.912391066551208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921080350875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927096366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143699645996</t>
+    <t xml:space="preserve">0.921080470085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927096307277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143580436707</t>
   </si>
   <si>
     <t xml:space="preserve">0.937122464179993</t>
@@ -398,82 +398,82 @@
     <t xml:space="preserve">0.955838322639465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953164577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527785778046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196192264557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982575237751007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98391181230545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972548723220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580218791962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987253904342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995274841785431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890755653381</t>
+    <t xml:space="preserve">0.953164637088776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527666568756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196013450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982575178146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97254866361618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580338001251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987254023551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995275020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98925918340683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601335048676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890874862671</t>
   </si>
   <si>
     <t xml:space="preserve">0.951827883720398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950490891933441</t>
+    <t xml:space="preserve">0.950490951538086</t>
   </si>
   <si>
     <t xml:space="preserve">0.948485672473907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94113290309906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501450061798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864479541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927530288696</t>
+    <t xml:space="preserve">0.941133141517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501330852509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864598751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985916972160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927470684052</t>
   </si>
   <si>
     <t xml:space="preserve">1.01265382766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02000653743744</t>
+    <t xml:space="preserve">1.02000641822815</t>
   </si>
   <si>
     <t xml:space="preserve">0.991932988166809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988590598106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996611893177032</t>
+    <t xml:space="preserve">0.988590717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996611833572388</t>
   </si>
   <si>
     <t xml:space="preserve">0.979901373386383</t>
@@ -482,49 +482,49 @@
     <t xml:space="preserve">0.967201292514801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98658549785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977896153926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885536193848</t>
+    <t xml:space="preserve">0.986585676670074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977896094322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885476589203</t>
   </si>
   <si>
     <t xml:space="preserve">0.995943367481232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02401697635651</t>
+    <t xml:space="preserve">1.02401685714722</t>
   </si>
   <si>
     <t xml:space="preserve">1.00864326953888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00262749195099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969206690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975222229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248744487762</t>
+    <t xml:space="preserve">1.00262761116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969206631183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975222408771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248625278473</t>
   </si>
   <si>
     <t xml:space="preserve">1.02936434745789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05342733860016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05543267726898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0761536359787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08952212333679</t>
+    <t xml:space="preserve">1.05342721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05543279647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07615351676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0895220041275</t>
   </si>
   <si>
     <t xml:space="preserve">1.09420096874237</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">1.09687447547913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07013773918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08751678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07749032974243</t>
+    <t xml:space="preserve">1.0701379776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08751654624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09353244304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07749056816101</t>
   </si>
   <si>
     <t xml:space="preserve">1.06479060649872</t>
@@ -551,64 +551,64 @@
     <t xml:space="preserve">1.06278514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04741156101227</t>
+    <t xml:space="preserve">1.04741168022156</t>
   </si>
   <si>
     <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06813251972198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05209064483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957843542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953833222389221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480333805084</t>
+    <t xml:space="preserve">1.06813263893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05209052562714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957843363285065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953832983970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480274200439</t>
   </si>
   <si>
     <t xml:space="preserve">0.935785710811615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942469954490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738437652588</t>
+    <t xml:space="preserve">0.942469894886017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780252933502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727879524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738378047943</t>
   </si>
   <si>
     <t xml:space="preserve">0.941801428794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918406844139099</t>
+    <t xml:space="preserve">0.918406784534454</t>
   </si>
   <si>
     <t xml:space="preserve">0.968538284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967869639396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569779872894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606673717499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948586940765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
+    <t xml:space="preserve">0.967869818210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569541454315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606554508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99794864654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332211494446</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532757282257</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203809261322</t>
+    <t xml:space="preserve">1.03203797340393</t>
   </si>
   <si>
     <t xml:space="preserve">1.04005885124207</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">1.03070104122162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01733291149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03604865074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0494167804718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275905132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0500853061676</t>
+    <t xml:space="preserve">1.01733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.036048412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874837398529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04941666126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275893211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05008542537689</t>
   </si>
   <si>
     <t xml:space="preserve">1.04072749614716</t>
@@ -656,37 +656,37 @@
     <t xml:space="preserve">1.04607486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02468550205231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0106486082077</t>
+    <t xml:space="preserve">1.02468526363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01064848899841</t>
   </si>
   <si>
     <t xml:space="preserve">1.00530123710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03003251552582</t>
+    <t xml:space="preserve">1.0300327539444</t>
   </si>
   <si>
     <t xml:space="preserve">1.0427325963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334845066071</t>
+    <t xml:space="preserve">1.02334856987</t>
   </si>
   <si>
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0561009645462</t>
+    <t xml:space="preserve">1.06412196159363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05610084533691</t>
   </si>
   <si>
     <t xml:space="preserve">1.05810618400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08484315872192</t>
+    <t xml:space="preserve">1.08484303951263</t>
   </si>
   <si>
     <t xml:space="preserve">1.07080626487732</t>
@@ -698,100 +698,100 @@
     <t xml:space="preserve">1.0688009262085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07815897464752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08283793926239</t>
+    <t xml:space="preserve">1.07815885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08283758163452</t>
   </si>
   <si>
     <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09620606899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754288196564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628483772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978452682495</t>
+    <t xml:space="preserve">1.0962061882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09954822063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754312038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628495693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978464603424</t>
   </si>
   <si>
     <t xml:space="preserve">1.22120034694672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22988963127136</t>
+    <t xml:space="preserve">1.22988986968994</t>
   </si>
   <si>
     <t xml:space="preserve">1.24058449268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26665282249451</t>
+    <t xml:space="preserve">1.26665270328522</t>
   </si>
   <si>
     <t xml:space="preserve">1.28002119064331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28336322307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29405808448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133178710938</t>
+    <t xml:space="preserve">1.28336334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29405796527863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133166790009</t>
   </si>
   <si>
     <t xml:space="preserve">1.26932656764984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30074238777161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009995937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475270748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007386207581</t>
+    <t xml:space="preserve">1.30074214935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31010007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007374286652</t>
   </si>
   <si>
     <t xml:space="preserve">1.3114367723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29004740715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28871071338654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29739999771118</t>
+    <t xml:space="preserve">1.29004752635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28871059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2720000743866</t>
+    <t xml:space="preserve">1.27200019359589</t>
   </si>
   <si>
     <t xml:space="preserve">1.2593001127243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29673159122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806852340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31076812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29338943958282</t>
+    <t xml:space="preserve">1.29673171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2980682849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31076836585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29338955879211</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814729213715</t>
@@ -800,22 +800,22 @@
     <t xml:space="preserve">1.30341589450836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33683657646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349478244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35421562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37025773525238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426805496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36491012573242</t>
+    <t xml:space="preserve">1.33683669567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35421550273895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3702574968338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426817417145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.364910364151</t>
   </si>
   <si>
     <t xml:space="preserve">1.37961542606354</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">1.34886825084686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39031004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41036260128021</t>
+    <t xml:space="preserve">1.3903101682663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036283969879</t>
   </si>
   <si>
     <t xml:space="preserve">1.42105734348297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175196647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4504679441452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39966809749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303658485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442559242249</t>
+    <t xml:space="preserve">1.43175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046782493591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303670406342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442583084106</t>
   </si>
   <si>
     <t xml:space="preserve">1.4170469045639</t>
@@ -860,34 +860,34 @@
     <t xml:space="preserve">1.40902590751648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43977344036102</t>
+    <t xml:space="preserve">1.43977308273315</t>
   </si>
   <si>
     <t xml:space="preserve">1.44779407978058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052049636841</t>
+    <t xml:space="preserve">1.4705206155777</t>
   </si>
   <si>
     <t xml:space="preserve">1.46784687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46116268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319400310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249938011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46650981903076</t>
+    <t xml:space="preserve">1.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249949932098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650993824005</t>
   </si>
   <si>
     <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48336613178253</t>
+    <t xml:space="preserve">1.48336637020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024653434753</t>
@@ -899,64 +899,64 @@
     <t xml:space="preserve">1.4228208065033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44208538532257</t>
+    <t xml:space="preserve">1.44208526611328</t>
   </si>
   <si>
     <t xml:space="preserve">1.40630829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3953001499176</t>
+    <t xml:space="preserve">1.39530003070831</t>
   </si>
   <si>
     <t xml:space="preserve">1.39942824840546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40080416202545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40218043327332</t>
+    <t xml:space="preserve">1.40080440044403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40218007564545</t>
   </si>
   <si>
     <t xml:space="preserve">1.38429176807404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4145644903183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42144477367401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43658113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43245315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42419672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.431077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44483733177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45997369289398</t>
+    <t xml:space="preserve">1.41456460952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42144465446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43658125400543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43245303630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42419683933258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43107688426971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483721256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45997357368469</t>
   </si>
   <si>
     <t xml:space="preserve">1.44621336460114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46685397624969</t>
+    <t xml:space="preserve">1.46685385704041</t>
   </si>
   <si>
     <t xml:space="preserve">1.48199033737183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46960580348969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758951663971</t>
+    <t xml:space="preserve">1.46960592269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758939743042</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923827171326</t>
@@ -965,37 +965,37 @@
     <t xml:space="preserve">1.50400698184967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50125479698181</t>
+    <t xml:space="preserve">1.50125467777252</t>
   </si>
   <si>
     <t xml:space="preserve">1.49987876415253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50675892829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602338790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54804003238678</t>
+    <t xml:space="preserve">1.50675904750824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602350711823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54803991317749</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52327120304108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189517021179</t>
+    <t xml:space="preserve">1.52327144145966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189528942108</t>
   </si>
   <si>
     <t xml:space="preserve">1.54528796672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968890666962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831263542175</t>
+    <t xml:space="preserve">1.57968878746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831275463104</t>
   </si>
   <si>
     <t xml:space="preserve">1.57556080818176</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">1.5631765127182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54666376113892</t>
+    <t xml:space="preserve">1.54666388034821</t>
   </si>
   <si>
     <t xml:space="preserve">1.55354416370392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56592857837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381700515747</t>
+    <t xml:space="preserve">1.56592833995819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381712436676</t>
   </si>
   <si>
     <t xml:space="preserve">1.5906970500946</t>
@@ -1025,91 +1025,91 @@
     <t xml:space="preserve">1.58656907081604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58244073390961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60996162891388</t>
+    <t xml:space="preserve">1.5824408531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60996150970459</t>
   </si>
   <si>
     <t xml:space="preserve">1.63197815418243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711463451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408972740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583341121674</t>
+    <t xml:space="preserve">1.64711475372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583364963531</t>
   </si>
   <si>
     <t xml:space="preserve">1.60032939910889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56455218791962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978359699249</t>
+    <t xml:space="preserve">1.5645524263382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978383541107</t>
   </si>
   <si>
     <t xml:space="preserve">1.53565573692322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54391181468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180059909821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042420864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427958488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005667686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868028640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234592437744</t>
+    <t xml:space="preserve">1.54391193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180024147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427994251251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005655765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234604358673</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684167385101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62922608852386</t>
+    <t xml:space="preserve">1.62922596931458</t>
   </si>
   <si>
     <t xml:space="preserve">1.61133778095245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59482514858246</t>
+    <t xml:space="preserve">1.59482550621033</t>
   </si>
   <si>
     <t xml:space="preserve">1.5728086233139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6182177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6250981092453</t>
+    <t xml:space="preserve">1.61821782588959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509799003601</t>
   </si>
   <si>
     <t xml:space="preserve">1.6608749628067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66637885570526</t>
+    <t xml:space="preserve">1.66637909412384</t>
   </si>
   <si>
     <t xml:space="preserve">1.69940400123596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70353221893311</t>
+    <t xml:space="preserve">1.70353209972382</t>
   </si>
   <si>
     <t xml:space="preserve">1.69802784919739</t>
@@ -1127,61 +1127,61 @@
     <t xml:space="preserve">1.64986670017242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62785005569458</t>
+    <t xml:space="preserve">1.62784993648529</t>
   </si>
   <si>
     <t xml:space="preserve">1.6622508764267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67601144313812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490801334381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105299472809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004437446594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518097400665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7668297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233409881592</t>
+    <t xml:space="preserve">1.67601132392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490825176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74894142150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105275630951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004449367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830080986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618947505951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76682949066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233362197876</t>
   </si>
   <si>
     <t xml:space="preserve">1.76545381546021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77371001243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7406849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8204950094223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022240638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747045993805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444531440735</t>
+    <t xml:space="preserve">1.77370989322662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74068510532379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049489021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022228717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747010231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444555282593</t>
   </si>
   <si>
     <t xml:space="preserve">1.79159832000732</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">1.79297423362732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7682056427002</t>
+    <t xml:space="preserve">1.76820552349091</t>
   </si>
   <si>
     <t xml:space="preserve">1.75857353210449</t>
@@ -1199,106 +1199,106 @@
     <t xml:space="preserve">1.72554838657379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72967648506165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142040729523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169324874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535864830017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031733512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481308460236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700740337372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85352003574371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86039996147156</t>
+    <t xml:space="preserve">1.7296769618988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142064571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169336795807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499075889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535852909088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481332302094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921414375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700716495514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85351991653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86040043830872</t>
   </si>
   <si>
     <t xml:space="preserve">1.88516879081726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85076785087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123054981232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710257053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79572629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737505435944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564355373383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573848247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473033905029</t>
+    <t xml:space="preserve">1.85076797008514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361472606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710245132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572653770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82737517356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564367294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6457382440567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738735675812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.634730219841</t>
   </si>
   <si>
     <t xml:space="preserve">1.68151557445526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6691312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6801393032074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298665523529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500306129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68701934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114768505096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335454463959</t>
+    <t xml:space="preserve">1.66913139820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68013954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.642986536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500294208527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701958656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
   </si>
   <si>
     <t xml:space="preserve">1.67463552951813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215582847595</t>
+    <t xml:space="preserve">1.71454048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215594768524</t>
   </si>
   <si>
     <t xml:space="preserve">1.69527590274811</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">1.68426764011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67876350879669</t>
+    <t xml:space="preserve">1.67876327037811</t>
   </si>
   <si>
     <t xml:space="preserve">1.65261876583099</t>
@@ -1316,49 +1316,49 @@
     <t xml:space="preserve">1.75306928157806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74756503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7241724729538</t>
+    <t xml:space="preserve">1.74756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930895328522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417283058167</t>
   </si>
   <si>
     <t xml:space="preserve">1.72692477703094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66362690925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289172649384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316421031952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343693256378</t>
+    <t xml:space="preserve">1.66362714767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289148807526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7131644487381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343705177307</t>
   </si>
   <si>
     <t xml:space="preserve">1.73380470275879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74206113815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994944572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178805828094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839550018311</t>
+    <t xml:space="preserve">1.74206125736237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178829669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839573860168</t>
   </si>
   <si>
     <t xml:space="preserve">1.65399467945099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64849054813385</t>
+    <t xml:space="preserve">1.64849042892456</t>
   </si>
   <si>
     <t xml:space="preserve">1.60720944404602</t>
@@ -1370,154 +1370,154 @@
     <t xml:space="preserve">1.59620118141174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53290355205536</t>
+    <t xml:space="preserve">1.53290331363678</t>
   </si>
   <si>
     <t xml:space="preserve">1.4929986000061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4503413438797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134972572327</t>
+    <t xml:space="preserve">1.45034146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134996414185</t>
   </si>
   <si>
     <t xml:space="preserve">1.4764860868454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48611855506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45722186565399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832493782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542124271393</t>
+    <t xml:space="preserve">1.48611843585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4751101732254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45722162723541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832481861115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776731014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079221725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542112350464</t>
   </si>
   <si>
     <t xml:space="preserve">1.56530702114105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54826188087463</t>
+    <t xml:space="preserve">1.54826211929321</t>
   </si>
   <si>
     <t xml:space="preserve">1.52411460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121662139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127373218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837598323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672763824463</t>
+    <t xml:space="preserve">1.5312168598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127397060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672751903534</t>
   </si>
   <si>
     <t xml:space="preserve">1.55536425113678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56246638298035</t>
+    <t xml:space="preserve">1.56246626377106</t>
   </si>
   <si>
     <t xml:space="preserve">1.59513604640961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60507893562317</t>
+    <t xml:space="preserve">1.60507881641388</t>
   </si>
   <si>
     <t xml:space="preserve">1.60934031009674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62212383747101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945429325104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57951128482819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223817825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60365855693817</t>
+    <t xml:space="preserve">1.62212371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5795111656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223805904388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60365843772888</t>
   </si>
   <si>
     <t xml:space="preserve">1.59371554851532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63632833957672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348722457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638533115387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076056957245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58803391456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59229516983032</t>
+    <t xml:space="preserve">1.63632810115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348734378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638545036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076045036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58803379535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59229528903961</t>
   </si>
   <si>
     <t xml:space="preserve">1.6888839006424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68178176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69882690906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013306617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729230880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757750511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894101142883</t>
+    <t xml:space="preserve">1.68178164958954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69882667064667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013318538666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729254722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911198616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757762432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894089221954</t>
   </si>
   <si>
     <t xml:space="preserve">1.67752063274384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67183899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343023300171</t>
+    <t xml:space="preserve">1.67183876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343047142029</t>
   </si>
   <si>
     <t xml:space="preserve">1.61928296089172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61786282062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57667064666748</t>
+    <t xml:space="preserve">1.61786293983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5766704082489</t>
   </si>
   <si>
     <t xml:space="preserve">1.56388664245605</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">1.5539436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5525233745575</t>
+    <t xml:space="preserve">1.55252325534821</t>
   </si>
   <si>
     <t xml:space="preserve">1.55110287666321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51701259613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559245586395</t>
+    <t xml:space="preserve">1.51701247692108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559233665466</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871829032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43462789058685</t>
+    <t xml:space="preserve">1.43462800979614</t>
   </si>
   <si>
     <t xml:space="preserve">1.44741189479828</t>
@@ -1556,43 +1556,43 @@
     <t xml:space="preserve">1.47155904769897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47013866901398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47297954559326</t>
+    <t xml:space="preserve">1.47013854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47297942638397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5326372385025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58377242088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973925113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275157928467</t>
+    <t xml:space="preserve">1.58377277851105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973937034607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275146007538</t>
   </si>
   <si>
     <t xml:space="preserve">1.4871838092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47724080085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144494533539</t>
+    <t xml:space="preserve">1.47724056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144506454468</t>
   </si>
   <si>
     <t xml:space="preserve">1.50138807296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996757507324</t>
+    <t xml:space="preserve">1.49996745586395</t>
   </si>
   <si>
     <t xml:space="preserve">1.49570631980896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41687273979187</t>
+    <t xml:space="preserve">1.41687285900116</t>
   </si>
   <si>
     <t xml:space="preserve">1.4218442440033</t>
@@ -1607,28 +1607,28 @@
     <t xml:space="preserve">1.37426006793976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35224342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994158267975</t>
+    <t xml:space="preserve">1.3522435426712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994170188904</t>
   </si>
   <si>
     <t xml:space="preserve">1.37070894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3657374382019</t>
+    <t xml:space="preserve">1.36573755741119</t>
   </si>
   <si>
     <t xml:space="preserve">1.37923145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37212955951691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35579442977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38633346557617</t>
+    <t xml:space="preserve">1.37212932109833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35579454898834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38633358478546</t>
   </si>
   <si>
     <t xml:space="preserve">1.3643171787262</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39130508899689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35863530635834</t>
+    <t xml:space="preserve">1.39130520820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35863542556763</t>
   </si>
   <si>
     <t xml:space="preserve">1.40906035900116</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">1.40124809741974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46019554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45309364795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439992427826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866117954254</t>
+    <t xml:space="preserve">1.46019566059113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45309352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439980506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866129875183</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593428611755</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39556646347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568044662476</t>
+    <t xml:space="preserve">1.39556634426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568056583405</t>
   </si>
   <si>
     <t xml:space="preserve">1.3870438337326</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">1.39201533794403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37781119346619</t>
+    <t xml:space="preserve">1.3778110742569</t>
   </si>
   <si>
     <t xml:space="preserve">1.40266859531403</t>
@@ -1694,31 +1694,31 @@
     <t xml:space="preserve">1.33519840240479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36076593399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940254688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320739269257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468512058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4204238653183</t>
+    <t xml:space="preserve">1.36076617240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940266609192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43178725242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320763111115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468523979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042374610901</t>
   </si>
   <si>
     <t xml:space="preserve">1.48150205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51985359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48860418796539</t>
+    <t xml:space="preserve">1.51985347270966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4886040687561</t>
   </si>
   <si>
     <t xml:space="preserve">1.49428594112396</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">1.54115998744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52553510665894</t>
+    <t xml:space="preserve">1.52553522586823</t>
   </si>
   <si>
     <t xml:space="preserve">1.5297966003418</t>
@@ -1739,25 +1739,25 @@
     <t xml:space="preserve">1.52695560455322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53405785560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51133096218109</t>
+    <t xml:space="preserve">1.53405773639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51133108139038</t>
   </si>
   <si>
     <t xml:space="preserve">1.50991034507751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48008155822754</t>
+    <t xml:space="preserve">1.48008179664612</t>
   </si>
   <si>
     <t xml:space="preserve">1.49854695796967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706970691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48292243480682</t>
+    <t xml:space="preserve">1.50706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48292255401611</t>
   </si>
   <si>
     <t xml:space="preserve">1.48434269428253</t>
@@ -1766,91 +1766,91 @@
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689873218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61644232273102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206708431244</t>
+    <t xml:space="preserve">1.53689849376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61644220352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780582904816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206696510315</t>
   </si>
   <si>
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496495246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939742088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62070345878601</t>
+    <t xml:space="preserve">1.62496483325958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939706325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62070369720459</t>
   </si>
   <si>
     <t xml:space="preserve">1.61502182483673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64627110958099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218106746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51417171955109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50422894954681</t>
+    <t xml:space="preserve">1.64627134799957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218094825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5141716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50422883033752</t>
   </si>
   <si>
     <t xml:space="preserve">1.48576331138611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46303653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45877516269684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49286532402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55678451061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57809066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58661341667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382953166962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916921615601</t>
+    <t xml:space="preserve">1.46303641796112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45877528190613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49286544322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5567843914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5780907869339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58661317825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57382965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916897773743</t>
   </si>
   <si>
     <t xml:space="preserve">1.70450854301453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70166766643524</t>
+    <t xml:space="preserve">1.70166754722595</t>
   </si>
   <si>
     <t xml:space="preserve">1.69172477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69061779975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69356298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69798123836517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294609546661</t>
+    <t xml:space="preserve">1.6906179189682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69356310367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69798111915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294585704803</t>
   </si>
   <si>
     <t xml:space="preserve">1.68325448036194</t>
@@ -1859,31 +1859,31 @@
     <t xml:space="preserve">1.68619990348816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72890710830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75099694728851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277840137482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74510610103607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73332536220551</t>
+    <t xml:space="preserve">1.72890686988831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7509970664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277852058411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74510633945465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73332524299622</t>
   </si>
   <si>
     <t xml:space="preserve">1.77161431312561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77750504016876</t>
+    <t xml:space="preserve">1.77750515937805</t>
   </si>
   <si>
     <t xml:space="preserve">1.79812204837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80106782913208</t>
+    <t xml:space="preserve">1.8010675907135</t>
   </si>
   <si>
     <t xml:space="preserve">1.80548548698425</t>
@@ -1895,121 +1895,121 @@
     <t xml:space="preserve">1.8113762140274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77455973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603232860565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76719653606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216091632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239901542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73921585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7701416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486835956573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928625583649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664981365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79517686367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370427131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78339552879333</t>
+    <t xml:space="preserve">1.77455985546112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603220939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76719629764557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216103553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239925384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921573162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77014172077179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928637504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79517698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370439052582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78339540958405</t>
   </si>
   <si>
     <t xml:space="preserve">1.79959499835968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80254018306732</t>
+    <t xml:space="preserve">1.8025404214859</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78192293643951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493900299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8202121257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81873965263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168459892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966540336609</t>
+    <t xml:space="preserve">1.78192281723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493876457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021200656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81873953342438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82168483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966552257538</t>
   </si>
   <si>
     <t xml:space="preserve">1.84819293022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82904815673828</t>
+    <t xml:space="preserve">1.82904827594757</t>
   </si>
   <si>
     <t xml:space="preserve">1.76425087451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81432151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990374088287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199334144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144709587097</t>
+    <t xml:space="preserve">1.81432163715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.809903383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83199346065521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144685745239</t>
   </si>
   <si>
     <t xml:space="preserve">1.91593539714813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655264377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213474750519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127952098846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042381763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569717884064</t>
+    <t xml:space="preserve">1.93655276298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127928256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569741725922</t>
   </si>
   <si>
     <t xml:space="preserve">1.94244337081909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94980669021606</t>
+    <t xml:space="preserve">1.94980680942535</t>
   </si>
   <si>
     <t xml:space="preserve">1.9615877866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98809587955475</t>
+    <t xml:space="preserve">1.98809564113617</t>
   </si>
   <si>
     <t xml:space="preserve">1.99693191051483</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">2.00724053382874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98367786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987733364105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0057680606842</t>
+    <t xml:space="preserve">1.983677983284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987745285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576782226562</t>
   </si>
   <si>
     <t xml:space="preserve">1.98073256015778</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">1.9718964099884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97631478309631</t>
+    <t xml:space="preserve">1.97631454467773</t>
   </si>
   <si>
     <t xml:space="preserve">1.94391596317291</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">1.96895122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96600592136383</t>
+    <t xml:space="preserve">1.96600580215454</t>
   </si>
   <si>
     <t xml:space="preserve">1.97484183311462</t>
@@ -2051,91 +2051,91 @@
     <t xml:space="preserve">2.01754927635193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04847502708435</t>
+    <t xml:space="preserve">2.04847526550293</t>
   </si>
   <si>
     <t xml:space="preserve">2.02049446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04552984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03374814987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05436587333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02785801887512</t>
+    <t xml:space="preserve">2.04552960395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03374838829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05436611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02785754203796</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227567672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04111170768738</t>
+    <t xml:space="preserve">2.04111194610596</t>
   </si>
   <si>
     <t xml:space="preserve">2.03816628456116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01018595695496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00871300697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99251401424408</t>
+    <t xml:space="preserve">2.01018571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00871276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99251425266266</t>
   </si>
   <si>
     <t xml:space="preserve">2.02638530731201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07940101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467413902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07203769683838</t>
+    <t xml:space="preserve">2.07940077781677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467390060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0720374584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.06172895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03522109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614708900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676409721375</t>
+    <t xml:space="preserve">2.03522086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933049201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645535469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08676433563232</t>
   </si>
   <si>
     <t xml:space="preserve">2.02196717262268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05731081962585</t>
+    <t xml:space="preserve">2.05731129646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.07351016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00282263755798</t>
+    <t xml:space="preserve">2.04700255393982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0028223991394</t>
   </si>
   <si>
     <t xml:space="preserve">2.0131311416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01460409164429</t>
+    <t xml:space="preserve">2.01460385322571</t>
   </si>
   <si>
     <t xml:space="preserve">2.04258418083191</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">2.13683462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10885429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12652659416199</t>
+    <t xml:space="preserve">2.10885453224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12652611732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.17659664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457744598389</t>
+    <t xml:space="preserve">2.20457768440247</t>
   </si>
   <si>
     <t xml:space="preserve">2.19426870346069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24581217765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22519469261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21341323852539</t>
+    <t xml:space="preserve">2.2458119392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22519445419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21341347694397</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
@@ -2186,40 +2186,40 @@
     <t xml:space="preserve">2.21783137321472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20163202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20752263069153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17365145683289</t>
+    <t xml:space="preserve">2.20163226127625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20752286911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17365121841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.23255801200867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21930432319641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21635866165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20310473442078</t>
+    <t xml:space="preserve">2.21930408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21635890007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20310497283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.24728488922119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2870466709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201128959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25022959709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11474514007568</t>
+    <t xml:space="preserve">2.28704643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201152801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25022983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1147449016571</t>
   </si>
   <si>
     <t xml:space="preserve">2.11621761322021</t>
@@ -2228,25 +2228,25 @@
     <t xml:space="preserve">2.15303421020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13094425201416</t>
+    <t xml:space="preserve">2.13094449043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.0249125957489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08823680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10296368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9822051525116</t>
+    <t xml:space="preserve">2.08823704719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1029634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220527172089</t>
   </si>
   <si>
     <t xml:space="preserve">1.83641159534454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65380120277405</t>
+    <t xml:space="preserve">1.65380108356476</t>
   </si>
   <si>
     <t xml:space="preserve">1.63318395614624</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35190522670746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35043263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30330717563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36442279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32171547412872</t>
+    <t xml:space="preserve">1.35190510749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35043251514435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30330729484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36442291736603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3217157125473</t>
   </si>
   <si>
     <t xml:space="preserve">1.31508874893188</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">1.40565729141235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37767672538757</t>
+    <t xml:space="preserve">1.37767684459686</t>
   </si>
   <si>
     <t xml:space="preserve">1.49475347995758</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">1.58311343193054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65674638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477694272995</t>
+    <t xml:space="preserve">1.65674650669098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071461200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54776930809021</t>
   </si>
   <si>
     <t xml:space="preserve">1.53598809242249</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56102323532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55365991592407</t>
+    <t xml:space="preserve">1.56102335453033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55366015434265</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">1.54187881946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58164072036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60225808620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434816360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256670951843</t>
+    <t xml:space="preserve">1.58164060115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60225820541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434792518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256682872772</t>
   </si>
   <si>
     <t xml:space="preserve">1.61698460578918</t>
@@ -2348,22 +2348,22 @@
     <t xml:space="preserve">1.66705513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64349257946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520315170288</t>
+    <t xml:space="preserve">1.64349269866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520327091217</t>
   </si>
   <si>
     <t xml:space="preserve">1.57575011253357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.587531208992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5580780506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427740097046</t>
+    <t xml:space="preserve">1.58753132820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55807816982269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427752017975</t>
   </si>
   <si>
     <t xml:space="preserve">1.59047675132751</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">1.59784007072449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64201986789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558241844177</t>
+    <t xml:space="preserve">1.64201998710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558265686035</t>
   </si>
   <si>
     <t xml:space="preserve">1.6287659406662</t>
@@ -2384,34 +2384,34 @@
     <t xml:space="preserve">1.61109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67883622646332</t>
+    <t xml:space="preserve">1.6788364648819</t>
   </si>
   <si>
     <t xml:space="preserve">1.71859848499298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76572358608246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75836062431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7200710773468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70828974246979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907468318939</t>
+    <t xml:space="preserve">1.76572370529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75836026668549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72007119655609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7082896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6390745639801</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70534443855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7112352848053</t>
+    <t xml:space="preserve">1.70534455776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71123504638672</t>
   </si>
   <si>
     <t xml:space="preserve">1.77756810188293</t>
@@ -2420,49 +2420,49 @@
     <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71468591690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69781517982483</t>
+    <t xml:space="preserve">1.71468603610992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69781529903412</t>
   </si>
   <si>
     <t xml:space="preserve">1.71161866188049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71621954441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69168043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70548367500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72542178630829</t>
+    <t xml:space="preserve">1.71621966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69168031215668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70548379421234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72542190551758</t>
   </si>
   <si>
     <t xml:space="preserve">1.73462426662445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73769164085388</t>
+    <t xml:space="preserve">1.73769176006317</t>
   </si>
   <si>
     <t xml:space="preserve">1.73002302646637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68707931041718</t>
+    <t xml:space="preserve">1.6870790719986</t>
   </si>
   <si>
     <t xml:space="preserve">1.68554544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67327582836151</t>
+    <t xml:space="preserve">1.67327570915222</t>
   </si>
   <si>
     <t xml:space="preserve">1.65793871879578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65487134456635</t>
+    <t xml:space="preserve">1.65487146377563</t>
   </si>
   <si>
     <t xml:space="preserve">1.68401181697845</t>
@@ -2471,16 +2471,16 @@
     <t xml:space="preserve">1.70241630077362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72235453128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7070175409317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66867470741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64566910266876</t>
+    <t xml:space="preserve">1.72235441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70701742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6686749458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64566898345947</t>
   </si>
   <si>
     <t xml:space="preserve">1.65333759784698</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">1.63646686077118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64720296859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67020833492279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407346725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68247818946838</t>
+    <t xml:space="preserve">1.64720273017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67020845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407370567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68247807025909</t>
   </si>
   <si>
     <t xml:space="preserve">1.7284893989563</t>
@@ -2513,28 +2513,28 @@
     <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75609588623047</t>
+    <t xml:space="preserve">1.75609612464905</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088255405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72082078456879</t>
+    <t xml:space="preserve">1.70088267326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7208206653595</t>
   </si>
   <si>
     <t xml:space="preserve">1.69321405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68094432353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67174220085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69934892654419</t>
+    <t xml:space="preserve">1.68094444274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67174208164215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69934904575348</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778769493103</t>
@@ -2543,31 +2543,31 @@
     <t xml:space="preserve">1.69014656543732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71008479595184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861281871796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6518040895462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64873647689819</t>
+    <t xml:space="preserve">1.71008491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861269950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65180397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64873659610748</t>
   </si>
   <si>
     <t xml:space="preserve">1.62573087215424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61959600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59659039974213</t>
+    <t xml:space="preserve">1.61959612369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59659051895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505665302277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58738803863525</t>
+    <t xml:space="preserve">1.58738815784454</t>
   </si>
   <si>
     <t xml:space="preserve">1.57971954345703</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">1.54904544353485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55057919025421</t>
+    <t xml:space="preserve">1.5505793094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996662139893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48156249523163</t>
+    <t xml:space="preserve">1.48156237602234</t>
   </si>
   <si>
     <t xml:space="preserve">1.4961324930191</t>
@@ -2594,25 +2594,25 @@
     <t xml:space="preserve">1.50303423404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51990485191345</t>
+    <t xml:space="preserve">1.51990497112274</t>
   </si>
   <si>
     <t xml:space="preserve">1.5475115776062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56438255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53064107894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60425901412964</t>
+    <t xml:space="preserve">1.5643824338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5306408405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60425889492035</t>
   </si>
   <si>
     <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965789318085</t>
+    <t xml:space="preserve">1.59965777397156</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
@@ -2621,31 +2621,31 @@
     <t xml:space="preserve">1.614994764328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58125329017639</t>
+    <t xml:space="preserve">1.58125340938568</t>
   </si>
   <si>
     <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60272514820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66100609302521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74075889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069724559784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388815879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628131389618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186585903168</t>
+    <t xml:space="preserve">1.6027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66100597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74075901508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388803958893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186573982239</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
@@ -2657,22 +2657,22 @@
     <t xml:space="preserve">1.5889219045639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60886001586914</t>
+    <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
     <t xml:space="preserve">1.6103937625885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61346137523651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585441112518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63953423500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64260172843933</t>
+    <t xml:space="preserve">1.61346125602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585464954376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6395343542099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64260160923004</t>
   </si>
   <si>
     <t xml:space="preserve">1.63493299484253</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">1.66714107990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62266337871552</t>
+    <t xml:space="preserve">1.6226634979248</t>
   </si>
   <si>
     <t xml:space="preserve">1.555180311203</t>
@@ -2693,31 +2693,31 @@
     <t xml:space="preserve">1.55671393871307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56131505966187</t>
+    <t xml:space="preserve">1.56131517887115</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57051753997803</t>
+    <t xml:space="preserve">1.57051742076874</t>
   </si>
   <si>
     <t xml:space="preserve">1.55978143215179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58278691768646</t>
+    <t xml:space="preserve">1.58278703689575</t>
   </si>
   <si>
     <t xml:space="preserve">1.60732626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63339948654175</t>
+    <t xml:space="preserve">1.63339960575104</t>
   </si>
   <si>
     <t xml:space="preserve">1.62419724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61192750930786</t>
+    <t xml:space="preserve">1.61192739009857</t>
   </si>
   <si>
     <t xml:space="preserve">1.58432078361511</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">1.61806237697601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64106810092926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.665607213974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67480957508087</t>
+    <t xml:space="preserve">1.64106798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66560733318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67480945587158</t>
   </si>
   <si>
     <t xml:space="preserve">1.71775329113007</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">1.8174444437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8082423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670821666718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80364108085632</t>
+    <t xml:space="preserve">1.80824220180511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670845508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80364096164703</t>
   </si>
   <si>
     <t xml:space="preserve">1.79903984069824</t>
@@ -2762,19 +2762,19 @@
     <t xml:space="preserve">1.79290521144867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82051205635071</t>
+    <t xml:space="preserve">1.82051217556</t>
   </si>
   <si>
     <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79443883895874</t>
+    <t xml:space="preserve">1.79443871974945</t>
   </si>
   <si>
     <t xml:space="preserve">1.83278167247772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80977594852448</t>
+    <t xml:space="preserve">1.80977582931519</t>
   </si>
   <si>
     <t xml:space="preserve">1.82971394062042</t>
@@ -2783,52 +2783,52 @@
     <t xml:space="preserve">1.85885453224182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83891630172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818031311035</t>
+    <t xml:space="preserve">1.83891642093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818043231964</t>
   </si>
   <si>
     <t xml:space="preserve">1.86498939990997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85578715801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345589160919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965229034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8711245059967</t>
+    <t xml:space="preserve">1.8557870388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8634557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965217113495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87112426757812</t>
   </si>
   <si>
     <t xml:space="preserve">1.89566338062286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90179860591888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91866934299469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90026462078094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91100072860718</t>
+    <t xml:space="preserve">1.90179836750031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91866910457611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90026450157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100060939789</t>
   </si>
   <si>
     <t xml:space="preserve">1.94627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95394444465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9156014919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173683643341</t>
+    <t xml:space="preserve">1.95394468307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91560173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173659801483</t>
   </si>
   <si>
     <t xml:space="preserve">1.91713535785675</t>
@@ -2843,31 +2843,31 @@
     <t xml:space="preserve">1.96007943153381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382054805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621382236481</t>
+    <t xml:space="preserve">1.99382066726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621406078339</t>
   </si>
   <si>
     <t xml:space="preserve">2.00609040260315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00762438774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375889778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00915789604187</t>
+    <t xml:space="preserve">2.00762414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00915765762329</t>
   </si>
   <si>
     <t xml:space="preserve">1.95701217651367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95854544639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96928155422211</t>
+    <t xml:space="preserve">1.95854568481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96928179264069</t>
   </si>
   <si>
     <t xml:space="preserve">1.97848355770111</t>
@@ -2876,16 +2876,16 @@
     <t xml:space="preserve">2.00302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01069188117981</t>
+    <t xml:space="preserve">2.01069164276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.01836037635803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0290961265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0336971282959</t>
+    <t xml:space="preserve">2.02909636497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
     <t xml:space="preserve">2.01682662963867</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">1.99563086032867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97335135936737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97175967693329</t>
+    <t xml:space="preserve">1.97335112094879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.971759557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9224259853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.916060090065</t>
+    <t xml:space="preserve">1.92242586612701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92719995975494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971653938293</t>
+    <t xml:space="preserve">1.92720007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971677780151</t>
   </si>
   <si>
     <t xml:space="preserve">1.96061992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95743715763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539425849915</t>
+    <t xml:space="preserve">1.95743703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539413928986</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
@@ -2942,19 +2942,19 @@
     <t xml:space="preserve">1.98926520347595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857678890228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287767887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94788837432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449099063873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223323822021</t>
+    <t xml:space="preserve">1.96857690811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94788873195648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449122905731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223347663879</t>
   </si>
   <si>
     <t xml:space="preserve">2.01950216293335</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">2.06087875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04337334632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04814720153809</t>
+    <t xml:space="preserve">2.04337358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04814743995667</t>
   </si>
   <si>
     <t xml:space="preserve">2.02427625656128</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07997560501099</t>
+    <t xml:space="preserve">2.07997608184814</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10543823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13726663589478</t>
+    <t xml:space="preserve">2.10543847084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13726687431335</t>
   </si>
   <si>
     <t xml:space="preserve">2.14522385597229</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">2.20251441001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1706862449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15158939361572</t>
+    <t xml:space="preserve">2.17068600654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15158915519714</t>
   </si>
   <si>
     <t xml:space="preserve">2.12453532218933</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">2.10066413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08315873146057</t>
+    <t xml:space="preserve">2.08315849304199</t>
   </si>
   <si>
     <t xml:space="preserve">2.07042741775513</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">2.10862112045288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08952403068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0847499370575</t>
+    <t xml:space="preserve">2.089524269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08474969863892</t>
   </si>
   <si>
     <t xml:space="preserve">2.0879328250885</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">2.14840626716614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12135219573975</t>
+    <t xml:space="preserve">2.12135243415833</t>
   </si>
   <si>
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339545249939</t>
+    <t xml:space="preserve">2.11339569091797</t>
   </si>
   <si>
     <t xml:space="preserve">2.13249230384827</t>
@@ -3062,28 +3062,28 @@
     <t xml:space="preserve">2.14363241195679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04178190231323</t>
+    <t xml:space="preserve">2.04178166389465</t>
   </si>
   <si>
     <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09588980674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02586793899536</t>
+    <t xml:space="preserve">2.04019045829773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09589004516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02586770057678</t>
   </si>
   <si>
     <t xml:space="preserve">2.03064227104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98767364025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01154494285583</t>
+    <t xml:space="preserve">1.98767387866974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01154518127441</t>
   </si>
   <si>
     <t xml:space="preserve">2.15477204322815</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">2.18341755867004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18978309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023467063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16113781929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20569729804993</t>
+    <t xml:space="preserve">2.18978357315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16113805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20569753646851</t>
   </si>
   <si>
     <t xml:space="preserve">2.21842861175537</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">2.27412796020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2534396648407</t>
+    <t xml:space="preserve">2.25343990325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.29481649398804</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">2.27571940422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27890229225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2216112613678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23115992546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20092296600342</t>
+    <t xml:space="preserve">2.27890253067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22161149978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23115968704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.200923204422</t>
   </si>
   <si>
     <t xml:space="preserve">2.17546057701111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19296598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19774055480957</t>
+    <t xml:space="preserve">2.19296622276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
     <t xml:space="preserve">2.10384702682495</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">2.15954637527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12930965423584</t>
+    <t xml:space="preserve">2.12930989265442</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771821022034</t>
@@ -3170,112 +3170,112 @@
     <t xml:space="preserve">2.10702991485596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07520174980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07201886177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08634161949158</t>
+    <t xml:space="preserve">2.07520151138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07201862335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.086341381073</t>
   </si>
   <si>
     <t xml:space="preserve">2.14204096794128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09748101234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09907293319702</t>
+    <t xml:space="preserve">2.09748148918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
     <t xml:space="preserve">2.09111571311951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06883549690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.014728307724</t>
+    <t xml:space="preserve">2.06883573532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01472783088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97812557220459</t>
+    <t xml:space="preserve">1.9781254529953</t>
   </si>
   <si>
     <t xml:space="preserve">1.97016847133636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03700733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1197612285614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354163646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98130822181702</t>
+    <t xml:space="preserve">2.03700757026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11976099014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03541612625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98130834102631</t>
   </si>
   <si>
     <t xml:space="preserve">2.02109336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96380257606506</t>
+    <t xml:space="preserve">1.96380281448364</t>
   </si>
   <si>
     <t xml:space="preserve">1.91128599643707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89378094673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969491004944</t>
+    <t xml:space="preserve">1.8937805891037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969467163086</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00199675559998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90651154518127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945771217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8126186132431</t>
+    <t xml:space="preserve">2.0019965171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90651178359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945783138275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261873245239</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75532782077789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79033863544464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85558676719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83330690860748</t>
+    <t xml:space="preserve">1.7553277015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79033875465393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85558664798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8333066701889</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83171546459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534992694855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81102705001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82694125175476</t>
+    <t xml:space="preserve">1.83171534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534968852997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81102728843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82694137096405</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">1.88423204421997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83808088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240375995636</t>
+    <t xml:space="preserve">1.83808124065399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240387916565</t>
   </si>
   <si>
     <t xml:space="preserve">1.88104939460754</t>
@@ -3299,40 +3299,40 @@
     <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89537191390991</t>
+    <t xml:space="preserve">1.89537179470062</t>
   </si>
   <si>
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881398677826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01791071891785</t>
+    <t xml:space="preserve">1.99881374835968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01791095733643</t>
   </si>
   <si>
     <t xml:space="preserve">2.01313638687134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98289978504181</t>
+    <t xml:space="preserve">1.98289966583252</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035879611969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94311416149139</t>
+    <t xml:space="preserve">1.9431140422821</t>
   </si>
   <si>
     <t xml:space="preserve">1.93197441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95107126235962</t>
+    <t xml:space="preserve">1.95107138156891</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786650657654</t>
+    <t xml:space="preserve">1.87786638736725</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95266270637512</t>
+    <t xml:space="preserve">1.96221125125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
     <t xml:space="preserve">1.93038308620453</t>
@@ -3356,52 +3356,52 @@
     <t xml:space="preserve">1.90014612674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91765177249908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192430973053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285521507263</t>
+    <t xml:space="preserve">1.91765189170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91924297809601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285545349121</t>
   </si>
   <si>
     <t xml:space="preserve">1.71235942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64233732223511</t>
+    <t xml:space="preserve">1.6423374414444</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66143429279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65984296798706</t>
+    <t xml:space="preserve">1.66143441200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65984284877777</t>
   </si>
   <si>
     <t xml:space="preserve">1.69007992744446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711153507233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61687481403351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483179569244</t>
+    <t xml:space="preserve">1.64711165428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6168749332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483191490173</t>
   </si>
   <si>
     <t xml:space="preserve">1.65506863594055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70758533477783</t>
+    <t xml:space="preserve">1.70758521556854</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964453458786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68053126335144</t>
+    <t xml:space="preserve">1.68053138256073</t>
   </si>
   <si>
     <t xml:space="preserve">1.65825176239014</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">1.57788527011871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58504641056061</t>
+    <t xml:space="preserve">1.58504664897919</t>
   </si>
   <si>
     <t xml:space="preserve">1.58743381500244</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446175575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50266945362091</t>
+    <t xml:space="preserve">1.51446163654327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5026695728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
@@ -3482,25 +3482,25 @@
     <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47403120994568</t>
+    <t xml:space="preserve">1.47403109073639</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48498117923737</t>
+    <t xml:space="preserve">1.48498106002808</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171948432922</t>
+    <t xml:space="preserve">1.49171960353851</t>
   </si>
   <si>
     <t xml:space="preserve">1.46645045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4571852684021</t>
+    <t xml:space="preserve">1.45718514919281</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">1.3990660905838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36200475692749</t>
+    <t xml:space="preserve">1.3620046377182</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">1.34178960323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766669750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26177072525024</t>
+    <t xml:space="preserve">1.26766681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26177060604095</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144769668579</t>
+    <t xml:space="preserve">1.23144781589508</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">1.20365166664124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20533645153046</t>
+    <t xml:space="preserve">1.20533633232117</t>
   </si>
   <si>
     <t xml:space="preserve">1.175013422966</t>
@@ -3584,22 +3584,22 @@
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942148208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10594439506531</t>
+    <t xml:space="preserve">1.11942136287689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1059445142746</t>
   </si>
   <si>
     <t xml:space="preserve">1.14300584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16911721229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965551376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16490566730499</t>
+    <t xml:space="preserve">1.16911733150482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965539455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16490578651428</t>
   </si>
   <si>
     <t xml:space="preserve">1.13710963726044</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">1.11352527141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12700212001801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12279045581818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08151769638062</t>
+    <t xml:space="preserve">1.12700223922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12279057502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0815178155899</t>
   </si>
   <si>
     <t xml:space="preserve">1.10425996780396</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553284645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427872657776</t>
+    <t xml:space="preserve">1.14553272724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427884578705</t>
   </si>
   <si>
     <t xml:space="preserve">1.22470927238464</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829375743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24492466449738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25334775447845</t>
+    <t xml:space="preserve">1.24829387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24492454528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25334763526917</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818624019623</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3165203332901</t>
+    <t xml:space="preserve">1.31652045249939</t>
   </si>
   <si>
     <t xml:space="preserve">1.3299971818924</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3535817861557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32747030258179</t>
+    <t xml:space="preserve">1.35358166694641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32747042179108</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33589327335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31062424182892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29546284675598</t>
+    <t xml:space="preserve">1.33589339256287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31062436103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29546272754669</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135893821716</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23650169372559</t>
+    <t xml:space="preserve">1.2365015745163</t>
   </si>
   <si>
     <t xml:space="preserve">1.25503218173981</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039021015167</t>
+    <t xml:space="preserve">1.21039032936096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46560823917389</t>
+    <t xml:space="preserve">1.4656081199646</t>
   </si>
   <si>
     <t xml:space="preserve">1.4041200876236</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">1.43360066413879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44370818138123</t>
+    <t xml:space="preserve">1.44370830059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42265069484711</t>
+    <t xml:space="preserve">1.42265057563782</t>
   </si>
   <si>
     <t xml:space="preserve">1.44623517990112</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770445346832</t>
+    <t xml:space="preserve">1.42770457267761</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727390766144</t>
+    <t xml:space="preserve">1.38727378845215</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37716627120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431636333466</t>
+    <t xml:space="preserve">1.37716639041901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431648254395</t>
   </si>
   <si>
     <t xml:space="preserve">1.34515881538391</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230878829956</t>
+    <t xml:space="preserve">1.31230890750885</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">1.53888845443726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56668448448181</t>
+    <t xml:space="preserve">1.5666846036911</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
@@ -3911,28 +3911,28 @@
     <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61132657527924</t>
+    <t xml:space="preserve">1.61132669448853</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57426536083221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5852153301239</t>
+    <t xml:space="preserve">1.57426524162292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521521091461</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942675590515</t>
+    <t xml:space="preserve">1.58942663669586</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784972667694</t>
+    <t xml:space="preserve">1.59784960746765</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">1.64754557609558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65007257461548</t>
+    <t xml:space="preserve">1.65007269382477</t>
   </si>
   <si>
     <t xml:space="preserve">1.62396109104156</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">1.62227654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58774209022522</t>
+    <t xml:space="preserve">1.58774220943451</t>
   </si>
   <si>
     <t xml:space="preserve">1.62480342388153</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5776344537735</t>
+    <t xml:space="preserve">1.57763457298279</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353054523468</t>
+    <t xml:space="preserve">1.58353066444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.57089602947235</t>
@@ -5313,6 +5313,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.72399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69799995422363</t>
   </si>
 </sst>
 </file>
@@ -70599,7 +70602,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.69125</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>492505</v>
@@ -70620,6 +70623,32 @@
         <v>1766</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911342593</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>672385</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>2.73799991607666</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>2.69799995422363</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>2.73799991607666</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>2.69799995422363</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469474315643</t>
+    <t xml:space="preserve">0.933469414710999</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806130886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927027106285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92187362909317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901902556419373</t>
+    <t xml:space="preserve">0.923806250095367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92702716588974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873331069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901902735233307</t>
   </si>
   <si>
     <t xml:space="preserve">0.898037552833557</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">0.918652415275574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903835594654083</t>
+    <t xml:space="preserve">0.903835296630859</t>
   </si>
   <si>
     <t xml:space="preserve">0.880643606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863893926143646</t>
+    <t xml:space="preserve">0.863893985748291</t>
   </si>
   <si>
     <t xml:space="preserve">0.841346442699432</t>
@@ -83,70 +83,70 @@
     <t xml:space="preserve">0.836192727088928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856163442134857</t>
+    <t xml:space="preserve">0.856163382530212</t>
   </si>
   <si>
     <t xml:space="preserve">0.857451856136322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869692027568817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441648006439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489890575409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374149799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855519115924835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279004096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798899650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481200695038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825241029262543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432958126068</t>
+    <t xml:space="preserve">0.869691908359528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441588401794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344805240631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374269008636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279182910919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798840045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481081485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432898521423</t>
   </si>
   <si>
     <t xml:space="preserve">0.869047701358795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876778304576874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172251224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161923885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709586143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296741485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075527667999</t>
+    <t xml:space="preserve">0.876778423786163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92316198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671551704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142787456512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709526538849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296562671661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075646877289</t>
   </si>
   <si>
     <t xml:space="preserve">0.941199839115143</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">0.947642028331757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930892705917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412184238434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918007969856262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954084277153015</t>
+    <t xml:space="preserve">0.930892527103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412303447723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008148670197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95408433675766</t>
   </si>
   <si>
     <t xml:space="preserve">0.964391767978668</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.999179482460022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01270806789398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02881348133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01657330989838</t>
+    <t xml:space="preserve">1.01270794868469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02881336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01657319068909</t>
   </si>
   <si>
     <t xml:space="preserve">1.02365958690643</t>
@@ -194,73 +194,73 @@
     <t xml:space="preserve">1.00175619125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00497722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755405426025</t>
+    <t xml:space="preserve">1.00497734546661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755429267883</t>
   </si>
   <si>
     <t xml:space="preserve">1.02172708511353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464068889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237117290497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99982362985611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01141953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206362247467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01786184310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430379390717</t>
+    <t xml:space="preserve">1.01464056968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999823689460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01141941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206374168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01786172389984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430391311646</t>
   </si>
   <si>
     <t xml:space="preserve">1.01850569248199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02688074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203427791595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0249480009079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0172176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00562155246735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988871872425079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368905067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03525543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02816903591156</t>
+    <t xml:space="preserve">1.0268806219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203439712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02494812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01721739768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00562179088593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988871932029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368893146515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0352555513382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02816915512085</t>
   </si>
   <si>
     <t xml:space="preserve">1.04040920734406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03396725654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0294576883316</t>
+    <t xml:space="preserve">1.03396713733673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02945756912231</t>
   </si>
   <si>
     <t xml:space="preserve">1.03010177612305</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">1.01592910289764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992093145847321</t>
+    <t xml:space="preserve">0.992092907428741</t>
   </si>
   <si>
     <t xml:space="preserve">1.03332281112671</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">1.02108263969421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04942846298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295692920685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05715882778168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07326412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06231248378754</t>
+    <t xml:space="preserve">1.0494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519698143005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295669078827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05715894699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07326436042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06231272220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.04749572277069</t>
@@ -317,52 +317,52 @@
     <t xml:space="preserve">1.06811058521271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04620718955994</t>
+    <t xml:space="preserve">1.04620707035065</t>
   </si>
   <si>
     <t xml:space="preserve">0.977275967597961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968256890773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965036153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978564620018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232907295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517287254333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712161540985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964807510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701663017273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680606365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101467132568</t>
+    <t xml:space="preserve">0.968257009983063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965035915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564441204071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522625923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232966899872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517227649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907712042331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876964926719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701603412628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680785179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101645946503</t>
   </si>
   <si>
     <t xml:space="preserve">0.935117423534393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939127922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909049093723297</t>
+    <t xml:space="preserve">0.939127743244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048914909363</t>
   </si>
   <si>
     <t xml:space="preserve">0.903033196926117</t>
@@ -371,19 +371,19 @@
     <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925091028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775212287903</t>
+    <t xml:space="preserve">0.925090909004211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775271892548</t>
   </si>
   <si>
     <t xml:space="preserve">0.925759375095367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912391066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921080529689789</t>
+    <t xml:space="preserve">0.912391126155853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921080589294434</t>
   </si>
   <si>
     <t xml:space="preserve">0.927096247673035</t>
@@ -395,217 +395,217 @@
     <t xml:space="preserve">0.937122583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955838263034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527606964111</t>
+    <t xml:space="preserve">0.955838203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164637088776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527666568756</t>
   </si>
   <si>
     <t xml:space="preserve">0.965196073055267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982575058937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98391181230545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97254878282547</t>
+    <t xml:space="preserve">0.982574999332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98391193151474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972548842430115</t>
   </si>
   <si>
     <t xml:space="preserve">0.973217248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984580159187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987254083156586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995274722576141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259421825409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890934467316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827943325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950490951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485672473907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94113302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501271247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864539146423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917031764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927530288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01265382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02000641822815</t>
+    <t xml:space="preserve">0.984580338001251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253904342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995274841785431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989259243011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99260139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827764511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950491070747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485553264618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941133081912994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501330852509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864598751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985916972160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927649497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01265370845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02000653743744</t>
   </si>
   <si>
     <t xml:space="preserve">0.99193286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988590717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996611773967743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901254177094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967201471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98658549785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977896153926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885595798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943307876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401673793793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00864315032959</t>
+    <t xml:space="preserve">0.988590836524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996612012386322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901373386383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201411724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986585378646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97789603471756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943486690521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00864326953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.00262749195099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206809997559</t>
+    <t xml:space="preserve">0.969206690788269</t>
   </si>
   <si>
     <t xml:space="preserve">0.97522246837616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985248506069183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02936434745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05342733860016</t>
+    <t xml:space="preserve">0.985248744487762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936410903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05342745780945</t>
   </si>
   <si>
     <t xml:space="preserve">1.05543255805969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0761536359787</t>
+    <t xml:space="preserve">1.07615351676941</t>
   </si>
   <si>
     <t xml:space="preserve">1.08952212333679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09420073032379</t>
+    <t xml:space="preserve">1.09420084953308</t>
   </si>
   <si>
     <t xml:space="preserve">1.09687447547913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07013773918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08751678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07749032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06479036808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06278514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04741156101227</t>
+    <t xml:space="preserve">1.07013785839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08751666545868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09353220462799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07749044895172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06479048728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0627852678299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04741168022156</t>
   </si>
   <si>
     <t xml:space="preserve">1.06078004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06813263893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05209064483643</t>
+    <t xml:space="preserve">1.06813251972198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05209076404572</t>
   </si>
   <si>
     <t xml:space="preserve">0.957843601703644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953832924365997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480453014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935785710811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469894886017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738616466522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941801428794861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406784534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538224697113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869877815247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99460643529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9979487657547</t>
+    <t xml:space="preserve">0.953833043575287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480512619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93578577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780550956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727879524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738318443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941801607608795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869818210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569779872894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606673717499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948586940765</t>
   </si>
   <si>
     <t xml:space="preserve">1.01332223415375</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">1.01532757282257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01599586009979</t>
+    <t xml:space="preserve">1.01599597930908</t>
   </si>
   <si>
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203797340393</t>
+    <t xml:space="preserve">1.03203809261322</t>
   </si>
   <si>
     <t xml:space="preserve">1.04005897045135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04473793506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070116043091</t>
+    <t xml:space="preserve">1.04473769664764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03070104122162</t>
   </si>
   <si>
     <t xml:space="preserve">1.01733267307281</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">1.03604853153229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04874837398529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04941689968109</t>
+    <t xml:space="preserve">1.04874849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494167804718</t>
   </si>
   <si>
     <t xml:space="preserve">1.05275893211365</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">1.0500853061676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04072749614716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02468538284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0106486082077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530123710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0300327539444</t>
+    <t xml:space="preserve">1.04072737693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04607462882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02468526363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01064848899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530111789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03003263473511</t>
   </si>
   <si>
     <t xml:space="preserve">1.0427325963974</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">1.02334856987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05676937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06412184238434</t>
+    <t xml:space="preserve">1.05676925182343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06412196159363</t>
   </si>
   <si>
     <t xml:space="preserve">1.05610108375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810618400574</t>
+    <t xml:space="preserve">1.05810630321503</t>
   </si>
   <si>
     <t xml:space="preserve">1.08484303951263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07080626487732</t>
+    <t xml:space="preserve">1.07080614566803</t>
   </si>
   <si>
     <t xml:space="preserve">1.08216941356659</t>
@@ -698,34 +698,34 @@
     <t xml:space="preserve">1.06880104541779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07815873622894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08283770084381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08818519115448</t>
+    <t xml:space="preserve">1.07815885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0828378200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
     <t xml:space="preserve">1.09620606899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09954822063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754300117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628483772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978464603424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120034694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988986968994</t>
+    <t xml:space="preserve">1.09954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754288196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628495693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978488445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2212005853653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988963127136</t>
   </si>
   <si>
     <t xml:space="preserve">1.24058449268341</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">1.26665282249451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28002107143402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28336322307587</t>
+    <t xml:space="preserve">1.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28336346149445</t>
   </si>
   <si>
     <t xml:space="preserve">1.29405784606934</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">1.30074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31010007858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475270748138</t>
+    <t xml:space="preserve">1.31009995937347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475258827209</t>
   </si>
   <si>
     <t xml:space="preserve">1.30007386207581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3114367723465</t>
+    <t xml:space="preserve">1.31143689155579</t>
   </si>
   <si>
     <t xml:space="preserve">1.29004740715027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28871059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29740011692047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28937900066376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2720000743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2593001127243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29673171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806852340698</t>
+    <t xml:space="preserve">1.28871047496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29739987850189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28937911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27200019359589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25930023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29673159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806840419769</t>
   </si>
   <si>
     <t xml:space="preserve">1.31076836585999</t>
@@ -794,100 +794,100 @@
     <t xml:space="preserve">1.29338943958282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32814729213715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30341565608978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683669567108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35421562194824</t>
+    <t xml:space="preserve">1.32814717292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30341589450836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349478244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35421574115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.37025773525238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37426793575287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.364910364151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37961554527283</t>
+    <t xml:space="preserve">1.37426829338074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36491024494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37961542606354</t>
   </si>
   <si>
     <t xml:space="preserve">1.33616828918457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34886837005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39031004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4103627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42105722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175220489502</t>
+    <t xml:space="preserve">1.34886813163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39031028747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42105746269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175208568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.4504679441452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39966821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303670406342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442571163177</t>
+    <t xml:space="preserve">1.39966809749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303658485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442559242249</t>
   </si>
   <si>
     <t xml:space="preserve">1.4170469045639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42239439487457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40902590751648</t>
+    <t xml:space="preserve">1.42239427566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40902614593506</t>
   </si>
   <si>
     <t xml:space="preserve">1.43977332115173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44779419898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052037715912</t>
+    <t xml:space="preserve">1.44779407978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4705206155777</t>
   </si>
   <si>
     <t xml:space="preserve">1.46784675121307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46116268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249949932098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46650993824005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48474228382111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48336625099182</t>
+    <t xml:space="preserve">1.46116244792938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319400310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4624992609024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4847424030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48336613178253</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024653434753</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">1.47235798835754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4228208065033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44208526611328</t>
+    <t xml:space="preserve">1.42282092571259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44208514690399</t>
   </si>
   <si>
     <t xml:space="preserve">1.40630841255188</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">1.3953001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39942824840546</t>
+    <t xml:space="preserve">1.39942812919617</t>
   </si>
   <si>
     <t xml:space="preserve">1.40080428123474</t>
@@ -917,43 +917,43 @@
     <t xml:space="preserve">1.40218031406403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38429176807404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41456437110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42144465446472</t>
+    <t xml:space="preserve">1.38429164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4145644903183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42144477367401</t>
   </si>
   <si>
     <t xml:space="preserve">1.43658113479614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43245315551758</t>
+    <t xml:space="preserve">1.43245303630829</t>
   </si>
   <si>
     <t xml:space="preserve">1.424196600914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43107688426971</t>
+    <t xml:space="preserve">1.431077003479</t>
   </si>
   <si>
     <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45997381210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44621336460114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46685373783112</t>
+    <t xml:space="preserve">1.45997369289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44621324539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46685385704041</t>
   </si>
   <si>
     <t xml:space="preserve">1.48199045658112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4696056842804</t>
+    <t xml:space="preserve">1.46960580348969</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758939743042</t>
@@ -962,49 +962,49 @@
     <t xml:space="preserve">1.47923827171326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50400698184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125467777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50675892829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602326869965</t>
+    <t xml:space="preserve">1.50400686264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125479698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987876415253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50675904750824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602314949036</t>
   </si>
   <si>
     <t xml:space="preserve">1.54804003238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54115986824036</t>
+    <t xml:space="preserve">1.54115974903107</t>
   </si>
   <si>
     <t xml:space="preserve">1.52327144145966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52189540863037</t>
+    <t xml:space="preserve">1.52189528942108</t>
   </si>
   <si>
     <t xml:space="preserve">1.5452880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968878746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831251621246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556068897247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693660259247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5631765127182</t>
+    <t xml:space="preserve">1.57968902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831263542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556080818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56317639350891</t>
   </si>
   <si>
     <t xml:space="preserve">1.5466639995575</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">1.55354416370392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56592833995819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069716930389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656919002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58244097232819</t>
+    <t xml:space="preserve">1.56592845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381676673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069740772247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656907081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5824408531189</t>
   </si>
   <si>
     <t xml:space="preserve">1.60996150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63197815418243</t>
+    <t xml:space="preserve">1.63197827339172</t>
   </si>
   <si>
     <t xml:space="preserve">1.64711463451385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61408996582031</t>
+    <t xml:space="preserve">1.61408972740173</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583364963531</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">1.5645524263382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53978383541107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565561771393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391205310822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180024147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941594600677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427958488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005667686462</t>
+    <t xml:space="preserve">1.53978371620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53565573692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180047988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005655765533</t>
   </si>
   <si>
     <t xml:space="preserve">1.56868052482605</t>
@@ -1079,40 +1079,40 @@
     <t xml:space="preserve">1.62234580516815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61684155464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922596931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821782588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509799003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66087508201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637885570526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353209972382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802796840668</t>
+    <t xml:space="preserve">1.61684167385101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133754253387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482514858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5728086233139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6250981092453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6608749628067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940388202667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353221893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69802784919739</t>
   </si>
   <si>
     <t xml:space="preserve">1.69252395629883</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.64986681938171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62785029411316</t>
+    <t xml:space="preserve">1.62785017490387</t>
   </si>
   <si>
     <t xml:space="preserve">1.6622508764267</t>
@@ -1136,142 +1136,142 @@
     <t xml:space="preserve">1.67601156234741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70490801334381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7310528755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004473209381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76682960987091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233350276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370977401733</t>
+    <t xml:space="preserve">1.7049081325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74894118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105275630951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004461288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518061637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830069065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7668297290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545393466949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77370989322662</t>
   </si>
   <si>
     <t xml:space="preserve">1.7406849861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82049477100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022240638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747022151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444531440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159832000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79297471046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7682056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75857353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554850578308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967684268951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169348716736</t>
+    <t xml:space="preserve">1.82049489021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747010231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444555282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7915985584259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297435283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76820576190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75857329368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554862499237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967660427094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142064571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169324874878</t>
   </si>
   <si>
     <t xml:space="preserve">1.81499075889587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80535840988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031697750092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481332302094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113574028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85352003574371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86040008068085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516867160797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076797008514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79572629928589</t>
+    <t xml:space="preserve">1.80535852909088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481308460236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921414375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113585948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700740337372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85351991653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86039996147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516855239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076761245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361472606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123066902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710221290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572653770447</t>
   </si>
   <si>
     <t xml:space="preserve">1.82737529277802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68564355373383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738711833954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66913115978241</t>
+    <t xml:space="preserve">1.68564343452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573836326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738735675812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.634730219841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151557445526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691312789917</t>
   </si>
   <si>
     <t xml:space="preserve">1.68013942241669</t>
@@ -1280,70 +1280,70 @@
     <t xml:space="preserve">1.64298665523529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66500306129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68701946735382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114756584167</t>
+    <t xml:space="preserve">1.66500318050385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6870197057724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114768505096</t>
   </si>
   <si>
     <t xml:space="preserve">1.63335418701172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7145402431488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527590274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426740169525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876350879669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65261888504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306951999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930895328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417271137238</t>
+    <t xml:space="preserve">1.67463517189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215594768524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426752090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6787633895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65261876583099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306940078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930907249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7241724729538</t>
   </si>
   <si>
     <t xml:space="preserve">1.72692477703094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66362679004669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289160728455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343705177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380482196808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206125736237</t>
+    <t xml:space="preserve">1.66362702846527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316421031952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343717098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380470275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74206101894379</t>
   </si>
   <si>
     <t xml:space="preserve">1.75994956493378</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">1.65399479866028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64849054813385</t>
+    <t xml:space="preserve">1.64849042892456</t>
   </si>
   <si>
     <t xml:space="preserve">1.60720944404602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59757721424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620130062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290343284607</t>
+    <t xml:space="preserve">1.59757745265961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620118141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290355205536</t>
   </si>
   <si>
     <t xml:space="preserve">1.4929986000061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46135008335114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47648596763611</t>
+    <t xml:space="preserve">1.45034158229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134984493256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4764860868454</t>
   </si>
   <si>
     <t xml:space="preserve">1.48611831665039</t>
@@ -1391,67 +1391,67 @@
     <t xml:space="preserve">1.4751101732254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45722162723541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832481861115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776731014252</t>
+    <t xml:space="preserve">1.4572217464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832493782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776719093323</t>
   </si>
   <si>
     <t xml:space="preserve">1.55079209804535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54542100429535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530714035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54826211929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52411460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5312168598175</t>
+    <t xml:space="preserve">1.54542112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530702114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54826200008392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52411484718323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121674060822</t>
   </si>
   <si>
     <t xml:space="preserve">1.52127385139465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52837610244751</t>
+    <t xml:space="preserve">1.52837598323822</t>
   </si>
   <si>
     <t xml:space="preserve">1.56672751903534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5553640127182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513604640961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507905483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934031009674</t>
+    <t xml:space="preserve">1.55536413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5951361656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507893562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934042930603</t>
   </si>
   <si>
     <t xml:space="preserve">1.62212383747101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58945417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57951128482819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223805904388</t>
+    <t xml:space="preserve">1.58945429325104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951140403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223817825317</t>
   </si>
   <si>
     <t xml:space="preserve">1.60365843772888</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">1.63632822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63348758220673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638533115387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076045036316</t>
+    <t xml:space="preserve">1.63348746299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638545036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076056957245</t>
   </si>
   <si>
     <t xml:space="preserve">1.58803379535675</t>
@@ -1478,55 +1478,55 @@
     <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68888366222382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68178164958954</t>
+    <t xml:space="preserve">1.6888839006424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68178188800812</t>
   </si>
   <si>
     <t xml:space="preserve">1.69882690906525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72013318538666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729218959808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911198616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757762432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894089221954</t>
+    <t xml:space="preserve">1.72013306617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729242801666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911210536957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757750511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894113063812</t>
   </si>
   <si>
     <t xml:space="preserve">1.67752051353455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67183899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343047142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928308010101</t>
+    <t xml:space="preserve">1.67183887958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343023300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6192831993103</t>
   </si>
   <si>
     <t xml:space="preserve">1.61786270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57667016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388664245605</t>
+    <t xml:space="preserve">1.57667064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388640403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.55962538719177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55394375324249</t>
+    <t xml:space="preserve">1.5539436340332</t>
   </si>
   <si>
     <t xml:space="preserve">1.55252325534821</t>
@@ -1538,28 +1538,28 @@
     <t xml:space="preserve">1.51701247692108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559221744537</t>
+    <t xml:space="preserve">1.51559233665466</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871829032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43462812900543</t>
+    <t xml:space="preserve">1.43462800979614</t>
   </si>
   <si>
     <t xml:space="preserve">1.44741189479828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45735478401184</t>
+    <t xml:space="preserve">1.45735490322113</t>
   </si>
   <si>
     <t xml:space="preserve">1.47155904769897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4701384305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47297942638397</t>
+    <t xml:space="preserve">1.47013854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47297954559326</t>
   </si>
   <si>
     <t xml:space="preserve">1.5326372385025</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">1.58377254009247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53973948955536</t>
+    <t xml:space="preserve">1.53973937034607</t>
   </si>
   <si>
     <t xml:space="preserve">1.51275134086609</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">1.4871838092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47724068164825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144506454468</t>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
   </si>
   <si>
     <t xml:space="preserve">1.50138819217682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996745586395</t>
+    <t xml:space="preserve">1.49996757507324</t>
   </si>
   <si>
     <t xml:space="preserve">1.49570620059967</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">1.41687273979187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42184436321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911735057831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35224366188049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994170188904</t>
+    <t xml:space="preserve">1.4218442440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065183162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426006793976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3522435426712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994158267975</t>
   </si>
   <si>
     <t xml:space="preserve">1.37070894241333</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">1.3657374382019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37923157215118</t>
+    <t xml:space="preserve">1.37923145294189</t>
   </si>
   <si>
     <t xml:space="preserve">1.37212944030762</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">1.38633358478546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3643171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39343571662903</t>
+    <t xml:space="preserve">1.36431705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130508899689</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">1.35863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40906047821045</t>
+    <t xml:space="preserve">1.40906035900116</t>
   </si>
   <si>
     <t xml:space="preserve">1.40124809741974</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">1.46019554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45309364795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439992427826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866129875183</t>
+    <t xml:space="preserve">1.45309352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439980506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866117954254</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593440532684</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39556634426117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568056583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38704371452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201533794403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37781119346619</t>
+    <t xml:space="preserve">1.39556646347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3870438337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201521873474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37781131267548</t>
   </si>
   <si>
     <t xml:space="preserve">1.40266859531403</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">1.38136219978333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33519852161407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36076605319977</t>
+    <t xml:space="preserve">1.3351982831955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36076593399048</t>
   </si>
   <si>
     <t xml:space="preserve">1.34940254688263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320775032043</t>
+    <t xml:space="preserve">1.43178725242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
   </si>
   <si>
     <t xml:space="preserve">1.42468512058258</t>
@@ -1721,25 +1721,25 @@
     <t xml:space="preserve">1.4886040687561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49428582191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258012771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52553522586823</t>
+    <t xml:space="preserve">1.49428570270538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258024692535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.5297966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52695560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5340576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51133108139038</t>
+    <t xml:space="preserve">1.52695548534393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405773639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51133096218109</t>
   </si>
   <si>
     <t xml:space="preserve">1.5099104642868</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">1.49854707717896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706970691681</t>
+    <t xml:space="preserve">1.50706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.48292243480682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48434293270111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50564908981323</t>
+    <t xml:space="preserve">1.48434281349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50564920902252</t>
   </si>
   <si>
     <t xml:space="preserve">1.53689861297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61644208431244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780559062958</t>
+    <t xml:space="preserve">1.61644232273102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780570983887</t>
   </si>
   <si>
     <t xml:space="preserve">1.63206696510315</t>
@@ -1778,133 +1778,133 @@
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496507167816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5993971824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6207035779953</t>
+    <t xml:space="preserve">1.62496483325958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939730167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62070345878601</t>
   </si>
   <si>
     <t xml:space="preserve">1.61502182483673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64627122879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218082904816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5141716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50422871112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4857634305954</t>
+    <t xml:space="preserve">1.64627134799957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218106746674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51417171955109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50422883033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576331138611</t>
   </si>
   <si>
     <t xml:space="preserve">1.46303641796112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45877528190613</t>
+    <t xml:space="preserve">1.45877516269684</t>
   </si>
   <si>
     <t xml:space="preserve">1.49286544322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567843914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57809054851532</t>
+    <t xml:space="preserve">1.55678451061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57809066772461</t>
   </si>
   <si>
     <t xml:space="preserve">1.58661329746246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57382965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916921615601</t>
+    <t xml:space="preserve">1.57382953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916897773743</t>
   </si>
   <si>
     <t xml:space="preserve">1.70450866222382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70166754722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69061779975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69356286525726</t>
+    <t xml:space="preserve">1.70166778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69356310367584</t>
   </si>
   <si>
     <t xml:space="preserve">1.69798123836517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67294585704803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325471878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68619990348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7289069890976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7509970664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277852058411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74510622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73332524299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7716144323349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750515937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812216758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80106770992279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80548560619354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137645244598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455985546112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603220939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76719629764557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216091632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239901542664</t>
+    <t xml:space="preserve">1.67294597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325448036194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68620002269745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72890710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75099694728851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277828216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74510633945465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73332512378693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750504016876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812228679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8010675907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80548536777496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401289463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137609481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455973625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76719641685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216115474701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239913463593</t>
   </si>
   <si>
     <t xml:space="preserve">1.73921573162079</t>
@@ -1913,112 +1913,112 @@
     <t xml:space="preserve">1.77014148235321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78486859798431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928637504578</t>
+    <t xml:space="preserve">1.78486824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928625583649</t>
   </si>
   <si>
     <t xml:space="preserve">1.79664981365204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79517686367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370427131653</t>
+    <t xml:space="preserve">1.79517698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370403289795</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79959487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254018306732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308690547943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7819230556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493900299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021188735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81873941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168471813202</t>
+    <t xml:space="preserve">1.79959511756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254030227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308678627014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192293643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493888378143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8202121257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81873953342438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8216849565506</t>
   </si>
   <si>
     <t xml:space="preserve">1.84966552257538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84819281101227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82904827594757</t>
+    <t xml:space="preserve">1.84819269180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82904815673828</t>
   </si>
   <si>
     <t xml:space="preserve">1.76425099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81432151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199346065521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91593539714813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655276298523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213474750519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127964019775</t>
+    <t xml:space="preserve">1.81432163715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990350246429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319935798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91593515872955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655264377594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127952098846</t>
   </si>
   <si>
     <t xml:space="preserve">1.97042405605316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94244349002838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980657100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96158790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809599876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693167209625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00724077224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98367762565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987745285034</t>
+    <t xml:space="preserve">1.95569717884064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244337081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980645179749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158802509308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809587955475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693191051483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00724053382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98367810249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987709522247</t>
   </si>
   <si>
     <t xml:space="preserve">2.00576782226562</t>
@@ -2030,31 +2030,31 @@
     <t xml:space="preserve">1.9718964099884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97631466388702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94391596317291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96895110607147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600604057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484195232391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01754903793335</t>
+    <t xml:space="preserve">1.97631454467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94391620159149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96895122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600592136383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484183311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01754927635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04847502708435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02049422264099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04552984237671</t>
+    <t xml:space="preserve">2.02049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04552960395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.03374838829041</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">2.05436563491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02785801887512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227543830872</t>
+    <t xml:space="preserve">2.02785778045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227591514587</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111170768738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03816628456116</t>
+    <t xml:space="preserve">2.03816652297974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01018571853638</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">2.00871300697327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99251389503479</t>
+    <t xml:space="preserve">1.99251401424408</t>
   </si>
   <si>
     <t xml:space="preserve">2.02638506889343</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">2.06467437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0720374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06172871589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03522086143494</t>
+    <t xml:space="preserve">2.07203769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03522109985352</t>
   </si>
   <si>
     <t xml:space="preserve">2.02933049201965</t>
@@ -2108,31 +2108,31 @@
     <t xml:space="preserve">2.06614685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676409721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0219669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05731058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07351016998291</t>
+    <t xml:space="preserve">2.07645535469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0867645740509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02196717262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05731081962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07351040840149</t>
   </si>
   <si>
     <t xml:space="preserve">2.04700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00282287597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0131311416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01460385322571</t>
+    <t xml:space="preserve">2.0028223991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313090324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01460409164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.04258441925049</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">2.12652635574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17659711837769</t>
+    <t xml:space="preserve">2.17659687995911</t>
   </si>
   <si>
     <t xml:space="preserve">2.20457744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19426870346069</t>
+    <t xml:space="preserve">2.19426846504211</t>
   </si>
   <si>
     <t xml:space="preserve">2.2458119392395</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">2.22519469261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21341347694397</t>
+    <t xml:space="preserve">2.21341371536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
@@ -2183,34 +2183,34 @@
     <t xml:space="preserve">2.2178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20163226127625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20752263069153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17365145683289</t>
+    <t xml:space="preserve">2.20163202285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17365121841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.23255801200867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21930408477783</t>
+    <t xml:space="preserve">2.21930384635925</t>
   </si>
   <si>
     <t xml:space="preserve">2.21635890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20310473442078</t>
+    <t xml:space="preserve">2.20310497283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.24728465080261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28704643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201128959656</t>
+    <t xml:space="preserve">2.28704690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201105117798</t>
   </si>
   <si>
     <t xml:space="preserve">2.25023007392883</t>
@@ -2219,55 +2219,55 @@
     <t xml:space="preserve">2.1147449016571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11621785163879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15303421020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13094425201416</t>
+    <t xml:space="preserve">2.11621761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1530339717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13094401359558</t>
   </si>
   <si>
     <t xml:space="preserve">2.0249125957489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08823680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10296368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220539093018</t>
+    <t xml:space="preserve">2.08823704719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1029634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9822051525116</t>
   </si>
   <si>
     <t xml:space="preserve">1.83641147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65380120277405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63318395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3872492313385</t>
+    <t xml:space="preserve">1.65380132198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63318371772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724899291992</t>
   </si>
   <si>
     <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35190522670746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35043263435364</t>
+    <t xml:space="preserve">1.35190510749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35043239593506</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330729484558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36442303657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32171559333801</t>
+    <t xml:space="preserve">1.36442291736603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32171547412872</t>
   </si>
   <si>
     <t xml:space="preserve">1.31508851051331</t>
@@ -2276,139 +2276,139 @@
     <t xml:space="preserve">1.40565741062164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37767684459686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49475336074829</t>
+    <t xml:space="preserve">1.37767672538757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49475347995758</t>
   </si>
   <si>
     <t xml:space="preserve">1.50948023796082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58311355113983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674650669098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54776954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53598809242249</t>
+    <t xml:space="preserve">1.58311331272125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674662590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5477694272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5359879732132</t>
   </si>
   <si>
     <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56102335453033</t>
+    <t xml:space="preserve">1.56102323532104</t>
   </si>
   <si>
     <t xml:space="preserve">1.55366003513336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54924213886261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54187870025635</t>
+    <t xml:space="preserve">1.54924201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54187881946564</t>
   </si>
   <si>
     <t xml:space="preserve">1.58164072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60225796699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434804439545</t>
+    <t xml:space="preserve">1.60225808620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434792518616</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61698472499847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64643788337708</t>
+    <t xml:space="preserve">1.61698460578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287533283234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64643776416779</t>
   </si>
   <si>
     <t xml:space="preserve">1.65527379512787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67589104175568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66705524921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349246025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520315170288</t>
+    <t xml:space="preserve">1.67589116096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66705513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349257946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520339012146</t>
   </si>
   <si>
     <t xml:space="preserve">1.57575011253357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58753132820129</t>
+    <t xml:space="preserve">1.587531208992</t>
   </si>
   <si>
     <t xml:space="preserve">1.55807816982269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57427752017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047675132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784007072449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64201986789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62876570224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61109399795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67883634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7185982465744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76572358608246</t>
+    <t xml:space="preserve">1.57427740097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047663211823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59783983230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64201998710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558241844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6287659406662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61109387874603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6788364648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859848499298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76572382450104</t>
   </si>
   <si>
     <t xml:space="preserve">1.75836050510406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72007083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70828986167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907468318939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821945667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70534443855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71123516559601</t>
+    <t xml:space="preserve">1.7200710773468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821921825409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70534455776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71123504638672</t>
   </si>
   <si>
     <t xml:space="preserve">1.77756810188293</t>
@@ -2417,31 +2417,31 @@
     <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71468603610992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69781506061554</t>
+    <t xml:space="preserve">1.71468579769135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69781517982483</t>
   </si>
   <si>
     <t xml:space="preserve">1.7116185426712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71621954441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69168055057526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70548355579376</t>
+    <t xml:space="preserve">1.71621966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69168031215668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70548379421234</t>
   </si>
   <si>
     <t xml:space="preserve">1.72542202472687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73462414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73769176006317</t>
+    <t xml:space="preserve">1.73462402820587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73769187927246</t>
   </si>
   <si>
     <t xml:space="preserve">1.73002314567566</t>
@@ -2450,43 +2450,43 @@
     <t xml:space="preserve">1.68707931041718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68554532527924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327570915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6579384803772</t>
+    <t xml:space="preserve">1.68554544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327558994293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65793871879578</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487134456635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68401193618774</t>
+    <t xml:space="preserve">1.68401181697845</t>
   </si>
   <si>
     <t xml:space="preserve">1.70241641998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72235441207886</t>
+    <t xml:space="preserve">1.72235465049744</t>
   </si>
   <si>
     <t xml:space="preserve">1.70701742172241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66867470741272</t>
+    <t xml:space="preserve">1.66867482662201</t>
   </si>
   <si>
     <t xml:space="preserve">1.64566910266876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65333759784698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.656405210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62726449966431</t>
+    <t xml:space="preserve">1.6533374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65640509128571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6272646188736</t>
   </si>
   <si>
     <t xml:space="preserve">1.63646686077118</t>
@@ -2495,28 +2495,28 @@
     <t xml:space="preserve">1.64720284938812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67020833492279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407370567322</t>
+    <t xml:space="preserve">1.67020845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407346725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.68247818946838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7284893989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73615777492523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75609600543976</t>
+    <t xml:space="preserve">1.72848927974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73615789413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75609624385834</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695565223694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088255405426</t>
+    <t xml:space="preserve">1.70088243484497</t>
   </si>
   <si>
     <t xml:space="preserve">1.72082078456879</t>
@@ -2531,37 +2531,37 @@
     <t xml:space="preserve">1.67174220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69934892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787683010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69014668464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008479595184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65180385112762</t>
+    <t xml:space="preserve">1.6993488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6778769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69014656543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861269950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6518040895462</t>
   </si>
   <si>
     <t xml:space="preserve">1.64873647689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62573063373566</t>
+    <t xml:space="preserve">1.62573075294495</t>
   </si>
   <si>
     <t xml:space="preserve">1.61959612369537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59659039974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505665302277</t>
+    <t xml:space="preserve">1.59659051895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505677223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.58738803863525</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">1.57358479499817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54904556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55057919025421</t>
+    <t xml:space="preserve">1.54904544353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057907104492</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996674060822</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">1.49613237380981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50303435325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51990497112274</t>
+    <t xml:space="preserve">1.50303411483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51990485191345</t>
   </si>
   <si>
     <t xml:space="preserve">1.5475115776062</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53064107894897</t>
+    <t xml:space="preserve">1.53064095973969</t>
   </si>
   <si>
     <t xml:space="preserve">1.60425889492035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59198939800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59965789318085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60119163990021</t>
+    <t xml:space="preserve">1.59198927879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59965777397156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60119152069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.614994764328</t>
@@ -2621,34 +2621,34 @@
     <t xml:space="preserve">1.58125340938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57511842250824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6027250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66100609302521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74075889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388827800751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628131389618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6318656206131</t>
+    <t xml:space="preserve">1.57511830329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60272514820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66100585460663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74075901508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388803958893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186573982239</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63033175468445</t>
+    <t xml:space="preserve">1.63033187389374</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889219045639</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61039388179779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346125602722</t>
+    <t xml:space="preserve">1.6103937625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346113681793</t>
   </si>
   <si>
     <t xml:space="preserve">1.58585453033447</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">1.63953423500061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64260172843933</t>
+    <t xml:space="preserve">1.64260160923004</t>
   </si>
   <si>
     <t xml:space="preserve">1.63493311405182</t>
@@ -2678,31 +2678,31 @@
     <t xml:space="preserve">1.65947246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66714096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62266337871552</t>
+    <t xml:space="preserve">1.66714107990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6226634979248</t>
   </si>
   <si>
     <t xml:space="preserve">1.55518043041229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56131517887115</t>
+    <t xml:space="preserve">1.55671393871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56131529808044</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57051742076874</t>
+    <t xml:space="preserve">1.57051753997803</t>
   </si>
   <si>
     <t xml:space="preserve">1.5597813129425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58278679847717</t>
+    <t xml:space="preserve">1.58278703689575</t>
   </si>
   <si>
     <t xml:space="preserve">1.60732638835907</t>
@@ -2711,46 +2711,46 @@
     <t xml:space="preserve">1.63339936733246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419712543488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192739009857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58432066440582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61806237697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106810092926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66560733318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67480957508087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71775341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517470836639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81744420528412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824208259583</t>
+    <t xml:space="preserve">1.62419724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192750930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58432078361511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61806225776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.665607213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67480969429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71775352954865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75762975215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8174444437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80824196338654</t>
   </si>
   <si>
     <t xml:space="preserve">1.80670833587646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80364120006561</t>
+    <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
     <t xml:space="preserve">1.79903995990753</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">1.82051181793213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78063535690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79443871974945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83278143405914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80977559089661</t>
+    <t xml:space="preserve">1.78063547611237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79443883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83278155326843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8097757101059</t>
   </si>
   <si>
     <t xml:space="preserve">1.82971394062042</t>
@@ -2783,28 +2783,28 @@
     <t xml:space="preserve">1.83891654014587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82818043231964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498939990997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85578727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8634557723999</t>
+    <t xml:space="preserve">1.82818031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8557870388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86345565319061</t>
   </si>
   <si>
     <t xml:space="preserve">1.84965252876282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87112414836884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89566338062286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90179836750031</t>
+    <t xml:space="preserve">1.87112438678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89566349983215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90179824829102</t>
   </si>
   <si>
     <t xml:space="preserve">1.9186692237854</t>
@@ -2813,31 +2813,31 @@
     <t xml:space="preserve">1.90026462078094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100084781647</t>
+    <t xml:space="preserve">1.91100072860718</t>
   </si>
   <si>
     <t xml:space="preserve">1.94627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95394456386566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91560161113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173659801483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713535785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553996086121</t>
+    <t xml:space="preserve">1.95394468307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91560173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173647880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713559627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553984165192</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695004940033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9600795507431</t>
+    <t xml:space="preserve">1.96007895469666</t>
   </si>
   <si>
     <t xml:space="preserve">1.99382066726685</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">1.96621406078339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00609040260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762391090393</t>
+    <t xml:space="preserve">2.00609064102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762438774109</t>
   </si>
   <si>
     <t xml:space="preserve">2.01375913619995</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">1.95701193809509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95854556560516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9692816734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9784836769104</t>
+    <t xml:space="preserve">1.95854544639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96928155422211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97848379611969</t>
   </si>
   <si>
     <t xml:space="preserve">2.00302314758301</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">2.01069164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0290961265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03369736671448</t>
+    <t xml:space="preserve">2.01836037635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02909636497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0336971282959</t>
   </si>
   <si>
     <t xml:space="preserve">2.01682662963867</t>
@@ -2891,25 +2891,25 @@
     <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563086032867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335112094879</t>
+    <t xml:space="preserve">1.99563074111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9733510017395</t>
   </si>
   <si>
     <t xml:space="preserve">1.97175967693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94470584392548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92242574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91606056690216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91446888446808</t>
+    <t xml:space="preserve">1.94470596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9224259853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91606020927429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9144686460495</t>
   </si>
   <si>
     <t xml:space="preserve">1.90332901477814</t>
@@ -2918,22 +2918,22 @@
     <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92720019817352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971653938293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96061992645264</t>
+    <t xml:space="preserve">1.92720007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9797168970108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96062004566193</t>
   </si>
   <si>
     <t xml:space="preserve">1.95743691921234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96539402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97494268417358</t>
+    <t xml:space="preserve">1.96539413928986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.974942445755</t>
   </si>
   <si>
     <t xml:space="preserve">1.98926544189453</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">1.96857702732086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91287744045258</t>
+    <t xml:space="preserve">1.91287732124329</t>
   </si>
   <si>
     <t xml:space="preserve">1.94788861274719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449099063873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223347663879</t>
+    <t xml:space="preserve">1.98449110984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223323822021</t>
   </si>
   <si>
     <t xml:space="preserve">2.01950216293335</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.04814743995667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02427625656128</t>
+    <t xml:space="preserve">2.02427649497986</t>
   </si>
   <si>
     <t xml:space="preserve">2.06247019767761</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">2.10543847084045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13726663589478</t>
+    <t xml:space="preserve">2.13726687431335</t>
   </si>
   <si>
     <t xml:space="preserve">2.14522385597229</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">2.10066437721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08315849304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07042741775513</t>
+    <t xml:space="preserve">2.08315873146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07042717933655</t>
   </si>
   <si>
     <t xml:space="preserve">2.10862135887146</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.089524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08475017547607</t>
+    <t xml:space="preserve">2.0847499370575</t>
   </si>
   <si>
     <t xml:space="preserve">2.0879328250885</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">2.06565308570862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180377006531</t>
+    <t xml:space="preserve">2.11180400848389</t>
   </si>
   <si>
     <t xml:space="preserve">2.14840650558472</t>
@@ -3047,28 +3047,28 @@
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612652778625</t>
+    <t xml:space="preserve">2.11339521408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249230384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612676620483</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363241195679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04178190231323</t>
+    <t xml:space="preserve">2.04178214073181</t>
   </si>
   <si>
     <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09589004516602</t>
+    <t xml:space="preserve">2.04019045829773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.02586770057678</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">2.18978333473206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023467063904</t>
+    <t xml:space="preserve">2.18023490905762</t>
   </si>
   <si>
     <t xml:space="preserve">2.16113781929016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21842861175537</t>
+    <t xml:space="preserve">2.20569753646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21842885017395</t>
   </si>
   <si>
     <t xml:space="preserve">2.29163360595703</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">2.2534396648407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29481649398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23593401908875</t>
+    <t xml:space="preserve">2.29481673240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23593425750732</t>
   </si>
   <si>
     <t xml:space="preserve">2.25025701522827</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">2.27571964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27890229225159</t>
+    <t xml:space="preserve">2.27890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.22161149978638</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.17546033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19296622276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19774055480957</t>
+    <t xml:space="preserve">2.19296598434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
     <t xml:space="preserve">2.10384702682495</t>
@@ -3152,16 +3152,16 @@
     <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17386937141418</t>
+    <t xml:space="preserve">2.17386913299561</t>
   </si>
   <si>
     <t xml:space="preserve">2.15954637527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12930989265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12771821022034</t>
+    <t xml:space="preserve">2.12930965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12771797180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.10702967643738</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">2.07520151138306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07201910018921</t>
+    <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
     <t xml:space="preserve">2.086341381073</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">2.14204096794128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09748125076294</t>
+    <t xml:space="preserve">2.09748148918152</t>
   </si>
   <si>
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111571311951</t>
+    <t xml:space="preserve">2.09111547470093</t>
   </si>
   <si>
     <t xml:space="preserve">2.06883573532104</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97812533378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97016823291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0370078086853</t>
+    <t xml:space="preserve">1.97812557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97016835212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03700757026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.1197612285614</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130810260773</t>
+    <t xml:space="preserve">1.98130822181702</t>
   </si>
   <si>
     <t xml:space="preserve">2.02109360694885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96380281448364</t>
+    <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
     <t xml:space="preserve">1.91128611564636</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">1.89378070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90969467163086</t>
+    <t xml:space="preserve">1.90969479084015</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
@@ -3236,28 +3236,28 @@
     <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90651178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8126186132431</t>
+    <t xml:space="preserve">1.90651190280914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945783138275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261849403381</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75532758235931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79033863544464</t>
+    <t xml:space="preserve">1.7553277015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79033887386322</t>
   </si>
   <si>
     <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83330690860748</t>
+    <t xml:space="preserve">1.83330678939819</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922087192535</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">1.83171546459198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82534968852997</t>
+    <t xml:space="preserve">1.82534980773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
@@ -3278,31 +3278,31 @@
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444665908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423204421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8380811214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240387916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104927539825</t>
+    <t xml:space="preserve">1.84444689750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423216342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83808100223541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240375995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104939460754</t>
   </si>
   <si>
     <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96698534488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99881398677826</t>
+    <t xml:space="preserve">1.8953720331192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96698546409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99881386756897</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.0035879611969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94311416149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95107126235962</t>
+    <t xml:space="preserve">1.94311439990997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197453022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107114315033</t>
   </si>
   <si>
     <t xml:space="preserve">1.95425426959991</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">1.87786626815796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90173757076263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221137046814</t>
+    <t xml:space="preserve">1.90173768997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833994865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221125125885</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038308620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993163108826</t>
+    <t xml:space="preserve">1.93038320541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993151187897</t>
   </si>
   <si>
     <t xml:space="preserve">1.90014636516571</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">1.91765177249908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9192430973053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8428555727005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71235954761505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64233732223511</t>
+    <t xml:space="preserve">1.91924333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71235942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6423374414444</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">1.62483191490173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65506863594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70758521556854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6964453458786</t>
+    <t xml:space="preserve">1.65506875514984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70758533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69644546508789</t>
   </si>
   <si>
     <t xml:space="preserve">1.68053138256073</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">1.56435811519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58345520496368</t>
+    <t xml:space="preserve">1.58345508575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">1.4784220457077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025021076202</t>
+    <t xml:space="preserve">1.51025009155273</t>
   </si>
   <si>
     <t xml:space="preserve">1.53383481502533</t>
@@ -70654,7 +70654,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6912037037</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>2165317</v>
@@ -70675,6 +70675,32 @@
         <v>1767</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911111111</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>2592232</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>2.66799998283386</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>2.53600001335144</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>2.66400003433228</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>2.55800008773804</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1720</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -38,163 +38,163 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469295501709</t>
+    <t xml:space="preserve">0.933469235897064</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92702716588974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921873509883881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901902794837952</t>
+    <t xml:space="preserve">0.923806250095367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927027344703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873450279236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901902616024017</t>
   </si>
   <si>
     <t xml:space="preserve">0.898037612438202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918652355670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835356235504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643606185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893926143646</t>
+    <t xml:space="preserve">0.918652236461639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835415840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643546581268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893985748291</t>
   </si>
   <si>
     <t xml:space="preserve">0.841346502304077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851653873920441</t>
+    <t xml:space="preserve">0.851653933525085</t>
   </si>
   <si>
     <t xml:space="preserve">0.818154633045197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836192667484283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163382530212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869691967964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441588401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489890575409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344984054565</t>
+    <t xml:space="preserve">0.836192607879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163442134857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451736927032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691908359528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441469192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875490009784698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344864845276</t>
   </si>
   <si>
     <t xml:space="preserve">0.888374269008636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855519115924835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279123306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798899650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481141090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825240969657898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86904776096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778185367584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172310829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671551704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142906665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709586143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296681880951</t>
+    <t xml:space="preserve">0.85551917552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279182910919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481081485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825240850448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432838916779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869047820568085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923161804676056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671313285828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709466934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296741485596</t>
   </si>
   <si>
     <t xml:space="preserve">0.916075587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941199839115143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947642028331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892586708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412184238434</t>
+    <t xml:space="preserve">0.941199958324432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642087936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412124633789</t>
   </si>
   <si>
     <t xml:space="preserve">0.918008148670197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954084098339081</t>
+    <t xml:space="preserve">0.954084277153015</t>
   </si>
   <si>
     <t xml:space="preserve">0.964391708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999179422855377</t>
+    <t xml:space="preserve">0.999179482460022</t>
   </si>
   <si>
     <t xml:space="preserve">1.01270794868469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02881324291229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01657319068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365970611572</t>
+    <t xml:space="preserve">1.02881336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0165730714798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365958690643</t>
   </si>
   <si>
     <t xml:space="preserve">1.00819849967957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00175631046295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0049774646759</t>
+    <t xml:space="preserve">1.00175607204437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497722625732</t>
   </si>
   <si>
     <t xml:space="preserve">1.00755417346954</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">1.02172696590424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464056968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237105369568</t>
+    <t xml:space="preserve">1.0146404504776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237117290497</t>
   </si>
   <si>
     <t xml:space="preserve">0.999823689460754</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.01141953468323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01206374168396</t>
+    <t xml:space="preserve">1.01206386089325</t>
   </si>
   <si>
     <t xml:space="preserve">1.01786172389984</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">1.02430379390717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01850581169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02688086032867</t>
+    <t xml:space="preserve">1.01850593090057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02688097953796</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203439712524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02494823932648</t>
+    <t xml:space="preserve">1.02494812011719</t>
   </si>
   <si>
     <t xml:space="preserve">1.01721751689911</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">1.00562155246735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98887175321579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03525531291962</t>
+    <t xml:space="preserve">0.988871932029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368893146515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0352555513382</t>
   </si>
   <si>
     <t xml:space="preserve">1.02816915512085</t>
@@ -263,25 +263,25 @@
     <t xml:space="preserve">1.02945756912231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03010189533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01592910289764</t>
+    <t xml:space="preserve">1.03010165691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01592898368835</t>
   </si>
   <si>
     <t xml:space="preserve">0.992093026638031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.033322930336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00948679447174</t>
+    <t xml:space="preserve">1.03332304954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00948703289032</t>
   </si>
   <si>
     <t xml:space="preserve">0.995958387851715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995313942432404</t>
+    <t xml:space="preserve">0.995314121246338</t>
   </si>
   <si>
     <t xml:space="preserve">1.0210827589035</t>
@@ -293,157 +293,157 @@
     <t xml:space="preserve">1.07519698143005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06295657157898</t>
+    <t xml:space="preserve">1.06295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">1.05715894699097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07326424121857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06231272220612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04749572277069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06360101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0616682767868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06811058521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04620718955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977275967597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968257188796997</t>
+    <t xml:space="preserve">1.07326412200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06231260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0474956035614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.063600897789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06166839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06811046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04620730876923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977276146411896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968257129192352</t>
   </si>
   <si>
     <t xml:space="preserve">0.965036034584045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978564381599426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522625923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232966899872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517108440399</t>
+    <t xml:space="preserve">0.978564500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522387504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979233026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517287254333</t>
   </si>
   <si>
     <t xml:space="preserve">0.90771222114563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876964807510376</t>
+    <t xml:space="preserve">0.876964926719666</t>
   </si>
   <si>
     <t xml:space="preserve">0.903701543807983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895680546760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117423534393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127802848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048914909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033256530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915733218193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925091087818146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775331497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925759434700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912391006946564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921080470085144</t>
+    <t xml:space="preserve">0.895680665969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117304325104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127743244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048974514008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033137321472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915733098983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925090849399567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775271892548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925759375095367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912391126155853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921080529689789</t>
   </si>
   <si>
     <t xml:space="preserve">0.92709618806839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945143759250641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122523784637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95583838224411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527666568756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196311473846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982575178146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98391193151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972548842430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580338001251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987253904342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995274841785431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259302616119</t>
+    <t xml:space="preserve">0.945143520832062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838143825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164398670197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527726173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196013450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982575118541718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98391181230545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972548723220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580218791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253844738007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99527496099472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989259243011475</t>
   </si>
   <si>
     <t xml:space="preserve">0.99260139465332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97589099407196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827764511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950491011142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485672473907</t>
+    <t xml:space="preserve">0.975890755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827704906464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950490891933441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485732078552</t>
   </si>
   <si>
     <t xml:space="preserve">0.94113302230835</t>
@@ -452,118 +452,118 @@
     <t xml:space="preserve">0.954501330852509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965864658355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917031764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927470684052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01265370845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02000653743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99193274974823</t>
+    <t xml:space="preserve">0.965864598751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917150974274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01265382766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02000641822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932988166809</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996611714363098</t>
+    <t xml:space="preserve">0.996611893177032</t>
   </si>
   <si>
     <t xml:space="preserve">0.979901373386383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967201232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986585319042206</t>
+    <t xml:space="preserve">0.96720153093338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986585438251495</t>
   </si>
   <si>
     <t xml:space="preserve">0.977896094322205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973885595798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943486690521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401685714722</t>
+    <t xml:space="preserve">0.973885536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943367481232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401697635651</t>
   </si>
   <si>
     <t xml:space="preserve">1.00864326953888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00262761116028</t>
+    <t xml:space="preserve">1.00262749195099</t>
   </si>
   <si>
     <t xml:space="preserve">0.969206631183624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975222408771515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248625278473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02936434745789</t>
+    <t xml:space="preserve">0.975222229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248744487762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936410903931</t>
   </si>
   <si>
     <t xml:space="preserve">1.05342733860016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05543267726898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07615339756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0895220041275</t>
+    <t xml:space="preserve">1.05543255805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0761536359787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08952188491821</t>
   </si>
   <si>
     <t xml:space="preserve">1.09420096874237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09687459468842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0701379776001</t>
+    <t xml:space="preserve">1.09687447547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07013785839081</t>
   </si>
   <si>
     <t xml:space="preserve">1.08751666545868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09353244304657</t>
+    <t xml:space="preserve">1.09353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479060649872</t>
+    <t xml:space="preserve">1.06479048728943</t>
   </si>
   <si>
     <t xml:space="preserve">1.06278514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04741156101227</t>
+    <t xml:space="preserve">1.04741168022156</t>
   </si>
   <si>
     <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06813251972198</t>
+    <t xml:space="preserve">1.06813263893127</t>
   </si>
   <si>
     <t xml:space="preserve">1.05209052562714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957843422889709</t>
+    <t xml:space="preserve">0.957843542098999</t>
   </si>
   <si>
     <t xml:space="preserve">0.953833043575287</t>
@@ -572,52 +572,52 @@
     <t xml:space="preserve">0.946480393409729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93578577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469954490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780431747437</t>
+    <t xml:space="preserve">0.935785710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780491352081</t>
   </si>
   <si>
     <t xml:space="preserve">0.913727879524231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917738556861877</t>
+    <t xml:space="preserve">0.917738318443298</t>
   </si>
   <si>
     <t xml:space="preserve">0.94180154800415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918406784534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538165092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869639396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569779872894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99794864654541</t>
+    <t xml:space="preserve">0.918406844139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538224697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869818210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569660663605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606673717499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948706150055</t>
   </si>
   <si>
     <t xml:space="preserve">1.01332235336304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01532745361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01599586009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02869594097137</t>
+    <t xml:space="preserve">1.01532733440399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0159957408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203797340393</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">1.04005897045135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04473805427551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070116043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01733267307281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.036048412323</t>
+    <t xml:space="preserve">1.04473781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03070092201233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03604853153229</t>
   </si>
   <si>
     <t xml:space="preserve">1.04874849319458</t>
@@ -653,115 +653,115 @@
     <t xml:space="preserve">1.04072737693787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04607486724854</t>
+    <t xml:space="preserve">1.04607462882996</t>
   </si>
   <si>
     <t xml:space="preserve">1.02468538284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01064848899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530111789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0300327539444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04273271560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05676937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06412184238434</t>
+    <t xml:space="preserve">1.0106486082077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530123710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03003263473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0427325963974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02334868907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.056769490242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06412220001221</t>
   </si>
   <si>
     <t xml:space="preserve">1.05610108375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810630321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484303951263</t>
+    <t xml:space="preserve">1.05810618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484315872192</t>
   </si>
   <si>
     <t xml:space="preserve">1.07080626487732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0821692943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06880104541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07815897464752</t>
+    <t xml:space="preserve">1.08216941356659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0688009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07815885543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.08283770084381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08818519115448</t>
+    <t xml:space="preserve">1.0881849527359</t>
   </si>
   <si>
     <t xml:space="preserve">1.09620606899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09954822063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754288196564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628483772278</t>
+    <t xml:space="preserve">1.09954810142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754300117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628495693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.18978476524353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22120034694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988986968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24058437347412</t>
+    <t xml:space="preserve">1.22120022773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988975048065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24058449268341</t>
   </si>
   <si>
     <t xml:space="preserve">1.26665270328522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28002107143402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28336334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29405784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133166790009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932644844055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30074214935303</t>
+    <t xml:space="preserve">1.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28336322307587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29405796527863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932656764984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30074203014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.31009995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30475258827209</t>
+    <t xml:space="preserve">1.30475246906281</t>
   </si>
   <si>
     <t xml:space="preserve">1.30007386207581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31143689155579</t>
+    <t xml:space="preserve">1.31143665313721</t>
   </si>
   <si>
     <t xml:space="preserve">1.29004740715027</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28937900066376</t>
+    <t xml:space="preserve">1.28937888145447</t>
   </si>
   <si>
     <t xml:space="preserve">1.27200019359589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2593001127243</t>
+    <t xml:space="preserve">1.25930023193359</t>
   </si>
   <si>
     <t xml:space="preserve">1.29673171043396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29806840419769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31076848506927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29338943958282</t>
+    <t xml:space="preserve">1.29806852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31076836585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2933896780014</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814729213715</t>
@@ -815,109 +815,109 @@
     <t xml:space="preserve">1.37426817417145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36491024494171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37961530685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33616840839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34886801242828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3903101682663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41036260128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42105722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45046806335449</t>
+    <t xml:space="preserve">1.364910364151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37961542606354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33616828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34886825084686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39031004905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4103627204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42105734348297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175208568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046782493591</t>
   </si>
   <si>
     <t xml:space="preserve">1.39966809749603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41303646564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442571163177</t>
+    <t xml:space="preserve">1.41303658485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442559242249</t>
   </si>
   <si>
     <t xml:space="preserve">1.4170469045639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42239439487457</t>
+    <t xml:space="preserve">1.42239427566528</t>
   </si>
   <si>
     <t xml:space="preserve">1.40902590751648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43977320194244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44779419898987</t>
+    <t xml:space="preserve">1.43977332115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44779407978058</t>
   </si>
   <si>
     <t xml:space="preserve">1.4705206155777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46784710884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319400310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249949932098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46651005744934</t>
+    <t xml:space="preserve">1.46784687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319388389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249938011169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650993824005</t>
   </si>
   <si>
     <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48336637020111</t>
+    <t xml:space="preserve">1.48336613178253</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47235822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42282092571259</t>
+    <t xml:space="preserve">1.47235810756683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4228208065033</t>
   </si>
   <si>
     <t xml:space="preserve">1.44208526611328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40630829334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39530003070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39942824840546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40080416202545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40218031406403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38429176807404</t>
+    <t xml:space="preserve">1.4063081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3953001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39942812919617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40080428123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40218007564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38429188728333</t>
   </si>
   <si>
     <t xml:space="preserve">1.41456460952759</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">1.43245303630829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42419683933258</t>
+    <t xml:space="preserve">1.42419672012329</t>
   </si>
   <si>
     <t xml:space="preserve">1.431077003479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483733177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45997357368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44621336460114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46685373783112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48199033737183</t>
+    <t xml:space="preserve">1.44483721256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45997369289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44621348381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46685385704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48199045658112</t>
   </si>
   <si>
     <t xml:space="preserve">1.46960592269897</t>
@@ -959,784 +959,784 @@
     <t xml:space="preserve">1.44758951663971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47923815250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125479698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987876415253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50675904750824</t>
+    <t xml:space="preserve">1.47923827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5012549161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50675892829895</t>
   </si>
   <si>
     <t xml:space="preserve">1.52602350711823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54804003238678</t>
+    <t xml:space="preserve">1.54803991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115998744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52327144145966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189517021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54528796672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57968878746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831275463104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556068897247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693684101105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5631765127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54666388034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55354392528534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592857837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381688594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656895160675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5824408531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60996162891388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63197815418243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711439609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408960819244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583364963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032951831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455254554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978383541107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5356559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180024147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427970409393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868064403534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234604358673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61684155464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482550621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57280874252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6182177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509787082672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6608749628067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940388202667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353198051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6980277299881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023435115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949892997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986658096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62784993648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6622508764267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601132392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490777492523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7489413022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105275630951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004437446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518073558807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830092906952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618947505951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7668297290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233374118805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545345783234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7737101316452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74068474769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049489021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444543361664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7929744720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76820552349091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7585734128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554862499237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967660427094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142052650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499087810516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031721591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481320381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85351991653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86039984226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516879081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076785087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8012307882309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710257053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82737505435944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564367294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573836326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738735675812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151533603668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66913115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68013942241669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64298617839813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500329971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701946735382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114768505096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454060077667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426752090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876350879669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6526186466217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306928157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930907249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417271137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692453861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362690925598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289160728455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343717098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380470275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74206137657166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994956493378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6883956193924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399491786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849030971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720956325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757733345032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620141983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290379047394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49299848079681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134984493256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4764860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611843585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45722162723541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832493782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776731014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530702114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54826211929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52411472797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121674060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127397060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837598323822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672751903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5553640127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246626377106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513592720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507905483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934019088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62212407588959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5795111656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223793983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60365831851959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371554851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63632810115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348734378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076056957245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58803391456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59229505062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68888413906097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68178176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69882667064667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013318538666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729230880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911198616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757750511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894101142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752051353455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183899879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343011379242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6192831993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61786282062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667028903961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388676166534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962538719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55394375324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5525233745575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55110275745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51701247692108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559233665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871829032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43462812900543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44741177558899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45735490322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47155916690826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47013854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47297942638397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53263735771179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58377254009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973937034607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275146007538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48718392848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138819217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49996745586395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49570620059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41687273979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4218442440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426006793976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3522435426712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994170188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37070894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3657374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37923157215118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37212944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35579454898834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38633358478546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36431705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39343571662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130520820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35863530635834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40906047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40124809741974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46019577980042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45309364795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439992427826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866117954254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593440532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894637584686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.440309882164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39556658267975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568056583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38704371452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201533794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37781119346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40266847610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38136231899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33519840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36076605319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940254688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43178713321686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468523979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4204238653183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48150193691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4886040687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428594112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258012771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115974903107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52327156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5218950510025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54528784751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57968890666962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831275463104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693660259247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56317639350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5466639995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55354416370392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592857837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069693088531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656907081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58244097232819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60996150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63197839260101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711499214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408960819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583364963531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6003292798996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978371620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180036067963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941630363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427970409393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005667686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868064403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61684167385101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922608852386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133778095245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6182177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66087472438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353209972382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802784919739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023470878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949892997742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986681938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785017490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6622508764267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601120471954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490801334381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105275630951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004449367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830069065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76682984828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233374118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370989322662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7406849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82049512863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022228717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747010231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444519519806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159820079803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7929744720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7682056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75857317447662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554862499237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967684268951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499087810516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535852909088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031721591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921378612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8370076417923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85351991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86039996147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516879081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076820850372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361472606659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123066902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710268974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957261800766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737517356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738699913025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68013942241669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298641681671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500306129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6870197057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114768505096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335430622101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463517189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527590274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426728248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876350879669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6526186466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306940078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930895328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7241724729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692453861237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362726688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289172649384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316432952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343693256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380494117737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206101894379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994956493378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178805828094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6883956193924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6539945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849054813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757721424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620130062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290379047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49299871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47648596763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611855506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45722162723541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832493782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776707172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542124271393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530702114105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54826200008392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52411460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121674060822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127397060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837598323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672739982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246638298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513592720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934007167816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6221239566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945405483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57951128482819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223829746246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60365855693817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371566772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63632810115814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348746299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.626384973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076068878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58803367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59229516983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68888401985168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68178200721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69882702827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013330459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729242801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911210536957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757750511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894101142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752039432526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343023300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928308010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61786282062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5766704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962550640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55394375324249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55252325534821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55110275745392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51701259613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559221744537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871829032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43462812900543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44741189479828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45735478401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47155904769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47013854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47297942638397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53263735771179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58377265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973937034607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4871838092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47724080085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4914448261261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138795375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49996745586395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49570631980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41687273979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42184436321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3991174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426006793976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35224342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994170188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37070882320404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573755741119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37923145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37212944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35579454898834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38633370399475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3643171787262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39343583583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130508899689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35863530635834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40906035900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40124821662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46019566059113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45309352874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439992427826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866117954254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593440532684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894637584686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.440309882164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39556634426117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568044662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38704371452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201533794403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37781119346619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40266859531403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3813624382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33519816398621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36076605319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940266609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468523979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4204238653183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48150193691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985371112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4886040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428606033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258036613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115998744965</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52979648113251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52695560455322</t>
+    <t xml:space="preserve">1.5297966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52695572376251</t>
   </si>
   <si>
     <t xml:space="preserve">1.53405773639679</t>
@@ -1745,103 +1745,103 @@
     <t xml:space="preserve">1.51133096218109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50991034507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008167743683</t>
+    <t xml:space="preserve">1.5099104642868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48008155822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.49854707717896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706946849823</t>
+    <t xml:space="preserve">1.50706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.48292243480682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48434293270111</t>
+    <t xml:space="preserve">1.48434281349182</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689873218536</t>
+    <t xml:space="preserve">1.53689849376678</t>
   </si>
   <si>
     <t xml:space="preserve">1.61644244194031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62780547142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206708431244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60081768035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62496471405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939742088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62070381641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61502182483673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627110958099</t>
+    <t xml:space="preserve">1.62780582904816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206696510315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6008175611496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62496483325958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939730167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62070345878601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61502194404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627146720886</t>
   </si>
   <si>
     <t xml:space="preserve">1.61218094825745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51417183876038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50422883033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4857634305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45877528190613</t>
+    <t xml:space="preserve">1.51417171955109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50422871112823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576331138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303641796112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45877516269684</t>
   </si>
   <si>
     <t xml:space="preserve">1.49286544322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55678451061249</t>
+    <t xml:space="preserve">1.5567843914032</t>
   </si>
   <si>
     <t xml:space="preserve">1.5780907869339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58661341667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916909694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450866222382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166766643524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69061768054962</t>
+    <t xml:space="preserve">1.58661353588104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57382953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916897773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450854301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166742801666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172465801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69061779975891</t>
   </si>
   <si>
     <t xml:space="preserve">1.69356310367584</t>
@@ -1850,43 +1850,43 @@
     <t xml:space="preserve">1.69798111915588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67294585704803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325448036194</t>
+    <t xml:space="preserve">1.67294597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325459957123</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7289069890976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7509970664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277840137482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74510657787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73332524299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161419391632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812216758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8010675907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80548548698425</t>
+    <t xml:space="preserve">1.72890710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75099718570709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277828216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74510610103607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73332512378693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161431312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750480175018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7981219291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80106794834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80548536777496</t>
   </si>
   <si>
     <t xml:space="preserve">1.80401289463043</t>
@@ -1901,52 +1901,52 @@
     <t xml:space="preserve">1.77603244781494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76719629764557</t>
+    <t xml:space="preserve">1.76719617843628</t>
   </si>
   <si>
     <t xml:space="preserve">1.74216103553772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70239913463593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73921585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7701416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486812114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928625583649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79517686367035</t>
+    <t xml:space="preserve">1.70239901542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921573162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77014183998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486835956573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928637504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664957523346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79517698287964</t>
   </si>
   <si>
     <t xml:space="preserve">1.79370427131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78339552879333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79959464073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254030227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192281723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493876457214</t>
+    <t xml:space="preserve">1.78339540958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79959487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254018306732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308714389801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192317485809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493900299072</t>
   </si>
   <si>
     <t xml:space="preserve">1.82021224498749</t>
@@ -1955,82 +1955,82 @@
     <t xml:space="preserve">1.8187392950058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82168483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966540336609</t>
+    <t xml:space="preserve">1.82168459892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966564178467</t>
   </si>
   <si>
     <t xml:space="preserve">1.84819281101227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82904815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425099372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81432151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.809903383255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199346065521</t>
+    <t xml:space="preserve">1.82904803752899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425063610077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81432163715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319935798645</t>
   </si>
   <si>
     <t xml:space="preserve">1.86144685745239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91593539714813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655288219452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127928256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042369842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569694042206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94244313240051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980645179749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9615877866745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809576034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693167209625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00724053382874</t>
+    <t xml:space="preserve">1.91593527793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655264377594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213498592377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127952098846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569705963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9424432516098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980657100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158802509308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809564113617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00724029541016</t>
   </si>
   <si>
     <t xml:space="preserve">1.983677983284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99987733364105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00576758384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98073244094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97189652919769</t>
+    <t xml:space="preserve">1.99987721443176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9807323217392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97189664840698</t>
   </si>
   <si>
     <t xml:space="preserve">1.97631466388702</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">1.94391596317291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96895134449005</t>
+    <t xml:space="preserve">1.96895110607147</t>
   </si>
   <si>
     <t xml:space="preserve">1.96600592136383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97484183311462</t>
+    <t xml:space="preserve">1.97484159469604</t>
   </si>
   <si>
     <t xml:space="preserve">2.01754903793335</t>
@@ -2054,34 +2054,34 @@
     <t xml:space="preserve">2.04847502708435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02049446105957</t>
+    <t xml:space="preserve">2.02049422264099</t>
   </si>
   <si>
     <t xml:space="preserve">2.04552960395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03374862670898</t>
+    <t xml:space="preserve">2.03374838829041</t>
   </si>
   <si>
     <t xml:space="preserve">2.05436563491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02785778045654</t>
+    <t xml:space="preserve">2.02785754203796</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227567672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04111170768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03816628456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01018571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00871300697327</t>
+    <t xml:space="preserve">2.04111194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03816604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01018595695496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00871324539185</t>
   </si>
   <si>
     <t xml:space="preserve">1.99251389503479</t>
@@ -2090,25 +2090,25 @@
     <t xml:space="preserve">2.02638506889343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07940101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467437744141</t>
+    <t xml:space="preserve">2.07940077781677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467413902283</t>
   </si>
   <si>
     <t xml:space="preserve">2.0720374584198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06172895431519</t>
+    <t xml:space="preserve">2.06172919273376</t>
   </si>
   <si>
     <t xml:space="preserve">2.03522109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02933049201965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614685058594</t>
+    <t xml:space="preserve">2.02933073043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614708900452</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645559310913</t>
@@ -2123,31 +2123,31 @@
     <t xml:space="preserve">2.05731081962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07351040840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04700207710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0028223991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0131311416626</t>
+    <t xml:space="preserve">2.07351016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04700231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00282263755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313090324402</t>
   </si>
   <si>
     <t xml:space="preserve">2.01460385322571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11179971694946</t>
+    <t xml:space="preserve">2.04258418083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11179947853088</t>
   </si>
   <si>
     <t xml:space="preserve">2.08087372779846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749831199646</t>
+    <t xml:space="preserve">2.07498288154602</t>
   </si>
   <si>
     <t xml:space="preserve">2.11032676696777</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">2.10885429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12652659416199</t>
+    <t xml:space="preserve">2.12652635574341</t>
   </si>
   <si>
     <t xml:space="preserve">2.17659687995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457744598389</t>
+    <t xml:space="preserve">2.20457720756531</t>
   </si>
   <si>
     <t xml:space="preserve">2.19426870346069</t>
@@ -2177,31 +2177,31 @@
     <t xml:space="preserve">2.22519493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21341347694397</t>
+    <t xml:space="preserve">2.21341323852539</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21783137321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20163202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20752286911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17365097999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23255825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21930384635925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21635866165161</t>
+    <t xml:space="preserve">2.2178316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20163226127625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17365121841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23255801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21930408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21635890007019</t>
   </si>
   <si>
     <t xml:space="preserve">2.20310473442078</t>
@@ -2210,58 +2210,58 @@
     <t xml:space="preserve">2.24728488922119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2870466709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201152801514</t>
+    <t xml:space="preserve">2.28704643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201105117798</t>
   </si>
   <si>
     <t xml:space="preserve">2.25023007392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1147449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11621761322021</t>
+    <t xml:space="preserve">2.11474466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11621737480164</t>
   </si>
   <si>
     <t xml:space="preserve">2.1530339717865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13094425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02491235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08823680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1029634475708</t>
+    <t xml:space="preserve">2.13094401359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02491283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08823728561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10296368598938</t>
   </si>
   <si>
     <t xml:space="preserve">1.9822051525116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83641135692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65380120277405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63318395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38724911212921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42921996116638</t>
+    <t xml:space="preserve">1.83641147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65380132198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63318383693695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
     <t xml:space="preserve">1.35190522670746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043251514435</t>
+    <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330729484558</t>
@@ -2273,43 +2273,43 @@
     <t xml:space="preserve">1.32171559333801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3150886297226</t>
+    <t xml:space="preserve">1.31508874893188</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565729141235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37767684459686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49475359916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50948023796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58311343193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674650669098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54776954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53598809242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249606609344</t>
+    <t xml:space="preserve">1.37767672538757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49475347995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50948011875153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58311331272125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674638748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5477694272995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5359879732132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249594688416</t>
   </si>
   <si>
     <t xml:space="preserve">1.56102323532104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55365991592407</t>
+    <t xml:space="preserve">1.55366003513336</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
@@ -2321,34 +2321,34 @@
     <t xml:space="preserve">1.58164072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60225796699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434780597687</t>
+    <t xml:space="preserve">1.60225808620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434804439545</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256659030914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61698472499847</t>
+    <t xml:space="preserve">1.61698460578918</t>
   </si>
   <si>
     <t xml:space="preserve">1.62287533283234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64643776416779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65527379512787</t>
+    <t xml:space="preserve">1.64643800258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65527391433716</t>
   </si>
   <si>
     <t xml:space="preserve">1.67589116096497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66705501079559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349257946014</t>
+    <t xml:space="preserve">1.66705513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349281787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.60520339012146</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">1.57575011253357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58753132820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55807816982269</t>
+    <t xml:space="preserve">1.587531208992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5580780506134</t>
   </si>
   <si>
     <t xml:space="preserve">1.57427740097046</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">1.59047675132751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784018993378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64201986789703</t>
+    <t xml:space="preserve">1.59783983230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64201998710632</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558241844177</t>
@@ -2384,70 +2384,70 @@
     <t xml:space="preserve">1.61109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67883658409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859848499298</t>
+    <t xml:space="preserve">1.6788364648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859860420227</t>
   </si>
   <si>
     <t xml:space="preserve">1.76572370529175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75836050510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72007119655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7082896232605</t>
+    <t xml:space="preserve">1.75836026668549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7200710773468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828986167908</t>
   </si>
   <si>
     <t xml:space="preserve">1.6390745639801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65821933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70534455776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71123492717743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756786346436</t>
+    <t xml:space="preserve">1.65821921825409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70534443855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71123504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756810188293</t>
   </si>
   <si>
     <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71468591690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69781517982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7116185426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71621954441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69168031215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70548367500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72542202472687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73462426662445</t>
+    <t xml:space="preserve">1.71468603610992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69781529903412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71161878108978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71621966362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69168043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70548343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72542178630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73462414741516</t>
   </si>
   <si>
     <t xml:space="preserve">1.73769152164459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73002326488495</t>
+    <t xml:space="preserve">1.73002302646637</t>
   </si>
   <si>
     <t xml:space="preserve">1.68707931041718</t>
@@ -2456,40 +2456,40 @@
     <t xml:space="preserve">1.68554544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67327570915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65793871879578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65487122535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68401193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70241641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235453128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70701766014099</t>
+    <t xml:space="preserve">1.67327582836151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65793883800507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65487134456635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68401181697845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70241630077362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235465049744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70701730251312</t>
   </si>
   <si>
     <t xml:space="preserve">1.66867470741272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64566886425018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65333759784698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65640509128571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6272646188736</t>
+    <t xml:space="preserve">1.64566898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6533374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.656405210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62726449966431</t>
   </si>
   <si>
     <t xml:space="preserve">1.63646697998047</t>
@@ -2498,40 +2498,40 @@
     <t xml:space="preserve">1.64720273017883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67020833492279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407382488251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68247818946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7284893989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73615765571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75609600543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72695577144623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70088255405426</t>
+    <t xml:space="preserve">1.67020845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407358646393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68247807025909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72848927974701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73615777492523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75609612464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72695565223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70088243484497</t>
   </si>
   <si>
     <t xml:space="preserve">1.72082078456879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69321393966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094432353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67174208164215</t>
+    <t xml:space="preserve">1.69321405887604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094420433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67174220085144</t>
   </si>
   <si>
     <t xml:space="preserve">1.6993488073349</t>
@@ -2540,28 +2540,28 @@
     <t xml:space="preserve">1.67787706851959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69014656543732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861305713654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65180397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64873659610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62573063373566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61959600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59659051895142</t>
+    <t xml:space="preserve">1.69014668464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008503437042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861293792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6518040895462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64873647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62573075294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61959612369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59659039974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505665302277</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">1.58738803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57971966266632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57358479499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54904556274414</t>
+    <t xml:space="preserve">1.57971954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57358491420746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54904544353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057919025421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4999668598175</t>
+    <t xml:space="preserve">1.49996674060822</t>
   </si>
   <si>
     <t xml:space="preserve">1.48156237602234</t>
@@ -2597,61 +2597,61 @@
     <t xml:space="preserve">1.51990497112274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54751169681549</t>
+    <t xml:space="preserve">1.54751181602478</t>
   </si>
   <si>
     <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53064107894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60425901412964</t>
+    <t xml:space="preserve">1.53064095973969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60425889492035</t>
   </si>
   <si>
     <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965789318085</t>
+    <t xml:space="preserve">1.59965777397156</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61499488353729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58125340938568</t>
+    <t xml:space="preserve">1.614994764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58125329017639</t>
   </si>
   <si>
     <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60272526741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6610062122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74075889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388803958893</t>
+    <t xml:space="preserve">1.60272514820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66100597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74075877666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069712638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388827800751</t>
   </si>
   <si>
     <t xml:space="preserve">1.69628131389618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6318656206131</t>
+    <t xml:space="preserve">1.63186585903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63033187389374</t>
+    <t xml:space="preserve">1.63033199310303</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889219045639</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">1.6103937625885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61346137523651</t>
+    <t xml:space="preserve">1.61346125602722</t>
   </si>
   <si>
     <t xml:space="preserve">1.58585453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6395343542099</t>
+    <t xml:space="preserve">1.63953423500061</t>
   </si>
   <si>
     <t xml:space="preserve">1.64260172843933</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947246551514</t>
+    <t xml:space="preserve">1.65947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">1.66714096069336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6226634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55518054962158</t>
+    <t xml:space="preserve">1.62266337871552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.555180311203</t>
   </si>
   <si>
     <t xml:space="preserve">1.55671393871307</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56898379325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57051742076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597813129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278703689575</t>
+    <t xml:space="preserve">1.56898367404938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57051753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55978143215179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278691768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.60732626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63339948654175</t>
+    <t xml:space="preserve">1.63339936733246</t>
   </si>
   <si>
     <t xml:space="preserve">1.62419712543488</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">1.58432078361511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806213855743</t>
+    <t xml:space="preserve">1.61806237697601</t>
   </si>
   <si>
     <t xml:space="preserve">1.64106810092926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66560733318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67480945587158</t>
+    <t xml:space="preserve">1.665607213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67480957508087</t>
   </si>
   <si>
     <t xml:space="preserve">1.71775341033936</t>
@@ -2741,37 +2741,37 @@
     <t xml:space="preserve">1.75762987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80517470836639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81744432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824208259583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670845508575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80364096164703</t>
+    <t xml:space="preserve">1.80517482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81744420528412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082423210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
     <t xml:space="preserve">1.79903984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79290533065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82051181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78063535690308</t>
+    <t xml:space="preserve">1.79290521144867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82051193714142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78063547611237</t>
   </si>
   <si>
     <t xml:space="preserve">1.79443871974945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83278167247772</t>
+    <t xml:space="preserve">1.83278155326843</t>
   </si>
   <si>
     <t xml:space="preserve">1.80977594852448</t>
@@ -2780,16 +2780,16 @@
     <t xml:space="preserve">1.82971405982971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885441303253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891654014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818055152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498951911926</t>
+    <t xml:space="preserve">1.85885453224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891630172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818043231964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498928070068</t>
   </si>
   <si>
     <t xml:space="preserve">1.85578727722168</t>
@@ -2798,61 +2798,61 @@
     <t xml:space="preserve">1.8634557723999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84965229034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87112414836884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89566326141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90179848670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9186692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90026473999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91100072860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627594947815</t>
+    <t xml:space="preserve">1.84965240955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87112426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89566349983215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90179836750031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91866934299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90026450157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100084781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627630710602</t>
   </si>
   <si>
     <t xml:space="preserve">1.95394456386566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91560161113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173671722412</t>
+    <t xml:space="preserve">1.91560173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173683643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.91713547706604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93553996086121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695004940033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007931232452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382078647614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621406078339</t>
+    <t xml:space="preserve">1.93553984165192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007907390594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382066726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621417999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.00609064102173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00762414932251</t>
+    <t xml:space="preserve">2.00762438774109</t>
   </si>
   <si>
     <t xml:space="preserve">2.01375889778137</t>
@@ -2861,31 +2861,31 @@
     <t xml:space="preserve">2.00915789604187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95701193809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854532718658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96928155422211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9784836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00302290916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01069188117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01836013793945</t>
+    <t xml:space="preserve">1.9570118188858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854544639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9692816734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97848379611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01069164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01836037635803</t>
   </si>
   <si>
     <t xml:space="preserve">2.0290961265564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03369760513306</t>
+    <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
     <t xml:space="preserve">2.01682662963867</t>
@@ -2894,16 +2894,16 @@
     <t xml:space="preserve">2.01631903648376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563097953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335124015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97175979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9447056055069</t>
+    <t xml:space="preserve">1.99563086032867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335135936737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.971759557724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
     <t xml:space="preserve">1.92242586612701</t>
@@ -2912,52 +2912,52 @@
     <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9144686460495</t>
+    <t xml:space="preserve">1.91446888446808</t>
   </si>
   <si>
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401731014252</t>
+    <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
     <t xml:space="preserve">1.92720007896423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9797168970108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96061968803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95743715763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539402008057</t>
+    <t xml:space="preserve">1.97971653938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96061992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95743727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539413928986</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926532268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857678890228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287744045258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94788873195648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449110984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01950216293335</t>
+    <t xml:space="preserve">1.98926520347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857690811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478884935379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449099063873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223347663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01950240135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">2.06087875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04337334632874</t>
+    <t xml:space="preserve">2.04337358474731</t>
   </si>
   <si>
     <t xml:space="preserve">2.04814743995667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02427649497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06247019767761</t>
+    <t xml:space="preserve">2.02427625656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06247043609619</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724452972412</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10543823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13726687431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522361755371</t>
+    <t xml:space="preserve">2.10543847084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13726663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.18819189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2025146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1706862449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15158939361572</t>
+    <t xml:space="preserve">2.20251441001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17068600654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15158915519714</t>
   </si>
   <si>
     <t xml:space="preserve">2.12453556060791</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">2.11816954612732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10066437721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08315849304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07042717933655</t>
+    <t xml:space="preserve">2.10066390037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08315873146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07042741775513</t>
   </si>
   <si>
     <t xml:space="preserve">2.10862112045288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.089524269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0847499370575</t>
+    <t xml:space="preserve">2.08952403068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08474969863892</t>
   </si>
   <si>
     <t xml:space="preserve">2.08793306350708</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">2.06565308570862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180424690247</t>
+    <t xml:space="preserve">2.11180400848389</t>
   </si>
   <si>
     <t xml:space="preserve">2.14840650558472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12135219573975</t>
+    <t xml:space="preserve">2.12135243415833</t>
   </si>
   <si>
     <t xml:space="preserve">2.1165783405304</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">2.13249254226685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612652778625</t>
+    <t xml:space="preserve">2.12612676620483</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363217353821</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02586770057678</t>
+    <t xml:space="preserve">2.02586793899536</t>
   </si>
   <si>
     <t xml:space="preserve">2.03064203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98767375946045</t>
+    <t xml:space="preserve">1.98767387866974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01154518127441</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341755867004</t>
+    <t xml:space="preserve">2.18341779708862</t>
   </si>
   <si>
     <t xml:space="preserve">2.18978333473206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023490905762</t>
+    <t xml:space="preserve">2.18023467063904</t>
   </si>
   <si>
     <t xml:space="preserve">2.16113805770874</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">2.21842861175537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29163384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27412796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25343990325928</t>
+    <t xml:space="preserve">2.29163360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27412819862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2534396648407</t>
   </si>
   <si>
     <t xml:space="preserve">2.29481649398804</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">2.25025701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27571964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27890229225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22161149978638</t>
+    <t xml:space="preserve">2.27571940422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27890253067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2216112613678</t>
   </si>
   <si>
     <t xml:space="preserve">2.23115992546082</t>
@@ -3149,16 +3149,16 @@
     <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10384678840637</t>
+    <t xml:space="preserve">2.10384702682495</t>
   </si>
   <si>
     <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17386937141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15954637527466</t>
+    <t xml:space="preserve">2.17386913299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15954613685608</t>
   </si>
   <si>
     <t xml:space="preserve">2.12930965423584</t>
@@ -3176,28 +3176,28 @@
     <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08634161949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14204072952271</t>
+    <t xml:space="preserve">2.086341381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14204096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.09748125076294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09907269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09111595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06883597373962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01472783088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02905035018921</t>
+    <t xml:space="preserve">2.09907293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09111571311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06883573532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01472806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
     <t xml:space="preserve">1.9781254529953</t>
@@ -3215,28 +3215,28 @@
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130810260773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02109360694885</t>
+    <t xml:space="preserve">1.98130834102631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02109336853027</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128623485565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89378046989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969479084015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00677061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00199675559998</t>
+    <t xml:space="preserve">1.91128599643707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89378070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969491004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00677084922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0019965171814</t>
   </si>
   <si>
     <t xml:space="preserve">1.90651178359985</t>
@@ -3245,58 +3245,58 @@
     <t xml:space="preserve">1.87945795059204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8126186132431</t>
+    <t xml:space="preserve">1.81261849403381</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7553277015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79033887386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85558676719666</t>
+    <t xml:space="preserve">1.75532782077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79033875465393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85558664798737</t>
   </si>
   <si>
     <t xml:space="preserve">1.83330678939819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922075271606</t>
+    <t xml:space="preserve">1.84922087192535</t>
   </si>
   <si>
     <t xml:space="preserve">1.83171534538269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82534968852997</t>
+    <t xml:space="preserve">1.82534980773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82694101333618</t>
+    <t xml:space="preserve">1.82694125175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444665908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423228263855</t>
+    <t xml:space="preserve">1.84444689750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423204421997</t>
   </si>
   <si>
     <t xml:space="preserve">1.8380811214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85240387916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104927539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92879152297974</t>
+    <t xml:space="preserve">1.85240375995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
     <t xml:space="preserve">1.89537191390991</t>
@@ -3305,34 +3305,34 @@
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881398677826</t>
+    <t xml:space="preserve">1.99881374835968</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313662528992</t>
+    <t xml:space="preserve">2.01313638687134</t>
   </si>
   <si>
     <t xml:space="preserve">1.98289966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0035879611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94311428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95107126235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9542543888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786638736725</t>
+    <t xml:space="preserve">2.00358819961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9431140422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197417259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107138156891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95425415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786650657654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3341,28 +3341,28 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221137046814</t>
+    <t xml:space="preserve">1.96221148967743</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038320541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993139266968</t>
+    <t xml:space="preserve">1.93038332462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993151187897</t>
   </si>
   <si>
     <t xml:space="preserve">1.90014612674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91765165328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192430973053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285545349121</t>
+    <t xml:space="preserve">1.91765189170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91924321651459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285533428192</t>
   </si>
   <si>
     <t xml:space="preserve">1.71235942840576</t>
@@ -3374,34 +3374,34 @@
     <t xml:space="preserve">1.61210060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66143441200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65984296798706</t>
+    <t xml:space="preserve">1.66143429279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65984284877777</t>
   </si>
   <si>
     <t xml:space="preserve">1.69007992744446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711153507233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6168749332428</t>
+    <t xml:space="preserve">1.64711165428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61687481403351</t>
   </si>
   <si>
     <t xml:space="preserve">1.62483179569244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65506863594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70758521556854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69644546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68053126335144</t>
+    <t xml:space="preserve">1.65506875514984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70758533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6964453458786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68053138256073</t>
   </si>
   <si>
     <t xml:space="preserve">1.65825164318085</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">1.58743369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54128265380859</t>
+    <t xml:space="preserve">1.54128289222717</t>
   </si>
   <si>
     <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025021076202</t>
+    <t xml:space="preserve">1.51025032997131</t>
   </si>
   <si>
     <t xml:space="preserve">1.53383469581604</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">1.51446175575256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5026695728302</t>
+    <t xml:space="preserve">1.50266945362091</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">1.50856566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51361954212189</t>
+    <t xml:space="preserve">1.5136194229126</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5481538772583</t>
+    <t xml:space="preserve">1.54815399646759</t>
   </si>
   <si>
     <t xml:space="preserve">1.48835027217865</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">1.47487342357635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087727069855</t>
+    <t xml:space="preserve">1.49087715148926</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4630811214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47403109073639</t>
+    <t xml:space="preserve">1.46308124065399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47403120994568</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171960353851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46645057201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45718502998352</t>
+    <t xml:space="preserve">1.49171948432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46645045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4571852684021</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39906620979309</t>
+    <t xml:space="preserve">1.3990660905838</t>
   </si>
   <si>
     <t xml:space="preserve">1.36200475692749</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178948402405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26766681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26177060604095</t>
+    <t xml:space="preserve">1.34178960323334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26766669750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26177072525024</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">1.20617866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23229002952576</t>
+    <t xml:space="preserve">1.23229014873505</t>
   </si>
   <si>
     <t xml:space="preserve">1.22976315021515</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144781589508</t>
+    <t xml:space="preserve">1.23144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3566,79 +3566,79 @@
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365178585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20533633232117</t>
+    <t xml:space="preserve">1.20365166664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20533645153046</t>
   </si>
   <si>
     <t xml:space="preserve">1.175013422966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13289833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14637494087219</t>
+    <t xml:space="preserve">1.13289821147919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14637506008148</t>
   </si>
   <si>
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942136287689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1059445142746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1430059671402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16911733150482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965539455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16490578651428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13710975646973</t>
+    <t xml:space="preserve">1.11942148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10594439506531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14300584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16911721229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965551376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16490566730499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13710963726044</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12700223922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12279057502747</t>
+    <t xml:space="preserve">1.12700212001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12279045581818</t>
   </si>
   <si>
     <t xml:space="preserve">1.08151769638062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10425984859467</t>
+    <t xml:space="preserve">1.10425996780396</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15985202789307</t>
+    <t xml:space="preserve">1.15985190868378</t>
   </si>
   <si>
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553272724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427884578705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22470939159393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2600861787796</t>
+    <t xml:space="preserve">1.14553284645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427872657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22470927238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">1.29462051391602</t>
@@ -3659,28 +3659,28 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829387664795</t>
+    <t xml:space="preserve">1.24829375743866</t>
   </si>
   <si>
     <t xml:space="preserve">1.24492466449738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25334763526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818612098694</t>
+    <t xml:space="preserve">1.25334775447845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818624019623</t>
   </si>
   <si>
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325875759125</t>
+    <t xml:space="preserve">1.32325887680054</t>
   </si>
   <si>
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31652045249939</t>
+    <t xml:space="preserve">1.3165203332901</t>
   </si>
   <si>
     <t xml:space="preserve">1.3299971818924</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915484905243</t>
+    <t xml:space="preserve">1.32915496826172</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021257400513</t>
+    <t xml:space="preserve">1.35021269321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35358166694641</t>
+    <t xml:space="preserve">1.3535817861557</t>
   </si>
   <si>
     <t xml:space="preserve">1.32747030258179</t>
@@ -3719,10 +3719,10 @@
     <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33589339256287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31062436103821</t>
+    <t xml:space="preserve">1.33589327335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31062424182892</t>
   </si>
   <si>
     <t xml:space="preserve">1.29546284675598</t>
@@ -3731,16 +3731,16 @@
     <t xml:space="preserve">1.30135893821716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25082087516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2365015745163</t>
+    <t xml:space="preserve">1.25082075595856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23650169372559</t>
   </si>
   <si>
     <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23734378814697</t>
+    <t xml:space="preserve">1.23734390735626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">1.34263181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37127006053925</t>
+    <t xml:space="preserve">1.37127017974854</t>
   </si>
   <si>
     <t xml:space="preserve">1.36958563327789</t>
@@ -3776,25 +3776,25 @@
     <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4656081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40411996841431</t>
+    <t xml:space="preserve">1.46560823917389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4041200876236</t>
   </si>
   <si>
     <t xml:space="preserve">1.38222014904022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39822375774384</t>
+    <t xml:space="preserve">1.39822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4336005449295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44370830059052</t>
+    <t xml:space="preserve">1.43360066413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44370818138123</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">1.44623517990112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232766628265</t>
+    <t xml:space="preserve">1.39232778549194</t>
   </si>
   <si>
     <t xml:space="preserve">1.41843914985657</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727378845215</t>
+    <t xml:space="preserve">1.38727390766144</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">1.39317011833191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37800872325897</t>
+    <t xml:space="preserve">1.37800860404968</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779333114624</t>
+    <t xml:space="preserve">1.35779321193695</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496230125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811612129211</t>
+    <t xml:space="preserve">1.40496218204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
     <t xml:space="preserve">1.37716627120972</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34515869617462</t>
+    <t xml:space="preserve">1.34515881538391</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3875,19 +3875,19 @@
     <t xml:space="preserve">1.41170072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4125429391861</t>
+    <t xml:space="preserve">1.41254305839539</t>
   </si>
   <si>
     <t xml:space="preserve">1.44202363491058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45634269714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42686223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707751274109</t>
+    <t xml:space="preserve">1.45634281635284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42686212062836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4470773935318</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
@@ -3908,25 +3908,25 @@
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6071150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61132669448853</t>
+    <t xml:space="preserve">1.60711514949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61132657527924</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57426524162292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521521091461</t>
+    <t xml:space="preserve">1.57426536083221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5852153301239</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942663669586</t>
+    <t xml:space="preserve">1.58942675590515</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037672519684</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62396121025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59953451156616</t>
+    <t xml:space="preserve">1.62396109104156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59953439235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">1.61806511878967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61048424243927</t>
+    <t xml:space="preserve">1.61048436164856</t>
   </si>
   <si>
     <t xml:space="preserve">1.64249193668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66186499595642</t>
+    <t xml:space="preserve">1.66186487674713</t>
   </si>
   <si>
     <t xml:space="preserve">1.62227654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58774220943451</t>
+    <t xml:space="preserve">1.58774209022522</t>
   </si>
   <si>
     <t xml:space="preserve">1.62480342388153</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57763457298279</t>
+    <t xml:space="preserve">1.5776344537735</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">1.58353054523468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57089614868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57595002651215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58437287807465</t>
+    <t xml:space="preserve">1.57089602947235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57594990730286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58437299728394</t>
   </si>
   <si>
     <t xml:space="preserve">1.58184599876404</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.57173836231232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59026896953583</t>
+    <t xml:space="preserve">1.59026908874512</t>
   </si>
   <si>
     <t xml:space="preserve">1.5801614522934</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5308746099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52102696895599</t>
+    <t xml:space="preserve">1.53087472915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5210268497467</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357869148254</t>
+    <t xml:space="preserve">1.47357881069183</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506461620331</t>
+    <t xml:space="preserve">1.4950647354126</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4088,52 +4088,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192211151123</t>
+    <t xml:space="preserve">1.52192223072052</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070407390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308526039124</t>
+    <t xml:space="preserve">1.61144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070395469666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308514118195</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786592960358</t>
+    <t xml:space="preserve">1.60786604881287</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039947509766</t>
+    <t xml:space="preserve">1.62039935588837</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801828861237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773198604584</t>
+    <t xml:space="preserve">1.59801816940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773210525513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937026977539</t>
+    <t xml:space="preserve">1.56937038898468</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6150279045105</t>
+    <t xml:space="preserve">1.61502802371979</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58279895782471</t>
+    <t xml:space="preserve">1.582799077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769539356232</t>
+    <t xml:space="preserve">1.67769527435303</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575263023376</t>
+    <t xml:space="preserve">1.68575251102448</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.664266705513</t>
+    <t xml:space="preserve">1.66426658630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977198123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887683868408</t>
+    <t xml:space="preserve">1.71977210044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887671947479</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843841552734</t>
+    <t xml:space="preserve">1.68843829631805</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159921646118</t>
+    <t xml:space="preserve">1.60159933567047</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340815544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399881839752</t>
+    <t xml:space="preserve">1.54340803623199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234211921692</t>
+    <t xml:space="preserve">1.61234223842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024723529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112420082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350538730621</t>
+    <t xml:space="preserve">1.63024711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112408161163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350526809692</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.745734333992</t>
+    <t xml:space="preserve">1.74573421478271</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201922416687</t>
+    <t xml:space="preserve">1.69201934337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79407751560211</t>
+    <t xml:space="preserve">1.78691565990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7940776348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525896072388</t>
+    <t xml:space="preserve">1.83525907993317</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272565364838</t>
+    <t xml:space="preserve">1.82272553443909</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558185577393</t>
+    <t xml:space="preserve">1.75558197498322</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7645343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857223987579</t>
+    <t xml:space="preserve">1.76453447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857235908508</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4409,16 +4409,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723855495453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859053611755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009487628937</t>
+    <t xml:space="preserve">1.70723843574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859065532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009499549866</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740909099579</t>
+    <t xml:space="preserve">1.63740921020508</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64099013805389</t>
+    <t xml:space="preserve">1.63919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6409900188446</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693407535553</t>
+    <t xml:space="preserve">1.72693395614624</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041777133942</t>
+    <t xml:space="preserve">1.56041789054871</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458960056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609394073486</t>
+    <t xml:space="preserve">1.58458948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609382152557</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205605506897</t>
+    <t xml:space="preserve">1.57205617427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278066158295</t>
+    <t xml:space="preserve">1.64278078079224</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754303455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129461765289</t>
+    <t xml:space="preserve">1.68754315376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129473686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708619594574</t>
+    <t xml:space="preserve">1.71708631515503</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274394989014</t>
+    <t xml:space="preserve">1.76274383068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602039813995</t>
+    <t xml:space="preserve">1.78602051734924</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -70738,7 +70738,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6909953704</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>1461756</v>
@@ -70759,6 +70759,32 @@
         <v>1769</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6912152778</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>2026989</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>2.57800006866455</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>2.5220000743866</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>2.55200004577637</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>2.53600001335144</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1772">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469295501709</t>
+    <t xml:space="preserve">0.933469355106354</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
@@ -50,115 +50,115 @@
     <t xml:space="preserve">0.927027225494385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921873509883881</t>
+    <t xml:space="preserve">0.921873569488525</t>
   </si>
   <si>
     <t xml:space="preserve">0.901902794837952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898037493228912</t>
+    <t xml:space="preserve">0.898037374019623</t>
   </si>
   <si>
     <t xml:space="preserve">0.918652296066284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903835415840149</t>
+    <t xml:space="preserve">0.903835237026215</t>
   </si>
   <si>
     <t xml:space="preserve">0.880643665790558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863893866539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346442699432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653873920441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154752254486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192607879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451856136322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869691967964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441588401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489890575409</t>
+    <t xml:space="preserve">0.863893806934357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346383094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85165399312973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192667484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163382530212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451736927032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869692027568817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88644152879715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875490009784698</t>
   </si>
   <si>
     <t xml:space="preserve">0.908344805240631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888374209403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279182910919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818799018859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837481141090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825241029262543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432838916779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86904776096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172132015228</t>
+    <t xml:space="preserve">0.888374149799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551917552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843279004096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798959255219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837481081485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241148471832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432898521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869047701358795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778304576874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172251224518</t>
   </si>
   <si>
     <t xml:space="preserve">0.923161864280701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927671432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142787456512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709586143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296681880951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075587272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941200017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947642147541046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892527103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113681316376</t>
+    <t xml:space="preserve">0.927671372890472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142906665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709407329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296622276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075527667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199839115143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642028331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113442897797</t>
   </si>
   <si>
     <t xml:space="preserve">0.906412124633789</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">0.954084277153015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964391648769379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179482460022</t>
+    <t xml:space="preserve">0.964391827583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179363250732</t>
   </si>
   <si>
     <t xml:space="preserve">1.01270806789398</t>
@@ -182,43 +182,43 @@
     <t xml:space="preserve">1.02881336212158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0165730714798</t>
+    <t xml:space="preserve">1.01657330989838</t>
   </si>
   <si>
     <t xml:space="preserve">1.02365958690643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00819838047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175631046295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00497734546661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755429267883</t>
+    <t xml:space="preserve">1.00819849967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175642967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0049774646759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755417346954</t>
   </si>
   <si>
     <t xml:space="preserve">1.02172708511353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237129211426</t>
+    <t xml:space="preserve">1.01464068889618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237117290497</t>
   </si>
   <si>
     <t xml:space="preserve">0.999823570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01141941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01786160469055</t>
+    <t xml:space="preserve">1.01141953468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206386089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01786172389984</t>
   </si>
   <si>
     <t xml:space="preserve">1.02430379390717</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">1.01850593090057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02688086032867</t>
+    <t xml:space="preserve">1.02688074111938</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203451633453</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">1.00562155246735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988871991634369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368893146515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0352555513382</t>
+    <t xml:space="preserve">0.988871932029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368916988373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03525531291962</t>
   </si>
   <si>
     <t xml:space="preserve">1.02816915512085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04040932655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03396713733673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0294576883316</t>
+    <t xml:space="preserve">1.04040920734406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03396689891815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02945744991302</t>
   </si>
   <si>
     <t xml:space="preserve">1.03010177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01592886447906</t>
+    <t xml:space="preserve">1.01592898368835</t>
   </si>
   <si>
     <t xml:space="preserve">0.992093026638031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.033322930336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00948679447174</t>
+    <t xml:space="preserve">1.03332304954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00948691368103</t>
   </si>
   <si>
     <t xml:space="preserve">0.995958268642426</t>
@@ -284,55 +284,55 @@
     <t xml:space="preserve">0.995314121246338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02108287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04942834377289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519686222076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295669078827</t>
+    <t xml:space="preserve">1.0210827589035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519698143005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">1.05715894699097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07326436042786</t>
+    <t xml:space="preserve">1.07326424121857</t>
   </si>
   <si>
     <t xml:space="preserve">1.06231260299683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0474956035614</t>
+    <t xml:space="preserve">1.04749572277069</t>
   </si>
   <si>
     <t xml:space="preserve">1.06360101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06166839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06811034679413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04620718955994</t>
+    <t xml:space="preserve">1.06166851520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06811046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04620730876923</t>
   </si>
   <si>
     <t xml:space="preserve">0.977276027202606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968257009983063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96503621339798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97856467962265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522447109222</t>
+    <t xml:space="preserve">0.968257069587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965036034584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522506713867</t>
   </si>
   <si>
     <t xml:space="preserve">0.979232907295227</t>
@@ -341,43 +341,43 @@
     <t xml:space="preserve">0.960517168045044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.907712280750275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964807510376</t>
+    <t xml:space="preserve">0.907712161540985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876964867115021</t>
   </si>
   <si>
     <t xml:space="preserve">0.903701543807983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895680725574493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101526737213</t>
+    <t xml:space="preserve">0.895680546760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101467132568</t>
   </si>
   <si>
     <t xml:space="preserve">0.935117363929749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939127743244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048914909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033196926117</t>
+    <t xml:space="preserve">0.939127802848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048974514008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033256530762</t>
   </si>
   <si>
     <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925090968608856</t>
+    <t xml:space="preserve">0.925090849399567</t>
   </si>
   <si>
     <t xml:space="preserve">0.931775271892548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925759553909302</t>
+    <t xml:space="preserve">0.925759613513947</t>
   </si>
   <si>
     <t xml:space="preserve">0.912391066551208</t>
@@ -386,79 +386,79 @@
     <t xml:space="preserve">0.921080529689789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927096247673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143640041351</t>
+    <t xml:space="preserve">0.927096307277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143699645996</t>
   </si>
   <si>
     <t xml:space="preserve">0.937122583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955838203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164458274841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527904987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196251869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982575058937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97254878282547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217129707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580338001251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995275020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259302616119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601096630096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951828002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950491011142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485553264618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94113302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501330852509</t>
+    <t xml:space="preserve">0.955838263034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164637088776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96452784538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196192264557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982574999332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911693096161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972548842430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580218791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253963947296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99527496099472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989259243011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601275444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827883720398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950490891933441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941133201122284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501450061798</t>
   </si>
   <si>
     <t xml:space="preserve">0.965864598751068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985917210578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927589893341</t>
+    <t xml:space="preserve">0.985917270183563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927530288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.01265382766724</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">1.02000653743744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99193274974823</t>
+    <t xml:space="preserve">0.99193286895752</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996611714363098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901254177094</t>
+    <t xml:space="preserve">0.996611773967743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901194572449</t>
   </si>
   <si>
     <t xml:space="preserve">0.967201292514801</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">0.986585438251495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977896094322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885595798492</t>
+    <t xml:space="preserve">0.977896213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885536193848</t>
   </si>
   <si>
     <t xml:space="preserve">0.995943248271942</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">1.02401697635651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00864315032959</t>
+    <t xml:space="preserve">1.00864338874817</t>
   </si>
   <si>
     <t xml:space="preserve">1.00262761116028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206750392914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975222527980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248684883118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0293642282486</t>
+    <t xml:space="preserve">0.969206631183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97522246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248744487762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02936410903931</t>
   </si>
   <si>
     <t xml:space="preserve">1.05342733860016</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.05543267726898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0761536359787</t>
+    <t xml:space="preserve">1.07615351676941</t>
   </si>
   <si>
     <t xml:space="preserve">1.0895220041275</t>
@@ -533,28 +533,28 @@
     <t xml:space="preserve">1.09687459468842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07013773918152</t>
+    <t xml:space="preserve">1.07013785839081</t>
   </si>
   <si>
     <t xml:space="preserve">1.08751666545868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09353244304657</t>
+    <t xml:space="preserve">1.09353256225586</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479036808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06278514862061</t>
+    <t xml:space="preserve">1.06479048728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06278502941132</t>
   </si>
   <si>
     <t xml:space="preserve">1.04741168022156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06078004837036</t>
+    <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
     <t xml:space="preserve">1.06813263893127</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">0.957843482494354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953833043575287</t>
+    <t xml:space="preserve">0.953833162784576</t>
   </si>
   <si>
     <t xml:space="preserve">0.946480393409729</t>
@@ -575,55 +575,55 @@
     <t xml:space="preserve">0.935785710811615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942469835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780372142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738318443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941801369190216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406844139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538165092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869818210602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98056972026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606673717499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99794864654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01532757282257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01599597930908</t>
+    <t xml:space="preserve">0.942469894886017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780491352081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727879524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738497257233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941801488399506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406784534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538224697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869699001312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569660663605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606554508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948706150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01532745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0159957408905</t>
   </si>
   <si>
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203797340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04005908966064</t>
+    <t xml:space="preserve">1.03203809261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04005885124207</t>
   </si>
   <si>
     <t xml:space="preserve">1.04473781585693</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">1.0307012796402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01733267307281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03604829311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0494167804718</t>
+    <t xml:space="preserve">1.01733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.036048412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874837398529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04941689968109</t>
   </si>
   <si>
     <t xml:space="preserve">1.05275905132294</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">1.02468526363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0106486082077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530123710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03003287315369</t>
+    <t xml:space="preserve">1.01064872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530111789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0300327539444</t>
   </si>
   <si>
     <t xml:space="preserve">1.04273271560669</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412208080292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0561009645462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05810630321503</t>
+    <t xml:space="preserve">1.06412220001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05610108375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05810618400574</t>
   </si>
   <si>
     <t xml:space="preserve">1.08484292030334</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">1.07080626487732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0821692943573</t>
+    <t xml:space="preserve">1.08216917514801</t>
   </si>
   <si>
     <t xml:space="preserve">1.06880104541779</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">1.09754288196564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12628495693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978464603424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120034694672</t>
+    <t xml:space="preserve">1.12628483772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978488445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22120046615601</t>
   </si>
   <si>
     <t xml:space="preserve">1.22988986968994</t>
@@ -731,34 +731,34 @@
     <t xml:space="preserve">1.24058449268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26665270328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28002119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28336322307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29405784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133166790009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932656764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30074226856232</t>
+    <t xml:space="preserve">1.26665282249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28002107143402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28336310386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29405796527863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932644844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30074214935303</t>
   </si>
   <si>
     <t xml:space="preserve">1.31009995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30475270748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007374286652</t>
+    <t xml:space="preserve">1.30475258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007386207581</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143701076508</t>
@@ -767,31 +767,31 @@
     <t xml:space="preserve">1.29004752635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28871047496796</t>
+    <t xml:space="preserve">1.28871059417725</t>
   </si>
   <si>
     <t xml:space="preserve">1.29739999771118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28937900066376</t>
+    <t xml:space="preserve">1.28937911987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.27200019359589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2593001127243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29673171043396</t>
+    <t xml:space="preserve">1.25930023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29673159122467</t>
   </si>
   <si>
     <t xml:space="preserve">1.29806840419769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31076836585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29338955879211</t>
+    <t xml:space="preserve">1.31076848506927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2933896780014</t>
   </si>
   <si>
     <t xml:space="preserve">1.32814729213715</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">1.33683681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33349466323853</t>
+    <t xml:space="preserve">1.33349454402924</t>
   </si>
   <si>
     <t xml:space="preserve">1.35421562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37025773525238</t>
+    <t xml:space="preserve">1.37025761604309</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426817417145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.364910364151</t>
+    <t xml:space="preserve">1.36491048336029</t>
   </si>
   <si>
     <t xml:space="preserve">1.37961542606354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33616828918457</t>
+    <t xml:space="preserve">1.33616840839386</t>
   </si>
   <si>
     <t xml:space="preserve">1.34886825084686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3903101682663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41036260128021</t>
+    <t xml:space="preserve">1.39031004905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036283969879</t>
   </si>
   <si>
     <t xml:space="preserve">1.42105734348297</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">1.43175232410431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45046806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39966821670532</t>
+    <t xml:space="preserve">1.4504679441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39966809749603</t>
   </si>
   <si>
     <t xml:space="preserve">1.41303646564484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43442571163177</t>
+    <t xml:space="preserve">1.43442583084106</t>
   </si>
   <si>
     <t xml:space="preserve">1.41704678535461</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">1.40902590751648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43977320194244</t>
+    <t xml:space="preserve">1.43977308273315</t>
   </si>
   <si>
     <t xml:space="preserve">1.44779407978058</t>
@@ -869,34 +869,34 @@
     <t xml:space="preserve">1.4705206155777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46784675121307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319400310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249938011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46650981903076</t>
+    <t xml:space="preserve">1.46784698963165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116244792938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319388389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249914169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46650993824005</t>
   </si>
   <si>
     <t xml:space="preserve">1.48474228382111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48336625099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49024629592896</t>
+    <t xml:space="preserve">1.48336613178253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49024653434753</t>
   </si>
   <si>
     <t xml:space="preserve">1.47235822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42282092571259</t>
+    <t xml:space="preserve">1.4228208065033</t>
   </si>
   <si>
     <t xml:space="preserve">1.44208526611328</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">1.3953001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39942812919617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40080428123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40218031406403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38429176807404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41456460952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42144465446472</t>
+    <t xml:space="preserve">1.39942824840546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40080416202545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40218043327332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38429188728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4145644903183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42144477367401</t>
   </si>
   <si>
     <t xml:space="preserve">1.43658113479614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.432452917099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42419672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43107688426971</t>
+    <t xml:space="preserve">1.43245303630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42419683933258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43107676506042</t>
   </si>
   <si>
     <t xml:space="preserve">1.44483733177185</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">1.48199021816254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46960604190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44758951663971</t>
+    <t xml:space="preserve">1.46960592269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.447589635849</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923827171326</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">1.50400686264038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50125467777252</t>
+    <t xml:space="preserve">1.50125479698181</t>
   </si>
   <si>
     <t xml:space="preserve">1.49987876415253</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">1.52602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54804015159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115986824036</t>
+    <t xml:space="preserve">1.54803991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115974903107</t>
   </si>
   <si>
     <t xml:space="preserve">1.52327132225037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52189528942108</t>
+    <t xml:space="preserve">1.52189517021179</t>
   </si>
   <si>
     <t xml:space="preserve">1.5452880859375</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">1.57968878746033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57831275463104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556045055389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693672180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56317639350891</t>
+    <t xml:space="preserve">1.57831263542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693660259247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5631765127182</t>
   </si>
   <si>
     <t xml:space="preserve">1.54666411876678</t>
@@ -1013,130 +1013,130 @@
     <t xml:space="preserve">1.55354416370392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56592845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5906970500946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656919002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58244073390961</t>
+    <t xml:space="preserve">1.56592857837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381688594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069716930389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656895160675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5824408531189</t>
   </si>
   <si>
     <t xml:space="preserve">1.60996174812317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63197815418243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408936977386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6058337688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6003292798996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455218791962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978371620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53565585613251</t>
+    <t xml:space="preserve">1.63197839260101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711463451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408960819244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583364963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032951831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978359699249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53565573692322</t>
   </si>
   <si>
     <t xml:space="preserve">1.54391193389893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56180024147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042432785034</t>
+    <t xml:space="preserve">1.56180047988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042408943176</t>
   </si>
   <si>
     <t xml:space="preserve">1.54941618442535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427982330322</t>
+    <t xml:space="preserve">1.53427970409393</t>
   </si>
   <si>
     <t xml:space="preserve">1.57005667686462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868064403534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234604358673</t>
+    <t xml:space="preserve">1.56868052482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234616279602</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684167385101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62922620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133778095245</t>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133754253387</t>
   </si>
   <si>
     <t xml:space="preserve">1.59482514858246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57280874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821782588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6608749628067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637909412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353198051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802796840668</t>
+    <t xml:space="preserve">1.57280850410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6182177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6250981092453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66087508201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940400123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353209972382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69802784919739</t>
   </si>
   <si>
     <t xml:space="preserve">1.69252395629883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64023435115814</t>
+    <t xml:space="preserve">1.64023447036743</t>
   </si>
   <si>
     <t xml:space="preserve">1.65949869155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64986670017242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785017490387</t>
+    <t xml:space="preserve">1.64986646175385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785029411316</t>
   </si>
   <si>
     <t xml:space="preserve">1.66225075721741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67601156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490789413452</t>
+    <t xml:space="preserve">1.67601132392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490801334381</t>
   </si>
   <si>
     <t xml:space="preserve">1.74894118309021</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">1.73105275630951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72004425525665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518085479736</t>
+    <t xml:space="preserve">1.72004449367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518097400665</t>
   </si>
   <si>
     <t xml:space="preserve">1.72830080986023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74618923664093</t>
+    <t xml:space="preserve">1.74618935585022</t>
   </si>
   <si>
     <t xml:space="preserve">1.7668297290802</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">1.76545369625092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77370965480804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74068522453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82049524784088</t>
+    <t xml:space="preserve">1.77370989322662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049512863159</t>
   </si>
   <si>
     <t xml:space="preserve">1.79022240638733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78747010231018</t>
+    <t xml:space="preserve">1.78747034072876</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444543361664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79159832000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7929744720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7682056427002</t>
+    <t xml:space="preserve">1.79159843921661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297411441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76820576190948</t>
   </si>
   <si>
     <t xml:space="preserve">1.75857329368591</t>
@@ -1199,34 +1199,34 @@
     <t xml:space="preserve">1.72554862499237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72967672348022</t>
+    <t xml:space="preserve">1.72967684268951</t>
   </si>
   <si>
     <t xml:space="preserve">1.72142052650452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75169348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499075889587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535876750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031733512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481308460236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921402454376</t>
+    <t xml:space="preserve">1.75169336795807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499087810516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535864830017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031721591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481320381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921378612518</t>
   </si>
   <si>
     <t xml:space="preserve">1.84113562107086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8370076417923</t>
+    <t xml:space="preserve">1.83700752258301</t>
   </si>
   <si>
     <t xml:space="preserve">1.85351979732513</t>
@@ -1235,49 +1235,49 @@
     <t xml:space="preserve">1.86039996147156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88516891002655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076797008514</t>
+    <t xml:space="preserve">1.88516879081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076808929443</t>
   </si>
   <si>
     <t xml:space="preserve">1.81361472606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80123054981232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710233211517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957261800766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737517356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738711833954</t>
+    <t xml:space="preserve">1.80123043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710257053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572606086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564355373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573836326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738735675812</t>
   </si>
   <si>
     <t xml:space="preserve">1.634730219841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68151545524597</t>
+    <t xml:space="preserve">1.68151569366455</t>
   </si>
   <si>
     <t xml:space="preserve">1.6691312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6801393032074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298629760742</t>
+    <t xml:space="preserve">1.68013918399811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.642986536026</t>
   </si>
   <si>
     <t xml:space="preserve">1.66500294208527</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">1.6870197057724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69114744663239</t>
+    <t xml:space="preserve">1.69114780426025</t>
   </si>
   <si>
     <t xml:space="preserve">1.63335418701172</t>
@@ -1295,40 +1295,40 @@
     <t xml:space="preserve">1.67463529109955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215606689453</t>
+    <t xml:space="preserve">1.71454012393951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215594768524</t>
   </si>
   <si>
     <t xml:space="preserve">1.69527578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68426764011383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876327037811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6526186466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306928157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930895328522</t>
+    <t xml:space="preserve">1.68426752090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876362800598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65261876583099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306904315948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930907249451</t>
   </si>
   <si>
     <t xml:space="preserve">1.72417283058167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72692477703094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362726688385</t>
+    <t xml:space="preserve">1.72692489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362690925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.68289160728455</t>
@@ -1343,52 +1343,52 @@
     <t xml:space="preserve">1.73380470275879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7420608997345</t>
+    <t xml:space="preserve">1.74206113815308</t>
   </si>
   <si>
     <t xml:space="preserve">1.75994956493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7117885351181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839573860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65399467945099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849054813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
+    <t xml:space="preserve">1.71178829669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6539945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720944404602</t>
   </si>
   <si>
     <t xml:space="preserve">1.59757745265961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59620130062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290355205536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49299871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4503413438797</t>
+    <t xml:space="preserve">1.59620118141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034146308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.46134984493256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47648584842682</t>
+    <t xml:space="preserve">1.47648596763611</t>
   </si>
   <si>
     <t xml:space="preserve">1.48611843585968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47511005401611</t>
+    <t xml:space="preserve">1.4751101732254</t>
   </si>
   <si>
     <t xml:space="preserve">1.45722162723541</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.42832493782043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51776742935181</t>
+    <t xml:space="preserve">1.51776719093323</t>
   </si>
   <si>
     <t xml:space="preserve">1.55079209804535</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">1.54826200008392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52411460876465</t>
+    <t xml:space="preserve">1.52411448955536</t>
   </si>
   <si>
     <t xml:space="preserve">1.5312168598175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52127397060394</t>
+    <t xml:space="preserve">1.52127408981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.52837598323822</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">1.55536413192749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56246626377106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513592720032</t>
+    <t xml:space="preserve">1.56246638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513604640961</t>
   </si>
   <si>
     <t xml:space="preserve">1.60507881641388</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">1.57951140403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60223805904388</t>
+    <t xml:space="preserve">1.60223817825317</t>
   </si>
   <si>
     <t xml:space="preserve">1.60365843772888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59371566772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922596931458</t>
+    <t xml:space="preserve">1.59371554851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922585010529</t>
   </si>
   <si>
     <t xml:space="preserve">1.63632810115814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63348746299744</t>
+    <t xml:space="preserve">1.63348734378815</t>
   </si>
   <si>
     <t xml:space="preserve">1.626384973526</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">1.61076056957245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58803367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59229528903961</t>
+    <t xml:space="preserve">1.58803391456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
     <t xml:space="preserve">1.6888839006424</t>
@@ -1487,46 +1487,46 @@
     <t xml:space="preserve">1.68178188800812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882690906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013318538666</t>
+    <t xml:space="preserve">1.69882702827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013330459595</t>
   </si>
   <si>
     <t xml:space="preserve">1.71729242801666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64911210536957</t>
+    <t xml:space="preserve">1.64911198616028</t>
   </si>
   <si>
     <t xml:space="preserve">1.6675773859024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67894113063812</t>
+    <t xml:space="preserve">1.67894089221954</t>
   </si>
   <si>
     <t xml:space="preserve">1.67752063274384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67183887958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64343047142029</t>
+    <t xml:space="preserve">1.67183899879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343023300171</t>
   </si>
   <si>
     <t xml:space="preserve">1.6192831993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61786270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5766704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388676166534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962550640106</t>
+    <t xml:space="preserve">1.61786282062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962538719177</t>
   </si>
   <si>
     <t xml:space="preserve">1.5539436340332</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.55252325534821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55110263824463</t>
+    <t xml:space="preserve">1.55110275745392</t>
   </si>
   <si>
     <t xml:space="preserve">1.51701259613037</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">1.51559221744537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46871829032898</t>
+    <t xml:space="preserve">1.46871817111969</t>
   </si>
   <si>
     <t xml:space="preserve">1.43462812900543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45735490322113</t>
+    <t xml:space="preserve">1.44741189479828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45735478401184</t>
   </si>
   <si>
     <t xml:space="preserve">1.47155904769897</t>
@@ -1562,19 +1562,19 @@
     <t xml:space="preserve">1.47013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47297942638397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5326372385025</t>
+    <t xml:space="preserve">1.47297954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53263735771179</t>
   </si>
   <si>
     <t xml:space="preserve">1.58377277851105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53973948955536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275157928467</t>
+    <t xml:space="preserve">1.53973960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275146007538</t>
   </si>
   <si>
     <t xml:space="preserve">1.48718369007111</t>
@@ -1583,55 +1583,55 @@
     <t xml:space="preserve">1.47724068164825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49144494533539</t>
+    <t xml:space="preserve">1.49144506454468</t>
   </si>
   <si>
     <t xml:space="preserve">1.50138807296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996745586395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49570631980896</t>
+    <t xml:space="preserve">1.49996757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49570643901825</t>
   </si>
   <si>
     <t xml:space="preserve">1.41687262058258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4218442440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911735057831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065195083618</t>
+    <t xml:space="preserve">1.42184436321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065207004547</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426006793976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3522435426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994182109833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37070882320404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573731899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37923157215118</t>
+    <t xml:space="preserve">1.35224366188049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994170188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37070906162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3657374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37923145294189</t>
   </si>
   <si>
     <t xml:space="preserve">1.37212944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35579454898834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38633370399475</t>
+    <t xml:space="preserve">1.35579466819763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38633358478546</t>
   </si>
   <si>
     <t xml:space="preserve">1.36431705951691</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">1.40906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40124821662903</t>
+    <t xml:space="preserve">1.40124809741974</t>
   </si>
   <si>
     <t xml:space="preserve">1.46019566059113</t>
@@ -1664,22 +1664,22 @@
     <t xml:space="preserve">1.47866106033325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45593440532684</t>
+    <t xml:space="preserve">1.45593452453613</t>
   </si>
   <si>
     <t xml:space="preserve">1.42894649505615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.440309882164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39556634426117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568056583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3870438337326</t>
+    <t xml:space="preserve">1.44030976295471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39556646347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38704371452332</t>
   </si>
   <si>
     <t xml:space="preserve">1.39201533794403</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">1.3778110742569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40266847610474</t>
+    <t xml:space="preserve">1.40266859531403</t>
   </si>
   <si>
     <t xml:space="preserve">1.38136219978333</t>
@@ -1697,16 +1697,16 @@
     <t xml:space="preserve">1.33519840240479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36076617240906</t>
+    <t xml:space="preserve">1.36076593399048</t>
   </si>
   <si>
     <t xml:space="preserve">1.34940266609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43178725242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320763111115</t>
+    <t xml:space="preserve">1.43178713321686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
   </si>
   <si>
     <t xml:space="preserve">1.42468523979187</t>
@@ -1721,46 +1721,46 @@
     <t xml:space="preserve">1.51985371112823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4886040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428606033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258036613464</t>
+    <t xml:space="preserve">1.48860418796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428594112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258024692535</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115998744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52553522586823</t>
+    <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.52979636192322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52695572376251</t>
+    <t xml:space="preserve">1.52695560455322</t>
   </si>
   <si>
     <t xml:space="preserve">1.53405785560608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51133096218109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50991034507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008167743683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49854707717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48292255401611</t>
+    <t xml:space="preserve">1.5113308429718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5099104642868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48008155822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49854695796967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50706970691681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48292243480682</t>
   </si>
   <si>
     <t xml:space="preserve">1.48434281349182</t>
@@ -1769,19 +1769,19 @@
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689849376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61644232273102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206696510315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60081768035889</t>
+    <t xml:space="preserve">1.53689861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61644244194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780559062958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206708431244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60081744194031</t>
   </si>
   <si>
     <t xml:space="preserve">1.62496495246887</t>
@@ -1790,16 +1790,16 @@
     <t xml:space="preserve">1.5993971824646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62070369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61502182483673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627122879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218094825745</t>
+    <t xml:space="preserve">1.62070381641388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61502170562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627110958099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218106746674</t>
   </si>
   <si>
     <t xml:space="preserve">1.51417183876038</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">1.46303653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45877516269684</t>
+    <t xml:space="preserve">1.45877528190613</t>
   </si>
   <si>
     <t xml:space="preserve">1.49286544322968</t>
@@ -1823,55 +1823,55 @@
     <t xml:space="preserve">1.5567843914032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57809090614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58661329746246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382953166962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916897773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450866222382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166778564453</t>
+    <t xml:space="preserve">1.5780907869339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58661317825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57382965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916909694672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450854301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166790485382</t>
   </si>
   <si>
     <t xml:space="preserve">1.69172465801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69061779975891</t>
+    <t xml:space="preserve">1.6906179189682</t>
   </si>
   <si>
     <t xml:space="preserve">1.69356298446655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69798123836517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294585704803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325448036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68619978427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72890686988831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75099694728851</t>
+    <t xml:space="preserve">1.69798111915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325459957123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68619966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72890710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7509970664978</t>
   </si>
   <si>
     <t xml:space="preserve">1.76277840137482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74510610103607</t>
+    <t xml:space="preserve">1.74510622024536</t>
   </si>
   <si>
     <t xml:space="preserve">1.73332524299622</t>
@@ -1886,46 +1886,46 @@
     <t xml:space="preserve">1.79812216758728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80106747150421</t>
+    <t xml:space="preserve">1.80106770992279</t>
   </si>
   <si>
     <t xml:space="preserve">1.80548548698425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80401277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137657165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455961704254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603220939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76719653606415</t>
+    <t xml:space="preserve">1.80401289463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455973625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603232860565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76719629764557</t>
   </si>
   <si>
     <t xml:space="preserve">1.74216115474701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70239925384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73921573162079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77014172077179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486835956573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928661346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664969444275</t>
+    <t xml:space="preserve">1.70239913463593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7392156124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77014148235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486847877502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928649425507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664957523346</t>
   </si>
   <si>
     <t xml:space="preserve">1.79517686367035</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">1.79370427131653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78339564800262</t>
+    <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
     <t xml:space="preserve">1.79959487915039</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">1.77308690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7819230556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8202121257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81873941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168471813202</t>
+    <t xml:space="preserve">1.78192317485809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493864536285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021200656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81873953342438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82168459892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.84966564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84819269180298</t>
+    <t xml:space="preserve">1.84819281101227</t>
   </si>
   <si>
     <t xml:space="preserve">1.82904827594757</t>
@@ -1973,49 +1973,49 @@
     <t xml:space="preserve">1.76425099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81432163715363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990350246429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199346065521</t>
+    <t xml:space="preserve">1.81432139873505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319935798645</t>
   </si>
   <si>
     <t xml:space="preserve">1.86144685745239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91593539714813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9321346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127928256989</t>
+    <t xml:space="preserve">1.91593551635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655288219452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213474750519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127904415131</t>
   </si>
   <si>
     <t xml:space="preserve">1.97042417526245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95569717884064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94244337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980657100677</t>
+    <t xml:space="preserve">1.95569705963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244301319122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980669021606</t>
   </si>
   <si>
     <t xml:space="preserve">1.9615877866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98809564113617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693191051483</t>
+    <t xml:space="preserve">1.98809587955475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693179130554</t>
   </si>
   <si>
     <t xml:space="preserve">2.00724053382874</t>
@@ -2027,52 +2027,52 @@
     <t xml:space="preserve">1.99987721443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00576782226562</t>
+    <t xml:space="preserve">2.00576758384705</t>
   </si>
   <si>
     <t xml:space="preserve">1.98073279857635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97189664840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97631454467773</t>
+    <t xml:space="preserve">1.97189652919769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97631466388702</t>
   </si>
   <si>
     <t xml:space="preserve">1.94391596317291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96895122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600580215454</t>
+    <t xml:space="preserve">1.96895134449005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600592136383</t>
   </si>
   <si>
     <t xml:space="preserve">1.97484183311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01754927635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04847526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02049446105957</t>
+    <t xml:space="preserve">2.01754903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04847502708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02049422264099</t>
   </si>
   <si>
     <t xml:space="preserve">2.04552984237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03374838829041</t>
+    <t xml:space="preserve">2.03374862670898</t>
   </si>
   <si>
     <t xml:space="preserve">2.05436587333679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02785778045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227567672729</t>
+    <t xml:space="preserve">2.02785754203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227591514587</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111194610596</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">2.03816628456116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01018571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00871300697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99251401424408</t>
+    <t xml:space="preserve">2.01018595695496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00871276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99251413345337</t>
   </si>
   <si>
     <t xml:space="preserve">2.02638506889343</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">2.07940077781677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467437744141</t>
+    <t xml:space="preserve">2.06467413902283</t>
   </si>
   <si>
     <t xml:space="preserve">2.0720374584198</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">2.06172919273376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03522086143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933025360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614685058594</t>
+    <t xml:space="preserve">2.03522109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933049201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614708900452</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645583152771</t>
@@ -2120,22 +2120,22 @@
     <t xml:space="preserve">2.08676433563232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02196741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05731105804443</t>
+    <t xml:space="preserve">2.02196717262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05731081962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.07351016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04700207710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0028223991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0131311416626</t>
+    <t xml:space="preserve">2.04700231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00282263755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313090324402</t>
   </si>
   <si>
     <t xml:space="preserve">2.01460385322571</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">2.04258441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11179947853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08087372779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07498288154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11032676696777</t>
+    <t xml:space="preserve">2.1117992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08087348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0749831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11032700538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">2.10885429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12652659416199</t>
+    <t xml:space="preserve">2.12652635574341</t>
   </si>
   <si>
     <t xml:space="preserve">2.17659664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457768440247</t>
+    <t xml:space="preserve">2.20457720756531</t>
   </si>
   <si>
     <t xml:space="preserve">2.19426870346069</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">2.2458119392395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519469261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21341323852539</t>
+    <t xml:space="preserve">2.22519493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21341371536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">2.20163226127625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20752263069153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17365121841431</t>
+    <t xml:space="preserve">2.20752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17365145683289</t>
   </si>
   <si>
     <t xml:space="preserve">2.23255801200867</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">2.21930384635925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21635842323303</t>
+    <t xml:space="preserve">2.21635890007019</t>
   </si>
   <si>
     <t xml:space="preserve">2.20310473442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24728441238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28704643249512</t>
+    <t xml:space="preserve">2.24728465080261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2870466709137</t>
   </si>
   <si>
     <t xml:space="preserve">2.26201128959656</t>
@@ -2234,25 +2234,25 @@
     <t xml:space="preserve">2.13094425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02491235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08823680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1029634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83641135692596</t>
+    <t xml:space="preserve">2.0249125957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08823704719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10296368598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9822051525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83641159534454</t>
   </si>
   <si>
     <t xml:space="preserve">1.65380120277405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63318395614624</t>
+    <t xml:space="preserve">1.63318383693695</t>
   </si>
   <si>
     <t xml:space="preserve">1.38724899291992</t>
@@ -2264,19 +2264,19 @@
     <t xml:space="preserve">1.35190510749817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043251514435</t>
+    <t xml:space="preserve">1.35043239593506</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330729484558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36442279815674</t>
+    <t xml:space="preserve">1.36442291736603</t>
   </si>
   <si>
     <t xml:space="preserve">1.32171559333801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31508874893188</t>
+    <t xml:space="preserve">1.3150886297226</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565741062164</t>
@@ -2285,16 +2285,16 @@
     <t xml:space="preserve">1.37767684459686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49475359916687</t>
+    <t xml:space="preserve">1.49475347995758</t>
   </si>
   <si>
     <t xml:space="preserve">1.50948011875153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58311331272125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674650669098</t>
+    <t xml:space="preserve">1.58311343193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674638748169</t>
   </si>
   <si>
     <t xml:space="preserve">1.55071485042572</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">1.55365991592407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5492422580719</t>
+    <t xml:space="preserve">1.54924213886261</t>
   </si>
   <si>
     <t xml:space="preserve">1.54187881946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58164060115814</t>
+    <t xml:space="preserve">1.58164072036743</t>
   </si>
   <si>
     <t xml:space="preserve">1.60225796699524</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">1.62434792518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61256670951843</t>
+    <t xml:space="preserve">1.61256659030914</t>
   </si>
   <si>
     <t xml:space="preserve">1.61698472499847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62287521362305</t>
+    <t xml:space="preserve">1.62287509441376</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643800258636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65527379512787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67589128017426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66705501079559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349257946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520327091217</t>
+    <t xml:space="preserve">1.65527391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67589116096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66705513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349246025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520339012146</t>
   </si>
   <si>
     <t xml:space="preserve">1.57575023174286</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">1.58753132820129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5580780506134</t>
+    <t xml:space="preserve">1.55807793140411</t>
   </si>
   <si>
     <t xml:space="preserve">1.57427752017975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59047675132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784018993378</t>
+    <t xml:space="preserve">1.59047663211823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59784007072449</t>
   </si>
   <si>
     <t xml:space="preserve">1.64202010631561</t>
@@ -2381,40 +2381,40 @@
     <t xml:space="preserve">1.66558241844177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6287659406662</t>
+    <t xml:space="preserve">1.62876570224762</t>
   </si>
   <si>
     <t xml:space="preserve">1.61109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67883658409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859848499298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76572358608246</t>
+    <t xml:space="preserve">1.6788364648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859860420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76572370529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.75836038589478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7200710773468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70828974246979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6390745639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821921825409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70534467697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71123504638672</t>
+    <t xml:space="preserve">1.72007119655609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828950405121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63907468318939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70534443855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71123516559601</t>
   </si>
   <si>
     <t xml:space="preserve">1.77756798267365</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69781517982483</t>
+    <t xml:space="preserve">1.69781529903412</t>
   </si>
   <si>
     <t xml:space="preserve">1.7116185426712</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">1.69168031215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548367500305</t>
+    <t xml:space="preserve">1.70548379421234</t>
   </si>
   <si>
     <t xml:space="preserve">1.72542190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73462402820587</t>
+    <t xml:space="preserve">1.73462414741516</t>
   </si>
   <si>
     <t xml:space="preserve">1.73769164085388</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">1.68707942962646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68554544448853</t>
+    <t xml:space="preserve">1.68554556369781</t>
   </si>
   <si>
     <t xml:space="preserve">1.67327570915222</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">1.65793871879578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65487122535706</t>
+    <t xml:space="preserve">1.65487134456635</t>
   </si>
   <si>
     <t xml:space="preserve">1.68401193618774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241641998291</t>
+    <t xml:space="preserve">1.7024165391922</t>
   </si>
   <si>
     <t xml:space="preserve">1.72235453128815</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">1.62726449966431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63646697998047</t>
+    <t xml:space="preserve">1.63646686077118</t>
   </si>
   <si>
     <t xml:space="preserve">1.64720273017883</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">1.66407382488251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68247807025909</t>
+    <t xml:space="preserve">1.68247818946838</t>
   </si>
   <si>
     <t xml:space="preserve">1.7284893989563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73615765571594</t>
+    <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
     <t xml:space="preserve">1.75609600543976</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">1.69321405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68094444274902</t>
+    <t xml:space="preserve">1.68094432353973</t>
   </si>
   <si>
     <t xml:space="preserve">1.67174208164215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6993488073349</t>
+    <t xml:space="preserve">1.69934892654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69014656543732</t>
+    <t xml:space="preserve">1.69014644622803</t>
   </si>
   <si>
     <t xml:space="preserve">1.71008503437042</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">1.59659039974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505653381348</t>
+    <t xml:space="preserve">1.59505665302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.58738803863525</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">1.57971954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57358467578888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54904556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55057907104492</t>
+    <t xml:space="preserve">1.57358479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54904544353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057919025421</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996674060822</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">1.48156237602234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4961324930191</t>
+    <t xml:space="preserve">1.49613261222839</t>
   </si>
   <si>
     <t xml:space="preserve">1.50303423404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51990497112274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54751169681549</t>
+    <t xml:space="preserve">1.51990485191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54751181602478</t>
   </si>
   <si>
     <t xml:space="preserve">1.5643824338913</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">1.53064095973969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60425901412964</t>
+    <t xml:space="preserve">1.60425889492035</t>
   </si>
   <si>
     <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965789318085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60119163990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61499500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58125340938568</t>
+    <t xml:space="preserve">1.59965777397156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60119152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61499488353729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58125329017639</t>
   </si>
   <si>
     <t xml:space="preserve">1.57511842250824</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">1.72388815879822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69628143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6318656206131</t>
+    <t xml:space="preserve">1.69628131389618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186573982239</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6103937625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346137523651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585464954376</t>
+    <t xml:space="preserve">1.61039364337921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346113681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585453033447</t>
   </si>
   <si>
     <t xml:space="preserve">1.6395343542099</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947258472443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66714107990265</t>
+    <t xml:space="preserve">1.65947246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66714096069336</t>
   </si>
   <si>
     <t xml:space="preserve">1.62266337871552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55518043041229</t>
+    <t xml:space="preserve">1.555180311203</t>
   </si>
   <si>
     <t xml:space="preserve">1.55671405792236</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">1.57051753997803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5597813129425</t>
+    <t xml:space="preserve">1.55978143215179</t>
   </si>
   <si>
     <t xml:space="preserve">1.58278703689575</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">1.60732626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63339960575104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62419700622559</t>
+    <t xml:space="preserve">1.63339948654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62419712543488</t>
   </si>
   <si>
     <t xml:space="preserve">1.61192750930786</t>
@@ -2726,31 +2726,31 @@
     <t xml:space="preserve">1.58432066440582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806213855743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106810092926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66560733318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71775341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75762963294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517494678497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81744420528412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824220180511</t>
+    <t xml:space="preserve">1.61806237697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106822013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.665607213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67480957508087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71775329113007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75762975215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517470836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81744432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80824208259583</t>
   </si>
   <si>
     <t xml:space="preserve">1.80670833587646</t>
@@ -2759,46 +2759,46 @@
     <t xml:space="preserve">1.80364096164703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290509223938</t>
+    <t xml:space="preserve">1.79903972148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290521144867</t>
   </si>
   <si>
     <t xml:space="preserve">1.82051169872284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78063523769379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79443860054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83278167247772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80977582931519</t>
+    <t xml:space="preserve">1.78063535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79443871974945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83278179168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8097757101059</t>
   </si>
   <si>
     <t xml:space="preserve">1.82971394062042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885465145111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891630172729</t>
+    <t xml:space="preserve">1.85885453224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891642093658</t>
   </si>
   <si>
     <t xml:space="preserve">1.82818055152893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86498928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85578727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345601081848</t>
+    <t xml:space="preserve">1.86498939990997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85578739643097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8634557723999</t>
   </si>
   <si>
     <t xml:space="preserve">1.84965217113495</t>
@@ -2807,76 +2807,76 @@
     <t xml:space="preserve">1.87112426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89566349983215</t>
+    <t xml:space="preserve">1.89566338062286</t>
   </si>
   <si>
     <t xml:space="preserve">1.90179836750031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91866946220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90026473999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9110004901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627594947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95394432544708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91560161113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173671722412</t>
+    <t xml:space="preserve">1.91866934299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90026462078094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100060939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627606868744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95394456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9156014919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173659801483</t>
   </si>
   <si>
     <t xml:space="preserve">1.91713547706604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93553996086121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695004940033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007907390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382102489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621406078339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00609040260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762438774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375913619995</t>
+    <t xml:space="preserve">1.93553984165192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007931232452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382090568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621417999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00609064102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375889778137</t>
   </si>
   <si>
     <t xml:space="preserve">2.00915789604187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95701169967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854556560516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96928155422211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9784836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00302314758301</t>
+    <t xml:space="preserve">1.9570118188858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854544639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9692816734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97848379611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00302290916443</t>
   </si>
   <si>
     <t xml:space="preserve">2.01069164276123</t>
@@ -2897,85 +2897,85 @@
     <t xml:space="preserve">2.01631903648376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99563074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335124015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97175967693329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9447056055069</t>
+    <t xml:space="preserve">1.99563086032867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335112094879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97175979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
     <t xml:space="preserve">1.92242586612701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91606020927429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91446888446808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90332925319672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92401731014252</t>
+    <t xml:space="preserve">1.91606044769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9144686460495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90332901477814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92401719093323</t>
   </si>
   <si>
     <t xml:space="preserve">1.92720007896423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9797168970108</t>
+    <t xml:space="preserve">1.97971701622009</t>
   </si>
   <si>
     <t xml:space="preserve">1.96061968803406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95743715763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97494292259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98926508426666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857702732086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287744045258</t>
+    <t xml:space="preserve">1.95743727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539413928986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97494268417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98926544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857690811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287755966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.94788873195648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449087142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01950240135193</t>
+    <t xml:space="preserve">1.98449099063873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223347663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01950216293335</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06087851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04337334632874</t>
+    <t xml:space="preserve">2.06087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04337358474731</t>
   </si>
   <si>
     <t xml:space="preserve">2.04814743995667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02427649497986</t>
+    <t xml:space="preserve">2.02427625656128</t>
   </si>
   <si>
     <t xml:space="preserve">2.06247019767761</t>
@@ -2984,28 +2984,28 @@
     <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07997608184814</t>
+    <t xml:space="preserve">2.07997584342957</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10543823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13726663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522385597229</t>
+    <t xml:space="preserve">2.10543847084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13726687431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522361755371</t>
   </si>
   <si>
     <t xml:space="preserve">2.18819165229797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2025146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1706862449646</t>
+    <t xml:space="preserve">2.20251441001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17068600654602</t>
   </si>
   <si>
     <t xml:space="preserve">2.15158939361572</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">2.12453556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1181697845459</t>
+    <t xml:space="preserve">2.11816954612732</t>
   </si>
   <si>
     <t xml:space="preserve">2.10066413879395</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">2.07042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10862135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.089524269104</t>
+    <t xml:space="preserve">2.10862112045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08952403068542</t>
   </si>
   <si>
     <t xml:space="preserve">2.0847499370575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0879328250885</t>
+    <t xml:space="preserve">2.08793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.06565308570862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180424690247</t>
+    <t xml:space="preserve">2.11180400848389</t>
   </si>
   <si>
     <t xml:space="preserve">2.14840650558472</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">2.12135219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1165783405304</t>
+    <t xml:space="preserve">2.11657857894897</t>
   </si>
   <si>
     <t xml:space="preserve">2.11339545249939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13249230384827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612676620483</t>
+    <t xml:space="preserve">2.13249254226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612652778625</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363217353821</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">2.04019045829773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09588980674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02586793899536</t>
+    <t xml:space="preserve">2.09589004516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02586770057678</t>
   </si>
   <si>
     <t xml:space="preserve">2.03064203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98767375946045</t>
+    <t xml:space="preserve">1.98767364025116</t>
   </si>
   <si>
     <t xml:space="preserve">2.01154518127441</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341755867004</t>
+    <t xml:space="preserve">2.18341779708862</t>
   </si>
   <si>
     <t xml:space="preserve">2.18978333473206</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">2.18023490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16113781929016</t>
+    <t xml:space="preserve">2.16113805770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.20569729804993</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">2.21842861175537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29163384437561</t>
+    <t xml:space="preserve">2.29163360595703</t>
   </si>
   <si>
     <t xml:space="preserve">2.27412819862366</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">2.29481649398804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23593425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25025677680969</t>
+    <t xml:space="preserve">2.23593401908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25025701522827</t>
   </si>
   <si>
     <t xml:space="preserve">2.27571964263916</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">2.19774055480957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10384702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15795516967773</t>
+    <t xml:space="preserve">2.10384678840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
     <t xml:space="preserve">2.17386913299561</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">2.12930965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12771797180176</t>
+    <t xml:space="preserve">2.12771844863892</t>
   </si>
   <si>
     <t xml:space="preserve">2.10702967643738</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">2.07201862335205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08634161949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14204072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09748125076294</t>
+    <t xml:space="preserve">2.086341381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14204096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09748101234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.09907269477844</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">2.01472806930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02905035018921</t>
+    <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
     <t xml:space="preserve">1.9781254529953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97016847133636</t>
+    <t xml:space="preserve">1.97016823291779</t>
   </si>
   <si>
     <t xml:space="preserve">2.03700757026672</t>
@@ -3218,40 +3218,40 @@
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130834102631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02109360694885</t>
+    <t xml:space="preserve">1.98130810260773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02109336853027</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128599643707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89378046989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969479084015</t>
+    <t xml:space="preserve">1.91128623485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8937805891037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969467163086</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00199675559998</t>
+    <t xml:space="preserve">2.0019965171814</t>
   </si>
   <si>
     <t xml:space="preserve">1.90651178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87945783138275</t>
+    <t xml:space="preserve">1.87945795059204</t>
   </si>
   <si>
     <t xml:space="preserve">1.8126186132431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79193031787872</t>
+    <t xml:space="preserve">1.79193043708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.7553277015686</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">1.79033887386322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85558664798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8333066701889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84922087192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83171558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534980773926</t>
+    <t xml:space="preserve">1.85558676719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83330678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84922075271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83171534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534968852997</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
@@ -3281,46 +3281,46 @@
     <t xml:space="preserve">1.82694113254547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83012413978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444677829742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83808124065399</t>
+    <t xml:space="preserve">1.83012402057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444665908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423216342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8380811214447</t>
   </si>
   <si>
     <t xml:space="preserve">1.85240387916565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88104951381683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92879176139832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89537191390991</t>
+    <t xml:space="preserve">1.88104927539825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92879164218903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89537179470062</t>
   </si>
   <si>
     <t xml:space="preserve">1.96698534488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99881386756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01791071891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01313662528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98289954662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0035879611969</t>
+    <t xml:space="preserve">1.99881398677826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01791095733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313638687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98289966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00358819961548</t>
   </si>
   <si>
     <t xml:space="preserve">1.94311428070068</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">1.93197441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95107126235962</t>
+    <t xml:space="preserve">1.95107138156891</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786638736725</t>
+    <t xml:space="preserve">1.87786650657654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93833994865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221137046814</t>
+    <t xml:space="preserve">1.93834018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221148967743</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038320541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993139266968</t>
+    <t xml:space="preserve">1.93038332462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993151187897</t>
   </si>
   <si>
     <t xml:space="preserve">1.90014612674713</t>
@@ -3362,16 +3362,16 @@
     <t xml:space="preserve">1.91765165328979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9192430973053</t>
+    <t xml:space="preserve">1.91924297809601</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71235954761505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64233732223511</t>
+    <t xml:space="preserve">1.71235942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6423374414444</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">1.69007980823517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711153507233</t>
+    <t xml:space="preserve">1.64711165428162</t>
   </si>
   <si>
     <t xml:space="preserve">1.6168749332428</t>
@@ -3401,16 +3401,16 @@
     <t xml:space="preserve">1.70758521556854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69644546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68053114414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65825152397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68848836421967</t>
+    <t xml:space="preserve">1.6964453458786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68053138256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65825164318085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68848824501038</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435811519623</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57151973247528</t>
+    <t xml:space="preserve">1.57151961326599</t>
   </si>
   <si>
     <t xml:space="preserve">1.57788527011871</t>
@@ -3431,37 +3431,37 @@
     <t xml:space="preserve">1.58743369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54128265380859</t>
+    <t xml:space="preserve">1.54128277301788</t>
   </si>
   <si>
     <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025032997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53383481502533</t>
+    <t xml:space="preserve">1.51025021076202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53383469581604</t>
   </si>
   <si>
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446175575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50266945362091</t>
+    <t xml:space="preserve">1.51446163654327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5026695728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51698851585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50856554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51361954212189</t>
+    <t xml:space="preserve">1.51698863506317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50856566429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5136194229126</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
@@ -3470,13 +3470,13 @@
     <t xml:space="preserve">1.54815399646759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48835039138794</t>
+    <t xml:space="preserve">1.48835027217865</t>
   </si>
   <si>
     <t xml:space="preserve">1.47487342357635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087727069855</t>
+    <t xml:space="preserve">1.49087715148926</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">1.49171960353851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46645057201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45718502998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41591227054596</t>
+    <t xml:space="preserve">1.46645045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45718514919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41591215133667</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201238155365</t>
@@ -3515,40 +3515,40 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39906620979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200487613678</t>
+    <t xml:space="preserve">1.3990660905838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3620046377182</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178948402405</t>
+    <t xml:space="preserve">1.34178960323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26177072525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27777433395386</t>
+    <t xml:space="preserve">1.26177060604095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27777445316315</t>
   </si>
   <si>
     <t xml:space="preserve">1.22892081737518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20617878437042</t>
+    <t xml:space="preserve">1.20617866516113</t>
   </si>
   <si>
     <t xml:space="preserve">1.23229014873505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22976326942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2920937538147</t>
+    <t xml:space="preserve">1.22976315021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29209363460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.31988966464996</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365178585052</t>
+    <t xml:space="preserve">1.20365166664124</t>
   </si>
   <si>
     <t xml:space="preserve">1.20533633232117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501330375671</t>
+    <t xml:space="preserve">1.175013422966</t>
   </si>
   <si>
     <t xml:space="preserve">1.13289821147919</t>
@@ -3596,31 +3596,31 @@
     <t xml:space="preserve">1.14300584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16911721229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965551376343</t>
+    <t xml:space="preserve">1.16911733150482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965539455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.16490578651428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13710975646973</t>
+    <t xml:space="preserve">1.13710963726044</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12700212001801</t>
+    <t xml:space="preserve">1.12700223922729</t>
   </si>
   <si>
     <t xml:space="preserve">1.12279057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08151769638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10425984859467</t>
+    <t xml:space="preserve">1.0815178155899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10425996780396</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.22470927238464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2600861787796</t>
+    <t xml:space="preserve">1.26008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">1.29462051391602</t>
@@ -3650,10 +3650,10 @@
     <t xml:space="preserve">1.28367066383362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26682436466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26935136318207</t>
+    <t xml:space="preserve">1.26682448387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26935148239136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28030133247375</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">1.24829387664795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24492466449738</t>
+    <t xml:space="preserve">1.24492454528809</t>
   </si>
   <si>
     <t xml:space="preserve">1.25334763526917</t>
@@ -3677,37 +3677,37 @@
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325875759125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31567823886871</t>
+    <t xml:space="preserve">1.32325887680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
     <t xml:space="preserve">1.31652045249939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32999730110168</t>
+    <t xml:space="preserve">1.3299971818924</t>
   </si>
   <si>
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915484905243</t>
+    <t xml:space="preserve">1.32915496826172</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021257400513</t>
+    <t xml:space="preserve">1.35021269321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3535817861557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32747030258179</t>
+    <t xml:space="preserve">1.35358166694641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32747042179108</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3719,37 +3719,37 @@
     <t xml:space="preserve">1.367058634758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32662796974182</t>
+    <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
     <t xml:space="preserve">1.33589339256287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31062424182892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29546284675598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135881900787</t>
+    <t xml:space="preserve">1.31062436103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29546272754669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135893821716</t>
   </si>
   <si>
     <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23650169372559</t>
+    <t xml:space="preserve">1.2365015745163</t>
   </si>
   <si>
     <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23734378814697</t>
+    <t xml:space="preserve">1.23734390735626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039021015167</t>
+    <t xml:space="preserve">1.21039032936096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3758,16 +3758,16 @@
     <t xml:space="preserve">1.2895667552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33842039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34263169765472</t>
+    <t xml:space="preserve">1.33842027187347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34263181686401</t>
   </si>
   <si>
     <t xml:space="preserve">1.37127017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3695855140686</t>
+    <t xml:space="preserve">1.36958563327789</t>
   </si>
   <si>
     <t xml:space="preserve">1.43865430355072</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">1.44539284706116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139657497406</t>
+    <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
     <t xml:space="preserve">1.4656081199646</t>
@@ -3794,16 +3794,16 @@
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4336005449295</t>
+    <t xml:space="preserve">1.43360066413879</t>
   </si>
   <si>
     <t xml:space="preserve">1.44370830059052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39653933048248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42265069484711</t>
+    <t xml:space="preserve">1.39653921127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42265057563782</t>
   </si>
   <si>
     <t xml:space="preserve">1.44623517990112</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770445346832</t>
+    <t xml:space="preserve">1.42770457267761</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38474690914154</t>
+    <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38727378845215</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">1.40327775478363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39316999912262</t>
+    <t xml:space="preserve">1.39317011833191</t>
   </si>
   <si>
     <t xml:space="preserve">1.37800860404968</t>
@@ -3842,25 +3842,25 @@
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779333114624</t>
+    <t xml:space="preserve">1.35779321193695</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496230125427</t>
+    <t xml:space="preserve">1.40496218204498</t>
   </si>
   <si>
     <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37716627120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431636333466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34515869617462</t>
+    <t xml:space="preserve">1.37716639041901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34515881538391</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">1.45634281635284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42686223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707751274109</t>
+    <t xml:space="preserve">1.42686212062836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4470773935318</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
@@ -3899,28 +3899,28 @@
     <t xml:space="preserve">1.48329651355743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.476557970047</t>
+    <t xml:space="preserve">1.47655808925629</t>
   </si>
   <si>
     <t xml:space="preserve">1.53888845443726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56668448448181</t>
+    <t xml:space="preserve">1.5666846036911</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6071150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61132657527924</t>
+    <t xml:space="preserve">1.60711514949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61132669448853</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57426536083221</t>
+    <t xml:space="preserve">1.57426524162292</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521521091461</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942675590515</t>
+    <t xml:space="preserve">1.58942663669586</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784984588623</t>
+    <t xml:space="preserve">1.59784960746765</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">1.64754557609558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65007257461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62396121025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59953451156616</t>
+    <t xml:space="preserve">1.65007269382477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62396109104156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59953439235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3968,22 +3968,22 @@
     <t xml:space="preserve">1.64249193668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66186499595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62227666378021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774209022522</t>
+    <t xml:space="preserve">1.66186487674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62227654457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774220943451</t>
   </si>
   <si>
     <t xml:space="preserve">1.62480342388153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61385357379913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795748233795</t>
+    <t xml:space="preserve">1.61385345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795736312866</t>
   </si>
   <si>
     <t xml:space="preserve">1.58100366592407</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">1.57342302799225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353054523468</t>
+    <t xml:space="preserve">1.58353066444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.57089602947235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57595002651215</t>
+    <t xml:space="preserve">1.57594990730286</t>
   </si>
   <si>
     <t xml:space="preserve">1.58437299728394</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.58184599876404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57173848152161</t>
+    <t xml:space="preserve">1.57173836231232</t>
   </si>
   <si>
     <t xml:space="preserve">1.59026908874512</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5308746099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52102696895599</t>
+    <t xml:space="preserve">1.53087472915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5210268497467</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357869148254</t>
+    <t xml:space="preserve">1.47357881069183</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506461620331</t>
+    <t xml:space="preserve">1.4950647354126</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4091,52 +4091,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192211151123</t>
+    <t xml:space="preserve">1.52192223072052</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070407390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308526039124</t>
+    <t xml:space="preserve">1.61144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070395469666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308514118195</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786592960358</t>
+    <t xml:space="preserve">1.60786604881287</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039947509766</t>
+    <t xml:space="preserve">1.62039935588837</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801828861237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773198604584</t>
+    <t xml:space="preserve">1.59801816940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773210525513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937026977539</t>
+    <t xml:space="preserve">1.56937038898468</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6150279045105</t>
+    <t xml:space="preserve">1.61502802371979</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58279895782471</t>
+    <t xml:space="preserve">1.582799077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769539356232</t>
+    <t xml:space="preserve">1.67769527435303</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575263023376</t>
+    <t xml:space="preserve">1.68575251102448</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.664266705513</t>
+    <t xml:space="preserve">1.66426658630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977198123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887683868408</t>
+    <t xml:space="preserve">1.71977210044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887671947479</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843841552734</t>
+    <t xml:space="preserve">1.68843829631805</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4226,16 +4226,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159921646118</t>
+    <t xml:space="preserve">1.60159933567047</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340815544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399881839752</t>
+    <t xml:space="preserve">1.54340803623199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4256,25 +4256,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234211921692</t>
+    <t xml:space="preserve">1.61234223842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024723529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112420082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350538730621</t>
+    <t xml:space="preserve">1.63024711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112408161163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350526809692</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.745734333992</t>
+    <t xml:space="preserve">1.74573421478271</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201922416687</t>
+    <t xml:space="preserve">1.69201934337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4304,10 +4304,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79407751560211</t>
+    <t xml:space="preserve">1.78691565990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7940776348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525896072388</t>
+    <t xml:space="preserve">1.83525907993317</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272565364838</t>
+    <t xml:space="preserve">1.82272553443909</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558185577393</t>
+    <t xml:space="preserve">1.75558197498322</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7645343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857223987579</t>
+    <t xml:space="preserve">1.76453447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857235908508</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723855495453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859053611755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009487628937</t>
+    <t xml:space="preserve">1.70723843574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859065532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009499549866</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740909099579</t>
+    <t xml:space="preserve">1.63740921020508</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64099013805389</t>
+    <t xml:space="preserve">1.63919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6409900188446</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693407535553</t>
+    <t xml:space="preserve">1.72693395614624</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041777133942</t>
+    <t xml:space="preserve">1.56041789054871</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458960056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609394073486</t>
+    <t xml:space="preserve">1.58458948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609382152557</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205605506897</t>
+    <t xml:space="preserve">1.57205617427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278066158295</t>
+    <t xml:space="preserve">1.64278078079224</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4529,10 +4529,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754303455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129461765289</t>
+    <t xml:space="preserve">1.68754315376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129473686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708619594574</t>
+    <t xml:space="preserve">1.71708631515503</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274394989014</t>
+    <t xml:space="preserve">1.76274383068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602039813995</t>
+    <t xml:space="preserve">1.78602051734924</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -5325,6 +5325,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.54200005531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54800009727478</t>
   </si>
 </sst>
 </file>
@@ -70767,25 +70770,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6911574074</v>
+        <v>45968.6927430556</v>
       </c>
       <c r="B2505" t="n">
-        <v>1566469</v>
+        <v>1264400</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.55200004577637</v>
+        <v>2.54800009727478</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.50799989700317</v>
+        <v>2.50600004196167</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.54200005531311</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.51999998092651</v>
+        <v>2.54800009727478</v>
       </c>
       <c r="G2505" t="s">
-        <v>1745</v>
+        <v>1771</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -38,199 +38,199 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469355106354</t>
+    <t xml:space="preserve">0.933469414710999</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806130886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927027225494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921873569488525</t>
+    <t xml:space="preserve">0.923806011676788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92702716588974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873509883881</t>
   </si>
   <si>
     <t xml:space="preserve">0.901902794837952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898037374019623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835237026215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643665790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893806934357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346383094788</t>
+    <t xml:space="preserve">0.898037493228912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652474880219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835415840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643486976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893866539001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346442699432</t>
   </si>
   <si>
     <t xml:space="preserve">0.85165399312973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192667484283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163382530212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451736927032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869692027568817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88644152879715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875490009784698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344805240631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374149799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551917552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279004096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798959255219</t>
+    <t xml:space="preserve">0.818154692649841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192727088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163322925568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451975345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691967964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441588401794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489890575409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374090194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84327906370163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798899650574</t>
   </si>
   <si>
     <t xml:space="preserve">0.837481081485748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825241148471832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432898521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869047701358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778304576874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172251224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161864280701</t>
+    <t xml:space="preserve">0.825240910053253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869047582149506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778364181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923161804676056</t>
   </si>
   <si>
     <t xml:space="preserve">0.927671372890472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914142906665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709407329559</t>
+    <t xml:space="preserve">0.914142847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709526538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.919296622276306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916075527667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941199839115143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947642028331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113442897797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918008148670197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954084277153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391827583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179363250732</t>
+    <t xml:space="preserve">0.916075468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199958324432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642147541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892586708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412303447723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008089065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954084098339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391648769379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179422855377</t>
   </si>
   <si>
     <t xml:space="preserve">1.01270806789398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02881336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01657330989838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365958690643</t>
+    <t xml:space="preserve">1.02881324291229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01657319068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365970611572</t>
   </si>
   <si>
     <t xml:space="preserve">1.00819849967957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00175642967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0049774646759</t>
+    <t xml:space="preserve">1.00175619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497722625732</t>
   </si>
   <si>
     <t xml:space="preserve">1.00755417346954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02172708511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01464068889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237117290497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999823570251465</t>
+    <t xml:space="preserve">1.02172696590424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0146404504776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999823689460754</t>
   </si>
   <si>
     <t xml:space="preserve">1.01141953468323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01206386089325</t>
+    <t xml:space="preserve">1.01206374168396</t>
   </si>
   <si>
     <t xml:space="preserve">1.01786172389984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02430379390717</t>
+    <t xml:space="preserve">1.02430391311646</t>
   </si>
   <si>
     <t xml:space="preserve">1.01850593090057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02688074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203451633453</t>
+    <t xml:space="preserve">1.0268806219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203439712524</t>
   </si>
   <si>
     <t xml:space="preserve">1.0249480009079</t>
@@ -239,145 +239,145 @@
     <t xml:space="preserve">1.01721751689911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00562155246735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988871932029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368916988373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03525531291962</t>
+    <t xml:space="preserve">1.00562167167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988871872425079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368905067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0352555513382</t>
   </si>
   <si>
     <t xml:space="preserve">1.02816915512085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04040920734406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03396689891815</t>
+    <t xml:space="preserve">1.04040932655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03396713733673</t>
   </si>
   <si>
     <t xml:space="preserve">1.02945744991302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01592898368835</t>
+    <t xml:space="preserve">1.03010165691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01592910289764</t>
   </si>
   <si>
     <t xml:space="preserve">0.992093026638031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03332304954529</t>
+    <t xml:space="preserve">1.03332281112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.00948691368103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995958268642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314121246338</t>
+    <t xml:space="preserve">0.99595832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995313882827759</t>
   </si>
   <si>
     <t xml:space="preserve">1.0210827589035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0494282245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519698143005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05715894699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07326424121857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06231260299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04749572277069</t>
+    <t xml:space="preserve">1.04942834377289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519686222076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295692920685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05715882778168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07326412200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06231272220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0474956035614</t>
   </si>
   <si>
     <t xml:space="preserve">1.06360101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06166851520538</t>
+    <t xml:space="preserve">1.06166839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.06811046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04620730876923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977276027202606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968257069587708</t>
+    <t xml:space="preserve">1.04620718955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977276086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968257009983063</t>
   </si>
   <si>
     <t xml:space="preserve">0.965036034584045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978564500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232907295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517168045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712161540985</t>
+    <t xml:space="preserve">0.978564560413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522447109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517227649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90771222114563</t>
   </si>
   <si>
     <t xml:space="preserve">0.876964867115021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903701543807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680546760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117363929749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127802848816</t>
+    <t xml:space="preserve">0.903701722621918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680725574493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127922058105</t>
   </si>
   <si>
     <t xml:space="preserve">0.909048974514008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903033256530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915733158588409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925090849399567</t>
+    <t xml:space="preserve">0.903033077716827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915733218193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925091087818146</t>
   </si>
   <si>
     <t xml:space="preserve">0.931775271892548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925759613513947</t>
+    <t xml:space="preserve">0.925759434700012</t>
   </si>
   <si>
     <t xml:space="preserve">0.912391066551208</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">0.927096307277679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945143699645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955838263034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164637088776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96452784538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196192264557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982574999332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911693096161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972548842430115</t>
+    <t xml:space="preserve">0.945143461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122523784637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838322639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164517879486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965196073055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982575058937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911871910095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97254866361618</t>
   </si>
   <si>
     <t xml:space="preserve">0.973217248916626</t>
@@ -422,40 +422,40 @@
     <t xml:space="preserve">0.984580218791962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987253963947296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99527496099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989259243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992601275444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890755653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827883720398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950490891933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941133201122284</t>
+    <t xml:space="preserve">0.987253904342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99527508020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989259302616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992601335048676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890815258026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827704906464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950491011142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485791683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941133081912994</t>
   </si>
   <si>
     <t xml:space="preserve">0.954501450061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965864598751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917270183563</t>
+    <t xml:space="preserve">0.965864539146423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917150974274</t>
   </si>
   <si>
     <t xml:space="preserve">0.989927530288696</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">1.02000653743744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99193286895752</t>
+    <t xml:space="preserve">0.991932809352875</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996611773967743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901194572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967201292514801</t>
+    <t xml:space="preserve">0.996611893177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901373386383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201471328735</t>
   </si>
   <si>
     <t xml:space="preserve">0.986585438251495</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">0.973885536193848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995943248271942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401697635651</t>
+    <t xml:space="preserve">0.995943188667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401685714722</t>
   </si>
   <si>
     <t xml:space="preserve">1.00864338874817</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">1.00262761116028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206631183624</t>
+    <t xml:space="preserve">0.969206690788269</t>
   </si>
   <si>
     <t xml:space="preserve">0.97522246837616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985248744487762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02936410903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05342733860016</t>
+    <t xml:space="preserve">0.985248684883118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0293642282486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05342721939087</t>
   </si>
   <si>
     <t xml:space="preserve">1.05543267726898</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">1.0895220041275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09420084953308</t>
+    <t xml:space="preserve">1.09420096874237</t>
   </si>
   <si>
     <t xml:space="preserve">1.09687459468842</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">1.07749032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479048728943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06278502941132</t>
+    <t xml:space="preserve">1.06479060649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06278514862061</t>
   </si>
   <si>
     <t xml:space="preserve">1.04741168022156</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">1.06813263893127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05209064483643</t>
+    <t xml:space="preserve">1.05209052562714</t>
   </si>
   <si>
     <t xml:space="preserve">0.957843482494354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953833162784576</t>
+    <t xml:space="preserve">0.953833103179932</t>
   </si>
   <si>
     <t xml:space="preserve">0.946480393409729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935785710811615</t>
+    <t xml:space="preserve">0.935785591602325</t>
   </si>
   <si>
     <t xml:space="preserve">0.942469894886017</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">0.913727879524231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917738497257233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941801488399506</t>
+    <t xml:space="preserve">0.917738437652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94180154800415</t>
   </si>
   <si>
     <t xml:space="preserve">0.918406784534454</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">0.968538224697113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967869699001312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569660663605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948706150055</t>
+    <t xml:space="preserve">0.967869877815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569779872894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606375694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948527336121</t>
   </si>
   <si>
     <t xml:space="preserve">1.01332235336304</t>
@@ -614,85 +614,85 @@
     <t xml:space="preserve">1.01532745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0159957408905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02869582176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203809261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04005885124207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04473781585693</t>
+    <t xml:space="preserve">1.01599597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0286957025528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203797340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04005908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04473793506622</t>
   </si>
   <si>
     <t xml:space="preserve">1.0307012796402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01733255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.036048412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874837398529</t>
+    <t xml:space="preserve">1.0173327922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03604829311371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874849319458</t>
   </si>
   <si>
     <t xml:space="preserve">1.04941689968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05275905132294</t>
+    <t xml:space="preserve">1.05275893211365</t>
   </si>
   <si>
     <t xml:space="preserve">1.05008518695831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04072749614716</t>
+    <t xml:space="preserve">1.04072737693787</t>
   </si>
   <si>
     <t xml:space="preserve">1.04607474803925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01064872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530111789703</t>
+    <t xml:space="preserve">1.02468538284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01064848899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530135631561</t>
   </si>
   <si>
     <t xml:space="preserve">1.0300327539444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04273271560669</t>
+    <t xml:space="preserve">1.04273247718811</t>
   </si>
   <si>
     <t xml:space="preserve">1.02334856987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05676937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06412220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05610108375549</t>
+    <t xml:space="preserve">1.05676925182343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06412196159363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0561009645462</t>
   </si>
   <si>
     <t xml:space="preserve">1.05810618400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08484292030334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07080626487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08216917514801</t>
+    <t xml:space="preserve">1.08484315872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07080614566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0821692943573</t>
   </si>
   <si>
     <t xml:space="preserve">1.06880104541779</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">1.07815885543823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08283770084381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08818519115448</t>
+    <t xml:space="preserve">1.0828378200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
     <t xml:space="preserve">1.0962061882019</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">1.09954822063446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754288196564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628483772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978488445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120046615601</t>
+    <t xml:space="preserve">1.09754300117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628495693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978476524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22120034694672</t>
   </si>
   <si>
     <t xml:space="preserve">1.22988986968994</t>
@@ -734,46 +734,46 @@
     <t xml:space="preserve">1.26665282249451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28002107143402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28336310386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29405796527863</t>
+    <t xml:space="preserve">1.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28336334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29405808448792</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26932644844055</t>
+    <t xml:space="preserve">1.26932656764984</t>
   </si>
   <si>
     <t xml:space="preserve">1.30074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31009995937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475258827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007386207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31143701076508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29004752635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28871059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29739999771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28937911987305</t>
+    <t xml:space="preserve">1.31010007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475270748138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007374286652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3114367723465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29004740715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28871071338654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29740023612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28937888145447</t>
   </si>
   <si>
     <t xml:space="preserve">1.27200019359589</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">1.31076848506927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2933896780014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814729213715</t>
+    <t xml:space="preserve">1.29338943958282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814717292786</t>
   </si>
   <si>
     <t xml:space="preserve">1.30341577529907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33683681488037</t>
+    <t xml:space="preserve">1.33683657646179</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349454402924</t>
@@ -809,106 +809,106 @@
     <t xml:space="preserve">1.35421562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37025761604309</t>
+    <t xml:space="preserve">1.37025773525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426817417145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36491048336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37961542606354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33616840839386</t>
+    <t xml:space="preserve">1.36491024494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37961554527283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33616828918457</t>
   </si>
   <si>
     <t xml:space="preserve">1.34886825084686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39031004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41036283969879</t>
+    <t xml:space="preserve">1.3903101682663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036260128021</t>
   </si>
   <si>
     <t xml:space="preserve">1.42105734348297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175232410431</t>
+    <t xml:space="preserve">1.43175220489502</t>
   </si>
   <si>
     <t xml:space="preserve">1.4504679441452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39966809749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303646564484</t>
+    <t xml:space="preserve">1.39966797828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303658485413</t>
   </si>
   <si>
     <t xml:space="preserve">1.43442583084106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704678535461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42239427566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40902590751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43977308273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44779407978058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4705206155777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46784698963165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116244792938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319388389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249914169312</t>
+    <t xml:space="preserve">1.41704702377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42239439487457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40902602672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43977320194244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44779419898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052037715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46784663200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249938011169</t>
   </si>
   <si>
     <t xml:space="preserve">1.46650993824005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48474228382111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48336613178253</t>
+    <t xml:space="preserve">1.4847424030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48336637020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47235822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4228208065033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44208526611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40630829334259</t>
+    <t xml:space="preserve">1.47235810756683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42282068729401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44208538532257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4063081741333</t>
   </si>
   <si>
     <t xml:space="preserve">1.3953001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39942824840546</t>
+    <t xml:space="preserve">1.39942812919617</t>
   </si>
   <si>
     <t xml:space="preserve">1.40080416202545</t>
@@ -926,127 +926,127 @@
     <t xml:space="preserve">1.42144477367401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43658113479614</t>
+    <t xml:space="preserve">1.43658137321472</t>
   </si>
   <si>
     <t xml:space="preserve">1.43245303630829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42419683933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43107676506042</t>
+    <t xml:space="preserve">1.42419672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.431077003479</t>
   </si>
   <si>
     <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45997369289398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44621348381042</t>
+    <t xml:space="preserve">1.45997381210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44621336460114</t>
   </si>
   <si>
     <t xml:space="preserve">1.46685385704041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48199021816254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46960592269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.447589635849</t>
+    <t xml:space="preserve">1.48199033737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46960580348969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44758951663971</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923827171326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50400686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125479698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987876415253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50675904750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602338790894</t>
+    <t xml:space="preserve">1.50400674343109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125467777252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50675892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602326869965</t>
   </si>
   <si>
     <t xml:space="preserve">1.54803991317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54115974903107</t>
+    <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
     <t xml:space="preserve">1.52327132225037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52189517021179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5452880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57968878746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693660259247</t>
+    <t xml:space="preserve">1.52189552783966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54528796672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57968890666962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831251621246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556068897247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693684101105</t>
   </si>
   <si>
     <t xml:space="preserve">1.5631765127182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54666411876678</t>
+    <t xml:space="preserve">1.5466639995575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55354416370392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56592857837677</t>
+    <t xml:space="preserve">1.56592845916748</t>
   </si>
   <si>
     <t xml:space="preserve">1.58381688594818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59069716930389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656895160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5824408531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60996174812317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63197839260101</t>
+    <t xml:space="preserve">1.5906970500946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656907081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58244097232819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60996162891388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63197827339172</t>
   </si>
   <si>
     <t xml:space="preserve">1.64711463451385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61408960819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583364963531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60032951831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455230712891</t>
+    <t xml:space="preserve">1.61408984661102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583353042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032916069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455254554749</t>
   </si>
   <si>
     <t xml:space="preserve">1.53978359699249</t>
@@ -1058,127 +1058,127 @@
     <t xml:space="preserve">1.54391193389893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56180047988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427970409393</t>
+    <t xml:space="preserve">1.56180036067963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941594600677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427982330322</t>
   </si>
   <si>
     <t xml:space="preserve">1.57005667686462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868052482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234616279602</t>
+    <t xml:space="preserve">1.56868040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234604358673</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684167385101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62922608852386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133754253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482514858246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280850410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6182177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6250981092453</t>
+    <t xml:space="preserve">1.62922596931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57280874252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509799003601</t>
   </si>
   <si>
     <t xml:space="preserve">1.66087508201599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66637897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940400123596</t>
+    <t xml:space="preserve">1.66637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940376281738</t>
   </si>
   <si>
     <t xml:space="preserve">1.70353209972382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69802784919739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986646175385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785029411316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66225075721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601132392883</t>
+    <t xml:space="preserve">1.6980277299881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252359867096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023458957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949881076813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986670017242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785017490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66225099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601144313812</t>
   </si>
   <si>
     <t xml:space="preserve">1.70490801334381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74894118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105275630951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004449367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518097400665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830080986023</t>
+    <t xml:space="preserve">1.74894106388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105263710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004437446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830069065094</t>
   </si>
   <si>
     <t xml:space="preserve">1.74618935585022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7668297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233386039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545369625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370989322662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7406849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82049512863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022240638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747034072876</t>
+    <t xml:space="preserve">1.76682949066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233374118805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545357704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77371001243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74068510532379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8204950094223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022228717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747022151947</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444543361664</t>
@@ -1187,34 +1187,34 @@
     <t xml:space="preserve">1.79159843921661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79297411441803</t>
+    <t xml:space="preserve">1.79297435283661</t>
   </si>
   <si>
     <t xml:space="preserve">1.76820576190948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75857329368591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554862499237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967684268951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169336795807</t>
+    <t xml:space="preserve">1.75857353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554850578308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142040729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169348716736</t>
   </si>
   <si>
     <t xml:space="preserve">1.81499087810516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80535864830017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031721591949</t>
+    <t xml:space="preserve">1.80535852909088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031709671021</t>
   </si>
   <si>
     <t xml:space="preserve">1.74481320381165</t>
@@ -1223,124 +1223,124 @@
     <t xml:space="preserve">1.77921378612518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85351979732513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86039996147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516879081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361472606659</t>
+    <t xml:space="preserve">1.84113585948944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700728416443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85352027416229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86040019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516891002655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076785087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361484527588</t>
   </si>
   <si>
     <t xml:space="preserve">1.80123043060303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79710257053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79572606086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8273754119873</t>
+    <t xml:space="preserve">1.79710268974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957261800766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82737517356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.68564355373383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64573836326599</t>
+    <t xml:space="preserve">1.64573848247528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67738735675812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.634730219841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151569366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68013918399811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.642986536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500294208527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6870197057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463529109955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454012393951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215594768524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426752090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876362800598</t>
+    <t xml:space="preserve">1.63473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151557445526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66913115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801393032074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64298665523529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500306129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114768505096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7145402431488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426764011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876350879669</t>
   </si>
   <si>
     <t xml:space="preserve">1.65261876583099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75306904315948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756526947021</t>
+    <t xml:space="preserve">1.75306940078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756503105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.73930907249451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72417283058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362690925598</t>
+    <t xml:space="preserve">1.72417259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692465782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362679004669</t>
   </si>
   <si>
     <t xml:space="preserve">1.68289160728455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71316409111023</t>
+    <t xml:space="preserve">1.7131644487381</t>
   </si>
   <si>
     <t xml:space="preserve">1.74343705177307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73380470275879</t>
+    <t xml:space="preserve">1.73380494117737</t>
   </si>
   <si>
     <t xml:space="preserve">1.74206113815308</t>
@@ -1352,67 +1352,67 @@
     <t xml:space="preserve">1.71178829669952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68839550018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6539945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849066734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720944404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757745265961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620118141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290367126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4929986000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47648596763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611843585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4751101732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45722162723541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832493782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776719093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079209804535</t>
+    <t xml:space="preserve">1.68839573860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399491786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849042892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720932483673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757721424103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620130062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290355205536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49299883842468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034158229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47648620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45722150802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832481861115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079221725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.54542124271393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56530690193176</t>
+    <t xml:space="preserve">1.56530702114105</t>
   </si>
   <si>
     <t xml:space="preserve">1.54826200008392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52411448955536</t>
+    <t xml:space="preserve">1.52411472797394</t>
   </si>
   <si>
     <t xml:space="preserve">1.5312168598175</t>
@@ -1424,37 +1424,37 @@
     <t xml:space="preserve">1.52837598323822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56672739982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
+    <t xml:space="preserve">1.56672763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5553640127182</t>
   </si>
   <si>
     <t xml:space="preserve">1.56246638298035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59513604640961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507881641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934019088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62212407588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945405483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57951140403748</t>
+    <t xml:space="preserve">1.59513592720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507893562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934007167816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62212383747101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945393562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951128482819</t>
   </si>
   <si>
     <t xml:space="preserve">1.60223817825317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60365843772888</t>
+    <t xml:space="preserve">1.60365855693817</t>
   </si>
   <si>
     <t xml:space="preserve">1.59371554851532</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">1.62922585010529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63632810115814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348734378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.626384973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076056957245</t>
+    <t xml:space="preserve">1.63632822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348746299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076068878174</t>
   </si>
   <si>
     <t xml:space="preserve">1.58803391456604</t>
@@ -1484,43 +1484,43 @@
     <t xml:space="preserve">1.6888839006424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68178188800812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69882702827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013330459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729242801666</t>
+    <t xml:space="preserve">1.68178164958954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69882678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013318538666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729218959808</t>
   </si>
   <si>
     <t xml:space="preserve">1.64911198616028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6675773859024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894089221954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752063274384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183899879456</t>
+    <t xml:space="preserve">1.66757762432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894077301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752051353455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183876037598</t>
   </si>
   <si>
     <t xml:space="preserve">1.64343023300171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6192831993103</t>
+    <t xml:space="preserve">1.61928296089172</t>
   </si>
   <si>
     <t xml:space="preserve">1.61786282062531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57667052745819</t>
+    <t xml:space="preserve">1.5766704082489</t>
   </si>
   <si>
     <t xml:space="preserve">1.56388664245605</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">1.5539436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55252325534821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55110275745392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51701259613037</t>
+    <t xml:space="preserve">1.55252313613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5511029958725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51701247692108</t>
   </si>
   <si>
     <t xml:space="preserve">1.51559221744537</t>
@@ -1550,37 +1550,37 @@
     <t xml:space="preserve">1.43462812900543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741189479828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45735478401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47155904769897</t>
+    <t xml:space="preserve">1.44741201400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45735466480255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47155916690826</t>
   </si>
   <si>
     <t xml:space="preserve">1.47013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47297954559326</t>
+    <t xml:space="preserve">1.47297942638397</t>
   </si>
   <si>
     <t xml:space="preserve">1.53263735771179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58377277851105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275146007538</t>
+    <t xml:space="preserve">1.58377265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973925113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275134086609</t>
   </si>
   <si>
     <t xml:space="preserve">1.48718369007111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47724068164825</t>
+    <t xml:space="preserve">1.47724080085754</t>
   </si>
   <si>
     <t xml:space="preserve">1.49144506454468</t>
@@ -1589,37 +1589,37 @@
     <t xml:space="preserve">1.50138807296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996757507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49570643901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41687262058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42184436321259</t>
+    <t xml:space="preserve">1.49996745586395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49570608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41687273979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4218442440033</t>
   </si>
   <si>
     <t xml:space="preserve">1.3991174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065207004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426006793976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35224366188049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994170188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37070906162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3657374382019</t>
+    <t xml:space="preserve">1.38065195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3522435426712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994182109833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37070894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573755741119</t>
   </si>
   <si>
     <t xml:space="preserve">1.37923145294189</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">1.35579466819763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38633358478546</t>
+    <t xml:space="preserve">1.38633370399475</t>
   </si>
   <si>
     <t xml:space="preserve">1.36431705951691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39343583583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130520820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35863530635834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40906047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40124809741974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46019566059113</t>
+    <t xml:space="preserve">1.39343595504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130508899689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35863542556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40906035900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40124797821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46019554138184</t>
   </si>
   <si>
     <t xml:space="preserve">1.45309364795685</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">1.47439992427826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47866106033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894649505615</t>
+    <t xml:space="preserve">1.47866129875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593440532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894637584686</t>
   </si>
   <si>
     <t xml:space="preserve">1.44030976295471</t>
@@ -1676,52 +1676,52 @@
     <t xml:space="preserve">1.39556646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37568044662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38704371452332</t>
+    <t xml:space="preserve">1.37568056583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3870438337326</t>
   </si>
   <si>
     <t xml:space="preserve">1.39201533794403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3778110742569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40266859531403</t>
+    <t xml:space="preserve">1.37781119346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40266847610474</t>
   </si>
   <si>
     <t xml:space="preserve">1.38136219978333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33519840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36076593399048</t>
+    <t xml:space="preserve">1.3351982831955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36076605319977</t>
   </si>
   <si>
     <t xml:space="preserve">1.34940266609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468523979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4204238653183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48150205612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985371112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48860418796539</t>
+    <t xml:space="preserve">1.43178725242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320763111115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468512058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042374610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48150217533112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48860430717468</t>
   </si>
   <si>
     <t xml:space="preserve">1.49428594112396</t>
@@ -1730,28 +1730,28 @@
     <t xml:space="preserve">1.54258024692535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54115998744965</t>
+    <t xml:space="preserve">1.54116010665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52979636192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52695560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405785560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5113308429718</t>
+    <t xml:space="preserve">1.52979648113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52695572376251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5340576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51133108139038</t>
   </si>
   <si>
     <t xml:space="preserve">1.5099104642868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48008155822754</t>
+    <t xml:space="preserve">1.48008179664612</t>
   </si>
   <si>
     <t xml:space="preserve">1.49854695796967</t>
@@ -1760,28 +1760,28 @@
     <t xml:space="preserve">1.50706970691681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48292243480682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48434281349182</t>
+    <t xml:space="preserve">1.4829226732254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48434269428253</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689861297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61644244194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780559062958</t>
+    <t xml:space="preserve">1.53689849376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61644232273102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780570983887</t>
   </si>
   <si>
     <t xml:space="preserve">1.63206708431244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60081744194031</t>
+    <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.62496495246887</t>
@@ -1790,46 +1790,46 @@
     <t xml:space="preserve">1.5993971824646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62070381641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61502170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627110958099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218106746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51417183876038</t>
+    <t xml:space="preserve">1.62070369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61502194404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627134799957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218094825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51417171955109</t>
   </si>
   <si>
     <t xml:space="preserve">1.50422871112823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48576331138611</t>
+    <t xml:space="preserve">1.4857634305954</t>
   </si>
   <si>
     <t xml:space="preserve">1.46303653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45877528190613</t>
+    <t xml:space="preserve">1.45877516269684</t>
   </si>
   <si>
     <t xml:space="preserve">1.49286544322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567843914032</t>
+    <t xml:space="preserve">1.55678451061249</t>
   </si>
   <si>
     <t xml:space="preserve">1.5780907869339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58661317825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382965087891</t>
+    <t xml:space="preserve">1.58661329746246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738297700882</t>
   </si>
   <si>
     <t xml:space="preserve">1.63916909694672</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">1.70450854301453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70166790485382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6906179189682</t>
+    <t xml:space="preserve">1.70166754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69061779975891</t>
   </si>
   <si>
     <t xml:space="preserve">1.69356298446655</t>
@@ -1853,61 +1853,61 @@
     <t xml:space="preserve">1.69798111915588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325459957123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68619966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72890710830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7509970664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277840137482</t>
+    <t xml:space="preserve">1.67294585704803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325436115265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68619990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7289069890976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75099694728851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277816295624</t>
   </si>
   <si>
     <t xml:space="preserve">1.74510622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73332524299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161419391632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750515937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812216758728</t>
+    <t xml:space="preserve">1.73332500457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750504016876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812228679657</t>
   </si>
   <si>
     <t xml:space="preserve">1.80106770992279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80548548698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401289463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137633323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603232860565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76719629764557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216115474701</t>
+    <t xml:space="preserve">1.80548536777496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137597560883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455961704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76719641685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216103553772</t>
   </si>
   <si>
     <t xml:space="preserve">1.70239913463593</t>
@@ -1919,49 +1919,49 @@
     <t xml:space="preserve">1.77014148235321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78486847877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928649425507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79664957523346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79517686367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370427131653</t>
+    <t xml:space="preserve">1.78486835956573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928625583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79664969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79517698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370415210724</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79959487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80254030227661</t>
+    <t xml:space="preserve">1.79959499835968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80254018306732</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78192317485809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493864536285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021200656891</t>
+    <t xml:space="preserve">1.78192293643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493888378143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8202121257782</t>
   </si>
   <si>
     <t xml:space="preserve">1.81873953342438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82168459892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966564178467</t>
+    <t xml:space="preserve">1.82168507575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966540336609</t>
   </si>
   <si>
     <t xml:space="preserve">1.84819281101227</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.76425099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81432139873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990362167358</t>
+    <t xml:space="preserve">1.81432151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990350246429</t>
   </si>
   <si>
     <t xml:space="preserve">1.8319935798645</t>
@@ -1985,34 +1985,34 @@
     <t xml:space="preserve">1.86144685745239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91593551635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655288219452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213474750519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127904415131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042417526245</t>
+    <t xml:space="preserve">1.91593527793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655240535736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127940177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042381763458</t>
   </si>
   <si>
     <t xml:space="preserve">1.95569705963135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94244301319122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9615877866745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809587955475</t>
+    <t xml:space="preserve">1.9424432516098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980645179749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809564113617</t>
   </si>
   <si>
     <t xml:space="preserve">1.99693179130554</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">2.00724053382874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98367774486542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987721443176</t>
+    <t xml:space="preserve">1.98367786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987709522247</t>
   </si>
   <si>
     <t xml:space="preserve">2.00576758384705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98073279857635</t>
+    <t xml:space="preserve">1.98073244094849</t>
   </si>
   <si>
     <t xml:space="preserve">1.97189652919769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97631466388702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94391596317291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96895134449005</t>
+    <t xml:space="preserve">1.97631442546844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9439160823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96895098686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.96600592136383</t>
@@ -2060,61 +2060,61 @@
     <t xml:space="preserve">2.02049422264099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04552984237671</t>
+    <t xml:space="preserve">2.04552960395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.03374862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05436587333679</t>
+    <t xml:space="preserve">2.05436563491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.02785754203796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227591514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04111194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03816628456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01018595695496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00871276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99251413345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02638506889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07940077781677</t>
+    <t xml:space="preserve">2.03227567672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04111170768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03816652297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01018571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00871300697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9925137758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02638530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07940101623535</t>
   </si>
   <si>
     <t xml:space="preserve">2.06467413902283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0720374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06172919273376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03522109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933049201965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614708900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645583152771</t>
+    <t xml:space="preserve">2.07203769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03522086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645535469055</t>
   </si>
   <si>
     <t xml:space="preserve">2.08676433563232</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">2.05731081962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07351016998291</t>
+    <t xml:space="preserve">2.07351040840149</t>
   </si>
   <si>
     <t xml:space="preserve">2.04700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00282263755798</t>
+    <t xml:space="preserve">2.0028223991394</t>
   </si>
   <si>
     <t xml:space="preserve">2.01313090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01460385322571</t>
+    <t xml:space="preserve">2.01460409164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.04258441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1117992401123</t>
+    <t xml:space="preserve">2.11179947853088</t>
   </si>
   <si>
     <t xml:space="preserve">2.08087348937988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749831199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11032700538635</t>
+    <t xml:space="preserve">2.07498288154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11032652854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">2.10885429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12652635574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17659664154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20457720756531</t>
+    <t xml:space="preserve">2.12652611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17659687995911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20457744598389</t>
   </si>
   <si>
     <t xml:space="preserve">2.19426870346069</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">2.2458119392395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21341371536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20899534225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21783137321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20163226127625</t>
+    <t xml:space="preserve">2.22519469261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21341347694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20899510383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2178316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20163202285767</t>
   </si>
   <si>
     <t xml:space="preserve">2.20752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17365145683289</t>
+    <t xml:space="preserve">2.17365097999573</t>
   </si>
   <si>
     <t xml:space="preserve">2.23255801200867</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">2.21635890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20310473442078</t>
+    <t xml:space="preserve">2.20310497283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.24728465080261</t>
@@ -2219,13 +2219,13 @@
     <t xml:space="preserve">2.26201128959656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25022983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1147449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11621737480164</t>
+    <t xml:space="preserve">2.25023007392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11474466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11621761322021</t>
   </si>
   <si>
     <t xml:space="preserve">2.15303421020508</t>
@@ -2234,22 +2234,22 @@
     <t xml:space="preserve">2.13094425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0249125957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08823704719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10296368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9822051525116</t>
+    <t xml:space="preserve">2.02491235733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08823680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1029634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220527172089</t>
   </si>
   <si>
     <t xml:space="preserve">1.83641159534454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65380120277405</t>
+    <t xml:space="preserve">1.65380132198334</t>
   </si>
   <si>
     <t xml:space="preserve">1.63318383693695</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.38724899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42922008037567</t>
+    <t xml:space="preserve">1.42921996116638</t>
   </si>
   <si>
     <t xml:space="preserve">1.35190510749817</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">1.36442291736603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32171559333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3150886297226</t>
+    <t xml:space="preserve">1.32171547412872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31508851051331</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565741062164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37767684459686</t>
+    <t xml:space="preserve">1.37767672538757</t>
   </si>
   <si>
     <t xml:space="preserve">1.49475347995758</t>
@@ -2294,79 +2294,79 @@
     <t xml:space="preserve">1.58311343193054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65674638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477694272995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53598821163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249594688416</t>
+    <t xml:space="preserve">1.65674662590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071461200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54776954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53598809242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
     <t xml:space="preserve">1.56102323532104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55365991592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54924213886261</t>
+    <t xml:space="preserve">1.55366003513336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">1.54187881946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58164072036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60225796699524</t>
+    <t xml:space="preserve">1.58164083957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60225808620453</t>
   </si>
   <si>
     <t xml:space="preserve">1.62434792518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61256659030914</t>
+    <t xml:space="preserve">1.61256670951843</t>
   </si>
   <si>
     <t xml:space="preserve">1.61698472499847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62287509441376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64643800258636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65527391433716</t>
+    <t xml:space="preserve">1.62287533283234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64643788337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65527379512787</t>
   </si>
   <si>
     <t xml:space="preserve">1.67589116096497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66705513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349246025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520339012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57575023174286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58753132820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55807793140411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427752017975</t>
+    <t xml:space="preserve">1.66705524921417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349257946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520350933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57575011253357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.587531208992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5580780506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427740097046</t>
   </si>
   <si>
     <t xml:space="preserve">1.59047663211823</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">1.59784007072449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64202010631561</t>
+    <t xml:space="preserve">1.64201998710632</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558241844177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62876570224762</t>
+    <t xml:space="preserve">1.6287659406662</t>
   </si>
   <si>
     <t xml:space="preserve">1.61109399795532</t>
@@ -2390,22 +2390,22 @@
     <t xml:space="preserve">1.6788364648819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71859860420227</t>
+    <t xml:space="preserve">1.71859836578369</t>
   </si>
   <si>
     <t xml:space="preserve">1.76572370529175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75836038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72007119655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70828950405121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907468318939</t>
+    <t xml:space="preserve">1.75836050510406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72007095813751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6390745639801</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821933746338</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">1.70534443855286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71123516559601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77756798267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71468603610992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69781529903412</t>
+    <t xml:space="preserve">1.71123492717743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77756810188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836574077606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71468591690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69781517982483</t>
   </si>
   <si>
     <t xml:space="preserve">1.7116185426712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71621942520142</t>
+    <t xml:space="preserve">1.71621966362</t>
   </si>
   <si>
     <t xml:space="preserve">1.69168031215668</t>
@@ -2441,19 +2441,19 @@
     <t xml:space="preserve">1.70548379421234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72542190551758</t>
+    <t xml:space="preserve">1.72542202472687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73462414741516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73769164085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73002302646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68707942962646</t>
+    <t xml:space="preserve">1.73769176006317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73002314567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68707931041718</t>
   </si>
   <si>
     <t xml:space="preserve">1.68554556369781</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">1.65487134456635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68401193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7024165391922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235453128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70701742172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66867470741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64566886425018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65333759784698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65640509128571</t>
+    <t xml:space="preserve">1.68401181697845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70241641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235465049744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70701730251312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66867482662201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64566898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6533374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65640497207642</t>
   </si>
   <si>
     <t xml:space="preserve">1.62726449966431</t>
@@ -2498,58 +2498,58 @@
     <t xml:space="preserve">1.63646686077118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64720273017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67020833492279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407382488251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68247818946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7284893989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73615777492523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75609600543976</t>
+    <t xml:space="preserve">1.64720284938812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67020845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407358646393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68247807025909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72848916053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73615789413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75609624385834</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695565223694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088255405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7208206653595</t>
+    <t xml:space="preserve">1.70088243484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72082090377808</t>
   </si>
   <si>
     <t xml:space="preserve">1.69321405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68094432353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67174208164215</t>
+    <t xml:space="preserve">1.68094420433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67174220085144</t>
   </si>
   <si>
     <t xml:space="preserve">1.69934892654419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69014644622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008503437042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861305713654</t>
+    <t xml:space="preserve">1.67787683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69014656543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861281871796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65180397033691</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">1.64873647689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62573063373566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61959600448608</t>
+    <t xml:space="preserve">1.62573075294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61959612369537</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659039974213</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">1.54904544353485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55057919025421</t>
+    <t xml:space="preserve">1.55057907104492</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996674060822</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">1.48156237602234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49613261222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50303423404694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51990485191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54751181602478</t>
+    <t xml:space="preserve">1.49613237380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50303411483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51990497112274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5475115776062</t>
   </si>
   <si>
     <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53064095973969</t>
+    <t xml:space="preserve">1.53064107894897</t>
   </si>
   <si>
     <t xml:space="preserve">1.60425889492035</t>
@@ -2621,40 +2621,40 @@
     <t xml:space="preserve">1.60119152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61499488353729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58125329017639</t>
+    <t xml:space="preserve">1.614994764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58125340938568</t>
   </si>
   <si>
     <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60272514820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66100609302521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74075901508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069724559784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388815879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628131389618</t>
+    <t xml:space="preserve">1.60272526741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66100597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7407591342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388803958893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628143310547</t>
   </si>
   <si>
     <t xml:space="preserve">1.63186573982239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62879836559296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63033199310303</t>
+    <t xml:space="preserve">1.62879848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63033187389374</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889219045639</t>
@@ -2663,82 +2663,82 @@
     <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61039364337921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346113681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585453033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6395343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64260172843933</t>
+    <t xml:space="preserve">1.6103937625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346125602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585441112518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63953423500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64260160923004</t>
   </si>
   <si>
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947246551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66714096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62266337871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.555180311203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56131517887115</t>
+    <t xml:space="preserve">1.65947258472443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66714107990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6226634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55518043041229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55671393871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56131529808044</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55978143215179</t>
+    <t xml:space="preserve">1.57051742076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55978119373322</t>
   </si>
   <si>
     <t xml:space="preserve">1.58278703689575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60732626914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63339948654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62419712543488</t>
+    <t xml:space="preserve">1.60732638835907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63339936733246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62419724464417</t>
   </si>
   <si>
     <t xml:space="preserve">1.61192750930786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58432066440582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61806237697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106822013855</t>
+    <t xml:space="preserve">1.58432078361511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61806225776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106798171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.665607213974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67480957508087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71775329113007</t>
+    <t xml:space="preserve">1.67480969429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71775352954865</t>
   </si>
   <si>
     <t xml:space="preserve">1.75762975215912</t>
@@ -2747,34 +2747,34 @@
     <t xml:space="preserve">1.80517470836639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81744432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824208259583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670833587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80364096164703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79903972148895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290521144867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82051169872284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78063535690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79443871974945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83278179168701</t>
+    <t xml:space="preserve">1.8174444437027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80824196338654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670845508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80364108085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79903995990753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290509223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82051181793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78063547611237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79443883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83278167247772</t>
   </si>
   <si>
     <t xml:space="preserve">1.8097757101059</t>
@@ -2783,58 +2783,58 @@
     <t xml:space="preserve">1.82971394062042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885453224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891642093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818055152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498939990997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85578739643097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8634557723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965217113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87112426757812</t>
+    <t xml:space="preserve">1.85885465145111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891654014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85578715801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86345565319061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965240955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87112438678741</t>
   </si>
   <si>
     <t xml:space="preserve">1.89566338062286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90179836750031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91866934299469</t>
+    <t xml:space="preserve">1.90179824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9186692237854</t>
   </si>
   <si>
     <t xml:space="preserve">1.90026462078094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100060939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627606868744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95394456386566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9156014919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173659801483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713547706604</t>
+    <t xml:space="preserve">1.91100072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95394444465637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91560173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173635959625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713559627533</t>
   </si>
   <si>
     <t xml:space="preserve">1.93553984165192</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">1.97695016860962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96007931232452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382090568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00609064102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375889778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00915789604187</t>
+    <t xml:space="preserve">1.96007895469666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382066726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621406078339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00609040260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762438774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00915813446045</t>
   </si>
   <si>
     <t xml:space="preserve">1.9570118188858</t>
@@ -2870,49 +2870,49 @@
     <t xml:space="preserve">1.95854544639587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9692816734314</t>
+    <t xml:space="preserve">1.96928155422211</t>
   </si>
   <si>
     <t xml:space="preserve">1.97848379611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00302290916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01069164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01836013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0290961265564</t>
+    <t xml:space="preserve">2.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01069140434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01836037635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02909636497498</t>
   </si>
   <si>
     <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01682686805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01631903648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99563086032867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335112094879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97175979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94470584392548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92242586612701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91606044769287</t>
+    <t xml:space="preserve">2.01682639122009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01631927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99563074111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9733510017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97175967693329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94470596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9224259853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
     <t xml:space="preserve">1.9144686460495</t>
@@ -2921,43 +2921,43 @@
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401719093323</t>
+    <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
     <t xml:space="preserve">1.92720007896423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97971701622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96061968803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95743727684021</t>
+    <t xml:space="preserve">1.9797168970108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96062004566193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95743691921234</t>
   </si>
   <si>
     <t xml:space="preserve">1.96539413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97494268417358</t>
+    <t xml:space="preserve">1.974942445755</t>
   </si>
   <si>
     <t xml:space="preserve">1.98926544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857690811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287755966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94788873195648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449099063873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223347663879</t>
+    <t xml:space="preserve">1.96857702732086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287732124329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94788861274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449110984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223323822021</t>
   </si>
   <si>
     <t xml:space="preserve">2.01950216293335</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">2.04655623435974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06087875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04337358474731</t>
+    <t xml:space="preserve">2.06087899208069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04337334632874</t>
   </si>
   <si>
     <t xml:space="preserve">2.04814743995667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02427625656128</t>
+    <t xml:space="preserve">2.02427649497986</t>
   </si>
   <si>
     <t xml:space="preserve">2.06247019767761</t>
@@ -2996,46 +2996,46 @@
     <t xml:space="preserve">2.13726687431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14522361755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18819165229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20251441001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17068600654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15158939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12453556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11816954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08315849304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07042741775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10862112045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08952403068542</t>
+    <t xml:space="preserve">2.14522385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18819189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2025146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1706862449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15158915519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12453532218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1181697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10066437721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08315873146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07042717933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10862135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.089524269104</t>
   </si>
   <si>
     <t xml:space="preserve">2.0847499370575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08793306350708</t>
+    <t xml:space="preserve">2.0879328250885</t>
   </si>
   <si>
     <t xml:space="preserve">2.06565308570862</t>
@@ -3047,25 +3047,25 @@
     <t xml:space="preserve">2.14840650558472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12135219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11657857894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11339545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612652778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363217353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04178190231323</t>
+    <t xml:space="preserve">2.12135243415833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1165783405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11339521408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249230384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363241195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04178214073181</t>
   </si>
   <si>
     <t xml:space="preserve">2.05928754806519</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">2.04019045829773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09589004516602</t>
+    <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.02586770057678</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.03064203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98767364025116</t>
+    <t xml:space="preserve">1.98767387866974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01154518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15477204322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18341779708862</t>
+    <t xml:space="preserve">2.15477228164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18341755867004</t>
   </si>
   <si>
     <t xml:space="preserve">2.18978333473206</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">2.18023490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16113805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21842861175537</t>
+    <t xml:space="preserve">2.16113781929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20569753646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21842885017395</t>
   </si>
   <si>
     <t xml:space="preserve">2.29163360595703</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">2.27412819862366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25343990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29481649398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23593401908875</t>
+    <t xml:space="preserve">2.2534396648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29481673240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23593425750732</t>
   </si>
   <si>
     <t xml:space="preserve">2.25025701522827</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.27571964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27890229225159</t>
+    <t xml:space="preserve">2.27890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.22161149978638</t>
@@ -3143,16 +3143,16 @@
     <t xml:space="preserve">2.200923204422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17546057701111</t>
+    <t xml:space="preserve">2.17546033859253</t>
   </si>
   <si>
     <t xml:space="preserve">2.19296598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19774055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10384678840637</t>
+    <t xml:space="preserve">2.19774031639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10384702682495</t>
   </si>
   <si>
     <t xml:space="preserve">2.15795493125916</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">2.12930965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12771844863892</t>
+    <t xml:space="preserve">2.12771797180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.10702967643738</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">2.07520151138306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07201862335205</t>
+    <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
     <t xml:space="preserve">2.086341381073</t>
@@ -3185,73 +3185,73 @@
     <t xml:space="preserve">2.14204096794128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09748101234436</t>
+    <t xml:space="preserve">2.09748148918152</t>
   </si>
   <si>
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06883597373962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01472806930542</t>
+    <t xml:space="preserve">2.09111547470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06883573532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01472783088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9781254529953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97016823291779</t>
+    <t xml:space="preserve">1.97812557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97016835212708</t>
   </si>
   <si>
     <t xml:space="preserve">2.03700757026672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11976099014282</t>
+    <t xml:space="preserve">2.1197612285614</t>
   </si>
   <si>
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130810260773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02109336853027</t>
+    <t xml:space="preserve">1.98130822181702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02109360694885</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91128623485565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8937805891037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969467163086</t>
+    <t xml:space="preserve">1.91128611564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89378070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969479084015</t>
   </si>
   <si>
     <t xml:space="preserve">2.00677084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0019965171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90651178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8126186132431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79193043708801</t>
+    <t xml:space="preserve">2.00199675559998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90651190280914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945783138275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261849403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79193019866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.7553277015686</t>
@@ -3266,103 +3266,103 @@
     <t xml:space="preserve">1.83330678939819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922075271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83171534538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534968852997</t>
+    <t xml:space="preserve">1.84922087192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83171546459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534980773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110271692276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82694113254547</t>
+    <t xml:space="preserve">1.82694137096405</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444665908813</t>
+    <t xml:space="preserve">1.84444689750671</t>
   </si>
   <si>
     <t xml:space="preserve">1.88423216342926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8380811214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240387916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104927539825</t>
+    <t xml:space="preserve">1.83808100223541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240375995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104939460754</t>
   </si>
   <si>
     <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89537179470062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96698534488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99881398677826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01791095733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01313638687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98289966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00358819961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94311428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95107138156891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9542543888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786650657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90173780918121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96221148967743</t>
+    <t xml:space="preserve">1.8953720331192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96698546409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99881386756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01791071891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313662528992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98289978504181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0035879611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94311439990997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197453022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107114315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95425426959991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786626815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90173768997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93833994865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96221125125885</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038332462311</t>
+    <t xml:space="preserve">1.93038320541382</t>
   </si>
   <si>
     <t xml:space="preserve">1.93993151187897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90014612674713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91765165328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91924297809601</t>
+    <t xml:space="preserve">1.90014636516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91765177249908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91924333572388</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285545349121</t>
@@ -3380,28 +3380,28 @@
     <t xml:space="preserve">1.66143441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65984296798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69007980823517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711165428162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6168749332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483179569244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65506863594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70758521556854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6964453458786</t>
+    <t xml:space="preserve">1.65984284877777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69007992744446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711153507233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61687481403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483191490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65506875514984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70758533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69644546508789</t>
   </si>
   <si>
     <t xml:space="preserve">1.68053138256073</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68848824501038</t>
+    <t xml:space="preserve">1.68848836421967</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435811519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58345520496368</t>
+    <t xml:space="preserve">1.58345508575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">1.57788527011871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58504664897919</t>
+    <t xml:space="preserve">1.5850465297699</t>
   </si>
   <si>
     <t xml:space="preserve">1.58743369579315</t>
@@ -3434,49 +3434,49 @@
     <t xml:space="preserve">1.54128277301788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47842192649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51025021076202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53383469581604</t>
+    <t xml:space="preserve">1.4784220457077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51025009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53383481502533</t>
   </si>
   <si>
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446163654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5026695728302</t>
+    <t xml:space="preserve">1.51446175575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50266945362091</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51698863506317</t>
+    <t xml:space="preserve">1.51698851585388</t>
   </si>
   <si>
     <t xml:space="preserve">1.50856566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5136194229126</t>
+    <t xml:space="preserve">1.51361954212189</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54815399646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48835027217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47487342357635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49087715148926</t>
+    <t xml:space="preserve">1.5481538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48835039138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47487354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49087727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171960353851</t>
+    <t xml:space="preserve">1.49171948432922</t>
   </si>
   <si>
     <t xml:space="preserve">1.46645045280457</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">1.45718514919281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41591215133667</t>
+    <t xml:space="preserve">1.41591227054596</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201238155365</t>
@@ -3515,25 +3515,25 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3990660905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3620046377182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34347414970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34178960323334</t>
+    <t xml:space="preserve">1.39906620979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200487613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34347426891327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34178948402405</t>
   </si>
   <si>
     <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26177060604095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27777445316315</t>
+    <t xml:space="preserve">1.26177072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27777433395386</t>
   </si>
   <si>
     <t xml:space="preserve">1.22892081737518</t>
@@ -3545,10 +3545,10 @@
     <t xml:space="preserve">1.23229014873505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22976315021515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29209363460541</t>
+    <t xml:space="preserve">1.22976326942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2920937538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.31988966464996</t>
@@ -3557,25 +3557,25 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144781589508</t>
+    <t xml:space="preserve">1.23144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21712863445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2255517244339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20365166664124</t>
+    <t xml:space="preserve">1.21712875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22555160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20365178585052</t>
   </si>
   <si>
     <t xml:space="preserve">1.20533633232117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.175013422966</t>
+    <t xml:space="preserve">1.17501330375671</t>
   </si>
   <si>
     <t xml:space="preserve">1.13289821147919</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">1.14637506008148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10173296928406</t>
+    <t xml:space="preserve">1.10173308849335</t>
   </si>
   <si>
     <t xml:space="preserve">1.11942136287689</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">1.14300584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16911733150482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965539455414</t>
+    <t xml:space="preserve">1.16911721229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965551376343</t>
   </si>
   <si>
     <t xml:space="preserve">1.16490578651428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13710963726044</t>
+    <t xml:space="preserve">1.13710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">1.12279057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0815178155899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10425996780396</t>
+    <t xml:space="preserve">1.08151769638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10425984859467</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553272724152</t>
+    <t xml:space="preserve">1.14553284645081</t>
   </si>
   <si>
     <t xml:space="preserve">1.18427884578705</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">1.22470927238464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26008605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29462051391602</t>
+    <t xml:space="preserve">1.2600861787796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29462039470673</t>
   </si>
   <si>
     <t xml:space="preserve">1.28367066383362</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">1.26682448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26935148239136</t>
+    <t xml:space="preserve">1.26935136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.28030133247375</t>
@@ -3665,10 +3665,10 @@
     <t xml:space="preserve">1.24829387664795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24492454528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25334763526917</t>
+    <t xml:space="preserve">1.24492466449738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25334775447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818624019623</t>
@@ -3680,34 +3680,34 @@
     <t xml:space="preserve">1.32325887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31567811965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31652045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3299971818924</t>
+    <t xml:space="preserve">1.31567823886871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3165203332901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32999730110168</t>
   </si>
   <si>
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915496826172</t>
+    <t xml:space="preserve">1.32915484905243</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021269321442</t>
+    <t xml:space="preserve">1.35021257400513</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35358166694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32747042179108</t>
+    <t xml:space="preserve">1.3535817861557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32747030258179</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">1.34937024116516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.367058634758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32662808895111</t>
+    <t xml:space="preserve">1.36705875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32662796974182</t>
   </si>
   <si>
     <t xml:space="preserve">1.33589339256287</t>
@@ -3731,25 +3731,25 @@
     <t xml:space="preserve">1.29546272754669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30135893821716</t>
+    <t xml:space="preserve">1.30135881900787</t>
   </si>
   <si>
     <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2365015745163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25503218173981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23734390735626</t>
+    <t xml:space="preserve">1.23650169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2550323009491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23734378814697</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039032936096</t>
+    <t xml:space="preserve">1.21039021015167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3767,22 +3767,22 @@
     <t xml:space="preserve">1.37127017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36958563327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43865430355072</t>
+    <t xml:space="preserve">1.3695855140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43865442276001</t>
   </si>
   <si>
     <t xml:space="preserve">1.44539284706116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4656081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4041200876236</t>
+    <t xml:space="preserve">1.46139657497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46560800075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40411996841431</t>
   </si>
   <si>
     <t xml:space="preserve">1.38222014904022</t>
@@ -3791,10 +3791,10 @@
     <t xml:space="preserve">1.39822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41338527202606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43360066413879</t>
+    <t xml:space="preserve">1.41338539123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4336005449295</t>
   </si>
   <si>
     <t xml:space="preserve">1.44370830059052</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42265057563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44623517990112</t>
+    <t xml:space="preserve">1.42265069484711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44623506069183</t>
   </si>
   <si>
     <t xml:space="preserve">1.39232778549194</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770457267761</t>
+    <t xml:space="preserve">1.42770445346832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727378845215</t>
+    <t xml:space="preserve">1.38727390766144</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">1.39317011833191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37800860404968</t>
+    <t xml:space="preserve">1.37800848484039</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548172473907</t>
@@ -3848,19 +3848,19 @@
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496218204498</t>
+    <t xml:space="preserve">1.40496230125427</t>
   </si>
   <si>
     <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37716639041901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34515881538391</t>
+    <t xml:space="preserve">1.37716627120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431636333466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34515869617462</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">1.35442411899567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34094715118408</t>
+    <t xml:space="preserve">1.34094727039337</t>
   </si>
   <si>
     <t xml:space="preserve">1.31230890750885</t>
@@ -3890,22 +3890,22 @@
     <t xml:space="preserve">1.42686212062836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4470773935318</t>
+    <t xml:space="preserve">1.44707751274109</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48329651355743</t>
+    <t xml:space="preserve">1.48329663276672</t>
   </si>
   <si>
     <t xml:space="preserve">1.47655808925629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53888845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5666846036911</t>
+    <t xml:space="preserve">1.53888857364655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56668448448181</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61132669448853</t>
+    <t xml:space="preserve">1.61132657527924</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
@@ -3929,22 +3929,22 @@
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942663669586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60037672519684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784960746765</t>
+    <t xml:space="preserve">1.58942675590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60037660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59784972667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64754557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65007269382477</t>
+    <t xml:space="preserve">1.64754569530487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
     <t xml:space="preserve">1.62396109104156</t>
@@ -3953,16 +3953,16 @@
     <t xml:space="preserve">1.59953439235687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6146959066391</t>
+    <t xml:space="preserve">1.61469602584839</t>
   </si>
   <si>
     <t xml:space="preserve">1.63322651386261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806511878967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61048436164856</t>
+    <t xml:space="preserve">1.61806499958038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61048424243927</t>
   </si>
   <si>
     <t xml:space="preserve">1.64249193668365</t>
@@ -3971,19 +3971,19 @@
     <t xml:space="preserve">1.66186487674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62227654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774220943451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62480342388153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61385345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795736312866</t>
+    <t xml:space="preserve">1.62227666378021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774209022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62480354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61385357379913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795748233795</t>
   </si>
   <si>
     <t xml:space="preserve">1.58100366592407</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">1.58353066444397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57089602947235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57594990730286</t>
+    <t xml:space="preserve">1.57089614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57595002651215</t>
   </si>
   <si>
     <t xml:space="preserve">1.58437299728394</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.58184599876404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57173836231232</t>
+    <t xml:space="preserve">1.57173848152161</t>
   </si>
   <si>
     <t xml:space="preserve">1.59026908874512</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53087472915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5210268497467</t>
+    <t xml:space="preserve">1.5308746099472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52102696895599</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357881069183</t>
+    <t xml:space="preserve">1.47357869148254</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4950647354126</t>
+    <t xml:space="preserve">1.49506461620331</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4091,52 +4091,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192223072052</t>
+    <t xml:space="preserve">1.52192211151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070395469666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308514118195</t>
+    <t xml:space="preserve">1.61144697666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070407390594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308526039124</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786604881287</t>
+    <t xml:space="preserve">1.60786592960358</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039935588837</t>
+    <t xml:space="preserve">1.62039947509766</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801816940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773210525513</t>
+    <t xml:space="preserve">1.59801828861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773198604584</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937038898468</t>
+    <t xml:space="preserve">1.56937026977539</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502802371979</t>
+    <t xml:space="preserve">1.6150279045105</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.582799077034</t>
+    <t xml:space="preserve">1.58279895782471</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769527435303</t>
+    <t xml:space="preserve">1.67769539356232</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575251102448</t>
+    <t xml:space="preserve">1.68575263023376</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66426658630371</t>
+    <t xml:space="preserve">1.664266705513</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977210044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887671947479</t>
+    <t xml:space="preserve">1.71977198123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843829631805</t>
+    <t xml:space="preserve">1.68843841552734</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4226,16 +4226,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159933567047</t>
+    <t xml:space="preserve">1.60159921646118</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340803623199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399869918823</t>
+    <t xml:space="preserve">1.54340815544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4256,25 +4256,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234223842621</t>
+    <t xml:space="preserve">1.61234211921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112408161163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350526809692</t>
+    <t xml:space="preserve">1.63024723529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112420082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350538730621</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74573421478271</t>
+    <t xml:space="preserve">1.745734333992</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201934337616</t>
+    <t xml:space="preserve">1.69201922416687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4304,10 +4304,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691565990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7940776348114</t>
+    <t xml:space="preserve">1.78691577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79407751560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525907993317</t>
+    <t xml:space="preserve">1.83525896072388</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272553443909</t>
+    <t xml:space="preserve">1.82272565364838</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558197498322</t>
+    <t xml:space="preserve">1.75558185577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76453447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857235908508</t>
+    <t xml:space="preserve">1.7645343542099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857223987579</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723843574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859065532684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874277591705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009499549866</t>
+    <t xml:space="preserve">1.70723855495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859053611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874289512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009487628937</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740921020508</t>
+    <t xml:space="preserve">1.63740909099579</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6409900188446</t>
+    <t xml:space="preserve">1.63919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64099013805389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693395614624</t>
+    <t xml:space="preserve">1.72693407535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041789054871</t>
+    <t xml:space="preserve">1.56041777133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458948135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609382152557</t>
+    <t xml:space="preserve">1.58458960056305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609394073486</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205617427826</t>
+    <t xml:space="preserve">1.57205605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278078079224</t>
+    <t xml:space="preserve">1.64278066158295</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4529,10 +4529,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754315376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129473686218</t>
+    <t xml:space="preserve">1.68754303455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129461765289</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708631515503</t>
+    <t xml:space="preserve">1.71708619594574</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274383068085</t>
+    <t xml:space="preserve">1.76274394989014</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602051734924</t>
+    <t xml:space="preserve">1.78602039813995</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -70770,27 +70770,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6927430556</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>2026989</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>2.57800006866455</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>2.5220000743866</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>2.55200004577637</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>2.53600001335144</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1720</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>1566469</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>2.55200004577637</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>2.50799989700317</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>2.54200005531311</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>1264400</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>2.54800009727478</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>2.50600004196167</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>2.52999997138977</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>2.54800009727478</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1771</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6911574074</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>1567443</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>2.55599999427795</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>2.53399991989136</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1718</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469235897064</t>
+    <t xml:space="preserve">0.933469414710999</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806130886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92702728509903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921873509883881</t>
+    <t xml:space="preserve">0.923806190490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927027106285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873569488525</t>
   </si>
   <si>
     <t xml:space="preserve">0.901902794837952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898037433624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652355670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835356235504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643725395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863894045352936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346383094788</t>
+    <t xml:space="preserve">0.898037493228912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652474880219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835475444794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643606185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893926143646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346442699432</t>
   </si>
   <si>
     <t xml:space="preserve">0.851653933525085</t>
@@ -80,49 +80,49 @@
     <t xml:space="preserve">0.818154573440552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836192727088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163382530212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451736927032</t>
+    <t xml:space="preserve">0.836192548274994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163442134857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451856136322</t>
   </si>
   <si>
     <t xml:space="preserve">0.869692027568817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886441648006439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344864845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374149799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279004096985</t>
+    <t xml:space="preserve">0.88644152879715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489771366119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374030590057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551917552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84327906370163</t>
   </si>
   <si>
     <t xml:space="preserve">0.818798959255219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837481021881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825241088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432838916779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869047820568085</t>
+    <t xml:space="preserve">0.837481141090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825241029262543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432958126068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86904776096344</t>
   </si>
   <si>
     <t xml:space="preserve">0.876778304576874</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">0.894172251224518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923161864280701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671372890472</t>
+    <t xml:space="preserve">0.923161923885345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671551704407</t>
   </si>
   <si>
     <t xml:space="preserve">0.914142966270447</t>
@@ -143,61 +143,61 @@
     <t xml:space="preserve">0.945709586143494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919296622276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075527667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941199958324432</t>
+    <t xml:space="preserve">0.919296741485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075587272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941200017929077</t>
   </si>
   <si>
     <t xml:space="preserve">0.947642028331757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930892527103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113681316376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412303447723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918008208274841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954084455966949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391827583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179601669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01270818710327</t>
+    <t xml:space="preserve">0.930892467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008029460907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954084277153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391767978668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0127078294754</t>
   </si>
   <si>
     <t xml:space="preserve">1.02881348133087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01657342910767</t>
+    <t xml:space="preserve">1.01657330989838</t>
   </si>
   <si>
     <t xml:space="preserve">1.02365958690643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00819861888885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175631046295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0049774646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755441188812</t>
+    <t xml:space="preserve">1.00819849967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497722625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755417346954</t>
   </si>
   <si>
     <t xml:space="preserve">1.02172696590424</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.02237117290497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999823689460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01141953468323</t>
+    <t xml:space="preserve">0.999823570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01141965389252</t>
   </si>
   <si>
     <t xml:space="preserve">1.01206374168396</t>
@@ -221,31 +221,31 @@
     <t xml:space="preserve">1.01786172389984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02430391311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01850581169128</t>
+    <t xml:space="preserve">1.02430379390717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01850593090057</t>
   </si>
   <si>
     <t xml:space="preserve">1.02688074111938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203439712524</t>
+    <t xml:space="preserve">1.03203415870667</t>
   </si>
   <si>
     <t xml:space="preserve">1.0249480009079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0172176361084</t>
+    <t xml:space="preserve">1.01721739768982</t>
   </si>
   <si>
     <t xml:space="preserve">1.00562155246735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988872110843658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00368893146515</t>
+    <t xml:space="preserve">0.988871872425079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00368881225586</t>
   </si>
   <si>
     <t xml:space="preserve">1.03525567054749</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.04040920734406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03396701812744</t>
+    <t xml:space="preserve">1.03396713733673</t>
   </si>
   <si>
     <t xml:space="preserve">1.02945756912231</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">1.03010189533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01592898368835</t>
+    <t xml:space="preserve">1.01592922210693</t>
   </si>
   <si>
     <t xml:space="preserve">0.992093026638031</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">1.033322930336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00948703289032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958387851715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314180850983</t>
+    <t xml:space="preserve">1.00948691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958268642426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995313882827759</t>
   </si>
   <si>
     <t xml:space="preserve">1.02108287811279</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">1.0494282245636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07519698143005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295680999756</t>
+    <t xml:space="preserve">1.07519710063934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295692920685</t>
   </si>
   <si>
     <t xml:space="preserve">1.05715882778168</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">1.07326412200928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06231272220612</t>
+    <t xml:space="preserve">1.06231260299683</t>
   </si>
   <si>
     <t xml:space="preserve">1.0474956035614</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">1.06360101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06166839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06811058521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04620718955994</t>
+    <t xml:space="preserve">1.0616682767868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06811046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04620730876923</t>
   </si>
   <si>
     <t xml:space="preserve">0.977276086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968256950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965036034584045</t>
+    <t xml:space="preserve">0.968257009983063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965035915374756</t>
   </si>
   <si>
     <t xml:space="preserve">0.978564500808716</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">0.962522506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979232966899872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517227649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712280750275</t>
+    <t xml:space="preserve">0.979232907295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907712042331696</t>
   </si>
   <si>
     <t xml:space="preserve">0.87696498632431</t>
@@ -350,37 +350,37 @@
     <t xml:space="preserve">0.903701603412628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895680606365204</t>
+    <t xml:space="preserve">0.895680785179138</t>
   </si>
   <si>
     <t xml:space="preserve">0.929101586341858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935117423534393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127802848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909049093723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033256530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915733277797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925090968608856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775093078613</t>
+    <t xml:space="preserve">0.935117304325104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127862453461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048855304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033137321472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91573303937912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925091087818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775271892548</t>
   </si>
   <si>
     <t xml:space="preserve">0.925759434700012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912391126155853</t>
+    <t xml:space="preserve">0.912391006946564</t>
   </si>
   <si>
     <t xml:space="preserve">0.921080470085144</t>
@@ -389,148 +389,148 @@
     <t xml:space="preserve">0.92709618806839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945143640041351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122583389282</t>
+    <t xml:space="preserve">0.945143580436707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122523784637</t>
   </si>
   <si>
     <t xml:space="preserve">0.95583838224411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953164577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527785778046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965196192264557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982575058937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972548842430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217129707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580338001251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987253785133362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99527508020401</t>
+    <t xml:space="preserve">0.95316469669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965195953845978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982574939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911693096161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97254866361618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253963947296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99527496099472</t>
   </si>
   <si>
     <t xml:space="preserve">0.98925918340683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99260139465332</t>
+    <t xml:space="preserve">0.992601335048676</t>
   </si>
   <si>
     <t xml:space="preserve">0.975890934467316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951827883720398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950491011142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485791683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94113302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501450061798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864658355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917150974274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927589893341</t>
+    <t xml:space="preserve">0.951827943325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950490951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485732078552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941133081912994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501509666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864539146423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927530288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.01265382766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02000641822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99193286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988590836524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996611833572388</t>
+    <t xml:space="preserve">1.02000653743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932988166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988590717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996611773967743</t>
   </si>
   <si>
     <t xml:space="preserve">0.979901373386383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967201352119446</t>
+    <t xml:space="preserve">0.967201471328735</t>
   </si>
   <si>
     <t xml:space="preserve">0.98658549785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977896213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885595798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943486690521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401697635651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00864338874817</t>
+    <t xml:space="preserve">0.977896153926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885476589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943307876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00864326953888</t>
   </si>
   <si>
     <t xml:space="preserve">1.00262761116028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206750392914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975222408771515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248625278473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02936434745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05342733860016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05543255805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07615375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08952212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09687447547913</t>
+    <t xml:space="preserve">0.969206690788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97522234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248744487762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0293642282486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05342721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05543267726898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0761536359787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08952188491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420096874237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09687459468842</t>
   </si>
   <si>
     <t xml:space="preserve">1.07013785839081</t>
@@ -542,175 +542,175 @@
     <t xml:space="preserve">1.09353244304657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06479060649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0627852678299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04741168022156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06077992916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06813263893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05209052562714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957843542098999</t>
+    <t xml:space="preserve">1.07749044895172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06479048728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06278502941132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04741144180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06078004837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06813251972198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05209040641785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957843601703644</t>
   </si>
   <si>
     <t xml:space="preserve">0.953833043575287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946480274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93578577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942469835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780372142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727998733521</t>
+    <t xml:space="preserve">0.946480453014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93578565120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942469954490662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780312538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727939128876</t>
   </si>
   <si>
     <t xml:space="preserve">0.917738437652588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94180154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406903743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538045883179</t>
+    <t xml:space="preserve">0.941801369190216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406784534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538224697113</t>
   </si>
   <si>
     <t xml:space="preserve">0.967869758605957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980569779872894</t>
+    <t xml:space="preserve">0.98056960105896</t>
   </si>
   <si>
     <t xml:space="preserve">0.994606554508209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99794864654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
+    <t xml:space="preserve">0.997948527336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332211494446</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532757282257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01599597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02869606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203809261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04005908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04473781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070116043091</t>
+    <t xml:space="preserve">1.01599586009979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02869582176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203797340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04005885124207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04473793506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03070104122162</t>
   </si>
   <si>
     <t xml:space="preserve">1.01733267307281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.036048412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874861240387</t>
+    <t xml:space="preserve">1.03604829311371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874837398529</t>
   </si>
   <si>
     <t xml:space="preserve">1.04941689968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05275905132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0500853061676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04072737693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04607486724854</t>
+    <t xml:space="preserve">1.05275893211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05008518695831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04072749614716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04607474803925</t>
   </si>
   <si>
     <t xml:space="preserve">1.02468538284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01064848899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530123710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0300327539444</t>
+    <t xml:space="preserve">1.0106486082077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530135631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03003263473511</t>
   </si>
   <si>
     <t xml:space="preserve">1.0427325963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334845066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05676925182343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06412208080292</t>
+    <t xml:space="preserve">1.02334868907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05676937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06412184238434</t>
   </si>
   <si>
     <t xml:space="preserve">1.05610108375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810618400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484327793121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07080626487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0821692943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06880116462708</t>
+    <t xml:space="preserve">1.05810630321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484303951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07080614566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08216941356659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06880104541779</t>
   </si>
   <si>
     <t xml:space="preserve">1.07815897464752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08283793926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08818519115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0962061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09954833984375</t>
+    <t xml:space="preserve">1.08283770084381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08818507194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09620606899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09954810142517</t>
   </si>
   <si>
     <t xml:space="preserve">1.09754288196564</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">1.18978464603424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22120046615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988986968994</t>
+    <t xml:space="preserve">1.22120022773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988975048065</t>
   </si>
   <si>
     <t xml:space="preserve">1.24058449268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26665270328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28002095222473</t>
+    <t xml:space="preserve">1.26665282249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28002107143402</t>
   </si>
   <si>
     <t xml:space="preserve">1.28336322307587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29405784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932644844055</t>
+    <t xml:space="preserve">1.29405796527863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133166790009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932656764984</t>
   </si>
   <si>
     <t xml:space="preserve">1.30074203014374</t>
@@ -761,31 +761,31 @@
     <t xml:space="preserve">1.30007374286652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3114367723465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29004728794098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28871035575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29739999771118</t>
+    <t xml:space="preserve">1.31143689155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29004740715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28871059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937900066376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27200031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2593001127243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29673171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806852340698</t>
+    <t xml:space="preserve">1.27200019359589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25930023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29673159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2980682849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.31076836585999</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">1.32814741134644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30341589450836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683693408966</t>
+    <t xml:space="preserve">1.30341577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683657646179</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349466323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35421562194824</t>
+    <t xml:space="preserve">1.35421550273895</t>
   </si>
   <si>
     <t xml:space="preserve">1.37025773525238</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">1.37426805496216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36491024494171</t>
+    <t xml:space="preserve">1.364910364151</t>
   </si>
   <si>
     <t xml:space="preserve">1.37961554527283</t>
@@ -824,22 +824,22 @@
     <t xml:space="preserve">1.33616828918457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34886825084686</t>
+    <t xml:space="preserve">1.34886801242828</t>
   </si>
   <si>
     <t xml:space="preserve">1.3903101682663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41036248207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42105746269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175208568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4504679441452</t>
+    <t xml:space="preserve">1.4103627204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42105722427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046806335449</t>
   </si>
   <si>
     <t xml:space="preserve">1.39966809749603</t>
@@ -851,46 +851,46 @@
     <t xml:space="preserve">1.43442559242249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704702377319</t>
+    <t xml:space="preserve">1.4170469045639</t>
   </si>
   <si>
     <t xml:space="preserve">1.42239439487457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40902578830719</t>
+    <t xml:space="preserve">1.40902590751648</t>
   </si>
   <si>
     <t xml:space="preserve">1.43977320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44779396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052049636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46784675121307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116244792938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319412231445</t>
+    <t xml:space="preserve">1.44779407978058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052037715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46784687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116268634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319400310516</t>
   </si>
   <si>
     <t xml:space="preserve">1.46249949932098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46650993824005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48474228382111</t>
+    <t xml:space="preserve">1.46650981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
     <t xml:space="preserve">1.48336637020111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49024641513824</t>
+    <t xml:space="preserve">1.49024653434753</t>
   </si>
   <si>
     <t xml:space="preserve">1.47235810756683</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">1.42282092571259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44208538532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40630805492401</t>
+    <t xml:space="preserve">1.44208526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40630829334259</t>
   </si>
   <si>
     <t xml:space="preserve">1.3953001499176</t>
@@ -914,25 +914,25 @@
     <t xml:space="preserve">1.40080428123474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40218031406403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38429188728333</t>
+    <t xml:space="preserve">1.40218043327332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38429164886475</t>
   </si>
   <si>
     <t xml:space="preserve">1.4145644903183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42144477367401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43658125400543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43245303630829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42419683933258</t>
+    <t xml:space="preserve">1.42144465446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43658113479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43245315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42419672012329</t>
   </si>
   <si>
     <t xml:space="preserve">1.43107688426971</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">1.45997369289398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44621324539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46685385704041</t>
+    <t xml:space="preserve">1.44621348381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46685373783112</t>
   </si>
   <si>
     <t xml:space="preserve">1.48199033737183</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">1.46960580348969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44758927822113</t>
+    <t xml:space="preserve">1.44758951663971</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923827171326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50400686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125467777252</t>
+    <t xml:space="preserve">1.50400698184967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125479698181</t>
   </si>
   <si>
     <t xml:space="preserve">1.49987888336182</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">1.52602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54804003238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115974903107</t>
+    <t xml:space="preserve">1.54804015159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
     <t xml:space="preserve">1.52327144145966</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">1.54528796672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968878746033</t>
+    <t xml:space="preserve">1.57968866825104</t>
   </si>
   <si>
     <t xml:space="preserve">1.57831263542175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57556092739105</t>
+    <t xml:space="preserve">1.57556068897247</t>
   </si>
   <si>
     <t xml:space="preserve">1.57693672180176</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">1.54666376113892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55354416370392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592833995819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381700515747</t>
+    <t xml:space="preserve">1.55354428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381712436676</t>
   </si>
   <si>
     <t xml:space="preserve">1.5906970500946</t>
@@ -1025,40 +1025,40 @@
     <t xml:space="preserve">1.58656907081604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5824408531189</t>
+    <t xml:space="preserve">1.58244073390961</t>
   </si>
   <si>
     <t xml:space="preserve">1.60996150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63197815418243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711475372314</t>
+    <t xml:space="preserve">1.63197803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711487293243</t>
   </si>
   <si>
     <t xml:space="preserve">1.61408996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6058337688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6003292798996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5645524263382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978359699249</t>
+    <t xml:space="preserve">1.60583364963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455254554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978371620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.53565573692322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54391181468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180036067963</t>
+    <t xml:space="preserve">1.54391193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180047988892</t>
   </si>
   <si>
     <t xml:space="preserve">1.56042432785034</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">1.54941606521606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427982330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005679607391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868040561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61684167385101</t>
+    <t xml:space="preserve">1.53427970409393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005655765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234604358673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6168417930603</t>
   </si>
   <si>
     <t xml:space="preserve">1.62922608852386</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">1.57280874252319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61821782588959</t>
+    <t xml:space="preserve">1.6182177066803</t>
   </si>
   <si>
     <t xml:space="preserve">1.6250981092453</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">1.70353221893311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6980277299881</t>
+    <t xml:space="preserve">1.69802796840668</t>
   </si>
   <si>
     <t xml:space="preserve">1.69252383708954</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">1.65949892997742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64986670017242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785017490387</t>
+    <t xml:space="preserve">1.64986681938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785005569458</t>
   </si>
   <si>
     <t xml:space="preserve">1.6622508764267</t>
@@ -1139,61 +1139,61 @@
     <t xml:space="preserve">1.70490801334381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74894118309021</t>
+    <t xml:space="preserve">1.74894142150879</t>
   </si>
   <si>
     <t xml:space="preserve">1.73105263710022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72004461288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518073558807</t>
+    <t xml:space="preserve">1.72004437446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518085479736</t>
   </si>
   <si>
     <t xml:space="preserve">1.72830057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74618947505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7668297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233386039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545393466949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74068510532379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82049489021301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022240638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747010231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444555282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159832000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79297435283661</t>
+    <t xml:space="preserve">1.74618911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76682949066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77371001243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74068486690521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8204950094223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022228717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444543361664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159843921661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297423362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.76820576190948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75857365131378</t>
+    <t xml:space="preserve">1.7585734128952</t>
   </si>
   <si>
     <t xml:space="preserve">1.72554838657379</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">1.72967684268951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72142064571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499087810516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535864830017</t>
+    <t xml:space="preserve">1.72142052650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169336795807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499075889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535888671875</t>
   </si>
   <si>
     <t xml:space="preserve">1.75031721591949</t>
@@ -1220,91 +1220,91 @@
     <t xml:space="preserve">1.74481320381165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77921390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113574028015</t>
+    <t xml:space="preserve">1.77921402454376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113597869873</t>
   </si>
   <si>
     <t xml:space="preserve">1.83700752258301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85351991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86040043830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516879081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076773166656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710257053375</t>
+    <t xml:space="preserve">1.85351979732513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86039996147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516843318939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361496448517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123054981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710245132446</t>
   </si>
   <si>
     <t xml:space="preserve">1.79572629928589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82737505435944</t>
+    <t xml:space="preserve">1.82737517356873</t>
   </si>
   <si>
     <t xml:space="preserve">1.68564367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64573848247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63473010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
+    <t xml:space="preserve">1.6457382440567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738747596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.634730219841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151533603668</t>
   </si>
   <si>
     <t xml:space="preserve">1.6691312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68013954162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298641681671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500318050385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68701946735382</t>
+    <t xml:space="preserve">1.68013942241669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.642986536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500294208527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701958656311</t>
   </si>
   <si>
     <t xml:space="preserve">1.69114780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6333544254303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463541030884</t>
+    <t xml:space="preserve">1.63335406780243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463564872742</t>
   </si>
   <si>
     <t xml:space="preserve">1.71454036235809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70215594768524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426764011383</t>
+    <t xml:space="preserve">1.70215606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426752090454</t>
   </si>
   <si>
     <t xml:space="preserve">1.6787633895874</t>
@@ -1313,34 +1313,34 @@
     <t xml:space="preserve">1.65261888504028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75306928157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756526947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692501544952</t>
+    <t xml:space="preserve">1.75306951999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930907249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417283058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692477703094</t>
   </si>
   <si>
     <t xml:space="preserve">1.66362702846527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68289172649384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7131644487381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343717098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380494117737</t>
+    <t xml:space="preserve">1.68289148807526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316456794739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343693256378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380470275879</t>
   </si>
   <si>
     <t xml:space="preserve">1.74206113815308</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">1.68839573860168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65399467945099</t>
+    <t xml:space="preserve">1.65399479866028</t>
   </si>
   <si>
     <t xml:space="preserve">1.64849054813385</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">1.60720932483673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59757721424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620118141174</t>
+    <t xml:space="preserve">1.59757733345032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620130062103</t>
   </si>
   <si>
     <t xml:space="preserve">1.53290343284607</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">1.45034146308899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46134996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4764860868454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611843585968</t>
+    <t xml:space="preserve">1.46134984493256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47648596763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611831665039</t>
   </si>
   <si>
     <t xml:space="preserve">1.4751101732254</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">1.45722162723541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42832469940186</t>
+    <t xml:space="preserve">1.42832493782043</t>
   </si>
   <si>
     <t xml:space="preserve">1.51776719093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55079209804535</t>
+    <t xml:space="preserve">1.55079221725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.54542124271393</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">1.56530690193176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54826200008392</t>
+    <t xml:space="preserve">1.54826211929321</t>
   </si>
   <si>
     <t xml:space="preserve">1.52411460876465</t>
@@ -1418,40 +1418,40 @@
     <t xml:space="preserve">1.5312168598175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52127397060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837598323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672739982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536425113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513604640961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934007167816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62212383747101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945405483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5795111656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223793983459</t>
+    <t xml:space="preserve">1.52127385139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672751903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55536413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5951361656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507881641388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934019088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62212371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951128482819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223805904388</t>
   </si>
   <si>
     <t xml:space="preserve">1.60365843772888</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">1.62638533115387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61076068878174</t>
+    <t xml:space="preserve">1.61076045036316</t>
   </si>
   <si>
     <t xml:space="preserve">1.58803379535675</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.68178176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882678985596</t>
+    <t xml:space="preserve">1.69882655143738</t>
   </si>
   <si>
     <t xml:space="preserve">1.72013318538666</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">1.71729242801666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64911210536957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757750511169</t>
+    <t xml:space="preserve">1.64911198616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6675773859024</t>
   </si>
   <si>
     <t xml:space="preserve">1.67894077301025</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">1.67752063274384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67183887958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.643430352211</t>
+    <t xml:space="preserve">1.67183876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343047142029</t>
   </si>
   <si>
     <t xml:space="preserve">1.61928296089172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61786293983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5766704082489</t>
+    <t xml:space="preserve">1.61786282062531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667028903961</t>
   </si>
   <si>
     <t xml:space="preserve">1.56388664245605</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">1.55252325534821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55110287666321</t>
+    <t xml:space="preserve">1.55110275745392</t>
   </si>
   <si>
     <t xml:space="preserve">1.51701247692108</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">1.51559221744537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46871829032898</t>
+    <t xml:space="preserve">1.46871817111969</t>
   </si>
   <si>
     <t xml:space="preserve">1.43462800979614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741189479828</t>
+    <t xml:space="preserve">1.44741201400757</t>
   </si>
   <si>
     <t xml:space="preserve">1.45735478401184</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">1.47013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47297930717468</t>
+    <t xml:space="preserve">1.47297942638397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5326372385025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58377265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973937034607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275146007538</t>
+    <t xml:space="preserve">1.58377254009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973925113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275134086609</t>
   </si>
   <si>
     <t xml:space="preserve">1.4871838092804</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">1.50138807296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49996745586395</t>
+    <t xml:space="preserve">1.49996757507324</t>
   </si>
   <si>
     <t xml:space="preserve">1.49570620059967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41687285900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42184436321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911735057831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065195083618</t>
+    <t xml:space="preserve">1.41687262058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4218442440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065183162689</t>
   </si>
   <si>
     <t xml:space="preserve">1.37425994873047</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">1.37994158267975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37070894241333</t>
+    <t xml:space="preserve">1.37070906162262</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573755741119</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">1.37923157215118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37212955951691</t>
+    <t xml:space="preserve">1.37212944030762</t>
   </si>
   <si>
     <t xml:space="preserve">1.35579454898834</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">1.38633358478546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3643171787262</t>
+    <t xml:space="preserve">1.36431705951691</t>
   </si>
   <si>
     <t xml:space="preserve">1.39343571662903</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">1.46019566059113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45309352874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439968585968</t>
+    <t xml:space="preserve">1.45309364795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439992427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866129875183</t>
@@ -1664,28 +1664,28 @@
     <t xml:space="preserve">1.45593440532684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42894637584686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.440309882164</t>
+    <t xml:space="preserve">1.42894649505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44031000137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.39556646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37568056583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38704371452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201545715332</t>
+    <t xml:space="preserve">1.37568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3870438337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201521873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.3778110742569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40266859531403</t>
+    <t xml:space="preserve">1.40266847610474</t>
   </si>
   <si>
     <t xml:space="preserve">1.38136208057404</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">1.34940266609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320751190186</t>
+    <t xml:space="preserve">1.43178725242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320775032043</t>
   </si>
   <si>
     <t xml:space="preserve">1.42468523979187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4204238653183</t>
+    <t xml:space="preserve">1.42042398452759</t>
   </si>
   <si>
     <t xml:space="preserve">1.48150217533112</t>
@@ -1718,34 +1718,34 @@
     <t xml:space="preserve">1.51985359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48860418796539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428570270538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258012771606</t>
+    <t xml:space="preserve">1.4886040687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428582191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258024692535</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115998744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52553522586823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52979648113251</t>
+    <t xml:space="preserve">1.52553510665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52979636192322</t>
   </si>
   <si>
     <t xml:space="preserve">1.52695560455322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53405773639679</t>
+    <t xml:space="preserve">1.5340576171875</t>
   </si>
   <si>
     <t xml:space="preserve">1.51133108139038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5099104642868</t>
+    <t xml:space="preserve">1.50991034507751</t>
   </si>
   <si>
     <t xml:space="preserve">1.48008167743683</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">1.50706958770752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48292255401611</t>
+    <t xml:space="preserve">1.48292243480682</t>
   </si>
   <si>
     <t xml:space="preserve">1.48434269428253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50564920902252</t>
+    <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.53689849376678</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">1.61644220352173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62780559062958</t>
+    <t xml:space="preserve">1.62780570983887</t>
   </si>
   <si>
     <t xml:space="preserve">1.63206708431244</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496483325958</t>
+    <t xml:space="preserve">1.62496495246887</t>
   </si>
   <si>
     <t xml:space="preserve">1.5993971824646</t>
@@ -1790,61 +1790,61 @@
     <t xml:space="preserve">1.62070381641388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502194404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627122879028</t>
+    <t xml:space="preserve">1.61502182483673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627134799957</t>
   </si>
   <si>
     <t xml:space="preserve">1.61218106746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51417171955109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50422871112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576331138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303653717041</t>
+    <t xml:space="preserve">1.5141716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50422883033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4857634305954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303641796112</t>
   </si>
   <si>
     <t xml:space="preserve">1.45877516269684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49286532402039</t>
+    <t xml:space="preserve">1.49286544322968</t>
   </si>
   <si>
     <t xml:space="preserve">1.5567843914032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57809090614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58661329746246</t>
+    <t xml:space="preserve">1.5780907869339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58661341667175</t>
   </si>
   <si>
     <t xml:space="preserve">1.5738297700882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63916909694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450854301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166754722595</t>
+    <t xml:space="preserve">1.63916897773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450866222382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166742801666</t>
   </si>
   <si>
     <t xml:space="preserve">1.69172465801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69061768054962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69356310367584</t>
+    <t xml:space="preserve">1.69061779975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69356298446655</t>
   </si>
   <si>
     <t xml:space="preserve">1.69798123836517</t>
@@ -1856,25 +1856,25 @@
     <t xml:space="preserve">1.68325436115265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68619990348816</t>
+    <t xml:space="preserve">1.68619978427887</t>
   </si>
   <si>
     <t xml:space="preserve">1.72890710830688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75099718570709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277828216553</t>
+    <t xml:space="preserve">1.75099730491638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277852058411</t>
   </si>
   <si>
     <t xml:space="preserve">1.74510622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73332512378693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161419391632</t>
+    <t xml:space="preserve">1.73332524299622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161431312561</t>
   </si>
   <si>
     <t xml:space="preserve">1.77750515937805</t>
@@ -1883,73 +1883,73 @@
     <t xml:space="preserve">1.79812204837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80106770992279</t>
+    <t xml:space="preserve">1.8010675907135</t>
   </si>
   <si>
     <t xml:space="preserve">1.80548560619354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80401277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81137633323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455973625183</t>
+    <t xml:space="preserve">1.80401313304901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8113762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455961704254</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603220939636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76719629764557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216091632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239925384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73921573162079</t>
+    <t xml:space="preserve">1.76719617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216115474701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239913463593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7392156124115</t>
   </si>
   <si>
     <t xml:space="preserve">1.77014172077179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78486824035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78928649425507</t>
+    <t xml:space="preserve">1.78486847877502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7892861366272</t>
   </si>
   <si>
     <t xml:space="preserve">1.79664957523346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79517674446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370427131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78339540958405</t>
+    <t xml:space="preserve">1.79517686367035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370450973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78339564800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.79959487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80254030227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308666706085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7819230556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021236419678</t>
+    <t xml:space="preserve">1.80254018306732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192293643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493912220001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8202121257782</t>
   </si>
   <si>
     <t xml:space="preserve">1.81873953342438</t>
@@ -1958,55 +1958,55 @@
     <t xml:space="preserve">1.8216849565506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84966564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84819281101227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82904815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425087451935</t>
+    <t xml:space="preserve">1.8496652841568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84819304943085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82904803752899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425099372864</t>
   </si>
   <si>
     <t xml:space="preserve">1.81432139873505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80990350246429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199369907379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8614467382431</t>
+    <t xml:space="preserve">1.80990314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83199346065521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144697666168</t>
   </si>
   <si>
     <t xml:space="preserve">1.91593515872955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93655264377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9321346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127928256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042393684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569741725922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94244313240051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94980669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9615877866745</t>
+    <t xml:space="preserve">1.93655276298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93213474750519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127940177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042405605316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569729804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9424432516098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94980657100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158790588379</t>
   </si>
   <si>
     <t xml:space="preserve">1.98809552192688</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">2.00724077224731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.983677983284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987709522247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00576758384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98073267936707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97189652919769</t>
+    <t xml:space="preserve">1.98367810249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987721443176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98073256015778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9718964099884</t>
   </si>
   <si>
     <t xml:space="preserve">1.97631466388702</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">1.94391596317291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96895110607147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600615978241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484183311462</t>
+    <t xml:space="preserve">1.96895134449005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484171390533</t>
   </si>
   <si>
     <t xml:space="preserve">2.01754927635193</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">2.04847502708435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02049446105957</t>
+    <t xml:space="preserve">2.02049422264099</t>
   </si>
   <si>
     <t xml:space="preserve">2.04552984237671</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">2.03374862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05436563491821</t>
+    <t xml:space="preserve">2.05436587333679</t>
   </si>
   <si>
     <t xml:space="preserve">2.02785801887512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227591514587</t>
+    <t xml:space="preserve">2.03227567672729</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111170768738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03816676139832</t>
+    <t xml:space="preserve">2.03816652297974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01018571853638</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">1.99251389503479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02638530731201</t>
+    <t xml:space="preserve">2.02638506889343</t>
   </si>
   <si>
     <t xml:space="preserve">2.07940077781677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467413902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0720374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06172871589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03522109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02933049201965</t>
+    <t xml:space="preserve">2.06467437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07203793525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03522086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02933073043823</t>
   </si>
   <si>
     <t xml:space="preserve">2.06614708900452</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">2.07645559310913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08676433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02196717262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05731105804443</t>
+    <t xml:space="preserve">2.0867645740509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0219669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05731081962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.07351016998291</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">2.01460385322571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04258465766907</t>
+    <t xml:space="preserve">2.04258418083191</t>
   </si>
   <si>
     <t xml:space="preserve">2.11179971694946</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">2.08087372779846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749831199646</t>
+    <t xml:space="preserve">2.07498288154602</t>
   </si>
   <si>
     <t xml:space="preserve">2.11032676696777</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">2.17659687995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457768440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19426870346069</t>
+    <t xml:space="preserve">2.20457744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19426846504211</t>
   </si>
   <si>
     <t xml:space="preserve">2.24581217765808</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">2.21341347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20899534225464</t>
+    <t xml:space="preserve">2.20899558067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.2178316116333</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">2.20752263069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17365145683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23255801200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21930408477783</t>
+    <t xml:space="preserve">2.17365121841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23255825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21930432319641</t>
   </si>
   <si>
     <t xml:space="preserve">2.21635866165161</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">2.11474514007568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11621785163879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1530339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13094425201416</t>
+    <t xml:space="preserve">2.11621761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15303421020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13094449043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.0249125957489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08823704719543</t>
+    <t xml:space="preserve">2.08823680877686</t>
   </si>
   <si>
     <t xml:space="preserve">2.1029634475708</t>
@@ -2243,22 +2243,22 @@
     <t xml:space="preserve">1.9822051525116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83641159534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65380108356476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63318407535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38724899291992</t>
+    <t xml:space="preserve">1.83641135692596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65380132198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63318395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3872492313385</t>
   </si>
   <si>
     <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35190522670746</t>
+    <t xml:space="preserve">1.35190510749817</t>
   </si>
   <si>
     <t xml:space="preserve">1.35043263435364</t>
@@ -2285,16 +2285,16 @@
     <t xml:space="preserve">1.49475347995758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50948023796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58311343193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674650669098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55071473121643</t>
+    <t xml:space="preserve">1.50948011875153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58311355113983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674662590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55071461200714</t>
   </si>
   <si>
     <t xml:space="preserve">1.54776954650879</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">1.53598809242249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56249594688416</t>
+    <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
     <t xml:space="preserve">1.56102335453033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55366003513336</t>
+    <t xml:space="preserve">1.55365991592407</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.54187893867493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58164072036743</t>
+    <t xml:space="preserve">1.58164060115814</t>
   </si>
   <si>
     <t xml:space="preserve">1.60225808620453</t>
@@ -2327,25 +2327,25 @@
     <t xml:space="preserve">1.62434804439545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61698472499847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287521362305</t>
+    <t xml:space="preserve">1.61256659030914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61698484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287509441376</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643812179565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65527391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67589128017426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66705524921417</t>
+    <t xml:space="preserve">1.65527379512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67589139938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66705513000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.64349269866943</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">1.57574999332428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58753144741058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5580780506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427752017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047675132751</t>
+    <t xml:space="preserve">1.58753132820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55807816982269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427763938904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047663211823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59784007072449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64201998710632</t>
+    <t xml:space="preserve">1.64201986789703</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558253765106</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">1.62876582145691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61109387874603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67883634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71859860420227</t>
+    <t xml:space="preserve">1.61109399795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6788364648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71859848499298</t>
   </si>
   <si>
     <t xml:space="preserve">1.76572370529175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75836050510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7200710773468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7082896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6390745639801</t>
+    <t xml:space="preserve">1.75836038589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72007131576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63907444477081</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821933746338</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">1.71123492717743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77756822109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836574077606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71468615531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69781517982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71161878108978</t>
+    <t xml:space="preserve">1.77756810188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71468603610992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69781529903412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71161866188049</t>
   </si>
   <si>
     <t xml:space="preserve">1.71621966362</t>
@@ -2435,31 +2435,31 @@
     <t xml:space="preserve">1.69168031215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548355579376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72542202472687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73462426662445</t>
+    <t xml:space="preserve">1.70548367500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72542190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73462414741516</t>
   </si>
   <si>
     <t xml:space="preserve">1.73769164085388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73002326488495</t>
+    <t xml:space="preserve">1.73002302646637</t>
   </si>
   <si>
     <t xml:space="preserve">1.6870790719986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68554556369781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327558994293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65793871879578</t>
+    <t xml:space="preserve">1.6855456829071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327570915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65793859958649</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487134456635</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">1.68401193618774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241618156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235441207886</t>
+    <t xml:space="preserve">1.70241630077362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235453128815</t>
   </si>
   <si>
     <t xml:space="preserve">1.70701742172241</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">1.64566898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65333771705627</t>
+    <t xml:space="preserve">1.65333759784698</t>
   </si>
   <si>
     <t xml:space="preserve">1.65640509128571</t>
@@ -2492,43 +2492,43 @@
     <t xml:space="preserve">1.6272646188736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63646697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64720284938812</t>
+    <t xml:space="preserve">1.63646686077118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64720273017883</t>
   </si>
   <si>
     <t xml:space="preserve">1.67020845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407370567322</t>
+    <t xml:space="preserve">1.66407382488251</t>
   </si>
   <si>
     <t xml:space="preserve">1.68247818946838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72848927974701</t>
+    <t xml:space="preserve">1.7284893989563</t>
   </si>
   <si>
     <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75609612464905</t>
+    <t xml:space="preserve">1.75609624385834</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088279247284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7208206653595</t>
+    <t xml:space="preserve">1.70088255405426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72082078456879</t>
   </si>
   <si>
     <t xml:space="preserve">1.69321405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68094432353973</t>
+    <t xml:space="preserve">1.68094444274902</t>
   </si>
   <si>
     <t xml:space="preserve">1.67174208164215</t>
@@ -2540,40 +2540,40 @@
     <t xml:space="preserve">1.6778769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69014668464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71008479595184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861269950867</t>
+    <t xml:space="preserve">1.69014656543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71008491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861281871796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65180397033691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64873659610748</t>
+    <t xml:space="preserve">1.64873671531677</t>
   </si>
   <si>
     <t xml:space="preserve">1.62573075294495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61959612369537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59659051895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505653381348</t>
+    <t xml:space="preserve">1.61959600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59659039974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505665302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.58738803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57971966266632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57358479499817</t>
+    <t xml:space="preserve">1.57971942424774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57358491420746</t>
   </si>
   <si>
     <t xml:space="preserve">1.54904544353485</t>
@@ -2585,67 +2585,67 @@
     <t xml:space="preserve">1.49996674060822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48156237602234</t>
+    <t xml:space="preserve">1.48156249523163</t>
   </si>
   <si>
     <t xml:space="preserve">1.4961324930191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50303423404694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51990497112274</t>
+    <t xml:space="preserve">1.50303435325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51990509033203</t>
   </si>
   <si>
     <t xml:space="preserve">1.5475115776062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56438255310059</t>
+    <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
     <t xml:space="preserve">1.53064095973969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60425901412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59198915958405</t>
+    <t xml:space="preserve">1.60425889492035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
     <t xml:space="preserve">1.59965777397156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60119163990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61499488353729</t>
+    <t xml:space="preserve">1.60119152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.614994764328</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125340938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57511854171753</t>
+    <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
     <t xml:space="preserve">1.60272514820099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6610062122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7407591342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069712638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388815879822</t>
+    <t xml:space="preserve">1.66100609302521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74075901508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388803958893</t>
   </si>
   <si>
     <t xml:space="preserve">1.69628143310547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6318656206131</t>
+    <t xml:space="preserve">1.63186585903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6103937625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346137523651</t>
+    <t xml:space="preserve">1.61039388179779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346125602722</t>
   </si>
   <si>
     <t xml:space="preserve">1.58585453033447</t>
@@ -2678,22 +2678,22 @@
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947246551514</t>
+    <t xml:space="preserve">1.65947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">1.66714107990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6226634979248</t>
+    <t xml:space="preserve">1.62266337871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.555180311203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55671393871307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56131517887115</t>
+    <t xml:space="preserve">1.55671405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
@@ -2702,40 +2702,40 @@
     <t xml:space="preserve">1.57051742076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5597813129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278715610504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60732626914978</t>
+    <t xml:space="preserve">1.55978143215179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278691768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60732638835907</t>
   </si>
   <si>
     <t xml:space="preserve">1.63339948654175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192762851715</t>
+    <t xml:space="preserve">1.62419724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192750930786</t>
   </si>
   <si>
     <t xml:space="preserve">1.58432066440582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806225776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106786251068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.665607213974</t>
+    <t xml:space="preserve">1.61806237697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66560733318329</t>
   </si>
   <si>
     <t xml:space="preserve">1.67480945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71775317192078</t>
+    <t xml:space="preserve">1.71775329113007</t>
   </si>
   <si>
     <t xml:space="preserve">1.75762987136841</t>
@@ -2744,97 +2744,97 @@
     <t xml:space="preserve">1.80517494678497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81744432449341</t>
+    <t xml:space="preserve">1.8174444437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.80824220180511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80670845508575</t>
+    <t xml:space="preserve">1.80670857429504</t>
   </si>
   <si>
     <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903995990753</t>
+    <t xml:space="preserve">1.79903984069824</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290521144867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82051205635071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78063523769379</t>
+    <t xml:space="preserve">1.82051193714142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
     <t xml:space="preserve">1.79443871974945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83278179168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8097757101059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82971405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85885465145111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891654014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498939990997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85578715801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8634557723999</t>
+    <t xml:space="preserve">1.83278167247772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80977582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82971394062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85885441303253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891642093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818043231964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85578727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86345565319061</t>
   </si>
   <si>
     <t xml:space="preserve">1.84965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87112426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89566349983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90179836750031</t>
+    <t xml:space="preserve">1.87112414836884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89566338062286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90179812908173</t>
   </si>
   <si>
     <t xml:space="preserve">1.9186692237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90026450157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91100072860718</t>
+    <t xml:space="preserve">1.90026462078094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100060939789</t>
   </si>
   <si>
     <t xml:space="preserve">1.94627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95394456386566</t>
+    <t xml:space="preserve">1.95394480228424</t>
   </si>
   <si>
     <t xml:space="preserve">1.91560161113739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92173671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713547706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553996086121</t>
+    <t xml:space="preserve">1.92173659801483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713535785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553972244263</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695004940033</t>
@@ -2843,28 +2843,28 @@
     <t xml:space="preserve">1.96007931232452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99382078647614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9662139415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00609064102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762391090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375889778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00915789604187</t>
+    <t xml:space="preserve">1.99382066726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621406078339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00609040260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00915765762329</t>
   </si>
   <si>
     <t xml:space="preserve">1.95701217651367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95854556560516</t>
+    <t xml:space="preserve">1.95854568481445</t>
   </si>
   <si>
     <t xml:space="preserve">1.96928155422211</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">1.9784836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00302290916443</t>
+    <t xml:space="preserve">2.00302314758301</t>
   </si>
   <si>
     <t xml:space="preserve">2.01069164276123</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">2.01836013793945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02909588813782</t>
+    <t xml:space="preserve">2.0290961265564</t>
   </si>
   <si>
     <t xml:space="preserve">2.03369736671448</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.01682662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01631927490234</t>
+    <t xml:space="preserve">2.01631951332092</t>
   </si>
   <si>
     <t xml:space="preserve">1.99563097953796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97335124015808</t>
+    <t xml:space="preserve">1.97335112094879</t>
   </si>
   <si>
     <t xml:space="preserve">1.97175967693329</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92242610454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91606020927429</t>
+    <t xml:space="preserve">1.9224259853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.916060090065</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2918,19 +2918,19 @@
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401731014252</t>
+    <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
     <t xml:space="preserve">1.92719995975494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9797168970108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96061968803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95743715763092</t>
+    <t xml:space="preserve">1.97971677780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96061992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95743691921234</t>
   </si>
   <si>
     <t xml:space="preserve">1.96539425849915</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926532268524</t>
+    <t xml:space="preserve">1.98926520347595</t>
   </si>
   <si>
     <t xml:space="preserve">1.96857702732086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91287744045258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9478884935379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449110984802</t>
+    <t xml:space="preserve">1.91287767887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94788861274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449122905731</t>
   </si>
   <si>
     <t xml:space="preserve">2.03223347663879</t>
@@ -2966,49 +2966,49 @@
     <t xml:space="preserve">2.06087875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04337334632874</t>
+    <t xml:space="preserve">2.04337358474731</t>
   </si>
   <si>
     <t xml:space="preserve">2.04814743995667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02427649497986</t>
+    <t xml:space="preserve">2.02427625656128</t>
   </si>
   <si>
     <t xml:space="preserve">2.06247043609619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07997608184814</t>
+    <t xml:space="preserve">2.06724429130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07997584342957</t>
   </si>
   <si>
     <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10543823242188</t>
+    <t xml:space="preserve">2.10543847084045</t>
   </si>
   <si>
     <t xml:space="preserve">2.13726663589478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14522385597229</t>
+    <t xml:space="preserve">2.14522409439087</t>
   </si>
   <si>
     <t xml:space="preserve">2.18819189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2025146484375</t>
+    <t xml:space="preserve">2.20251441001892</t>
   </si>
   <si>
     <t xml:space="preserve">2.1706862449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15158939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12453556060791</t>
+    <t xml:space="preserve">2.15158915519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12453532218933</t>
   </si>
   <si>
     <t xml:space="preserve">2.11816954612732</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">2.08315849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07042717933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10862135887146</t>
+    <t xml:space="preserve">2.07042741775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10862112045288</t>
   </si>
   <si>
     <t xml:space="preserve">2.089524269104</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">2.11180400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14840650558472</t>
+    <t xml:space="preserve">2.14840626716614</t>
   </si>
   <si>
     <t xml:space="preserve">2.12135243415833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11657810211182</t>
+    <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
     <t xml:space="preserve">2.11339569091797</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">2.13249230384827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612652778625</t>
+    <t xml:space="preserve">2.12612676620483</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363241195679</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">2.04178190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05928730964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04019045829773</t>
+    <t xml:space="preserve">2.05928754806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04019021987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.09589004516602</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">2.02586770057678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03064203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98767375946045</t>
+    <t xml:space="preserve">2.03064227104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98767364025116</t>
   </si>
   <si>
     <t xml:space="preserve">2.01154518127441</t>
@@ -3089,34 +3089,34 @@
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341732025146</t>
+    <t xml:space="preserve">2.18341755867004</t>
   </si>
   <si>
     <t xml:space="preserve">2.18978333473206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16113781929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20569729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21842885017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29163384437561</t>
+    <t xml:space="preserve">2.18023467063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16113805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20569753646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21842861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29163360595703</t>
   </si>
   <si>
     <t xml:space="preserve">2.27412796020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25343990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29481625556946</t>
+    <t xml:space="preserve">2.2534396648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29481649398804</t>
   </si>
   <si>
     <t xml:space="preserve">2.23593425750732</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">2.22161149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23115992546082</t>
+    <t xml:space="preserve">2.23115968704224</t>
   </si>
   <si>
     <t xml:space="preserve">2.200923204422</t>
@@ -3143,16 +3143,16 @@
     <t xml:space="preserve">2.17546057701111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19296598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19774031639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10384678840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15795516967773</t>
+    <t xml:space="preserve">2.19296622276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19774055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10384702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
     <t xml:space="preserve">2.17386937141418</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">2.10702991485596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07520151138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07201862335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.086341381073</t>
+    <t xml:space="preserve">2.07520174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07201886177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08634161949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.14204096794128</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06883597373962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01472783088684</t>
+    <t xml:space="preserve">2.09111571311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06883549690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01472806930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9781254529953</t>
+    <t xml:space="preserve">1.97812533378601</t>
   </si>
   <si>
     <t xml:space="preserve">1.97016847133636</t>
@@ -3209,124 +3209,124 @@
     <t xml:space="preserve">2.03700733184814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1197612285614</t>
+    <t xml:space="preserve">2.11976099014282</t>
   </si>
   <si>
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130834102631</t>
+    <t xml:space="preserve">1.98130822181702</t>
   </si>
   <si>
     <t xml:space="preserve">2.02109336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96380257606506</t>
+    <t xml:space="preserve">1.96380281448364</t>
   </si>
   <si>
     <t xml:space="preserve">1.91128599643707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89378046989441</t>
+    <t xml:space="preserve">1.89378070831299</t>
   </si>
   <si>
     <t xml:space="preserve">1.90969467163086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00677084922791</t>
+    <t xml:space="preserve">2.00677061080933</t>
   </si>
   <si>
     <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90651202201843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945783138275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81261885166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79193019866943</t>
+    <t xml:space="preserve">1.90651178359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945771217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8126186132431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.7553277015686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79033887386322</t>
+    <t xml:space="preserve">1.79033875465393</t>
   </si>
   <si>
     <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83330678939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84922075271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83171534538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534980773926</t>
+    <t xml:space="preserve">1.8333066701889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84922099113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83171546459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534968852997</t>
   </si>
   <si>
     <t xml:space="preserve">1.81102728843689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82694125175476</t>
+    <t xml:space="preserve">1.82694137096405</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.844447016716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83808100223541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240387916565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104927539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92879176139832</t>
+    <t xml:space="preserve">1.84444689750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423204421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8380811214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240375995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104939460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
     <t xml:space="preserve">1.89537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96698558330536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99881386756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01791095733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01313662528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98289966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00358772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94311428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9510715007782</t>
+    <t xml:space="preserve">1.96698534488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99881374835968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01791071891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313638687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98289978504181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0035879611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94311416149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197453022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107126235962</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542543888092</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038320541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93993139266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90014636516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91765189170837</t>
+    <t xml:space="preserve">1.93038308620453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93993151187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90014612674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91765177249908</t>
   </si>
   <si>
     <t xml:space="preserve">1.9192430973053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84285533428192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71235966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6423374414444</t>
+    <t xml:space="preserve">1.84285545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71235942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64233732223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.61210060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66143453121185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65984284877777</t>
+    <t xml:space="preserve">1.66143441200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65984296798706</t>
   </si>
   <si>
     <t xml:space="preserve">1.69007992744446</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">1.64711153507233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61687505245209</t>
+    <t xml:space="preserve">1.6168749332428</t>
   </si>
   <si>
     <t xml:space="preserve">1.62483191490173</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">1.70758521556854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69644546508789</t>
+    <t xml:space="preserve">1.6964453458786</t>
   </si>
   <si>
     <t xml:space="preserve">1.68053126335144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65825164318085</t>
+    <t xml:space="preserve">1.65825176239014</t>
   </si>
   <si>
     <t xml:space="preserve">1.68848836421967</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">1.56435811519623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58345532417297</t>
+    <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.577885389328</t>
+    <t xml:space="preserve">1.57788527011871</t>
   </si>
   <si>
     <t xml:space="preserve">1.5850465297699</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">1.58743381500244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54128265380859</t>
+    <t xml:space="preserve">1.54128277301788</t>
   </si>
   <si>
     <t xml:space="preserve">1.47842192649841</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446175575256</t>
+    <t xml:space="preserve">1.51446163654327</t>
   </si>
   <si>
     <t xml:space="preserve">1.5026695728302</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">1.50856566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51361954212189</t>
+    <t xml:space="preserve">1.5136194229126</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5481538772583</t>
+    <t xml:space="preserve">1.54815399646759</t>
   </si>
   <si>
     <t xml:space="preserve">1.48835027217865</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">1.47487342357635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087727069855</t>
+    <t xml:space="preserve">1.49087715148926</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4630811214447</t>
+    <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
     <t xml:space="preserve">1.47403109073639</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48498117923737</t>
+    <t xml:space="preserve">1.48498106002808</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">1.49171960353851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46645057201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45718502998352</t>
+    <t xml:space="preserve">1.46645045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45718514919281</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3512,16 +3512,16 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39906620979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200475692749</t>
+    <t xml:space="preserve">1.3990660905838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3620046377182</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178948402405</t>
+    <t xml:space="preserve">1.34178960323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.26766681671143</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">1.20617866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23229002952576</t>
+    <t xml:space="preserve">1.23229014873505</t>
   </si>
   <si>
     <t xml:space="preserve">1.22976315021515</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365178585052</t>
+    <t xml:space="preserve">1.20365166664124</t>
   </si>
   <si>
     <t xml:space="preserve">1.20533633232117</t>
@@ -3575,10 +3575,10 @@
     <t xml:space="preserve">1.175013422966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13289833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14637494087219</t>
+    <t xml:space="preserve">1.13289821147919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14637506008148</t>
   </si>
   <si>
     <t xml:space="preserve">1.10173296928406</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">1.1059445142746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1430059671402</t>
+    <t xml:space="preserve">1.14300584793091</t>
   </si>
   <si>
     <t xml:space="preserve">1.16911733150482</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">1.16490578651428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13710975646973</t>
+    <t xml:space="preserve">1.13710963726044</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">1.12279057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08151769638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10425984859467</t>
+    <t xml:space="preserve">1.0815178155899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10425996780396</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15985202789307</t>
+    <t xml:space="preserve">1.15985190868378</t>
   </si>
   <si>
     <t xml:space="preserve">1.16322124004364</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">1.18427884578705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22470939159393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2600861787796</t>
+    <t xml:space="preserve">1.22470927238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">1.29462051391602</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">1.24829387664795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24492466449738</t>
+    <t xml:space="preserve">1.24492454528809</t>
   </si>
   <si>
     <t xml:space="preserve">1.25334763526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23818612098694</t>
+    <t xml:space="preserve">1.23818624019623</t>
   </si>
   <si>
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325875759125</t>
+    <t xml:space="preserve">1.32325887680054</t>
   </si>
   <si>
     <t xml:space="preserve">1.31567811965942</t>
@@ -3689,13 +3689,13 @@
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915484905243</t>
+    <t xml:space="preserve">1.32915496826172</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021257400513</t>
+    <t xml:space="preserve">1.35021269321442</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">1.35358166694641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32747030258179</t>
+    <t xml:space="preserve">1.32747042179108</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">1.31062436103821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29546284675598</t>
+    <t xml:space="preserve">1.29546272754669</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135893821716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25082087516785</t>
+    <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
     <t xml:space="preserve">1.2365015745163</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23734378814697</t>
+    <t xml:space="preserve">1.23734390735626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039021015167</t>
+    <t xml:space="preserve">1.21039032936096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">1.34263181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37127006053925</t>
+    <t xml:space="preserve">1.37127017974854</t>
   </si>
   <si>
     <t xml:space="preserve">1.36958563327789</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">1.4656081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40411996841431</t>
+    <t xml:space="preserve">1.4041200876236</t>
   </si>
   <si>
     <t xml:space="preserve">1.38222014904022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39822375774384</t>
+    <t xml:space="preserve">1.39822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4336005449295</t>
+    <t xml:space="preserve">1.43360066413879</t>
   </si>
   <si>
     <t xml:space="preserve">1.44370830059052</t>
@@ -3800,13 +3800,13 @@
     <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42265069484711</t>
+    <t xml:space="preserve">1.42265057563782</t>
   </si>
   <si>
     <t xml:space="preserve">1.44623517990112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39232766628265</t>
+    <t xml:space="preserve">1.39232778549194</t>
   </si>
   <si>
     <t xml:space="preserve">1.41843914985657</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770445346832</t>
+    <t xml:space="preserve">1.42770457267761</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
@@ -3833,31 +3833,31 @@
     <t xml:space="preserve">1.39317011833191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37800872325897</t>
+    <t xml:space="preserve">1.37800860404968</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779333114624</t>
+    <t xml:space="preserve">1.35779321193695</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496230125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37716627120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431636333466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34515869617462</t>
+    <t xml:space="preserve">1.40496218204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3881162405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37716639041901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34515881538391</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3869,25 +3869,25 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230878829956</t>
+    <t xml:space="preserve">1.31230890750885</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4125429391861</t>
+    <t xml:space="preserve">1.41254305839539</t>
   </si>
   <si>
     <t xml:space="preserve">1.44202363491058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45634269714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42686223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707751274109</t>
+    <t xml:space="preserve">1.45634281635284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42686212062836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4470773935318</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">1.53888845443726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56668448448181</t>
+    <t xml:space="preserve">1.5666846036911</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6071150302887</t>
+    <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
     <t xml:space="preserve">1.61132669448853</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784972667694</t>
+    <t xml:space="preserve">1.59784960746765</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">1.64754557609558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65007257461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62396121025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59953451156616</t>
+    <t xml:space="preserve">1.65007269382477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62396109104156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59953439235687</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">1.61806511878967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61048424243927</t>
+    <t xml:space="preserve">1.61048436164856</t>
   </si>
   <si>
     <t xml:space="preserve">1.64249193668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66186499595642</t>
+    <t xml:space="preserve">1.66186487674713</t>
   </si>
   <si>
     <t xml:space="preserve">1.62227654457092</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">1.57342302799225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353054523468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57089614868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57595002651215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58437287807465</t>
+    <t xml:space="preserve">1.58353066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57089602947235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57594990730286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58437299728394</t>
   </si>
   <si>
     <t xml:space="preserve">1.58184599876404</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.57173836231232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59026896953583</t>
+    <t xml:space="preserve">1.59026908874512</t>
   </si>
   <si>
     <t xml:space="preserve">1.5801614522934</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5308746099472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52102696895599</t>
+    <t xml:space="preserve">1.53087472915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5210268497467</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357869148254</t>
+    <t xml:space="preserve">1.47357881069183</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49506461620331</t>
+    <t xml:space="preserve">1.4950647354126</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4088,52 +4088,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192211151123</t>
+    <t xml:space="preserve">1.52192223072052</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070407390594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308526039124</t>
+    <t xml:space="preserve">1.61144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070395469666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308514118195</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786592960358</t>
+    <t xml:space="preserve">1.60786604881287</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039947509766</t>
+    <t xml:space="preserve">1.62039935588837</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801828861237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773198604584</t>
+    <t xml:space="preserve">1.59801816940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773210525513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937026977539</t>
+    <t xml:space="preserve">1.56937038898468</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6150279045105</t>
+    <t xml:space="preserve">1.61502802371979</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58279895782471</t>
+    <t xml:space="preserve">1.582799077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769539356232</t>
+    <t xml:space="preserve">1.67769527435303</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575263023376</t>
+    <t xml:space="preserve">1.68575251102448</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.664266705513</t>
+    <t xml:space="preserve">1.66426658630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977198123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887683868408</t>
+    <t xml:space="preserve">1.71977210044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887671947479</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843841552734</t>
+    <t xml:space="preserve">1.68843829631805</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159921646118</t>
+    <t xml:space="preserve">1.60159933567047</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340815544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399881839752</t>
+    <t xml:space="preserve">1.54340803623199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234211921692</t>
+    <t xml:space="preserve">1.61234223842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024723529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112420082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350538730621</t>
+    <t xml:space="preserve">1.63024711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112408161163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350526809692</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.745734333992</t>
+    <t xml:space="preserve">1.74573421478271</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201922416687</t>
+    <t xml:space="preserve">1.69201934337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79407751560211</t>
+    <t xml:space="preserve">1.78691565990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7940776348114</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525896072388</t>
+    <t xml:space="preserve">1.83525907993317</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272565364838</t>
+    <t xml:space="preserve">1.82272553443909</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558185577393</t>
+    <t xml:space="preserve">1.75558197498322</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7645343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857223987579</t>
+    <t xml:space="preserve">1.76453447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857235908508</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4409,16 +4409,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723855495453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859053611755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874289512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009487628937</t>
+    <t xml:space="preserve">1.70723843574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859065532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874277591705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009499549866</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740909099579</t>
+    <t xml:space="preserve">1.63740921020508</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64099013805389</t>
+    <t xml:space="preserve">1.63919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6409900188446</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693407535553</t>
+    <t xml:space="preserve">1.72693395614624</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041777133942</t>
+    <t xml:space="preserve">1.56041789054871</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458960056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609394073486</t>
+    <t xml:space="preserve">1.58458948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609382152557</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205605506897</t>
+    <t xml:space="preserve">1.57205617427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278066158295</t>
+    <t xml:space="preserve">1.64278078079224</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754303455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129461765289</t>
+    <t xml:space="preserve">1.68754315376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129473686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708619594574</t>
+    <t xml:space="preserve">1.71708631515503</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274394989014</t>
+    <t xml:space="preserve">1.76274383068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602039813995</t>
+    <t xml:space="preserve">1.78602051734924</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -70900,7 +70900,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911689815</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>2279171</v>
@@ -70921,6 +70921,32 @@
         <v>1771</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6910763889</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>2370291</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>2.46600008010864</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -44,40 +44,40 @@
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927027106285095</t>
+    <t xml:space="preserve">0.923806130886078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92702704668045</t>
   </si>
   <si>
     <t xml:space="preserve">0.921873569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901902794837952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898037493228912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652474880219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835475444794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643606185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893926143646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346442699432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653933525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154573440552</t>
+    <t xml:space="preserve">0.901902675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898037552833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652355670929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835356235504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643546581268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863893985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346323490143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851653814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154513835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.836192548274994</t>
@@ -86,88 +86,88 @@
     <t xml:space="preserve">0.856163442134857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857451856136322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869692027568817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88644152879715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489771366119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374030590057</t>
+    <t xml:space="preserve">0.857451975345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691908359528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441588401794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344924449921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374149799347</t>
   </si>
   <si>
     <t xml:space="preserve">0.85551917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84327906370163</t>
+    <t xml:space="preserve">0.843279004096985</t>
   </si>
   <si>
     <t xml:space="preserve">0.818798959255219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837481141090393</t>
+    <t xml:space="preserve">0.837480962276459</t>
   </si>
   <si>
     <t xml:space="preserve">0.825241029262543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848432958126068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86904776096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778304576874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172251224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161923885345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671551704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709586143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296741485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916075587272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941200017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947642028331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113621711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412124633789</t>
+    <t xml:space="preserve">0.848432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869047701358795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778185367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923161745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671492099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709407329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296443462372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916075468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941199958324432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947642147541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892586708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113562107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412184238434</t>
   </si>
   <si>
     <t xml:space="preserve">0.918008029460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954084277153015</t>
+    <t xml:space="preserve">0.95408433675766</t>
   </si>
   <si>
     <t xml:space="preserve">0.964391767978668</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">1.0127078294754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02881348133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01657330989838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365958690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00819849967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00497722625732</t>
+    <t xml:space="preserve">1.02881336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0165730714798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00819838047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175631046295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497734546661</t>
   </si>
   <si>
     <t xml:space="preserve">1.00755417346954</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">1.02172696590424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464056968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237117290497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999823570251465</t>
+    <t xml:space="preserve">1.01464068889618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999823689460754</t>
   </si>
   <si>
     <t xml:space="preserve">1.01141965389252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01206374168396</t>
+    <t xml:space="preserve">1.01206350326538</t>
   </si>
   <si>
     <t xml:space="preserve">1.01786172389984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02430379390717</t>
+    <t xml:space="preserve">1.02430391311646</t>
   </si>
   <si>
     <t xml:space="preserve">1.01850593090057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02688074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03203415870667</t>
+    <t xml:space="preserve">1.0268806219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03203451633453</t>
   </si>
   <si>
     <t xml:space="preserve">1.0249480009079</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">1.01721739768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00562155246735</t>
+    <t xml:space="preserve">1.00562179088593</t>
   </si>
   <si>
     <t xml:space="preserve">0.988871872425079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00368881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03525567054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02816915512085</t>
+    <t xml:space="preserve">1.00368893146515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03525531291962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02816903591156</t>
   </si>
   <si>
     <t xml:space="preserve">1.04040920734406</t>
@@ -260,43 +260,43 @@
     <t xml:space="preserve">1.03396713733673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02945756912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03010189533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01592922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992093026638031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.033322930336</t>
+    <t xml:space="preserve">1.0294576883316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01592910289764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992093086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03332281112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.00948691368103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995958268642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995313882827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02108287811279</t>
+    <t xml:space="preserve">0.99595832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995314002037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02108263969421</t>
   </si>
   <si>
     <t xml:space="preserve">1.0494282245636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07519710063934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295692920685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05715882778168</t>
+    <t xml:space="preserve">1.07519698143005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05715906620026</t>
   </si>
   <si>
     <t xml:space="preserve">1.07326412200928</t>
@@ -314,115 +314,115 @@
     <t xml:space="preserve">1.0616682767868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06811046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04620730876923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977276086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968257009983063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965035915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978564500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522506713867</t>
+    <t xml:space="preserve">1.06811058521271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04620718955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977275967597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968257129192352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965036153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564560413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522566318512</t>
   </si>
   <si>
     <t xml:space="preserve">0.979232907295227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960517406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712042331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87696498632431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701603412628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680785179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101586341858</t>
+    <t xml:space="preserve">0.960517227649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907712280750275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876964867115021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701663017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680665969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101407527924</t>
   </si>
   <si>
     <t xml:space="preserve">0.935117304325104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939127862453461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048855304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033137321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91573303937912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925091087818146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775271892548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925759434700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912391006946564</t>
+    <t xml:space="preserve">0.939127683639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048914909363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033196926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915733218193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925090968608856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775212287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925759494304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912391185760498</t>
   </si>
   <si>
     <t xml:space="preserve">0.921080470085144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92709618806839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143580436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122523784637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95583838224411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95316469669342</t>
+    <t xml:space="preserve">0.927096307277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143699645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122583389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838322639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953164517879486</t>
   </si>
   <si>
     <t xml:space="preserve">0.964527606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965195953845978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982574939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911693096161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97254866361618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580278396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987253963947296</t>
+    <t xml:space="preserve">0.965196073055267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982575058937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983911871910095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97254878282547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217070102692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580218791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253904342651</t>
   </si>
   <si>
     <t xml:space="preserve">0.99527496099472</t>
@@ -434,40 +434,40 @@
     <t xml:space="preserve">0.992601335048676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975890934467316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827943325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950490951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485732078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941133081912994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501509666443</t>
+    <t xml:space="preserve">0.975890815258026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827824115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950490891933441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485672473907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941133201122284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501330852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.965864539146423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985917091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989927530288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01265382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02000653743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932988166809</t>
+    <t xml:space="preserve">0.985917150974274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989927649497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01265406608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02000665664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932809352875</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">0.996611773967743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979901373386383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967201471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98658549785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977896153926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885476589203</t>
+    <t xml:space="preserve">0.979901194572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201352119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986585557460785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977896213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885595798492</t>
   </si>
   <si>
     <t xml:space="preserve">0.995943307876587</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">1.02401685714722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00864326953888</t>
+    <t xml:space="preserve">1.00864338874817</t>
   </si>
   <si>
     <t xml:space="preserve">1.00262761116028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969206690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97522234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248744487762</t>
+    <t xml:space="preserve">0.969206571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975222587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248684883118</t>
   </si>
   <si>
     <t xml:space="preserve">1.0293642282486</t>
@@ -518,298 +518,298 @@
     <t xml:space="preserve">1.05342721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05543267726898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0761536359787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08952188491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420096874237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09687459468842</t>
+    <t xml:space="preserve">1.0554324388504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07615351676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0895220041275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420073032379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09687471389771</t>
   </si>
   <si>
     <t xml:space="preserve">1.07013785839081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08751666545868</t>
+    <t xml:space="preserve">1.08751678466797</t>
   </si>
   <si>
     <t xml:space="preserve">1.09353244304657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749044895172</t>
+    <t xml:space="preserve">1.07749056816101</t>
   </si>
   <si>
     <t xml:space="preserve">1.06479048728943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06278502941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04741144180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06078004837036</t>
+    <t xml:space="preserve">1.06278514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04741168022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06077992916107</t>
   </si>
   <si>
     <t xml:space="preserve">1.06813251972198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05209040641785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957843601703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953833043575287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480453014374</t>
+    <t xml:space="preserve">1.05209052562714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957843363285065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953832864761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480393409729</t>
   </si>
   <si>
     <t xml:space="preserve">0.93578565120697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942469954490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780312538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727939128876</t>
+    <t xml:space="preserve">0.942469894886017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780550956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727879524231</t>
   </si>
   <si>
     <t xml:space="preserve">0.917738437652588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941801369190216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406784534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538224697113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98056960105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606554508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948527336121</t>
+    <t xml:space="preserve">0.94180154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406903743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538343906403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869877815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569660663605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997948586940765</t>
   </si>
   <si>
     <t xml:space="preserve">1.01332211494446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01532757282257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01599586009979</t>
+    <t xml:space="preserve">1.01532745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01599597930908</t>
   </si>
   <si>
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203797340393</t>
+    <t xml:space="preserve">1.03203785419464</t>
   </si>
   <si>
     <t xml:space="preserve">1.04005885124207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04473793506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03070104122162</t>
+    <t xml:space="preserve">1.04473781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03070116043091</t>
   </si>
   <si>
     <t xml:space="preserve">1.01733267307281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03604829311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04874837398529</t>
+    <t xml:space="preserve">1.036048412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04874849319458</t>
   </si>
   <si>
     <t xml:space="preserve">1.04941689968109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05275893211365</t>
+    <t xml:space="preserve">1.05275905132294</t>
   </si>
   <si>
     <t xml:space="preserve">1.05008518695831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04072749614716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04607474803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02468538284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0106486082077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00530135631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03003263473511</t>
+    <t xml:space="preserve">1.04072737693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04607486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02468514442444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01064848899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00530123710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0300327539444</t>
   </si>
   <si>
     <t xml:space="preserve">1.0427325963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334868907928</t>
+    <t xml:space="preserve">1.02334856987</t>
   </si>
   <si>
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412184238434</t>
+    <t xml:space="preserve">1.06412208080292</t>
   </si>
   <si>
     <t xml:space="preserve">1.05610108375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810630321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08484303951263</t>
+    <t xml:space="preserve">1.05810618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08484292030334</t>
   </si>
   <si>
     <t xml:space="preserve">1.07080614566803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08216941356659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06880104541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07815897464752</t>
+    <t xml:space="preserve">1.0821692943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0688009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07815885543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.08283770084381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08818507194519</t>
+    <t xml:space="preserve">1.08818519115448</t>
   </si>
   <si>
     <t xml:space="preserve">1.09620606899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09954810142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754288196564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628495693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18978464603424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22120022773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22988975048065</t>
+    <t xml:space="preserve">1.09954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754300117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628483772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18978476524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22120046615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22988986968994</t>
   </si>
   <si>
     <t xml:space="preserve">1.24058449268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26665282249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28002107143402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28336322307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29405796527863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133166790009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26932656764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30074203014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31010007858276</t>
+    <t xml:space="preserve">1.26665270328522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28336334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29405784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26932644844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30074214935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009995937347</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475258827209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30007374286652</t>
+    <t xml:space="preserve">1.30007386207581</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143689155579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29004740715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28871059417725</t>
+    <t xml:space="preserve">1.29004752635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28871071338654</t>
   </si>
   <si>
     <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28937900066376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27200019359589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25930023193359</t>
+    <t xml:space="preserve">1.28937911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27200031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2593001127243</t>
   </si>
   <si>
     <t xml:space="preserve">1.29673159122467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2980682849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31076836585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29338955879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814741134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30341577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683657646179</t>
+    <t xml:space="preserve">1.29806864261627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31076848506927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29338943958282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814729213715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30341589450836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683669567108</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349466323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35421550273895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37025773525238</t>
+    <t xml:space="preserve">1.35421562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37025761604309</t>
   </si>
   <si>
     <t xml:space="preserve">1.37426805496216</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">1.364910364151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37961554527283</t>
+    <t xml:space="preserve">1.37961542606354</t>
   </si>
   <si>
     <t xml:space="preserve">1.33616828918457</t>
@@ -827,64 +827,64 @@
     <t xml:space="preserve">1.34886801242828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3903101682663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4103627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42105722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45046806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39966809749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303658485413</t>
+    <t xml:space="preserve">1.39031004905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41036260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42105746269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175208568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4504679441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303646564484</t>
   </si>
   <si>
     <t xml:space="preserve">1.43442559242249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4170469045639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42239439487457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40902590751648</t>
+    <t xml:space="preserve">1.41704678535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42239415645599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40902578830719</t>
   </si>
   <si>
     <t xml:space="preserve">1.43977320194244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44779407978058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47052037715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46784687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116268634796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319400310516</t>
+    <t xml:space="preserve">1.44779419898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47052049636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46784675121307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319388389587</t>
   </si>
   <si>
     <t xml:space="preserve">1.46249949932098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46650981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4847424030304</t>
+    <t xml:space="preserve">1.46650993824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48474228382111</t>
   </si>
   <si>
     <t xml:space="preserve">1.48336637020111</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">1.49024653434753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47235810756683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42282092571259</t>
+    <t xml:space="preserve">1.47235822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42282068729401</t>
   </si>
   <si>
     <t xml:space="preserve">1.44208526611328</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">1.40630829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3953001499176</t>
+    <t xml:space="preserve">1.39530038833618</t>
   </si>
   <si>
     <t xml:space="preserve">1.39942812919617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40080428123474</t>
+    <t xml:space="preserve">1.40080416202545</t>
   </si>
   <si>
     <t xml:space="preserve">1.40218043327332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38429164886475</t>
+    <t xml:space="preserve">1.38429188728333</t>
   </si>
   <si>
     <t xml:space="preserve">1.4145644903183</t>
@@ -926,46 +926,46 @@
     <t xml:space="preserve">1.42144465446472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43658113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43245315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42419672012329</t>
+    <t xml:space="preserve">1.43658125400543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43245303630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42419683933258</t>
   </si>
   <si>
     <t xml:space="preserve">1.43107688426971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483733177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45997369289398</t>
+    <t xml:space="preserve">1.44483721256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4599734544754</t>
   </si>
   <si>
     <t xml:space="preserve">1.44621348381042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46685373783112</t>
+    <t xml:space="preserve">1.46685385704041</t>
   </si>
   <si>
     <t xml:space="preserve">1.48199033737183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46960580348969</t>
+    <t xml:space="preserve">1.46960592269897</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758951663971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47923827171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400698184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125479698181</t>
+    <t xml:space="preserve">1.47923815250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400686264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125467777252</t>
   </si>
   <si>
     <t xml:space="preserve">1.49987888336182</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.50675904750824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602338790894</t>
+    <t xml:space="preserve">1.52602326869965</t>
   </si>
   <si>
     <t xml:space="preserve">1.54804015159607</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52327144145966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189517021179</t>
+    <t xml:space="preserve">1.52327120304108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189528942108</t>
   </si>
   <si>
     <t xml:space="preserve">1.54528796672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968866825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556068897247</t>
+    <t xml:space="preserve">1.57968878746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831275463104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556080818176</t>
   </si>
   <si>
     <t xml:space="preserve">1.57693672180176</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">1.56317639350891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54666376113892</t>
+    <t xml:space="preserve">1.5466639995575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55354428291321</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">1.56592845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58381712436676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5906970500946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656907081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58244073390961</t>
+    <t xml:space="preserve">1.58381688594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656895160675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58244097232819</t>
   </si>
   <si>
     <t xml:space="preserve">1.60996150970459</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">1.63197803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711487293243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408996582031</t>
+    <t xml:space="preserve">1.64711463451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408960819244</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583364963531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60032939910889</t>
+    <t xml:space="preserve">1.60032916069031</t>
   </si>
   <si>
     <t xml:space="preserve">1.56455254554749</t>
@@ -1061,46 +1061,46 @@
     <t xml:space="preserve">1.56180047988892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56042432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941606521606</t>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941618442535</t>
   </si>
   <si>
     <t xml:space="preserve">1.53427970409393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57005655765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868028640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234604358673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6168417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922608852386</t>
+    <t xml:space="preserve">1.57005679607391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868052482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234580516815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61684155464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922596931458</t>
   </si>
   <si>
     <t xml:space="preserve">1.61133778095245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59482538700104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6182177066803</t>
+    <t xml:space="preserve">1.59482514858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57280898094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
   </si>
   <si>
     <t xml:space="preserve">1.6250981092453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66087508201599</t>
+    <t xml:space="preserve">1.66087484359741</t>
   </si>
   <si>
     <t xml:space="preserve">1.66637909412384</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">1.69940400123596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70353221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802796840668</t>
+    <t xml:space="preserve">1.70353209972382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69802761077881</t>
   </si>
   <si>
     <t xml:space="preserve">1.69252383708954</t>
@@ -1121,73 +1121,73 @@
     <t xml:space="preserve">1.64023447036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65949892997742</t>
+    <t xml:space="preserve">1.65949881076813</t>
   </si>
   <si>
     <t xml:space="preserve">1.64986681938171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62785005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6622508764267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601132392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490801334381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105263710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004437446594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76682949066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233362197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545381546021</t>
+    <t xml:space="preserve">1.62785017490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66225099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490789413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7489413022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7310528755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004449367523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518073558807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830069065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76682984828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233397960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545369625092</t>
   </si>
   <si>
     <t xml:space="preserve">1.77371001243591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74068486690521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8204950094223</t>
+    <t xml:space="preserve">1.7406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049489021301</t>
   </si>
   <si>
     <t xml:space="preserve">1.79022228717804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78747034072876</t>
+    <t xml:space="preserve">1.78747022151947</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444543361664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79159843921661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79297423362732</t>
+    <t xml:space="preserve">1.7915985584259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297411441803</t>
   </si>
   <si>
     <t xml:space="preserve">1.76820576190948</t>
@@ -1196,61 +1196,61 @@
     <t xml:space="preserve">1.7585734128952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72554838657379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967684268951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169336795807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499075889587</t>
+    <t xml:space="preserve">1.72554874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142064571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499087810516</t>
   </si>
   <si>
     <t xml:space="preserve">1.80535888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031721591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481320381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921402454376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85351979732513</t>
+    <t xml:space="preserve">1.75031733512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481308460236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113562107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700740337372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.853520154953</t>
   </si>
   <si>
     <t xml:space="preserve">1.86039996147156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88516843318939</t>
+    <t xml:space="preserve">1.88516891002655</t>
   </si>
   <si>
     <t xml:space="preserve">1.85076808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81361496448517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123054981232</t>
+    <t xml:space="preserve">1.8136146068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123043060303</t>
   </si>
   <si>
     <t xml:space="preserve">1.79710245132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79572629928589</t>
+    <t xml:space="preserve">1.7957261800766</t>
   </si>
   <si>
     <t xml:space="preserve">1.82737517356873</t>
@@ -1259,139 +1259,139 @@
     <t xml:space="preserve">1.68564367294312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6457382440567</t>
+    <t xml:space="preserve">1.64573848247528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67738747596741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.634730219841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151533603668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68013942241669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.642986536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500294208527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68701958656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335406780243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463564872742</t>
+    <t xml:space="preserve">1.63472998142242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151545524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66913139820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801393032074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64298641681671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500318050385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6870197057724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114768505096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463541030884</t>
   </si>
   <si>
     <t xml:space="preserve">1.71454036235809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70215606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527590274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426752090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6787633895874</t>
+    <t xml:space="preserve">1.70215582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527566432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876350879669</t>
   </si>
   <si>
     <t xml:space="preserve">1.65261888504028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75306951999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930907249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417283058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692477703094</t>
+    <t xml:space="preserve">1.75306928157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930883407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7241724729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692465782166</t>
   </si>
   <si>
     <t xml:space="preserve">1.66362702846527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68289148807526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316456794739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343693256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206113815308</t>
+    <t xml:space="preserve">1.68289124965668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316421031952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343717098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7338045835495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7420608997345</t>
   </si>
   <si>
     <t xml:space="preserve">1.75994956493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71178805828094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839573860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65399479866028</t>
+    <t xml:space="preserve">1.71178829669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6539945602417</t>
   </si>
   <si>
     <t xml:space="preserve">1.64849054813385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60720932483673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757733345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620130062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290343284607</t>
+    <t xml:space="preserve">1.60720956325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757709503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620118141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290367126465</t>
   </si>
   <si>
     <t xml:space="preserve">1.49299871921539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47648596763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4751101732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45722162723541</t>
+    <t xml:space="preserve">1.45034158229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4764860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611843585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45722150802612</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832493782043</t>
@@ -1400,40 +1400,40 @@
     <t xml:space="preserve">1.51776719093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55079221725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542124271393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530690193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54826211929321</t>
+    <t xml:space="preserve">1.55079209804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530702114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54826200008392</t>
   </si>
   <si>
     <t xml:space="preserve">1.52411460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5312168598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127385139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837610244751</t>
+    <t xml:space="preserve">1.53121674060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127397060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837598323822</t>
   </si>
   <si>
     <t xml:space="preserve">1.56672751903534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55536413192749</t>
+    <t xml:space="preserve">1.5553640127182</t>
   </si>
   <si>
     <t xml:space="preserve">1.56246638298035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5951361656189</t>
+    <t xml:space="preserve">1.59513604640961</t>
   </si>
   <si>
     <t xml:space="preserve">1.60507881641388</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">1.60934019088745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62212371826172</t>
+    <t xml:space="preserve">1.6221239566803</t>
   </si>
   <si>
     <t xml:space="preserve">1.58945417404175</t>
@@ -1451,82 +1451,82 @@
     <t xml:space="preserve">1.57951128482819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60223805904388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60365843772888</t>
+    <t xml:space="preserve">1.60223817825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60365855693817</t>
   </si>
   <si>
     <t xml:space="preserve">1.59371554851532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63632822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348734378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638533115387</t>
+    <t xml:space="preserve">1.63632810115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348722457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638509273529</t>
   </si>
   <si>
     <t xml:space="preserve">1.61076045036316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58803379535675</t>
+    <t xml:space="preserve">1.58803391456604</t>
   </si>
   <si>
     <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6888839006424</t>
+    <t xml:space="preserve">1.68888378143311</t>
   </si>
   <si>
     <t xml:space="preserve">1.68178176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882655143738</t>
+    <t xml:space="preserve">1.69882667064667</t>
   </si>
   <si>
     <t xml:space="preserve">1.72013318538666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71729242801666</t>
+    <t xml:space="preserve">1.71729254722595</t>
   </si>
   <si>
     <t xml:space="preserve">1.64911198616028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6675773859024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894077301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752063274384</t>
+    <t xml:space="preserve">1.66757762432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894101142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752039432526</t>
   </si>
   <si>
     <t xml:space="preserve">1.67183876037598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64343047142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928296089172</t>
+    <t xml:space="preserve">1.643430352211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6192831993103</t>
   </si>
   <si>
     <t xml:space="preserve">1.61786282062531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57667028903961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962538719177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55394375324249</t>
+    <t xml:space="preserve">1.57667052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388676166534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962550640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55394351482391</t>
   </si>
   <si>
     <t xml:space="preserve">1.55252325534821</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">1.55110275745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51701247692108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559221744537</t>
+    <t xml:space="preserve">1.51701271533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559233665466</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871817111969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43462800979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44741201400757</t>
+    <t xml:space="preserve">1.43462812900543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44741189479828</t>
   </si>
   <si>
     <t xml:space="preserve">1.45735478401184</t>
@@ -1559,22 +1559,22 @@
     <t xml:space="preserve">1.47013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47297942638397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5326372385025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58377254009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973925113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275134086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4871838092804</t>
+    <t xml:space="preserve">1.47297954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53263735771179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58377277851105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275146007538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48718392848969</t>
   </si>
   <si>
     <t xml:space="preserve">1.47724068164825</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.49144506454468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50138807296753</t>
+    <t xml:space="preserve">1.50138795375824</t>
   </si>
   <si>
     <t xml:space="preserve">1.49996757507324</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">1.49570620059967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41687262058258</t>
+    <t xml:space="preserve">1.41687273979187</t>
   </si>
   <si>
     <t xml:space="preserve">1.4218442440033</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">1.3991174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38065183162689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35224366188049</t>
+    <t xml:space="preserve">1.38065195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426006793976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3522435426712</t>
   </si>
   <si>
     <t xml:space="preserve">1.37994158267975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37070906162262</t>
+    <t xml:space="preserve">1.37070894241333</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573755741119</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">1.37212944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35579454898834</t>
+    <t xml:space="preserve">1.35579442977905</t>
   </si>
   <si>
     <t xml:space="preserve">1.38633358478546</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">1.36431705951691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39343571662903</t>
+    <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130508899689</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">1.35863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40906023979187</t>
+    <t xml:space="preserve">1.40906035900116</t>
   </si>
   <si>
     <t xml:space="preserve">1.40124809741974</t>
@@ -1652,136 +1652,136 @@
     <t xml:space="preserve">1.46019566059113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45309364795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439992427826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866129875183</t>
+    <t xml:space="preserve">1.45309352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47440004348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866117954254</t>
   </si>
   <si>
     <t xml:space="preserve">1.45593440532684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42894649505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44031000137329</t>
+    <t xml:space="preserve">1.42894637584686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
     <t xml:space="preserve">1.39556646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37568044662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3870438337326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201521873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3778110742569</t>
+    <t xml:space="preserve">1.37568032741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38704371452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37781119346619</t>
   </si>
   <si>
     <t xml:space="preserve">1.40266847610474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38136208057404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33519840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36076605319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940266609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43178725242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320775032043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468523979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42042398452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48150217533112</t>
+    <t xml:space="preserve">1.38136219978333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351982831955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36076593399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940254688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43178737163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320763111115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468512058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042374610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48150205612183</t>
   </si>
   <si>
     <t xml:space="preserve">1.51985359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4886040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428582191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258024692535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115998744965</t>
+    <t xml:space="preserve">1.48860418796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428594112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258036613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54116010665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52979636192322</t>
+    <t xml:space="preserve">1.52979648113251</t>
   </si>
   <si>
     <t xml:space="preserve">1.52695560455322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5340576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51133108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50991034507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008167743683</t>
+    <t xml:space="preserve">1.53405797481537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51133096218109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5099104642868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48008179664612</t>
   </si>
   <si>
     <t xml:space="preserve">1.49854707717896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48292243480682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48434269428253</t>
+    <t xml:space="preserve">1.50706946849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48292255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48434293270111</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689849376678</t>
+    <t xml:space="preserve">1.53689873218536</t>
   </si>
   <si>
     <t xml:space="preserve">1.61644220352173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62780570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206708431244</t>
+    <t xml:space="preserve">1.62780547142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206684589386</t>
   </si>
   <si>
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496495246887</t>
+    <t xml:space="preserve">1.62496483325958</t>
   </si>
   <si>
     <t xml:space="preserve">1.5993971824646</t>
@@ -1793,22 +1793,22 @@
     <t xml:space="preserve">1.61502182483673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64627134799957</t>
+    <t xml:space="preserve">1.64627110958099</t>
   </si>
   <si>
     <t xml:space="preserve">1.61218106746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5141716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50422883033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4857634305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303641796112</t>
+    <t xml:space="preserve">1.51417183876038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50422871112823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303653717041</t>
   </si>
   <si>
     <t xml:space="preserve">1.45877516269684</t>
@@ -1817,109 +1817,109 @@
     <t xml:space="preserve">1.49286544322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5567843914032</t>
+    <t xml:space="preserve">1.55678451061249</t>
   </si>
   <si>
     <t xml:space="preserve">1.5780907869339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58661341667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5738297700882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916897773743</t>
+    <t xml:space="preserve">1.58661329746246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57382965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916909694672</t>
   </si>
   <si>
     <t xml:space="preserve">1.70450866222382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70166742801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69061779975891</t>
+    <t xml:space="preserve">1.70166754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69061768054962</t>
   </si>
   <si>
     <t xml:space="preserve">1.69356298446655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69798123836517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325436115265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68619978427887</t>
+    <t xml:space="preserve">1.69798099994659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294585704803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325471878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68619966506958</t>
   </si>
   <si>
     <t xml:space="preserve">1.72890710830688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75099730491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277852058411</t>
+    <t xml:space="preserve">1.75099682807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277840137482</t>
   </si>
   <si>
     <t xml:space="preserve">1.74510622024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73332524299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161431312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750515937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812204837799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8010675907135</t>
+    <t xml:space="preserve">1.73332500457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161419391632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750504016876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7981219291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80106747150421</t>
   </si>
   <si>
     <t xml:space="preserve">1.80548560619354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80401313304901</t>
+    <t xml:space="preserve">1.80401289463043</t>
   </si>
   <si>
     <t xml:space="preserve">1.8113762140274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77455961704254</t>
+    <t xml:space="preserve">1.77455973625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603220939636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76719617843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216115474701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239913463593</t>
+    <t xml:space="preserve">1.76719641685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74216091632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239925384521</t>
   </si>
   <si>
     <t xml:space="preserve">1.7392156124115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77014172077179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486847877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7892861366272</t>
+    <t xml:space="preserve">1.77014148235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486835956573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78928637504578</t>
   </si>
   <si>
     <t xml:space="preserve">1.79664957523346</t>
@@ -1928,25 +1928,25 @@
     <t xml:space="preserve">1.79517686367035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79370450973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78339564800262</t>
+    <t xml:space="preserve">1.79370427131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78339552879333</t>
   </si>
   <si>
     <t xml:space="preserve">1.79959487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80254018306732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192293643951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493912220001</t>
+    <t xml:space="preserve">1.80254030227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308678627014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7819230556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493888378143</t>
   </si>
   <si>
     <t xml:space="preserve">1.8202121257782</t>
@@ -1955,127 +1955,127 @@
     <t xml:space="preserve">1.81873953342438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8216849565506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8496652841568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84819304943085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82904803752899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425099372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81432139873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80990314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83199346065521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91593515872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655276298523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93213474750519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127940177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042405605316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569729804993</t>
+    <t xml:space="preserve">1.82168483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84819281101227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82904827594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425087451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81432127952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80990350246429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319935798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91593527793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655288219452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9321346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9512791633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042381763458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569705963135</t>
   </si>
   <si>
     <t xml:space="preserve">1.9424432516098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94980657100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96158790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693191051483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00724077224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98367810249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987721443176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00576782226562</t>
+    <t xml:space="preserve">1.94980669021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809564113617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00724005699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98367774486542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987733364105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576758384705</t>
   </si>
   <si>
     <t xml:space="preserve">1.98073256015778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9718964099884</t>
+    <t xml:space="preserve">1.97189652919769</t>
   </si>
   <si>
     <t xml:space="preserve">1.97631466388702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94391596317291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96895134449005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96600604057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484171390533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01754927635193</t>
+    <t xml:space="preserve">1.94391584396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96895122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96600592136383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484183311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01754903793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.04847502708435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02049422264099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04552984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03374862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05436587333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02785801887512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227567672729</t>
+    <t xml:space="preserve">2.02049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04552960395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03374838829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05436563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02785754203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227591514587</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111170768738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03816652297974</t>
+    <t xml:space="preserve">2.03816628456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.01018571853638</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">2.00871300697327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99251389503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02638506889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07940077781677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07203793525696</t>
+    <t xml:space="preserve">1.99251401424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02638530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07940101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467413902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0720374584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.06172895431519</t>
@@ -2105,52 +2105,52 @@
     <t xml:space="preserve">2.03522086143494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02933073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614708900452</t>
+    <t xml:space="preserve">2.02933049201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614685058594</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645559310913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0867645740509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0219669342041</t>
+    <t xml:space="preserve">2.08676433563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02196717262268</t>
   </si>
   <si>
     <t xml:space="preserve">2.05731081962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07351016998291</t>
+    <t xml:space="preserve">2.07351040840149</t>
   </si>
   <si>
     <t xml:space="preserve">2.04700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00282263755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0131311416626</t>
+    <t xml:space="preserve">2.0028223991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01313090324402</t>
   </si>
   <si>
     <t xml:space="preserve">2.01460385322571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04258418083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11179971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08087372779846</t>
+    <t xml:space="preserve">2.04258441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11179947853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08087348937988</t>
   </si>
   <si>
     <t xml:space="preserve">2.07498288154602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11032676696777</t>
+    <t xml:space="preserve">2.11032700538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">2.20457744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19426846504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24581217765808</t>
+    <t xml:space="preserve">2.19426870346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2458119392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">2.21341347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20899558067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2178316116333</t>
+    <t xml:space="preserve">2.20899534225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21783137321472</t>
   </si>
   <si>
     <t xml:space="preserve">2.20163202285767</t>
@@ -2198,28 +2198,28 @@
     <t xml:space="preserve">2.23255825042725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21930432319641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21635866165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20310497283936</t>
+    <t xml:space="preserve">2.21930408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21635890007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20310473442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.24728465080261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28704643249512</t>
+    <t xml:space="preserve">2.2870466709137</t>
   </si>
   <si>
     <t xml:space="preserve">2.26201128959656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25023007392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11474514007568</t>
+    <t xml:space="preserve">2.25023031234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11474466323853</t>
   </si>
   <si>
     <t xml:space="preserve">2.11621761322021</t>
@@ -2228,34 +2228,34 @@
     <t xml:space="preserve">2.15303421020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13094449043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0249125957489</t>
+    <t xml:space="preserve">2.13094401359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02491211891174</t>
   </si>
   <si>
     <t xml:space="preserve">2.08823680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1029634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9822051525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83641135692596</t>
+    <t xml:space="preserve">2.10296368598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220479488373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83641159534454</t>
   </si>
   <si>
     <t xml:space="preserve">1.65380132198334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63318395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3872492313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42922008037567</t>
+    <t xml:space="preserve">1.63318383693695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38724899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42921984195709</t>
   </si>
   <si>
     <t xml:space="preserve">1.35190510749817</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30330729484558</t>
+    <t xml:space="preserve">1.30330717563629</t>
   </si>
   <si>
     <t xml:space="preserve">1.36442291736603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32171559333801</t>
+    <t xml:space="preserve">1.32171547412872</t>
   </si>
   <si>
     <t xml:space="preserve">1.3150886297226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40565741062164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37767684459686</t>
+    <t xml:space="preserve">1.40565729141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37767672538757</t>
   </si>
   <si>
     <t xml:space="preserve">1.49475347995758</t>
@@ -2288,28 +2288,28 @@
     <t xml:space="preserve">1.50948011875153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58311355113983</t>
+    <t xml:space="preserve">1.58311343193054</t>
   </si>
   <si>
     <t xml:space="preserve">1.65674662590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55071461200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54776954650879</t>
+    <t xml:space="preserve">1.55071473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5477694272995</t>
   </si>
   <si>
     <t xml:space="preserve">1.53598809242249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56249606609344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56102335453033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55365991592407</t>
+    <t xml:space="preserve">1.56249594688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56102323532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55366003513336</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">1.60225808620453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62434804439545</t>
+    <t xml:space="preserve">1.62434792518616</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256659030914</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">1.61698484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62287509441376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64643812179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65527379512787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67589139938354</t>
+    <t xml:space="preserve">1.62287521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64643800258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65527403354645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67589116096497</t>
   </si>
   <si>
     <t xml:space="preserve">1.66705513000488</t>
@@ -2351,37 +2351,37 @@
     <t xml:space="preserve">1.64349269866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60520327091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57574999332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58753132820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55807816982269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427763938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047663211823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784007072449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64201986789703</t>
+    <t xml:space="preserve">1.60520339012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57575011253357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.587531208992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5580780506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427740097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5904768705368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59784018993378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64202010631561</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558253765106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62876582145691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61109399795532</t>
+    <t xml:space="preserve">1.6287659406662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61109387874603</t>
   </si>
   <si>
     <t xml:space="preserve">1.6788364648819</t>
@@ -2390,55 +2390,55 @@
     <t xml:space="preserve">1.71859848499298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76572370529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75836038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72007131576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70828974246979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907444477081</t>
+    <t xml:space="preserve">1.76572382450104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7583601474762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7200710773468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7082896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63907468318939</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70534443855286</t>
+    <t xml:space="preserve">1.70534455776215</t>
   </si>
   <si>
     <t xml:space="preserve">1.71123492717743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77756810188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76836585998535</t>
+    <t xml:space="preserve">1.77756786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76836562156677</t>
   </si>
   <si>
     <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69781529903412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71161866188049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71621966362</t>
+    <t xml:space="preserve">1.69781506061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7116185426712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71621954441071</t>
   </si>
   <si>
     <t xml:space="preserve">1.69168031215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548367500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72542190551758</t>
+    <t xml:space="preserve">1.70548379421234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72542202472687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73462414741516</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">1.73769164085388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73002302646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6870790719986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6855456829071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327570915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65793859958649</t>
+    <t xml:space="preserve">1.73002314567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68707919120789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68554556369781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327582836151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65793871879578</t>
   </si>
   <si>
     <t xml:space="preserve">1.65487134456635</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">1.68401193618774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241630077362</t>
+    <t xml:space="preserve">1.70241641998291</t>
   </si>
   <si>
     <t xml:space="preserve">1.72235453128815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70701742172241</t>
+    <t xml:space="preserve">1.7070175409317</t>
   </si>
   <si>
     <t xml:space="preserve">1.66867482662201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64566898345947</t>
+    <t xml:space="preserve">1.64566886425018</t>
   </si>
   <si>
     <t xml:space="preserve">1.65333759784698</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">1.65640509128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6272646188736</t>
+    <t xml:space="preserve">1.62726449966431</t>
   </si>
   <si>
     <t xml:space="preserve">1.63646686077118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64720273017883</t>
+    <t xml:space="preserve">1.64720261096954</t>
   </si>
   <si>
     <t xml:space="preserve">1.67020845413208</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">1.66407382488251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68247818946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7284893989563</t>
+    <t xml:space="preserve">1.68247807025909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72848927974701</t>
   </si>
   <si>
     <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75609624385834</t>
+    <t xml:space="preserve">1.75609612464905</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">1.72082078456879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69321405887604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094444274902</t>
+    <t xml:space="preserve">1.69321393966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094420433044</t>
   </si>
   <si>
     <t xml:space="preserve">1.67174208164215</t>
@@ -2537,76 +2537,76 @@
     <t xml:space="preserve">1.69934904575348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778769493103</t>
+    <t xml:space="preserve">1.67787683010101</t>
   </si>
   <si>
     <t xml:space="preserve">1.69014656543732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71008491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861281871796</t>
+    <t xml:space="preserve">1.71008503437042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861293792725</t>
   </si>
   <si>
     <t xml:space="preserve">1.65180397033691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64873671531677</t>
+    <t xml:space="preserve">1.64873647689819</t>
   </si>
   <si>
     <t xml:space="preserve">1.62573075294495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61959600448608</t>
+    <t xml:space="preserve">1.61959612369537</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659039974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505665302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58738803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57971942424774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57358491420746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54904544353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55057919025421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49996674060822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48156249523163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4961324930191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50303435325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51990509033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5475115776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5643824338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53064095973969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60425889492035</t>
+    <t xml:space="preserve">1.59505653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58738815784454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57971954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57358479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54904556274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4999668598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48156237602234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49613237380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50303423404694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51990497112274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54751169681549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56438255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53064107894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60425901412964</t>
   </si>
   <si>
     <t xml:space="preserve">1.59198927879333</t>
@@ -2618,34 +2618,34 @@
     <t xml:space="preserve">1.60119152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.614994764328</t>
+    <t xml:space="preserve">1.61499488353729</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125340938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57511842250824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60272514820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66100609302521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74075901508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069736480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388803958893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186585903168</t>
+    <t xml:space="preserve">1.57511830329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60272526741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6610062122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7407591342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069712638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388815879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628131389618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6318656206131</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">1.60886013507843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61039388179779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346125602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58585453033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6395343542099</t>
+    <t xml:space="preserve">1.6103937625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346137523651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58585441112518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63953423500061</t>
   </si>
   <si>
     <t xml:space="preserve">1.64260160923004</t>
@@ -2678,22 +2678,22 @@
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947234630585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66714107990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62266337871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.555180311203</t>
+    <t xml:space="preserve">1.65947258472443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66714096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6226634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55518043041229</t>
   </si>
   <si>
     <t xml:space="preserve">1.55671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56131505966187</t>
+    <t xml:space="preserve">1.56131517887115</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">1.57051742076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55978143215179</t>
+    <t xml:space="preserve">1.5597813129425</t>
   </si>
   <si>
     <t xml:space="preserve">1.58278691768646</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">1.63339948654175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62419724464417</t>
+    <t xml:space="preserve">1.62419700622559</t>
   </si>
   <si>
     <t xml:space="preserve">1.61192750930786</t>
@@ -2723,25 +2723,25 @@
     <t xml:space="preserve">1.58432066440582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806237697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106798171997</t>
+    <t xml:space="preserve">1.61806225776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106810092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.66560733318329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71775329113007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80517494678497</t>
+    <t xml:space="preserve">1.67480957508087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71775341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75762975215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80517470836639</t>
   </si>
   <si>
     <t xml:space="preserve">1.8174444437027</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290521144867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82051193714142</t>
+    <t xml:space="preserve">1.79903972148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290509223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82051181793213</t>
   </si>
   <si>
     <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79443871974945</t>
+    <t xml:space="preserve">1.79443883895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.83278167247772</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">1.82971394062042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885441303253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891642093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818043231964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85578727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345565319061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965229034424</t>
+    <t xml:space="preserve">1.85885465145111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891654014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498951911926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85578715801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86345589160919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965217113495</t>
   </si>
   <si>
     <t xml:space="preserve">1.87112414836884</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">1.89566338062286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90179812908173</t>
+    <t xml:space="preserve">1.90179848670959</t>
   </si>
   <si>
     <t xml:space="preserve">1.9186692237854</t>
@@ -2816,34 +2816,34 @@
     <t xml:space="preserve">1.90026462078094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91100060939789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627594947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95394480228424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91560161113739</t>
+    <t xml:space="preserve">1.91100072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95394432544708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9156014919281</t>
   </si>
   <si>
     <t xml:space="preserve">1.92173659801483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91713535785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695004940033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007931232452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382066726685</t>
+    <t xml:space="preserve">1.91713559627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553960323334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382090568542</t>
   </si>
   <si>
     <t xml:space="preserve">1.96621406078339</t>
@@ -2858,28 +2858,28 @@
     <t xml:space="preserve">2.01375913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00915765762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95701217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854568481445</t>
+    <t xml:space="preserve">2.00915813446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9570118188858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854544639587</t>
   </si>
   <si>
     <t xml:space="preserve">1.96928155422211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9784836769104</t>
+    <t xml:space="preserve">1.97848379611969</t>
   </si>
   <si>
     <t xml:space="preserve">2.00302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01069164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01836013793945</t>
+    <t xml:space="preserve">2.01069140434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01836037635803</t>
   </si>
   <si>
     <t xml:space="preserve">2.0290961265564</t>
@@ -2891,25 +2891,25 @@
     <t xml:space="preserve">2.01682662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01631951332092</t>
+    <t xml:space="preserve">2.01631927490234</t>
   </si>
   <si>
     <t xml:space="preserve">1.99563097953796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97335112094879</t>
+    <t xml:space="preserve">1.97335124015808</t>
   </si>
   <si>
     <t xml:space="preserve">1.97175967693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94470584392548</t>
+    <t xml:space="preserve">1.94470572471619</t>
   </si>
   <si>
     <t xml:space="preserve">1.9224259853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.916060090065</t>
+    <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2921,40 +2921,40 @@
     <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92719995975494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96061992645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95743691921234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539425849915</t>
+    <t xml:space="preserve">1.92720031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9797168970108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96061980724335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95743715763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539390087128</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926520347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96857702732086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287767887115</t>
+    <t xml:space="preserve">1.98926544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96857678890228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287732124329</t>
   </si>
   <si>
     <t xml:space="preserve">1.94788861274719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449122905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03223347663879</t>
+    <t xml:space="preserve">1.98449087142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03223323822021</t>
   </si>
   <si>
     <t xml:space="preserve">2.01950216293335</t>
@@ -2966,64 +2966,64 @@
     <t xml:space="preserve">2.06087875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04337358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04814743995667</t>
+    <t xml:space="preserve">2.04337334632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04814767837524</t>
   </si>
   <si>
     <t xml:space="preserve">2.02427625656128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06247043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06724429130554</t>
+    <t xml:space="preserve">2.06247019767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.07997584342957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09270715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10543847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13726663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14522409439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18819189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20251441001892</t>
+    <t xml:space="preserve">2.09270739555359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10543823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13726687431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14522361755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18819165229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2025146484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.1706862449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15158915519714</t>
+    <t xml:space="preserve">2.15158939361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.12453532218933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11816954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10066413879395</t>
+    <t xml:space="preserve">2.1181697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10066437721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.08315849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07042741775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10862112045288</t>
+    <t xml:space="preserve">2.07042717933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10862135887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.089524269104</t>
@@ -3032,61 +3032,61 @@
     <t xml:space="preserve">2.0847499370575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0879328250885</t>
+    <t xml:space="preserve">2.08793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.06565308570862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14840626716614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12135243415833</t>
+    <t xml:space="preserve">2.11180424690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14840650558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12135219573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339569091797</t>
+    <t xml:space="preserve">2.11339521408081</t>
   </si>
   <si>
     <t xml:space="preserve">2.13249230384827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612676620483</t>
+    <t xml:space="preserve">2.12612652778625</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363241195679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04178190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05928754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09589004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02586770057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03064227104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98767364025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01154518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15477204322815</t>
+    <t xml:space="preserve">2.04178214073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05928730964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04019045829773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09588980674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02586793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03064203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98767375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01154494285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15477228164673</t>
   </si>
   <si>
     <t xml:space="preserve">2.18341755867004</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">2.18978333473206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023467063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16113805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20569753646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21842861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29163360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27412796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2534396648407</t>
+    <t xml:space="preserve">2.18023490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16113781929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20569777488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21842885017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29163384437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27412819862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25343990325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.29481649398804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23593425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25025677680969</t>
+    <t xml:space="preserve">2.23593401908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25025701522827</t>
   </si>
   <si>
     <t xml:space="preserve">2.27571940422058</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">2.27890229225159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22161149978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23115968704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.200923204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17546057701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19296622276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19774055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10384702682495</t>
+    <t xml:space="preserve">2.22161173820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23115992546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20092296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17546033859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19296598434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19774031639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10384726524353</t>
   </si>
   <si>
     <t xml:space="preserve">2.15795493125916</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">2.17386937141418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15954637527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12930989265442</t>
+    <t xml:space="preserve">2.15954661369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12930965423584</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771821022034</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">2.10702991485596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07520174980164</t>
+    <t xml:space="preserve">2.07520151138306</t>
   </si>
   <si>
     <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08634161949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14204096794128</t>
+    <t xml:space="preserve">2.086341381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14204049110413</t>
   </si>
   <si>
     <t xml:space="preserve">2.09748125076294</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">2.09111571311951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06883549690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01472806930542</t>
+    <t xml:space="preserve">2.06883597373962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01472783088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97812533378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97016847133636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03700733184814</t>
+    <t xml:space="preserve">1.97812557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97016859054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03700757026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.11976099014282</t>
@@ -3218,34 +3218,34 @@
     <t xml:space="preserve">1.98130822181702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02109336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380281448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91128599643707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89378070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00677061080933</t>
+    <t xml:space="preserve">2.02109360694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380257606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91128623485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89378046989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969479084015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00677084922791</t>
   </si>
   <si>
     <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90651178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945771217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8126186132431</t>
+    <t xml:space="preserve">1.90651166439056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945783138275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261873245239</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
@@ -3254,64 +3254,64 @@
     <t xml:space="preserve">1.7553277015686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79033875465393</t>
+    <t xml:space="preserve">1.79033887386322</t>
   </si>
   <si>
     <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8333066701889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84922099113464</t>
+    <t xml:space="preserve">1.83330690860748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84922087192535</t>
   </si>
   <si>
     <t xml:space="preserve">1.83171546459198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82534968852997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81102728843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82694137096405</t>
+    <t xml:space="preserve">1.82534980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81102705001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82694113254547</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444689750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88423204421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8380811214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85240375995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88104939460754</t>
+    <t xml:space="preserve">1.84444665908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88423216342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83808100223541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85240387916565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88104927539825</t>
   </si>
   <si>
     <t xml:space="preserve">1.92879164218903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96698534488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99881374835968</t>
+    <t xml:space="preserve">1.8953720331192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96698546409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99881386756897</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313638687134</t>
+    <t xml:space="preserve">2.01313662528992</t>
   </si>
   <si>
     <t xml:space="preserve">1.98289978504181</t>
@@ -3326,28 +3326,28 @@
     <t xml:space="preserve">1.93197453022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95107126235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9542543888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786626815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90173780918121</t>
+    <t xml:space="preserve">1.95107138156891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95425450801849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786638736725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90173768997192</t>
   </si>
   <si>
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9526629447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93038308620453</t>
+    <t xml:space="preserve">1.96221125125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95266270637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93038320541382</t>
   </si>
   <si>
     <t xml:space="preserve">1.93993151187897</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">1.66143441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65984296798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69007992744446</t>
+    <t xml:space="preserve">1.65984284877777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69007980823517</t>
   </si>
   <si>
     <t xml:space="preserve">1.64711153507233</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">1.6168749332428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483191490173</t>
+    <t xml:space="preserve">1.62483179569244</t>
   </si>
   <si>
     <t xml:space="preserve">1.65506863594055</t>
@@ -3398,22 +3398,22 @@
     <t xml:space="preserve">1.70758521556854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6964453458786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68053126335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65825176239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68848836421967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56435811519623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58345520496368</t>
+    <t xml:space="preserve">1.69644546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68053138256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65825164318085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68848824501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56435823440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58345508575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">1.5850465297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58743381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54128277301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47842192649841</t>
+    <t xml:space="preserve">1.58743369579315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54128265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4784220457077</t>
   </si>
   <si>
     <t xml:space="preserve">1.51025021076202</t>
@@ -3443,13 +3443,13 @@
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446163654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5026695728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50688099861145</t>
+    <t xml:space="preserve">1.51446175575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50266945362091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50688111782074</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698863506317</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">1.54141545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54815399646759</t>
+    <t xml:space="preserve">1.5481538772583</t>
   </si>
   <si>
     <t xml:space="preserve">1.48835027217865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47487342357635</t>
+    <t xml:space="preserve">1.47487354278564</t>
   </si>
   <si>
     <t xml:space="preserve">1.49087715148926</t>
@@ -3482,19 +3482,19 @@
     <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47403109073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47150421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48498106002808</t>
+    <t xml:space="preserve">1.47403120994568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47150409221649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48498117923737</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171960353851</t>
+    <t xml:space="preserve">1.49171948432922</t>
   </si>
   <si>
     <t xml:space="preserve">1.46645045280457</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">1.3990660905838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3620046377182</t>
+    <t xml:space="preserve">1.36200487613678</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26177060604095</t>
+    <t xml:space="preserve">1.26177084445953</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3539,34 +3539,34 @@
     <t xml:space="preserve">1.20617866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23229014873505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22976315021515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29209363460541</t>
+    <t xml:space="preserve">1.23229002952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22976326942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2920937538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.31988966464996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798972606659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23144781589508</t>
+    <t xml:space="preserve">1.29798984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21712863445282</t>
+    <t xml:space="preserve">1.21712875366211</t>
   </si>
   <si>
     <t xml:space="preserve">1.2255517244339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20365166664124</t>
+    <t xml:space="preserve">1.20365178585052</t>
   </si>
   <si>
     <t xml:space="preserve">1.20533633232117</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">1.175013422966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13289821147919</t>
+    <t xml:space="preserve">1.13289833068848</t>
   </si>
   <si>
     <t xml:space="preserve">1.14637506008148</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">1.11942136287689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1059445142746</t>
+    <t xml:space="preserve">1.10594439506531</t>
   </si>
   <si>
     <t xml:space="preserve">1.14300584793091</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">1.16911733150482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21965539455414</t>
+    <t xml:space="preserve">1.21965551376343</t>
   </si>
   <si>
     <t xml:space="preserve">1.16490578651428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13710963726044</t>
+    <t xml:space="preserve">1.13710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">1.11352527141571</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">1.12279057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0815178155899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10425996780396</t>
+    <t xml:space="preserve">1.08151769638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10425984859467</t>
   </si>
   <si>
     <t xml:space="preserve">1.15732502937317</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.14553272724152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18427884578705</t>
+    <t xml:space="preserve">1.18427872657776</t>
   </si>
   <si>
     <t xml:space="preserve">1.22470927238464</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.26008605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29462051391602</t>
+    <t xml:space="preserve">1.29462039470673</t>
   </si>
   <si>
     <t xml:space="preserve">1.28367066383362</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">1.26682448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26935148239136</t>
+    <t xml:space="preserve">1.26935136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.28030133247375</t>
@@ -3659,16 +3659,16 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24492454528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25334763526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818624019623</t>
+    <t xml:space="preserve">1.24829375743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24492466449738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25334775447845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818612098694</t>
   </si>
   <si>
     <t xml:space="preserve">1.30809736251831</t>
@@ -3680,16 +3680,16 @@
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31652045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3299971818924</t>
+    <t xml:space="preserve">1.3165203332901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32999730110168</t>
   </si>
   <si>
     <t xml:space="preserve">1.32831275463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32915496826172</t>
+    <t xml:space="preserve">1.32915484905243</t>
   </si>
   <si>
     <t xml:space="preserve">1.33168184757233</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35358166694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32747042179108</t>
+    <t xml:space="preserve">1.3535817861557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32747030258179</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3716,37 +3716,37 @@
     <t xml:space="preserve">1.367058634758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32662808895111</t>
+    <t xml:space="preserve">1.32662796974182</t>
   </si>
   <si>
     <t xml:space="preserve">1.33589339256287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31062436103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29546272754669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30135893821716</t>
+    <t xml:space="preserve">1.31062424182892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29546284675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30135881900787</t>
   </si>
   <si>
     <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2365015745163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25503218173981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23734390735626</t>
+    <t xml:space="preserve">1.23650169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2550323009491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23734378814697</t>
   </si>
   <si>
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039032936096</t>
+    <t xml:space="preserve">1.21039021015167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3761,19 +3761,19 @@
     <t xml:space="preserve">1.34263181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37127017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36958563327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43865430355072</t>
+    <t xml:space="preserve">1.37127006053925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3695855140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43865442276001</t>
   </si>
   <si>
     <t xml:space="preserve">1.44539284706116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139669418335</t>
+    <t xml:space="preserve">1.46139657497406</t>
   </si>
   <si>
     <t xml:space="preserve">1.4656081199646</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">1.41338527202606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43360066413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44370830059052</t>
+    <t xml:space="preserve">1.4336005449295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44370818138123</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42265057563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44623517990112</t>
+    <t xml:space="preserve">1.42265069484711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44623506069183</t>
   </si>
   <si>
     <t xml:space="preserve">1.39232778549194</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770457267761</t>
+    <t xml:space="preserve">1.42770445346832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
@@ -3824,13 +3824,13 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727378845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40327775478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39317011833191</t>
+    <t xml:space="preserve">1.38727390766144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40327763557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39316999912262</t>
   </si>
   <si>
     <t xml:space="preserve">1.37800860404968</t>
@@ -3851,13 +3851,13 @@
     <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37716639041901</t>
+    <t xml:space="preserve">1.37716615200043</t>
   </si>
   <si>
     <t xml:space="preserve">1.34431648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34515881538391</t>
+    <t xml:space="preserve">1.34515869617462</t>
   </si>
   <si>
     <t xml:space="preserve">1.31820511817932</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.41170072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41254305839539</t>
+    <t xml:space="preserve">1.41254317760468</t>
   </si>
   <si>
     <t xml:space="preserve">1.44202363491058</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">1.42686212062836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4470773935318</t>
+    <t xml:space="preserve">1.44707751274109</t>
   </si>
   <si>
     <t xml:space="preserve">1.48666572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48329651355743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47655808925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53888845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5666846036911</t>
+    <t xml:space="preserve">1.48329663276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47655820846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53888857364655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56668448448181</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61132669448853</t>
+    <t xml:space="preserve">1.61132657527924</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
@@ -3926,25 +3926,25 @@
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942663669586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60037672519684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59784960746765</t>
+    <t xml:space="preserve">1.58942675590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60037660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59784972667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64754557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65007269382477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62396109104156</t>
+    <t xml:space="preserve">1.64754569530487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65007257461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62396121025085</t>
   </si>
   <si>
     <t xml:space="preserve">1.59953439235687</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">1.61806511878967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61048436164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64249193668365</t>
+    <t xml:space="preserve">1.61048424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64249181747437</t>
   </si>
   <si>
     <t xml:space="preserve">1.66186487674713</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">1.62480342388153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61385345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795736312866</t>
+    <t xml:space="preserve">1.61385357379913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795748233795</t>
   </si>
   <si>
     <t xml:space="preserve">1.58100366592407</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">1.58353066444397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57089602947235</t>
+    <t xml:space="preserve">1.57089614868164</t>
   </si>
   <si>
     <t xml:space="preserve">1.57594990730286</t>
@@ -4007,19 +4007,19 @@
     <t xml:space="preserve">1.58437299728394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58184599876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57173836231232</t>
+    <t xml:space="preserve">1.58184611797333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57173848152161</t>
   </si>
   <si>
     <t xml:space="preserve">1.59026908874512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5801614522934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55152308940887</t>
+    <t xml:space="preserve">1.58016133308411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55152320861816</t>
   </si>
   <si>
     <t xml:space="preserve">1.54877960681915</t>
@@ -70926,7 +70926,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6910763889</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>2370291</v>
@@ -70947,6 +70947,32 @@
         <v>1712</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6911805556</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>1198697</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>2.55200004577637</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>2.50399994850159</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>2.5460000038147</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>2.53600001335144</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -38,139 +38,139 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933469414710999</t>
+    <t xml:space="preserve">0.933469295501709</t>
   </si>
   <si>
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806130886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92702704668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921873569488525</t>
+    <t xml:space="preserve">0.923806190490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927027225494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873390674591</t>
   </si>
   <si>
     <t xml:space="preserve">0.901902675628662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898037552833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652355670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835356235504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880643546581268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863893985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346323490143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851653814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154513835907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192548274994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163442134857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451975345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869691908359528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886441588401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344924449921</t>
+    <t xml:space="preserve">0.898037433624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652474880219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835237026215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880643486976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863894045352936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346442699432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851653933525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154633045197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192786693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163322925568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869691967964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886441469192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875489830970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344864845276</t>
   </si>
   <si>
     <t xml:space="preserve">0.888374149799347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85551917552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279004096985</t>
+    <t xml:space="preserve">0.85551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84327906370163</t>
   </si>
   <si>
     <t xml:space="preserve">0.818798959255219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837480962276459</t>
+    <t xml:space="preserve">0.837481081485748</t>
   </si>
   <si>
     <t xml:space="preserve">0.825241029262543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848432779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869047701358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778185367584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172191619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671492099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142847061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709407329559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919296443462372</t>
+    <t xml:space="preserve">0.848432898521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86904764175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172251224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923161923885345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671372890472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709466934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919296503067017</t>
   </si>
   <si>
     <t xml:space="preserve">0.916075468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941199958324432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947642147541046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892586708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906412184238434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918008029460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95408433675766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391767978668</t>
+    <t xml:space="preserve">0.941199898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947641909122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892527103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934113442897797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906412303447723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918008387088776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954084277153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391708374023</t>
   </si>
   <si>
     <t xml:space="preserve">0.999179363250732</t>
@@ -182,85 +182,85 @@
     <t xml:space="preserve">1.02881336212158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0165730714798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00819838047028</t>
+    <t xml:space="preserve">1.01657330989838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00819849967957</t>
   </si>
   <si>
     <t xml:space="preserve">1.00175631046295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00497734546661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00755417346954</t>
+    <t xml:space="preserve">1.00497722625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00755429267883</t>
   </si>
   <si>
     <t xml:space="preserve">1.02172696590424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01464068889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02237105369568</t>
+    <t xml:space="preserve">1.01464056968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02237117290497</t>
   </si>
   <si>
     <t xml:space="preserve">0.999823689460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01141965389252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01786172389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430391311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01850593090057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0268806219101</t>
+    <t xml:space="preserve">1.01141941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206374168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01786160469055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430379390717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01850581169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02688086032867</t>
   </si>
   <si>
     <t xml:space="preserve">1.03203451633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0249480009079</t>
+    <t xml:space="preserve">1.02494812011719</t>
   </si>
   <si>
     <t xml:space="preserve">1.01721739768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00562179088593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988871872425079</t>
+    <t xml:space="preserve">1.00562155246735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988871812820435</t>
   </si>
   <si>
     <t xml:space="preserve">1.00368893146515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03525531291962</t>
+    <t xml:space="preserve">1.0352555513382</t>
   </si>
   <si>
     <t xml:space="preserve">1.02816903591156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04040920734406</t>
+    <t xml:space="preserve">1.04040932655334</t>
   </si>
   <si>
     <t xml:space="preserve">1.03396713733673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0294576883316</t>
+    <t xml:space="preserve">1.02945756912231</t>
   </si>
   <si>
     <t xml:space="preserve">1.03010177612305</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">1.01592910289764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992093086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03332281112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00948691368103</t>
+    <t xml:space="preserve">0.992092967033386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.033322930336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00948679447174</t>
   </si>
   <si>
     <t xml:space="preserve">0.99595832824707</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">0.995314002037048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02108263969421</t>
+    <t xml:space="preserve">1.02108299732208</t>
   </si>
   <si>
     <t xml:space="preserve">1.0494282245636</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">1.06295680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05715906620026</t>
+    <t xml:space="preserve">1.05715894699097</t>
   </si>
   <si>
     <t xml:space="preserve">1.07326412200928</t>
@@ -308,58 +308,58 @@
     <t xml:space="preserve">1.0474956035614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06360101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0616682767868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06811058521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04620718955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977275967597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968257129192352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965036153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978564560413361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962522566318512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979232907295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517227649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712280750275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964867115021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701663017273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101407527924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117304325104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127683639526</t>
+    <t xml:space="preserve">1.06360113620758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06166851520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06811034679413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04620730876923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977276146411896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968257188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965035796165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978564441204071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962522387504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232847690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517346858978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90771210193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87696498632431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701543807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680606365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127862453461</t>
   </si>
   <si>
     <t xml:space="preserve">0.909048914909363</t>
@@ -368,160 +368,160 @@
     <t xml:space="preserve">0.903033196926117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915733218193054</t>
+    <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
     <t xml:space="preserve">0.925090968608856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931775212287903</t>
+    <t xml:space="preserve">0.931775152683258</t>
   </si>
   <si>
     <t xml:space="preserve">0.925759494304657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912391185760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921080470085144</t>
+    <t xml:space="preserve">0.912391126155853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921080648899078</t>
   </si>
   <si>
     <t xml:space="preserve">0.927096307277679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945143699645996</t>
+    <t xml:space="preserve">0.945143640041351</t>
   </si>
   <si>
     <t xml:space="preserve">0.937122583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955838322639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164517879486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964527606964111</t>
+    <t xml:space="preserve">0.955838143825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95316469669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964527666568756</t>
   </si>
   <si>
     <t xml:space="preserve">0.965196073055267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982575058937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983911871910095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97254878282547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973217070102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984580218791962</t>
+    <t xml:space="preserve">0.982574939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98391181230545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972548842430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973217129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984580457210541</t>
   </si>
   <si>
     <t xml:space="preserve">0.987253904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99527496099472</t>
+    <t xml:space="preserve">0.995274841785431</t>
   </si>
   <si>
     <t xml:space="preserve">0.98925918340683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992601335048676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890815258026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827824115753</t>
+    <t xml:space="preserve">0.99260139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975890934467316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827764511108</t>
   </si>
   <si>
     <t xml:space="preserve">0.950490891933441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948485672473907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941133201122284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501330852509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864539146423</t>
+    <t xml:space="preserve">0.948485791683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94113302230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501450061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864598751068</t>
   </si>
   <si>
     <t xml:space="preserve">0.985917150974274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989927649497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01265406608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02000665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932809352875</t>
+    <t xml:space="preserve">0.989927589893341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01265370845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02000641822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99193274974823</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996611773967743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979901194572449</t>
+    <t xml:space="preserve">0.996611714363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979901254177094</t>
   </si>
   <si>
     <t xml:space="preserve">0.967201352119446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986585557460785</t>
+    <t xml:space="preserve">0.98658549785614</t>
   </si>
   <si>
     <t xml:space="preserve">0.977896213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973885595798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995943307876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02401685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00864338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00262761116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969206571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975222587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248684883118</t>
+    <t xml:space="preserve">0.973885416984558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995943486690521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02401697635651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00864326953888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00262749195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969206511974335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975222289562225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248625278473</t>
   </si>
   <si>
     <t xml:space="preserve">1.0293642282486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05342721939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0554324388504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07615351676941</t>
+    <t xml:space="preserve">1.05342733860016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05543255805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07615339756012</t>
   </si>
   <si>
     <t xml:space="preserve">1.0895220041275</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">1.09420073032379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09687471389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07013785839081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08751678466797</t>
+    <t xml:space="preserve">1.09687459468842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07013773918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08751666545868</t>
   </si>
   <si>
     <t xml:space="preserve">1.09353244304657</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">1.07749056816101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06479048728943</t>
+    <t xml:space="preserve">1.06479060649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.06278514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04741168022156</t>
+    <t xml:space="preserve">1.04741156101227</t>
   </si>
   <si>
     <t xml:space="preserve">1.06077992916107</t>
@@ -563,52 +563,52 @@
     <t xml:space="preserve">1.05209052562714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957843363285065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953832864761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946480393409729</t>
+    <t xml:space="preserve">0.957843542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953832924365997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946480631828308</t>
   </si>
   <si>
     <t xml:space="preserve">0.93578565120697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942469894886017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933780550956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913727879524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738437652588</t>
+    <t xml:space="preserve">0.942469835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933780372142792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913727760314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738258838654</t>
   </si>
   <si>
     <t xml:space="preserve">0.94180154800415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918406903743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968538343906403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967869877815247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980569660663605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994606494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997948586940765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332211494446</t>
+    <t xml:space="preserve">0.918406784534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968538165092468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967869758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980569779872894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994606554508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9979487657547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332235336304</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532745361328</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203785419464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04005885124207</t>
+    <t xml:space="preserve">1.03203797340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04005908966064</t>
   </si>
   <si>
     <t xml:space="preserve">1.04473781585693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03070116043091</t>
+    <t xml:space="preserve">1.03070104122162</t>
   </si>
   <si>
     <t xml:space="preserve">1.01733267307281</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">1.036048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04874849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04941689968109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275905132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05008518695831</t>
+    <t xml:space="preserve">1.04874837398529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494167804718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275893211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0500853061676</t>
   </si>
   <si>
     <t xml:space="preserve">1.04072737693787</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">1.04607486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02468514442444</t>
+    <t xml:space="preserve">1.02468538284302</t>
   </si>
   <si>
     <t xml:space="preserve">1.01064848899841</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">1.00530123710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0300327539444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0427325963974</t>
+    <t xml:space="preserve">1.03003287315369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04273247718811</t>
   </si>
   <si>
     <t xml:space="preserve">1.02334856987</t>
@@ -677,46 +677,46 @@
     <t xml:space="preserve">1.05676937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06412208080292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05610108375549</t>
+    <t xml:space="preserve">1.06412196159363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0561009645462</t>
   </si>
   <si>
     <t xml:space="preserve">1.05810618400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08484292030334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07080614566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0821692943573</t>
+    <t xml:space="preserve">1.08484303951263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07080626487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08216917514801</t>
   </si>
   <si>
     <t xml:space="preserve">1.0688009262085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07815885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08283770084381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08818519115448</t>
+    <t xml:space="preserve">1.07815897464752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0828378200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
     <t xml:space="preserve">1.09620606899261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754300117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12628483772278</t>
+    <t xml:space="preserve">1.09954822063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754312038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12628495693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.18978476524353</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">1.22120046615601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22988986968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24058449268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26665270328522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28002119064331</t>
+    <t xml:space="preserve">1.22988998889923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24058437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26665282249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28002107143402</t>
   </si>
   <si>
     <t xml:space="preserve">1.28336334228516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29405784606934</t>
+    <t xml:space="preserve">1.29405808448792</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26932644844055</t>
+    <t xml:space="preserve">1.26932656764984</t>
   </si>
   <si>
     <t xml:space="preserve">1.30074214935303</t>
@@ -755,40 +755,40 @@
     <t xml:space="preserve">1.31009995937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30475258827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007386207581</t>
+    <t xml:space="preserve">1.30475270748138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007374286652</t>
   </si>
   <si>
     <t xml:space="preserve">1.31143689155579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29004752635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28871071338654</t>
+    <t xml:space="preserve">1.29004740715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28871047496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28937911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27200031280518</t>
+    <t xml:space="preserve">1.28937923908234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2720000743866</t>
   </si>
   <si>
     <t xml:space="preserve">1.2593001127243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29673159122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806864261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31076848506927</t>
+    <t xml:space="preserve">1.29673171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806840419769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31076836585999</t>
   </si>
   <si>
     <t xml:space="preserve">1.29338943958282</t>
@@ -797,25 +797,25 @@
     <t xml:space="preserve">1.32814729213715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30341589450836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683669567108</t>
+    <t xml:space="preserve">1.30341577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683681488037</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349466323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35421562194824</t>
+    <t xml:space="preserve">1.35421574115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.37025761604309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37426805496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.364910364151</t>
+    <t xml:space="preserve">1.37426817417145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36491024494171</t>
   </si>
   <si>
     <t xml:space="preserve">1.37961542606354</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">1.33616828918457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34886801242828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39031004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41036260128021</t>
+    <t xml:space="preserve">1.34886813163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3903101682663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4103627204895</t>
   </si>
   <si>
     <t xml:space="preserve">1.42105746269226</t>
@@ -839,97 +839,97 @@
     <t xml:space="preserve">1.43175208568573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4504679441452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39966821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41303646564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43442559242249</t>
+    <t xml:space="preserve">1.45046782493591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39966809749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41303658485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43442571163177</t>
   </si>
   <si>
     <t xml:space="preserve">1.41704678535461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42239415645599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40902578830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43977320194244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44779419898987</t>
+    <t xml:space="preserve">1.42239451408386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40902590751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43977332115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44779407978058</t>
   </si>
   <si>
     <t xml:space="preserve">1.47052049636841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46784675121307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46116256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319388389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46249949932098</t>
+    <t xml:space="preserve">1.46784687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46116268634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46249914169312</t>
   </si>
   <si>
     <t xml:space="preserve">1.46650993824005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48474228382111</t>
+    <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
     <t xml:space="preserve">1.48336637020111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49024653434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47235822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42282068729401</t>
+    <t xml:space="preserve">1.49024641513824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47235798835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42282092571259</t>
   </si>
   <si>
     <t xml:space="preserve">1.44208526611328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40630829334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39530038833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39942812919617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40080416202545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40218043327332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38429188728333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4145644903183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42144465446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43658125400543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43245303630829</t>
+    <t xml:space="preserve">1.4063081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3953001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39942800998688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40080428123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40218031406403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38429200649261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41456460952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42144477367401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43658113479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.432452917099</t>
   </si>
   <si>
     <t xml:space="preserve">1.42419683933258</t>
@@ -938,124 +938,124 @@
     <t xml:space="preserve">1.43107688426971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483721256256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4599734544754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44621348381042</t>
+    <t xml:space="preserve">1.44483733177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45997369289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44621336460114</t>
   </si>
   <si>
     <t xml:space="preserve">1.46685385704041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48199033737183</t>
+    <t xml:space="preserve">1.48199045658112</t>
   </si>
   <si>
     <t xml:space="preserve">1.46960592269897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44758951663971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923815250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125467777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50675904750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602326869965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54804015159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54115986824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52327120304108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189528942108</t>
+    <t xml:space="preserve">1.44758939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400698184967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50125479698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987876415253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50675892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602338790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54804003238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115998744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52327156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189552783966</t>
   </si>
   <si>
     <t xml:space="preserve">1.54528796672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57968878746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831275463104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556080818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693672180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56317639350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5466639995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55354428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381688594818</t>
+    <t xml:space="preserve">1.57968890666962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831263542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556068897247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693684101105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5631765127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54666388034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55354404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592833995819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381700515747</t>
   </si>
   <si>
     <t xml:space="preserve">1.59069728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58656895160675</t>
+    <t xml:space="preserve">1.58656907081604</t>
   </si>
   <si>
     <t xml:space="preserve">1.58244097232819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60996150970459</t>
+    <t xml:space="preserve">1.60996162891388</t>
   </si>
   <si>
     <t xml:space="preserve">1.63197803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711463451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408960819244</t>
+    <t xml:space="preserve">1.64711487293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408972740173</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583364963531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60032916069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455254554749</t>
+    <t xml:space="preserve">1.6003292798996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455230712891</t>
   </si>
   <si>
     <t xml:space="preserve">1.53978371620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53565573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
+    <t xml:space="preserve">1.53565585613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391181468964</t>
   </si>
   <si>
     <t xml:space="preserve">1.56180047988892</t>
@@ -1067,448 +1067,451 @@
     <t xml:space="preserve">1.54941618442535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427970409393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005679607391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868052482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234580516815</t>
+    <t xml:space="preserve">1.53427946567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005667686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234592437744</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684155464172</t>
   </si>
   <si>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482514858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57280874252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509799003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6608749628067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940388202667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7035323381424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69802784919739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252383708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949869155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986658096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785017490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6622508764267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6760116815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490825176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7489413022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7310528755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004437446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830069065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76682984828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233397960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545357704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77370989322662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74068474769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049512863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022240638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747022151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444519519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159820079803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297435283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7682056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7585734128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554838657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142040729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169336795807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499087810516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921378612518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8370076417923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85351979732513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86039996147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516891002655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076773166656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123054981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710257053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79572629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564367294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.634730219841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151557445526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6801393032074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64298641681671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500318050385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701958656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463552951813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454036235809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426764011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876350879669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65261876583099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306940078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930895328522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417235374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692453861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362690925598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289148807526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71316432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343693256378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380494117737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7420608997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994944572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178829669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839573860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399479866028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720944404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757721424103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620130062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034158229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47648620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611843585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4751101732254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572217464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832493782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776719093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079209804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530690193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54826188087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52411460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121674060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127397060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837586402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672751903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55536413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513604640961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934007167816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6221239566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951128482819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223817825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60365855693817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371554851532</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.62922596931458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61133778095245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482514858246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280898094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6250981092453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66087484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637909412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353209972382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69802761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252383708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949881076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986681938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785017490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66225099563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490789413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7489413022995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7310528755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004449367523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518073558807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830069065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618923664093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76682984828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233397960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545369625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77371001243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7406849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82049489021301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022228717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747022151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444543361664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7915985584259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79297411441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76820576190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7585734128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142064571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499087810516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031733512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481308460236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113562107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700740337372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.853520154953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86039996147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516891002655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8136146068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957261800766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737517356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573848247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738747596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472998142242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66913139820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6801393032074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64298641681671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500318050385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6870197057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114768505096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63335430622101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215582847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527566432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67876350879669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65261888504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306928157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73930883407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7241724729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692465782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362702846527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289124965668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71316421031952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343717098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7338045835495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7420608997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75994956493378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178829669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68839550018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6539945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849054813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757709503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620118141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290367126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49299871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034158229828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4764860868454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611843585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45722150802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832493782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776719093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079209804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542112350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530702114105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54826200008392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52411460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121674060822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127397060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837598323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672751903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5553640127182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246638298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59513604640961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507881641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934019088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6221239566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57951128482819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223817825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60365855693817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371554851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63632810115814</t>
+    <t xml:space="preserve">1.63632822036743</t>
   </si>
   <si>
     <t xml:space="preserve">1.63348722457886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62638509273529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076045036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58803391456604</t>
+    <t xml:space="preserve">1.626384973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076056957245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58803367614746</t>
   </si>
   <si>
     <t xml:space="preserve">1.59229516983032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68888378143311</t>
+    <t xml:space="preserve">1.68888413906097</t>
   </si>
   <si>
     <t xml:space="preserve">1.68178176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69882667064667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013318538666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729254722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911198616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66757762432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894101142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752039432526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.643430352211</t>
+    <t xml:space="preserve">1.69882678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013306617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729230880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911210536957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757750511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894089221954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752051353455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183887958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64343047142029</t>
   </si>
   <si>
     <t xml:space="preserve">1.6192831993103</t>
@@ -1526,10 +1529,10 @@
     <t xml:space="preserve">1.55962550640106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55394351482391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55252325534821</t>
+    <t xml:space="preserve">1.5539436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5525233745575</t>
   </si>
   <si>
     <t xml:space="preserve">1.55110275745392</t>
@@ -1538,13 +1541,13 @@
     <t xml:space="preserve">1.51701271533966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51559233665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871817111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43462812900543</t>
+    <t xml:space="preserve">1.51559221744537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871829032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43462800979614</t>
   </si>
   <si>
     <t xml:space="preserve">1.44741189479828</t>
@@ -1559,43 +1562,43 @@
     <t xml:space="preserve">1.47013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47297954559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53263735771179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58377277851105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973960876465</t>
+    <t xml:space="preserve">1.47297942638397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5326372385025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58377265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973948955536</t>
   </si>
   <si>
     <t xml:space="preserve">1.51275146007538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48718392848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47724068164825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144506454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138795375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49996757507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49570620059967</t>
+    <t xml:space="preserve">1.4871838092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138807296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49996745586395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49570631980896</t>
   </si>
   <si>
     <t xml:space="preserve">1.41687273979187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4218442440033</t>
+    <t xml:space="preserve">1.42184448242188</t>
   </si>
   <si>
     <t xml:space="preserve">1.3991174697876</t>
@@ -1604,49 +1607,49 @@
     <t xml:space="preserve">1.38065195083618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37426006793976</t>
+    <t xml:space="preserve">1.37426018714905</t>
   </si>
   <si>
     <t xml:space="preserve">1.3522435426712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37994158267975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37070894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573755741119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37923157215118</t>
+    <t xml:space="preserve">1.37994170188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37070906162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573731899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37923145294189</t>
   </si>
   <si>
     <t xml:space="preserve">1.37212944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35579442977905</t>
+    <t xml:space="preserve">1.35579454898834</t>
   </si>
   <si>
     <t xml:space="preserve">1.38633358478546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36431705951691</t>
+    <t xml:space="preserve">1.3643171787262</t>
   </si>
   <si>
     <t xml:space="preserve">1.39343583583832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39130508899689</t>
+    <t xml:space="preserve">1.39130520820618</t>
   </si>
   <si>
     <t xml:space="preserve">1.35863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40906035900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40124809741974</t>
+    <t xml:space="preserve">1.40906023979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40124821662903</t>
   </si>
   <si>
     <t xml:space="preserve">1.46019566059113</t>
@@ -1655,13 +1658,13 @@
     <t xml:space="preserve">1.45309352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47440004348755</t>
+    <t xml:space="preserve">1.47439980506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.47866117954254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45593440532684</t>
+    <t xml:space="preserve">1.45593428611755</t>
   </si>
   <si>
     <t xml:space="preserve">1.42894637584686</t>
@@ -1670,16 +1673,16 @@
     <t xml:space="preserve">1.440309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39556646347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568032741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38704371452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201545715332</t>
+    <t xml:space="preserve">1.39556634426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3870438337326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201533794403</t>
   </si>
   <si>
     <t xml:space="preserve">1.37781119346619</t>
@@ -1691,19 +1694,19 @@
     <t xml:space="preserve">1.38136219978333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3351982831955</t>
+    <t xml:space="preserve">1.33519840240479</t>
   </si>
   <si>
     <t xml:space="preserve">1.36076593399048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940254688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43178737163544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320763111115</t>
+    <t xml:space="preserve">1.34940266609192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43178713321686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
   </si>
   <si>
     <t xml:space="preserve">1.42468512058258</t>
@@ -1715,10 +1718,10 @@
     <t xml:space="preserve">1.48150205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51985359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48860418796539</t>
+    <t xml:space="preserve">1.51985371112823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48860394954681</t>
   </si>
   <si>
     <t xml:space="preserve">1.49428594112396</t>
@@ -1727,9 +1730,6 @@
     <t xml:space="preserve">1.54258036613464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54116010665894</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">1.52695560455322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53405797481537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51133096218109</t>
+    <t xml:space="preserve">1.53405773639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5113308429718</t>
   </si>
   <si>
     <t xml:space="preserve">1.5099104642868</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">1.49854707717896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50706946849823</t>
+    <t xml:space="preserve">1.50706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.48292255401611</t>
@@ -1766,31 +1766,31 @@
     <t xml:space="preserve">1.50564908981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53689873218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61644220352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780547142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63206684589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60081768035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62496483325958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5993971824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62070381641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61502182483673</t>
+    <t xml:space="preserve">1.53689861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61644244194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63206720352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6008175611496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62496471405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939742088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62070369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61502194404602</t>
   </si>
   <si>
     <t xml:space="preserve">1.64627110958099</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">1.61218106746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51417183876038</t>
+    <t xml:space="preserve">1.51417171955109</t>
   </si>
   <si>
     <t xml:space="preserve">1.50422871112823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48576354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45877516269684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49286544322968</t>
+    <t xml:space="preserve">1.48576331138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4630366563797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45877528190613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49286532402039</t>
   </si>
   <si>
     <t xml:space="preserve">1.55678451061249</t>
@@ -1829,91 +1829,91 @@
     <t xml:space="preserve">1.57382965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63916909694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450866222382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166754722595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172477722168</t>
+    <t xml:space="preserve">1.63916921615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450854301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166766643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172465801239</t>
   </si>
   <si>
     <t xml:space="preserve">1.69061768054962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69356298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69798099994659</t>
+    <t xml:space="preserve">1.69356310367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69798111915588</t>
   </si>
   <si>
     <t xml:space="preserve">1.67294585704803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68325471878052</t>
+    <t xml:space="preserve">1.68325459957123</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72890710830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75099682807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76277840137482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74510622024536</t>
+    <t xml:space="preserve">1.7289069890976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75099718570709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277828216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74510633945465</t>
   </si>
   <si>
     <t xml:space="preserve">1.73332500457764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77161419391632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750504016876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7981219291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80106747150421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80548560619354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401289463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8113762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455973625183</t>
+    <t xml:space="preserve">1.77161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812228679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8010675907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80548548698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401301383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455961704254</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603220939636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76719641685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216091632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239925384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7392156124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77014148235321</t>
+    <t xml:space="preserve">1.76719653606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7421612739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239913463593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921573162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7701416015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78486835956573</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">1.79517686367035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79370427131653</t>
+    <t xml:space="preserve">1.79370450973511</t>
   </si>
   <si>
     <t xml:space="preserve">1.78339552879333</t>
@@ -1937,31 +1937,31 @@
     <t xml:space="preserve">1.79959487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80254030227661</t>
+    <t xml:space="preserve">1.80254018306732</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308678627014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7819230556488</t>
+    <t xml:space="preserve">1.78192293643951</t>
   </si>
   <si>
     <t xml:space="preserve">1.83493888378143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8202121257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81873953342438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168483734131</t>
+    <t xml:space="preserve">1.82021200656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81873941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82168471813202</t>
   </si>
   <si>
     <t xml:space="preserve">1.84966564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84819281101227</t>
+    <t xml:space="preserve">1.84819293022156</t>
   </si>
   <si>
     <t xml:space="preserve">1.82904827594757</t>
@@ -1970,64 +1970,64 @@
     <t xml:space="preserve">1.76425087451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81432127952576</t>
+    <t xml:space="preserve">1.81432139873505</t>
   </si>
   <si>
     <t xml:space="preserve">1.80990350246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8319935798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91593527793884</t>
+    <t xml:space="preserve">1.83199381828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8614467382431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91593539714813</t>
   </si>
   <si>
     <t xml:space="preserve">1.93655288219452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9321346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512791633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97042381763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95569705963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9424432516098</t>
+    <t xml:space="preserve">1.93213486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127928256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97042393684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95569694042206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94244337081909</t>
   </si>
   <si>
     <t xml:space="preserve">1.94980669021606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96158766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809564113617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693179130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00724005699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98367774486542</t>
+    <t xml:space="preserve">1.9615877866745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693191051483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00724053382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.983677983284</t>
   </si>
   <si>
     <t xml:space="preserve">1.99987733364105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00576758384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98073256015778</t>
+    <t xml:space="preserve">2.00576782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98073267936707</t>
   </si>
   <si>
     <t xml:space="preserve">1.97189652919769</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">1.97631466388702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94391584396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96895122528076</t>
+    <t xml:space="preserve">1.94391596317291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96895110607147</t>
   </si>
   <si>
     <t xml:space="preserve">1.96600592136383</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">1.97484183311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01754903793335</t>
+    <t xml:space="preserve">2.01754927635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04847502708435</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">2.04552960395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03374838829041</t>
+    <t xml:space="preserve">2.03374862670898</t>
   </si>
   <si>
     <t xml:space="preserve">2.05436563491821</t>
@@ -2069,49 +2069,49 @@
     <t xml:space="preserve">2.02785754203796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227591514587</t>
+    <t xml:space="preserve">2.03227567672729</t>
   </si>
   <si>
     <t xml:space="preserve">2.04111170768738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03816628456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01018571853638</t>
+    <t xml:space="preserve">2.03816652297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01018595695496</t>
   </si>
   <si>
     <t xml:space="preserve">2.00871300697327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99251401424408</t>
+    <t xml:space="preserve">1.99251413345337</t>
   </si>
   <si>
     <t xml:space="preserve">2.02638530731201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07940101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467413902283</t>
+    <t xml:space="preserve">2.07940077781677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467437744141</t>
   </si>
   <si>
     <t xml:space="preserve">2.0720374584198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06172895431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03522086143494</t>
+    <t xml:space="preserve">2.06172871589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03522133827209</t>
   </si>
   <si>
     <t xml:space="preserve">2.02933049201965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06614685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07645559310913</t>
+    <t xml:space="preserve">2.06614661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07645583152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.08676433563232</t>
@@ -2132,31 +2132,31 @@
     <t xml:space="preserve">2.0028223991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01313090324402</t>
+    <t xml:space="preserve">2.0131311416626</t>
   </si>
   <si>
     <t xml:space="preserve">2.01460385322571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11179947853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08087348937988</t>
+    <t xml:space="preserve">2.04258465766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11179971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08087396621704</t>
   </si>
   <si>
     <t xml:space="preserve">2.07498288154602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11032700538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13683485984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10885429382324</t>
+    <t xml:space="preserve">2.11032676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10885405540466</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652635574341</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">2.17659687995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20457744598389</t>
+    <t xml:space="preserve">2.20457768440247</t>
   </si>
   <si>
     <t xml:space="preserve">2.19426870346069</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">2.21341347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20899534225464</t>
+    <t xml:space="preserve">2.20899558067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.21783137321472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20163202285767</t>
+    <t xml:space="preserve">2.20163178443909</t>
   </si>
   <si>
     <t xml:space="preserve">2.20752263069153</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">2.23255825042725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21930408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21635890007019</t>
+    <t xml:space="preserve">2.21930360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21635842323303</t>
   </si>
   <si>
     <t xml:space="preserve">2.20310473442078</t>
@@ -2210,16 +2210,16 @@
     <t xml:space="preserve">2.24728465080261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2870466709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26201128959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25023031234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11474466323853</t>
+    <t xml:space="preserve">2.28704643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26201105117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25023007392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1147449016571</t>
   </si>
   <si>
     <t xml:space="preserve">2.11621761322021</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">2.15303421020508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13094401359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02491211891174</t>
+    <t xml:space="preserve">2.13094425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02491235733032</t>
   </si>
   <si>
     <t xml:space="preserve">2.08823680877686</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">2.10296368598938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220479488373</t>
+    <t xml:space="preserve">1.9822051525116</t>
   </si>
   <si>
     <t xml:space="preserve">1.83641159534454</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">1.63318383693695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38724899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42921984195709</t>
+    <t xml:space="preserve">1.38724911212921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42922008037567</t>
   </si>
   <si>
     <t xml:space="preserve">1.35190510749817</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">1.35043263435364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30330717563629</t>
+    <t xml:space="preserve">1.30330729484558</t>
   </si>
   <si>
     <t xml:space="preserve">1.36442291736603</t>
@@ -2273,25 +2273,25 @@
     <t xml:space="preserve">1.32171547412872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3150886297226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40565729141235</t>
+    <t xml:space="preserve">1.31508874893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40565741062164</t>
   </si>
   <si>
     <t xml:space="preserve">1.37767672538757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49475347995758</t>
+    <t xml:space="preserve">1.49475359916687</t>
   </si>
   <si>
     <t xml:space="preserve">1.50948011875153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58311343193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65674662590027</t>
+    <t xml:space="preserve">1.58311331272125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65674650669098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55071473121643</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">1.53598809242249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56249594688416</t>
+    <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
     <t xml:space="preserve">1.56102323532104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55366003513336</t>
+    <t xml:space="preserve">1.55365991592407</t>
   </si>
   <si>
     <t xml:space="preserve">1.54924213886261</t>
@@ -2321,28 +2321,28 @@
     <t xml:space="preserve">1.58164060115814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60225808620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434792518616</t>
+    <t xml:space="preserve">1.60225796699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434804439545</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256659030914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61698484420776</t>
+    <t xml:space="preserve">1.61698472499847</t>
   </si>
   <si>
     <t xml:space="preserve">1.62287521362305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64643800258636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65527403354645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67589116096497</t>
+    <t xml:space="preserve">1.64643788337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65527367591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67589128017426</t>
   </si>
   <si>
     <t xml:space="preserve">1.66705513000488</t>
@@ -2354,22 +2354,22 @@
     <t xml:space="preserve">1.60520339012146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57575011253357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.587531208992</t>
+    <t xml:space="preserve">1.57575023174286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58753132820129</t>
   </si>
   <si>
     <t xml:space="preserve">1.5580780506134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57427740097046</t>
+    <t xml:space="preserve">1.57427728176117</t>
   </si>
   <si>
     <t xml:space="preserve">1.5904768705368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784018993378</t>
+    <t xml:space="preserve">1.59784007072449</t>
   </si>
   <si>
     <t xml:space="preserve">1.64202010631561</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">1.66558253765106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6287659406662</t>
+    <t xml:space="preserve">1.62876582145691</t>
   </si>
   <si>
     <t xml:space="preserve">1.61109387874603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6788364648819</t>
+    <t xml:space="preserve">1.67883658409119</t>
   </si>
   <si>
     <t xml:space="preserve">1.71859848499298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76572382450104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7583601474762</t>
+    <t xml:space="preserve">1.76572370529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75836026668549</t>
   </si>
   <si>
     <t xml:space="preserve">1.7200710773468</t>
@@ -2405,28 +2405,28 @@
     <t xml:space="preserve">1.63907468318939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65821933746338</t>
+    <t xml:space="preserve">1.65821945667267</t>
   </si>
   <si>
     <t xml:space="preserve">1.70534455776215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71123492717743</t>
+    <t xml:space="preserve">1.71123504638672</t>
   </si>
   <si>
     <t xml:space="preserve">1.77756786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76836562156677</t>
+    <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
     <t xml:space="preserve">1.71468603610992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69781506061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7116185426712</t>
+    <t xml:space="preserve">1.69781517982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71161866188049</t>
   </si>
   <si>
     <t xml:space="preserve">1.71621954441071</t>
@@ -2435,28 +2435,28 @@
     <t xml:space="preserve">1.69168031215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70548379421234</t>
+    <t xml:space="preserve">1.70548367500305</t>
   </si>
   <si>
     <t xml:space="preserve">1.72542202472687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73462414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73769164085388</t>
+    <t xml:space="preserve">1.73462426662445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73769152164459</t>
   </si>
   <si>
     <t xml:space="preserve">1.73002314567566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68707919120789</t>
+    <t xml:space="preserve">1.68707942962646</t>
   </si>
   <si>
     <t xml:space="preserve">1.68554556369781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67327582836151</t>
+    <t xml:space="preserve">1.67327570915222</t>
   </si>
   <si>
     <t xml:space="preserve">1.65793871879578</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">1.68401193618774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241641998291</t>
+    <t xml:space="preserve">1.70241630077362</t>
   </si>
   <si>
     <t xml:space="preserve">1.72235453128815</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">1.7070175409317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66867482662201</t>
+    <t xml:space="preserve">1.66867470741272</t>
   </si>
   <si>
     <t xml:space="preserve">1.64566886425018</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">1.65333759784698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640509128571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62726449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63646686077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64720261096954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67020845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66407382488251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68247807025909</t>
+    <t xml:space="preserve">1.656405210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6272646188736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63646697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64720273017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67020833492279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66407370567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68247818946838</t>
   </si>
   <si>
     <t xml:space="preserve">1.72848927974701</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75609612464905</t>
+    <t xml:space="preserve">1.75609600543976</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">1.69321393966675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68094420433044</t>
+    <t xml:space="preserve">1.68094444274902</t>
   </si>
   <si>
     <t xml:space="preserve">1.67174208164215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69934904575348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67787683010101</t>
+    <t xml:space="preserve">1.6993488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6778769493103</t>
   </si>
   <si>
     <t xml:space="preserve">1.69014656543732</t>
@@ -2549,37 +2549,37 @@
     <t xml:space="preserve">1.68861293792725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65180397033691</t>
+    <t xml:space="preserve">1.65180385112762</t>
   </si>
   <si>
     <t xml:space="preserve">1.64873647689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62573075294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61959612369537</t>
+    <t xml:space="preserve">1.62573063373566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61959600448608</t>
   </si>
   <si>
     <t xml:space="preserve">1.59659039974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505653381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58738815784454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57971954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57358479499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54904556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55057907104492</t>
+    <t xml:space="preserve">1.59505665302277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58738803863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57971978187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57358467578888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54904544353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057919025421</t>
   </si>
   <si>
     <t xml:space="preserve">1.4999668598175</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">1.51990497112274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54751169681549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56438255310059</t>
+    <t xml:space="preserve">1.5475115776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5643824338913</t>
   </si>
   <si>
     <t xml:space="preserve">1.53064107894897</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965777397156</t>
+    <t xml:space="preserve">1.59965789318085</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">1.58125340938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57511830329895</t>
+    <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
     <t xml:space="preserve">1.60272526741028</t>
@@ -2633,25 +2633,25 @@
     <t xml:space="preserve">1.6610062122345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7407591342926</t>
+    <t xml:space="preserve">1.74075901508331</t>
   </si>
   <si>
     <t xml:space="preserve">1.76069712638855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388815879822</t>
+    <t xml:space="preserve">1.72388803958893</t>
   </si>
   <si>
     <t xml:space="preserve">1.69628131389618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6318656206131</t>
+    <t xml:space="preserve">1.63186573982239</t>
   </si>
   <si>
     <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63033187389374</t>
+    <t xml:space="preserve">1.63033199310303</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889219045639</t>
@@ -2666,34 +2666,34 @@
     <t xml:space="preserve">1.61346137523651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58585441112518</t>
+    <t xml:space="preserve">1.58585453033447</t>
   </si>
   <si>
     <t xml:space="preserve">1.63953423500061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64260160923004</t>
+    <t xml:space="preserve">1.64260172843933</t>
   </si>
   <si>
     <t xml:space="preserve">1.63493311405182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65947258472443</t>
+    <t xml:space="preserve">1.65947246551514</t>
   </si>
   <si>
     <t xml:space="preserve">1.66714096069336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6226634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55518043041229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56131517887115</t>
+    <t xml:space="preserve">1.62266337871552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55518054962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55671393871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56131505966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">1.57051742076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5597813129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278691768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60732638835907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63339948654175</t>
+    <t xml:space="preserve">1.55978143215179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278703689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60732626914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63339960575104</t>
   </si>
   <si>
     <t xml:space="preserve">1.62419700622559</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">1.58432066440582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806225776672</t>
+    <t xml:space="preserve">1.61806213855743</t>
   </si>
   <si>
     <t xml:space="preserve">1.64106810092926</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">1.66560733318329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67480957508087</t>
+    <t xml:space="preserve">1.67480945587158</t>
   </si>
   <si>
     <t xml:space="preserve">1.71775341033936</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">1.80517470836639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8174444437027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80824220180511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670857429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80364108085632</t>
+    <t xml:space="preserve">1.81744432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80824208259583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80364096164703</t>
   </si>
   <si>
     <t xml:space="preserve">1.79903972148895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79290509223938</t>
+    <t xml:space="preserve">1.79290533065796</t>
   </si>
   <si>
     <t xml:space="preserve">1.82051181793213</t>
@@ -2768,43 +2768,43 @@
     <t xml:space="preserve">1.78063535690308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79443883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83278167247772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80977582931519</t>
+    <t xml:space="preserve">1.79443871974945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83278179168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80977594852448</t>
   </si>
   <si>
     <t xml:space="preserve">1.82971394062042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85885465145111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83891654014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82818031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86498951911926</t>
+    <t xml:space="preserve">1.85885453224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83891642093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82818055152893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86498939990997</t>
   </si>
   <si>
     <t xml:space="preserve">1.85578715801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86345589160919</t>
+    <t xml:space="preserve">1.8634557723999</t>
   </si>
   <si>
     <t xml:space="preserve">1.84965217113495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87112414836884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89566338062286</t>
+    <t xml:space="preserve">1.87112426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89566326141357</t>
   </si>
   <si>
     <t xml:space="preserve">1.90179848670959</t>
@@ -2813,70 +2813,70 @@
     <t xml:space="preserve">1.9186692237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90026462078094</t>
+    <t xml:space="preserve">1.90026450157166</t>
   </si>
   <si>
     <t xml:space="preserve">1.91100072860718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94627618789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95394432544708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9156014919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92173659801483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91713559627533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93553960323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382090568542</t>
+    <t xml:space="preserve">1.94627594947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95394456386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91560161113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92173671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91713547706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93553984165192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695004940033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007931232452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382078647614</t>
   </si>
   <si>
     <t xml:space="preserve">1.96621406078339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00609040260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762414932251</t>
+    <t xml:space="preserve">2.00609064102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762438774109</t>
   </si>
   <si>
     <t xml:space="preserve">2.01375913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00915813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9570118188858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95854544639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96928155422211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97848379611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01069140434265</t>
+    <t xml:space="preserve">2.00915789604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95701193809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95854556560516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9692816734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9784836769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00302290916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01069188117981</t>
   </si>
   <si>
     <t xml:space="preserve">2.01836037635803</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01682662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01631927490234</t>
+    <t xml:space="preserve">2.01682686805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01631903648376</t>
   </si>
   <si>
     <t xml:space="preserve">1.99563097953796</t>
@@ -2900,58 +2900,58 @@
     <t xml:space="preserve">1.97335124015808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97175967693329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94470572471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9224259853363</t>
+    <t xml:space="preserve">1.97175979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9447056055069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92242586612701</t>
   </si>
   <si>
     <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91446888446808</t>
+    <t xml:space="preserve">1.9144686460495</t>
   </si>
   <si>
     <t xml:space="preserve">1.90332901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92720031738281</t>
+    <t xml:space="preserve">1.92401731014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92720007896423</t>
   </si>
   <si>
     <t xml:space="preserve">1.9797168970108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96061980724335</t>
+    <t xml:space="preserve">1.96061968803406</t>
   </si>
   <si>
     <t xml:space="preserve">1.95743715763092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96539390087128</t>
+    <t xml:space="preserve">1.96539402008057</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98926544189453</t>
+    <t xml:space="preserve">1.98926532268524</t>
   </si>
   <si>
     <t xml:space="preserve">1.96857678890228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91287732124329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94788861274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449087142944</t>
+    <t xml:space="preserve">1.91287744045258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94788873195648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449110984802</t>
   </si>
   <si>
     <t xml:space="preserve">2.03223323822021</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">2.04337334632874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04814767837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02427625656128</t>
+    <t xml:space="preserve">2.04814743995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02427649497986</t>
   </si>
   <si>
     <t xml:space="preserve">2.06247019767761</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">2.07997584342957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09270739555359</t>
+    <t xml:space="preserve">2.09270715713501</t>
   </si>
   <si>
     <t xml:space="preserve">2.10543823242188</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">2.14522361755371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18819165229797</t>
+    <t xml:space="preserve">2.18819189071655</t>
   </si>
   <si>
     <t xml:space="preserve">2.2025146484375</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">2.15158939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12453532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1181697845459</t>
+    <t xml:space="preserve">2.12453556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11816954612732</t>
   </si>
   <si>
     <t xml:space="preserve">2.10066437721252</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">2.07042717933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10862135887146</t>
+    <t xml:space="preserve">2.10862112045288</t>
   </si>
   <si>
     <t xml:space="preserve">2.089524269104</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339521408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249230384827</t>
+    <t xml:space="preserve">2.11339545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249254226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612652778625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363241195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04178214073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05928730964661</t>
+    <t xml:space="preserve">2.14363217353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04178190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
     <t xml:space="preserve">2.04019045829773</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">2.09588980674744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02586793899536</t>
+    <t xml:space="preserve">2.02586770057678</t>
   </si>
   <si>
     <t xml:space="preserve">2.03064203262329</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">1.98767375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01154494285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15477228164673</t>
+    <t xml:space="preserve">2.01154518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
     <t xml:space="preserve">2.18341755867004</t>
@@ -3098,19 +3098,19 @@
     <t xml:space="preserve">2.18023490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16113781929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20569777488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21842885017395</t>
+    <t xml:space="preserve">2.16113805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20569729804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21842861175537</t>
   </si>
   <si>
     <t xml:space="preserve">2.29163384437561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27412819862366</t>
+    <t xml:space="preserve">2.27412796020508</t>
   </si>
   <si>
     <t xml:space="preserve">2.25343990325928</t>
@@ -3119,28 +3119,28 @@
     <t xml:space="preserve">2.29481649398804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23593401908875</t>
+    <t xml:space="preserve">2.23593425750732</t>
   </si>
   <si>
     <t xml:space="preserve">2.25025701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27571940422058</t>
+    <t xml:space="preserve">2.27571964263916</t>
   </si>
   <si>
     <t xml:space="preserve">2.27890229225159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22161173820496</t>
+    <t xml:space="preserve">2.22161149978638</t>
   </si>
   <si>
     <t xml:space="preserve">2.23115992546082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20092296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17546033859253</t>
+    <t xml:space="preserve">2.200923204422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17546057701111</t>
   </si>
   <si>
     <t xml:space="preserve">2.19296598434448</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10384726524353</t>
+    <t xml:space="preserve">2.10384678840637</t>
   </si>
   <si>
     <t xml:space="preserve">2.15795493125916</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">2.17386937141418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15954661369324</t>
+    <t xml:space="preserve">2.15954637527466</t>
   </si>
   <si>
     <t xml:space="preserve">2.12930965423584</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">2.12771821022034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10702991485596</t>
+    <t xml:space="preserve">2.10702967643738</t>
   </si>
   <si>
     <t xml:space="preserve">2.07520151138306</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.086341381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14204049110413</t>
+    <t xml:space="preserve">2.08634161949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14204072952271</t>
   </si>
   <si>
     <t xml:space="preserve">2.09748125076294</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">2.09907269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09111571311951</t>
+    <t xml:space="preserve">2.09111595153809</t>
   </si>
   <si>
     <t xml:space="preserve">2.06883597373962</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">2.01472783088684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02905058860779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97812557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97016859054565</t>
+    <t xml:space="preserve">2.02905035018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9781254529953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97016847133636</t>
   </si>
   <si>
     <t xml:space="preserve">2.03700757026672</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130822181702</t>
+    <t xml:space="preserve">1.98130810260773</t>
   </si>
   <si>
     <t xml:space="preserve">2.02109360694885</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">1.90969479084015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00677084922791</t>
+    <t xml:space="preserve">2.00677061080933</t>
   </si>
   <si>
     <t xml:space="preserve">2.00199675559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90651166439056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87945783138275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81261873245239</t>
+    <t xml:space="preserve">1.90651178359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87945795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8126186132431</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">1.85558676719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83330690860748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84922087192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83171546459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81102705001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82694113254547</t>
+    <t xml:space="preserve">1.83330678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84922075271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83171534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534968852997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8110271692276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82694101333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">1.84444665908813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88423216342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83808100223541</t>
+    <t xml:space="preserve">1.88423228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8380811214447</t>
   </si>
   <si>
     <t xml:space="preserve">1.85240387916565</t>
@@ -3296,16 +3296,16 @@
     <t xml:space="preserve">1.88104927539825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92879164218903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8953720331192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96698546409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99881386756897</t>
+    <t xml:space="preserve">1.92879152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96698534488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99881398677826</t>
   </si>
   <si>
     <t xml:space="preserve">2.01791071891785</t>
@@ -3314,49 +3314,49 @@
     <t xml:space="preserve">2.01313662528992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98289978504181</t>
+    <t xml:space="preserve">1.98289966583252</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035879611969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94311416149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197453022003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95107138156891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95425450801849</t>
+    <t xml:space="preserve">1.94311428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107126235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9542543888092</t>
   </si>
   <si>
     <t xml:space="preserve">1.87786638736725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90173768997192</t>
+    <t xml:space="preserve">1.90173780918121</t>
   </si>
   <si>
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221125125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95266270637512</t>
+    <t xml:space="preserve">1.96221137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
     <t xml:space="preserve">1.93038320541382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93993151187897</t>
+    <t xml:space="preserve">1.93993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">1.90014612674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91765177249908</t>
+    <t xml:space="preserve">1.91765165328979</t>
   </si>
   <si>
     <t xml:space="preserve">1.9192430973053</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">1.66143441200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65984284877777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69007980823517</t>
+    <t xml:space="preserve">1.65984296798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69007992744446</t>
   </si>
   <si>
     <t xml:space="preserve">1.64711153507233</t>
@@ -3401,19 +3401,19 @@
     <t xml:space="preserve">1.69644546508789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68053138256073</t>
+    <t xml:space="preserve">1.68053126335144</t>
   </si>
   <si>
     <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68848824501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56435823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58345508575439</t>
+    <t xml:space="preserve">1.68848836421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56435811519623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58345520496368</t>
   </si>
   <si>
     <t xml:space="preserve">1.57151961326599</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">1.54128265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4784220457077</t>
+    <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
     <t xml:space="preserve">1.51025021076202</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">1.51446175575256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50266945362091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50688111782074</t>
+    <t xml:space="preserve">1.5026695728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50688099861145</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698863506317</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">1.50856566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5136194229126</t>
+    <t xml:space="preserve">1.51361954212189</t>
   </si>
   <si>
     <t xml:space="preserve">1.54141545295715</t>
@@ -3470,22 +3470,22 @@
     <t xml:space="preserve">1.48835027217865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47487354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49087715148926</t>
+    <t xml:space="preserve">1.47487342357635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49087727069855</t>
   </si>
   <si>
     <t xml:space="preserve">1.47571575641632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46308124065399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47403120994568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47150409221649</t>
+    <t xml:space="preserve">1.4630811214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47403109073639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
     <t xml:space="preserve">1.48498117923737</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171948432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46645045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45718514919281</t>
+    <t xml:space="preserve">1.49171960353851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46645057201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45718502998352</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3512,22 +3512,22 @@
     <t xml:space="preserve">1.40748918056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3990660905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200487613678</t>
+    <t xml:space="preserve">1.39906620979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200475692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34178960323334</t>
+    <t xml:space="preserve">1.34178948402405</t>
   </si>
   <si>
     <t xml:space="preserve">1.26766681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26177084445953</t>
+    <t xml:space="preserve">1.26177060604095</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3542,25 +3542,25 @@
     <t xml:space="preserve">1.23229002952576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22976326942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2920937538147</t>
+    <t xml:space="preserve">1.22976315021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29209363460541</t>
   </si>
   <si>
     <t xml:space="preserve">1.31988966464996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23144769668579</t>
+    <t xml:space="preserve">1.29798972606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23144781589508</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21712875366211</t>
+    <t xml:space="preserve">1.21712863445282</t>
   </si>
   <si>
     <t xml:space="preserve">1.2255517244339</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">1.13289833068848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14637506008148</t>
+    <t xml:space="preserve">1.14637494087219</t>
   </si>
   <si>
     <t xml:space="preserve">1.10173296928406</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">1.11942136287689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10594439506531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14300584793091</t>
+    <t xml:space="preserve">1.1059445142746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1430059671402</t>
   </si>
   <si>
     <t xml:space="preserve">1.16911733150482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21965551376343</t>
+    <t xml:space="preserve">1.21965539455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.16490578651428</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">1.15732502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15985190868378</t>
+    <t xml:space="preserve">1.15985202789307</t>
   </si>
   <si>
     <t xml:space="preserve">1.16322124004364</t>
@@ -3632,16 +3632,16 @@
     <t xml:space="preserve">1.14553272724152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18427872657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22470927238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26008605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29462039470673</t>
+    <t xml:space="preserve">1.18427884578705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22470939159393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2600861787796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29462051391602</t>
   </si>
   <si>
     <t xml:space="preserve">1.28367066383362</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">1.26682448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26935136318207</t>
+    <t xml:space="preserve">1.26935148239136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28030133247375</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829375743866</t>
+    <t xml:space="preserve">1.24829387664795</t>
   </si>
   <si>
     <t xml:space="preserve">1.24492466449738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25334775447845</t>
+    <t xml:space="preserve">1.25334763526917</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818612098694</t>
@@ -3674,16 +3674,16 @@
     <t xml:space="preserve">1.30809736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32325887680054</t>
+    <t xml:space="preserve">1.32325875759125</t>
   </si>
   <si>
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3165203332901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32999730110168</t>
+    <t xml:space="preserve">1.31652045249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3299971818924</t>
   </si>
   <si>
     <t xml:space="preserve">1.32831275463104</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">1.33168184757233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35021269321442</t>
+    <t xml:space="preserve">1.35021257400513</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3535817861557</t>
+    <t xml:space="preserve">1.35358166694641</t>
   </si>
   <si>
     <t xml:space="preserve">1.32747030258179</t>
@@ -3716,28 +3716,28 @@
     <t xml:space="preserve">1.367058634758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32662796974182</t>
+    <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
     <t xml:space="preserve">1.33589339256287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31062424182892</t>
+    <t xml:space="preserve">1.31062436103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.29546284675598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30135881900787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25082075595856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23650169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2550323009491</t>
+    <t xml:space="preserve">1.30135893821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25082087516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2365015745163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25503218173981</t>
   </si>
   <si>
     <t xml:space="preserve">1.23734378814697</t>
@@ -3764,28 +3764,28 @@
     <t xml:space="preserve">1.37127006053925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3695855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43865442276001</t>
+    <t xml:space="preserve">1.36958563327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43865430355072</t>
   </si>
   <si>
     <t xml:space="preserve">1.44539284706116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46139657497406</t>
+    <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
     <t xml:space="preserve">1.4656081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4041200876236</t>
+    <t xml:space="preserve">1.40411996841431</t>
   </si>
   <si>
     <t xml:space="preserve">1.38222014904022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39822387695312</t>
+    <t xml:space="preserve">1.39822375774384</t>
   </si>
   <si>
     <t xml:space="preserve">1.41338527202606</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">1.4336005449295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44370818138123</t>
+    <t xml:space="preserve">1.44370830059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">1.42265069484711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44623506069183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39232778549194</t>
+    <t xml:space="preserve">1.44623517990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39232766628265</t>
   </si>
   <si>
     <t xml:space="preserve">1.41843914985657</t>
@@ -3824,37 +3824,37 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727390766144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40327763557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39316999912262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37800860404968</t>
+    <t xml:space="preserve">1.38727378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40327775478363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39317011833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37800872325897</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548172473907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35779321193695</t>
+    <t xml:space="preserve">1.35779333114624</t>
   </si>
   <si>
     <t xml:space="preserve">1.39569687843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40496218204498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3881162405014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37716615200043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431648254395</t>
+    <t xml:space="preserve">1.40496230125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811612129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37716627120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
     <t xml:space="preserve">1.34515869617462</t>
@@ -3869,22 +3869,22 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230890750885</t>
+    <t xml:space="preserve">1.31230878829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41254317760468</t>
+    <t xml:space="preserve">1.4125429391861</t>
   </si>
   <si>
     <t xml:space="preserve">1.44202363491058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45634281635284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42686212062836</t>
+    <t xml:space="preserve">1.45634269714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42686223983765</t>
   </si>
   <si>
     <t xml:space="preserve">1.44707751274109</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">1.48666572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48329663276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47655820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53888857364655</t>
+    <t xml:space="preserve">1.48329651355743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47655808925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53888845443726</t>
   </si>
   <si>
     <t xml:space="preserve">1.56668448448181</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">1.58689975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60711514949799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61132657527924</t>
+    <t xml:space="preserve">1.6071150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61132669448853</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942675590515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60037660598755</t>
+    <t xml:space="preserve">1.58942663669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
     <t xml:space="preserve">1.59784972667694</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">1.60543048381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64754569530487</t>
+    <t xml:space="preserve">1.64754557609558</t>
   </si>
   <si>
     <t xml:space="preserve">1.65007257461548</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.62396121025085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59953439235687</t>
+    <t xml:space="preserve">1.59953451156616</t>
   </si>
   <si>
     <t xml:space="preserve">1.6146959066391</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">1.61048424243927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64249181747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66186487674713</t>
+    <t xml:space="preserve">1.64249193668365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66186499595642</t>
   </si>
   <si>
     <t xml:space="preserve">1.62227654457092</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">1.62480342388153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61385357379913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795748233795</t>
+    <t xml:space="preserve">1.61385345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795736312866</t>
   </si>
   <si>
     <t xml:space="preserve">1.58100366592407</t>
@@ -3995,31 +3995,31 @@
     <t xml:space="preserve">1.57342302799225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353066444397</t>
+    <t xml:space="preserve">1.58353054523468</t>
   </si>
   <si>
     <t xml:space="preserve">1.57089614868164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57594990730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58437299728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58184611797333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57173848152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59026908874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58016133308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55152320861816</t>
+    <t xml:space="preserve">1.57595002651215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58437287807465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58184599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57173836231232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59026896953583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5801614522934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55152308940887</t>
   </si>
   <si>
     <t xml:space="preserve">1.54877960681915</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">1.51386487483978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53087472915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5210268497467</t>
+    <t xml:space="preserve">1.5308746099472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52102696895599</t>
   </si>
   <si>
     <t xml:space="preserve">1.47984552383423</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.4691025018692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47357881069183</t>
+    <t xml:space="preserve">1.47357869148254</t>
   </si>
   <si>
     <t xml:space="preserve">1.48432171344757</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">1.49864566326141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4950647354126</t>
+    <t xml:space="preserve">1.49506461620331</t>
   </si>
   <si>
     <t xml:space="preserve">1.50670289993286</t>
@@ -4088,52 +4088,52 @@
     <t xml:space="preserve">1.52729368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52192223072052</t>
+    <t xml:space="preserve">1.52192211151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60070395469666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308514118195</t>
+    <t xml:space="preserve">1.61144697666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60070407390594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308526039124</t>
   </si>
   <si>
     <t xml:space="preserve">1.59622776508331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60786604881287</t>
+    <t xml:space="preserve">1.60786592960358</t>
   </si>
   <si>
     <t xml:space="preserve">1.64815211296082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62039935588837</t>
+    <t xml:space="preserve">1.62039947509766</t>
   </si>
   <si>
     <t xml:space="preserve">1.60607552528381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59801816940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55773210525513</t>
+    <t xml:space="preserve">1.59801828861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55773198604584</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057013034821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56937038898468</t>
+    <t xml:space="preserve">1.56937026977539</t>
   </si>
   <si>
     <t xml:space="preserve">1.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502802371979</t>
+    <t xml:space="preserve">1.6150279045105</t>
   </si>
   <si>
     <t xml:space="preserve">1.59085619449615</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.55862736701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.582799077034</t>
+    <t xml:space="preserve">1.58279895782471</t>
   </si>
   <si>
     <t xml:space="preserve">1.5926468372345</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">1.68306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769527435303</t>
+    <t xml:space="preserve">1.67769539356232</t>
   </si>
   <si>
     <t xml:space="preserve">1.69022881984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68575251102448</t>
+    <t xml:space="preserve">1.68575263023376</t>
   </si>
   <si>
     <t xml:space="preserve">1.70992422103882</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">1.68485736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66426658630371</t>
+    <t xml:space="preserve">1.664266705513</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918131828308</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">1.70544803142548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71977210044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71887671947479</t>
+    <t xml:space="preserve">1.71977198123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">1.77975368499756</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">1.76811552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68843829631805</t>
+    <t xml:space="preserve">1.68843841552734</t>
   </si>
   <si>
     <t xml:space="preserve">1.6705334186554</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">1.63382828235626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60159933567047</t>
+    <t xml:space="preserve">1.60159921646118</t>
   </si>
   <si>
     <t xml:space="preserve">1.55504631996155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54340803623199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56399869918823</t>
+    <t xml:space="preserve">1.54340815544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56399881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.59533250331879</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">1.61771368980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61234223842621</t>
+    <t xml:space="preserve">1.61234211921692</t>
   </si>
   <si>
     <t xml:space="preserve">1.61592316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63024711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69112408161163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71350526809692</t>
+    <t xml:space="preserve">1.63024723529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69112420082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71350538730621</t>
   </si>
   <si>
     <t xml:space="preserve">1.73946738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74573421478271</t>
+    <t xml:space="preserve">1.745734333992</t>
   </si>
   <si>
     <t xml:space="preserve">1.73678183555603</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.7027622461319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69201934337616</t>
+    <t xml:space="preserve">1.69201922416687</t>
   </si>
   <si>
     <t xml:space="preserve">1.73409605026245</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.78333461284637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78691565990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7940776348114</t>
+    <t xml:space="preserve">1.78691577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79407751560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.7904965877533</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">1.86569762229919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83525907993317</t>
+    <t xml:space="preserve">1.83525896072388</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451617717743</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">1.80303013324738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82272553443909</t>
+    <t xml:space="preserve">1.82272565364838</t>
   </si>
   <si>
     <t xml:space="preserve">1.8621164560318</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">1.73499119281769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75558197498322</t>
+    <t xml:space="preserve">1.75558185577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.75289618968964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76453447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73857235908508</t>
+    <t xml:space="preserve">1.7645343542099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73857223987579</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617263793945</t>
@@ -4409,16 +4409,16 @@
     <t xml:space="preserve">1.71529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70723843574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67859065532684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66874277591705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64009499549866</t>
+    <t xml:space="preserve">1.70723855495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67859053611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66874289512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64009487628937</t>
   </si>
   <si>
     <t xml:space="preserve">1.62218999862671</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.58906579017639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740921020508</t>
+    <t xml:space="preserve">1.63740909099579</t>
   </si>
   <si>
     <t xml:space="preserve">1.64367592334747</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">1.67142856121063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6409900188446</t>
+    <t xml:space="preserve">1.63919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64099013805389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62756145000458</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">1.7323055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72693395614624</t>
+    <t xml:space="preserve">1.72693407535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.73588645458221</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">1.52908408641815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56041789054871</t>
+    <t xml:space="preserve">1.56041777133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.56131303310394</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">1.57742750644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58458948135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54609382152557</t>
+    <t xml:space="preserve">1.58458960056305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54609394073486</t>
   </si>
   <si>
     <t xml:space="preserve">1.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57205617427826</t>
+    <t xml:space="preserve">1.57205605506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.59354197978973</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">1.6186089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64278078079224</t>
+    <t xml:space="preserve">1.64278066158295</t>
   </si>
   <si>
     <t xml:space="preserve">1.686647772789</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">1.70097172260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68754315376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129473686218</t>
+    <t xml:space="preserve">1.68754303455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129461765289</t>
   </si>
   <si>
     <t xml:space="preserve">1.63561868667603</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">1.74304854869843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71708631515503</t>
+    <t xml:space="preserve">1.71708619594574</t>
   </si>
   <si>
     <t xml:space="preserve">1.72066736221313</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.74394369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76274383068085</t>
+    <t xml:space="preserve">1.76274394989014</t>
   </si>
   <si>
     <t xml:space="preserve">1.78154420852661</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">1.78870618343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78602051734924</t>
+    <t xml:space="preserve">1.78602039813995</t>
   </si>
   <si>
     <t xml:space="preserve">1.75737249851227</t>
@@ -22532,7 +22532,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G649" t="s">
-        <v>356</v>
+        <v>482</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22558,7 +22558,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G650" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22584,7 +22584,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G651" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22610,7 +22610,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22636,7 +22636,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G653" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22662,7 +22662,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G654" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22688,7 +22688,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G655" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22714,7 +22714,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G656" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22740,7 +22740,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G657" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22766,7 +22766,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G658" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22792,7 +22792,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G659" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22818,7 +22818,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G660" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22844,7 +22844,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G661" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22870,7 +22870,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G662" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22896,7 +22896,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G663" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22922,7 +22922,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22948,7 +22948,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G665" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22974,7 +22974,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G666" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23000,7 +23000,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G667" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23026,7 +23026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G668" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23052,7 +23052,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23078,7 +23078,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G670" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23104,7 +23104,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G671" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23130,7 +23130,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G672" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23156,7 +23156,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G673" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23208,7 +23208,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G675" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23234,7 +23234,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G676" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23286,7 +23286,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G678" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23312,7 +23312,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G679" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23338,7 +23338,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G680" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23364,7 +23364,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23390,7 +23390,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G682" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23416,7 +23416,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G683" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23442,7 +23442,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G684" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23468,7 +23468,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G685" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23494,7 +23494,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G686" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23520,7 +23520,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G687" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23572,7 +23572,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23624,7 +23624,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G691" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23728,7 +23728,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G695" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23754,7 +23754,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23780,7 +23780,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G697" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23806,7 +23806,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G698" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23832,7 +23832,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23858,7 +23858,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G700" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23884,7 +23884,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G701" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23910,7 +23910,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G702" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23936,7 +23936,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G703" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23962,7 +23962,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23988,7 +23988,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -24014,7 +24014,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G706" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -24040,7 +24040,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G707" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24066,7 +24066,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G708" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -24092,7 +24092,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G709" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -24118,7 +24118,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G710" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24144,7 +24144,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G711" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24170,7 +24170,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G712" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24196,7 +24196,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G713" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24222,7 +24222,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G714" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24248,7 +24248,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G715" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24274,7 +24274,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G716" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24300,7 +24300,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G717" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24326,7 +24326,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G718" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24352,7 +24352,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G719" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24378,7 +24378,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G720" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24404,7 +24404,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G721" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24430,7 +24430,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G722" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24456,7 +24456,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G723" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24482,7 +24482,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G724" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24508,7 +24508,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G725" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24534,7 +24534,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G726" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24560,7 +24560,7 @@
         <v>1.97300004959106</v>
       </c>
       <c r="G727" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24586,7 +24586,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G728" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24612,7 +24612,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G729" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24638,7 +24638,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G730" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24664,7 +24664,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24690,7 +24690,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G732" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24716,7 +24716,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G733" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24742,7 +24742,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G734" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24768,7 +24768,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G735" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24794,7 +24794,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G736" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24820,7 +24820,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G737" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24846,7 +24846,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G738" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24872,7 +24872,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G739" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24898,7 +24898,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G740" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24924,7 +24924,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G741" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24950,7 +24950,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G742" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24976,7 +24976,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -25002,7 +25002,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G744" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -25028,7 +25028,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G745" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -25054,7 +25054,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G746" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -25080,7 +25080,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G747" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G749" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -25158,7 +25158,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -25184,7 +25184,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G751" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25210,7 +25210,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G752" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25236,7 +25236,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G753" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25262,7 +25262,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G754" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25288,7 +25288,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25314,7 +25314,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G756" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25340,7 +25340,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G757" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25366,7 +25366,7 @@
         <v>2</v>
       </c>
       <c r="G758" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25392,7 +25392,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G759" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25418,7 +25418,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G760" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25444,7 +25444,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25470,7 +25470,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G762" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25496,7 +25496,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G763" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25522,7 +25522,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G764" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25574,7 +25574,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G766" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25600,7 +25600,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G767" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25626,7 +25626,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>571</v>
+        <v>322</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25678,7 +25678,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G770" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25756,7 +25756,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>571</v>
+        <v>322</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25912,7 +25912,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26094,7 +26094,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G786" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -26120,7 +26120,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G787" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26198,7 +26198,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G790" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26328,7 +26328,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26406,7 +26406,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G798" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26510,7 +26510,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G802" t="s">
-        <v>571</v>
+        <v>322</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26562,7 +26562,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G804" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26588,7 +26588,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G805" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26614,7 +26614,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26640,7 +26640,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G807" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26666,7 +26666,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G808" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26744,7 +26744,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G811" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26796,7 +26796,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G813" t="s">
-        <v>356</v>
+        <v>482</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26822,7 +26822,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G814" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26926,7 +26926,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G818" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26978,7 +26978,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G820" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27056,7 +27056,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -27186,7 +27186,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27290,7 +27290,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27550,7 +27550,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G842" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27576,7 +27576,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G843" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27602,7 +27602,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G844" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27628,7 +27628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27680,7 +27680,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G847" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27836,7 +27836,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G853" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G858" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28044,7 +28044,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G861" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28096,7 +28096,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G863" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28174,7 +28174,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G866" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28278,7 +28278,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G870" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28330,7 +28330,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28382,7 +28382,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G874" t="s">
-        <v>356</v>
+        <v>482</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28408,7 +28408,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G875" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28486,7 +28486,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G878" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28512,7 +28512,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G879" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28616,7 +28616,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G883" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -70952,7 +70952,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6911805556</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>1198697</v>
@@ -70973,6 +70973,32 @@
         <v>1719</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6909837963</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>1387079</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.52600002288818</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.53600001335144</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.55399990081787</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IRE.MI.xlsx
+++ b/data/IRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="1773">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,49 +44,49 @@
     <t xml:space="preserve">IRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923806250095367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927027225494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92187362909317</t>
+    <t xml:space="preserve">0.923806071281433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92702704668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921873390674591</t>
   </si>
   <si>
     <t xml:space="preserve">0.901902675628662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898037493228912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918652296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903835415840149</t>
+    <t xml:space="preserve">0.898037314414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918652474880219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903835237026215</t>
   </si>
   <si>
     <t xml:space="preserve">0.880643665790558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863893985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841346442699432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85165399312973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818154633045197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836192727088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856163382530212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857451856136322</t>
+    <t xml:space="preserve">0.863893926143646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841346502304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851653873920441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818154513835907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836192607879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856163322925568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857451915740967</t>
   </si>
   <si>
     <t xml:space="preserve">0.869691908359528</t>
@@ -95,136 +95,136 @@
     <t xml:space="preserve">0.886441588401794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.875489771366119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908344805240631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888374090194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855519354343414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843279004096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818798899650574</t>
+    <t xml:space="preserve">0.875489950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908344864845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888374149799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85551917552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84327906370163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818798840045929</t>
   </si>
   <si>
     <t xml:space="preserve">0.837481141090393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825241029262543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848432838916779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869047701358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876778364181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894172072410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923161864280701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927671372890472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914142727851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945709586143494</t>
+    <t xml:space="preserve">0.825241088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869047820568085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876778185367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894172191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923161923885345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927671492099762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914142787456512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945709407329559</t>
   </si>
   <si>
     <t xml:space="preserve">0.919296622276306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916075468063354</t>
+    <t xml:space="preserve">0.916075587272644</t>
   </si>
   <si>
     <t xml:space="preserve">0.941200017929077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947642087936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930892527103424</t>
+    <t xml:space="preserve">0.947642028331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930892586708069</t>
   </si>
   <si>
     <t xml:space="preserve">0.934113621711731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906412243843079</t>
+    <t xml:space="preserve">0.906412303447723</t>
   </si>
   <si>
     <t xml:space="preserve">0.918008148670197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95408433675766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964391827583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999179363250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01270806789398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02881348133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0165730714798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02365958690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00819838047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00175631046295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00497734546661</t>
+    <t xml:space="preserve">0.954084455966949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964391887187958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999179482460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01270771026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02881336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01657319068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02365970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00819849967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00175619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00497722625732</t>
   </si>
   <si>
     <t xml:space="preserve">1.00755429267883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02172696590424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01464068889618</t>
+    <t xml:space="preserve">1.02172684669495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0146404504776</t>
   </si>
   <si>
     <t xml:space="preserve">1.02237117290497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999823689460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01141941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01206374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01786172389984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430367469788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01850569248199</t>
+    <t xml:space="preserve">0.999823749065399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01141953468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01206362247467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01786184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430391311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01850593090057</t>
   </si>
   <si>
     <t xml:space="preserve">1.02688074111938</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">1.03203451633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02494788169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01721739768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00562155246735</t>
+    <t xml:space="preserve">1.02494812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01721751689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00562167167664</t>
   </si>
   <si>
     <t xml:space="preserve">0.988871932029724</t>
@@ -248,55 +248,55 @@
     <t xml:space="preserve">1.00368881225586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03525543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02816927433014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04040908813477</t>
+    <t xml:space="preserve">1.03525567054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02816903591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04040920734406</t>
   </si>
   <si>
     <t xml:space="preserve">1.03396713733673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02945756912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03010189533234</t>
+    <t xml:space="preserve">1.0294576883316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03010177612305</t>
   </si>
   <si>
     <t xml:space="preserve">1.01592910289764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992092967033386</t>
+    <t xml:space="preserve">0.992093026638031</t>
   </si>
   <si>
     <t xml:space="preserve">1.033322930336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00948679447174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995958566665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995314121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02108263969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04942834377289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07519686222076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06295692920685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05715894699097</t>
+    <t xml:space="preserve">1.00948703289032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995958268642426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995314240455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0210827589035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07519698143005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06295680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05715882778168</t>
   </si>
   <si>
     <t xml:space="preserve">1.07326424121857</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">1.06360101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0616682767868</t>
+    <t xml:space="preserve">1.06166839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.06811046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04620730876923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977276027202606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968257069587708</t>
+    <t xml:space="preserve">1.04620718955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977276086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968257009983063</t>
   </si>
   <si>
     <t xml:space="preserve">0.965036034584045</t>
@@ -332,73 +332,73 @@
     <t xml:space="preserve">0.978564560413361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962522447109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979233086109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960517346858978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907712280750275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876964926719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903701603412628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895680606365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929101526737213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935117304325104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939127743244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909048974514008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903033137321472</t>
+    <t xml:space="preserve">0.962522506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979232847690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960517287254333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907712161540985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87696498632431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903701722621918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895680665969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929101467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935117423534393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939127802848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909048914909363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903033196926117</t>
   </si>
   <si>
     <t xml:space="preserve">0.915733158588409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925090849399567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931775212287903</t>
+    <t xml:space="preserve">0.925090909004211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931775033473969</t>
   </si>
   <si>
     <t xml:space="preserve">0.925759375095367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912391066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921080589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927096247673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945143580436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937122523784637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955838143825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953164517879486</t>
+    <t xml:space="preserve">0.912391185760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921080470085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927096307277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945143699645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937122702598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955838024616241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95316469669342</t>
   </si>
   <si>
     <t xml:space="preserve">0.964527666568756</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">0.982574999332428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98391181230545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972548842430115</t>
+    <t xml:space="preserve">0.98391193151474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972548604011536</t>
   </si>
   <si>
     <t xml:space="preserve">0.973217129707336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984580338001251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987254023551941</t>
+    <t xml:space="preserve">0.984580218791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987253904342651</t>
   </si>
   <si>
     <t xml:space="preserve">0.995274841785431</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">0.989259243011475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99260139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975890874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951827883720398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950490891933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948485553264618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941132962703705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954501509666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965864598751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985917091369629</t>
+    <t xml:space="preserve">0.992601275444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97589099407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951827824115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950491070747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948485612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94113302230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954501390457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965864479541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985917210578918</t>
   </si>
   <si>
     <t xml:space="preserve">0.989927649497986</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">1.02000641822815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99193286895752</t>
+    <t xml:space="preserve">0.99193274974823</t>
   </si>
   <si>
     <t xml:space="preserve">0.988590717315674</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">0.996611773967743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979901373386383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96720153093338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98658561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977896153926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973885536193848</t>
+    <t xml:space="preserve">0.979901134967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967201292514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986585378646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977896273136139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973885655403137</t>
   </si>
   <si>
     <t xml:space="preserve">0.995943367481232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02401685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00864326953888</t>
+    <t xml:space="preserve">1.02401697635651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00864338874817</t>
   </si>
   <si>
     <t xml:space="preserve">1.00262749195099</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.969206690788269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97522234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985248684883118</t>
+    <t xml:space="preserve">0.97522246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985248565673828</t>
   </si>
   <si>
     <t xml:space="preserve">1.0293642282486</t>
@@ -518,49 +518,49 @@
     <t xml:space="preserve">1.05342733860016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05543255805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07615339756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08952212333679</t>
+    <t xml:space="preserve">1.05543267726898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07615351676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08952188491821</t>
   </si>
   <si>
     <t xml:space="preserve">1.09420084953308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09687459468842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07013773918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08751666545868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09353256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07749032974243</t>
+    <t xml:space="preserve">1.09687447547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0701379776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08751678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09353244304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07749044895172</t>
   </si>
   <si>
     <t xml:space="preserve">1.06479048728943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06278502941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04741156101227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06077992916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06813251972198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05209052562714</t>
+    <t xml:space="preserve">1.0627852678299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04741168022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06077980995178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06813263893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05209040641785</t>
   </si>
   <si>
     <t xml:space="preserve">0.957843482494354</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">0.953833043575287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946480333805084</t>
+    <t xml:space="preserve">0.946480393409729</t>
   </si>
   <si>
     <t xml:space="preserve">0.93578565120697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942469775676727</t>
+    <t xml:space="preserve">0.942469954490662</t>
   </si>
   <si>
     <t xml:space="preserve">0.933780372142792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913727939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917738437652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941801428794861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918406844139099</t>
+    <t xml:space="preserve">0.913727879524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917738497257233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941801488399506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918406903743744</t>
   </si>
   <si>
     <t xml:space="preserve">0.968538165092468</t>
@@ -599,55 +599,55 @@
     <t xml:space="preserve">0.967869758605957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980569779872894</t>
+    <t xml:space="preserve">0.980569660663605</t>
   </si>
   <si>
     <t xml:space="preserve">0.994606554508209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997948825359344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01332223415375</t>
+    <t xml:space="preserve">0.997948706150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01332211494446</t>
   </si>
   <si>
     <t xml:space="preserve">1.01532757282257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0159957408905</t>
+    <t xml:space="preserve">1.01599597930908</t>
   </si>
   <si>
     <t xml:space="preserve">1.02869582176208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03203797340393</t>
+    <t xml:space="preserve">1.03203809261322</t>
   </si>
   <si>
     <t xml:space="preserve">1.04005897045135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04473793506622</t>
+    <t xml:space="preserve">1.04473781585693</t>
   </si>
   <si>
     <t xml:space="preserve">1.03070116043091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0173327922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.036048412323</t>
+    <t xml:space="preserve">1.01733267307281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03604829311371</t>
   </si>
   <si>
     <t xml:space="preserve">1.04874849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0494167804718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05275905132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0500853061676</t>
+    <t xml:space="preserve">1.04941701889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05275893211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05008518695831</t>
   </si>
   <si>
     <t xml:space="preserve">1.04072737693787</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">1.04607474803925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02468526363373</t>
+    <t xml:space="preserve">1.02468550205231</t>
   </si>
   <si>
     <t xml:space="preserve">1.01064848899841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00530099868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03003251552582</t>
+    <t xml:space="preserve">1.00530111789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03003263473511</t>
   </si>
   <si>
     <t xml:space="preserve">1.0427325963974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02334856987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05676925182343</t>
+    <t xml:space="preserve">1.02334845066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.056769490242</t>
   </si>
   <si>
     <t xml:space="preserve">1.06412196159363</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">1.05610108375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05810630321503</t>
+    <t xml:space="preserve">1.05810618400574</t>
   </si>
   <si>
     <t xml:space="preserve">1.08484303951263</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">1.07080626487732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0821692943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06880104541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07815873622894</t>
+    <t xml:space="preserve">1.08216953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0688009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07815885543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.0828378200531</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">1.08818507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09620606899261</t>
+    <t xml:space="preserve">1.0962061882019</t>
   </si>
   <si>
     <t xml:space="preserve">1.09954822063446</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">1.09754288196564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12628483772278</t>
+    <t xml:space="preserve">1.12628495693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.18978464603424</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">1.22120034694672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22988975048065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24058437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26665282249451</t>
+    <t xml:space="preserve">1.22988986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24058449268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2666529417038</t>
   </si>
   <si>
     <t xml:space="preserve">1.28002107143402</t>
@@ -743,85 +743,85 @@
     <t xml:space="preserve">1.29405784606934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27133166790009</t>
+    <t xml:space="preserve">1.27133178710938</t>
   </si>
   <si>
     <t xml:space="preserve">1.26932644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30074214935303</t>
+    <t xml:space="preserve">1.30074203014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.31009984016418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30475270748138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30007386207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31143689155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29004740715027</t>
+    <t xml:space="preserve">1.30475258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30007374286652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3114367723465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29004728794098</t>
   </si>
   <si>
     <t xml:space="preserve">1.28871059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29739999771118</t>
+    <t xml:space="preserve">1.29740011692047</t>
   </si>
   <si>
     <t xml:space="preserve">1.28937911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2720000743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25930023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29673159122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29806864261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3107682466507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29338943958282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32814717292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30341577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33683681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349466323853</t>
+    <t xml:space="preserve">1.27200019359589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2593001127243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29673171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29806852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31076836585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2933896780014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32814729213715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30341601371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33683669567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349478244781</t>
   </si>
   <si>
     <t xml:space="preserve">1.35421574115753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37025773525238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426817417145</t>
+    <t xml:space="preserve">1.37025761604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426805496216</t>
   </si>
   <si>
     <t xml:space="preserve">1.364910364151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37961542606354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33616840839386</t>
+    <t xml:space="preserve">1.37961554527283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33616816997528</t>
   </si>
   <si>
     <t xml:space="preserve">1.34886813163757</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">1.3903101682663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41036283969879</t>
+    <t xml:space="preserve">1.4103627204895</t>
   </si>
   <si>
     <t xml:space="preserve">1.42105734348297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175196647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4504679441452</t>
+    <t xml:space="preserve">1.43175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45046782493591</t>
   </si>
   <si>
     <t xml:space="preserve">1.39966809749603</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">1.41303658485413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43442559242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4170469045639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42239427566528</t>
+    <t xml:space="preserve">1.43442571163177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704678535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42239439487457</t>
   </si>
   <si>
     <t xml:space="preserve">1.40902590751648</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">1.44779396057129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47052037715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46784687042236</t>
+    <t xml:space="preserve">1.47052049636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46784663200378</t>
   </si>
   <si>
     <t xml:space="preserve">1.46116256713867</t>
@@ -887,40 +887,40 @@
     <t xml:space="preserve">1.4847424030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48336637020111</t>
+    <t xml:space="preserve">1.48336613178253</t>
   </si>
   <si>
     <t xml:space="preserve">1.49024641513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47235798835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42282092571259</t>
+    <t xml:space="preserve">1.47235822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42282068729401</t>
   </si>
   <si>
     <t xml:space="preserve">1.44208526611328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40630853176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3953001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39942824840546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40080416202545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40218031406403</t>
+    <t xml:space="preserve">1.40630829334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39530003070831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39942800998688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40080428123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40218019485474</t>
   </si>
   <si>
     <t xml:space="preserve">1.38429188728333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41456460952759</t>
+    <t xml:space="preserve">1.4145644903183</t>
   </si>
   <si>
     <t xml:space="preserve">1.4214448928833</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">1.44483733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45997381210327</t>
+    <t xml:space="preserve">1.45997369289398</t>
   </si>
   <si>
     <t xml:space="preserve">1.44621336460114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46685397624969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48199045658112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46960592269897</t>
+    <t xml:space="preserve">1.46685385704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48199057579041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46960580348969</t>
   </si>
   <si>
     <t xml:space="preserve">1.44758951663971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47923839092255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50400698184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50125479698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49987876415253</t>
+    <t xml:space="preserve">1.47923815250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50400686264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5012549161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49987888336182</t>
   </si>
   <si>
     <t xml:space="preserve">1.50675892829895</t>
@@ -977,769 +977,769 @@
     <t xml:space="preserve">1.52602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54804015159607</t>
+    <t xml:space="preserve">1.54803991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54115998744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52327144145966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52189517021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54528784751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57968902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57831275463104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57556068897247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693696022034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5631765127182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5466639995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55354416370392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56592857837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58381688594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069740772247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58656907081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58244097232819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60996150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63197827339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64711463451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61408960819244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583364963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60032939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455254554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53978371620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53565561771393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54391193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56180024147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54941594600677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427958488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57005643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62234592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61684167385101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62922608852386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61133766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59482526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5728086233139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62509787082672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6608749628067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66637909412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69940400123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70353209972382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6980277299881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69252395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64023447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65949892997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64986658096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62785041332245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6622508764267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67601144313812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70490789413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74894118309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73105275630951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72004437446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73518085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72830069065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7668297290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77233362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77371001243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82049465179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79022228717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78747022151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444531440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79159843921661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79297471046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76820576190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75857353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72554850578308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72967672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72142040729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75169324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81499099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80535876750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74481332302094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77921390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84113574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83700752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85351955890656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86040031909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88516855239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85076785087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80123054981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79710257053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957261800766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82737505435944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564355373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64573848247528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67738723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68151533603668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66913115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68013942241669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.642986536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66500306129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68701946735382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69114780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63335430622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463529109955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71454036235809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70215582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69527578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68426740169525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67876362800598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65261876583099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75306916236877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74756491184235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73930883407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72417259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72692453861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362702846527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68289172649384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7131644487381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74343705177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73380470275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74206137657166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75994968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71178817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68839538097382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65399479866028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64849042892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60720944404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59757709503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59620118141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290355205536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46134984493256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4764860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48611855506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47511005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572217464447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42832493782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51776742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55079209804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54542100429535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56530702114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54826211929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52411472797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121662139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52127397060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52837598323822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56672763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55536413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56246626377106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59513592720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60507905483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60934019088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6221239566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58945429325104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57951128482819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60223805904388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60365843772888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59371554851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63632810115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63348746299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62638509273529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61076056957245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58803379535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59229516983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6888839006424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68178188800812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69882702827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72013318538666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71729242801666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64911198616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66757762432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67894113063812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67752039432526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67183887958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.643430352211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6192831993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61786293983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56388664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962526798248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55394375324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55252325534821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55110263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51701235771179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51559245586395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871829032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43462812900543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44741189479828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45735478401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47155904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47013854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47297942638397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5326372385025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58377242088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973948955536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51275134086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48718392848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47724080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49144494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50138819217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49996757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49570631980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41687273979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4218442440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38065183162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37426018714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3522435426712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37994170188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37070894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573755741119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37923169136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37212944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35579442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38633358478546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36431705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39343571662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130520820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35863530635834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40906047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40124809741974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45309364795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47439980506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47866117954254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45593428611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42894649505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44030976295471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39556634426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38704371452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39201533794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37781119346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40266859531403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38136208057404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351982831955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36076593399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940254688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43178713321686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43320751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42468512058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042374610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48150205612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51985359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4886040687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49428594112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54258012771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.54115986824036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52327144145966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52189517021179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5452880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57968878746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57831263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57556056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693684101105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56317639350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5466639995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55354428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56592857837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58381700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58656907081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58244073390961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60996150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63197827339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64711475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61408960819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583353042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60032951831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53978395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5356559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54391193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56180047988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56042420864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54941618442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427982330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57005655765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868028640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62234592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61684155464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61133754253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59482550621033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57280850410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61821782588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62509775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66087484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66637885570526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69940388202667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70353209972382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6980277299881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69252359867096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65949869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64986670017242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62785005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6622508764267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67601132392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70490789413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74894118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73105311393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72004425525665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73518109321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72830092906952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76682960987091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77233397960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545369625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77370989322662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74068510532379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8204950094223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79022216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78747022151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444531440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79159843921661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79297423362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76820552349091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75857353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72554874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72967672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72142052650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75169312953949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81499075889587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80535864830017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031709671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74481320381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77921414375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84113574028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83700752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85351991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86039996147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88516855239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85076785087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80123043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79710245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957261800766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82737529277802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64573848247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67738711833954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.634730219841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68151545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66913104057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68013918399811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.642986536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66500282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68701958656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69114744663239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6333544254303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463517189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71454036235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70215582847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69527566432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68426740169525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6787633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6526186466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75306940078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74756503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7393091917038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72417271137238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72692489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6636266708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68289160728455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7131644487381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74343717098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73380470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74206113815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7599493265152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71178805828094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6883956193924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65399467945099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64849054813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60720956325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59757721424103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59620118141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290367126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4929986000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46134984493256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47648596763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48611843585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4751101732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4572217464447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42832493782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51776719093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55079221725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54542124271393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56530702114105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54826200008392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52411460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5312168598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52127373218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52837598323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56672751903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55536413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56246626377106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5951361656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60507893562317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60934031009674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62212371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58945441246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5795111656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60223829746246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60365855693817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59371554851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62922608852386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63632822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63348734378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62638509273529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61076045036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58803403377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59229516983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68888413906097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68178188800812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69882690906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72013294696808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71729207038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64911198616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6675773859024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67894077301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67752027511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67183876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.643430352211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61928296089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61786282062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5766704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56388652324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962550640106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5539436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5525233745575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55110275745392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51701259613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51559245586395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871829032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43462800979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44741189479828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45735502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47155916690826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47013866901398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47297954559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53263735771179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58377265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973925113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51275146007538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48718392848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47724080085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49144494533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50138819217682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49996769428253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49570620059967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41687273979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4218442440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39911735057831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38065183162689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37426006793976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3522435426712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37994170188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37070882320404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3657374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37923145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37212944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35579454898834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38633358478546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36431705951691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39343571662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3913049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35863542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40906035900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40124809741974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46019566059113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45309364795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47439992427826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47866117954254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45593452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42894649505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.440309882164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39556634426117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37568032741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38704371452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39201521873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37781119346619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40266859531403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38136219978333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33519840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36076593399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940254688263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43178713321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43320763111115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42468512058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4204238653183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48150205612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51985347270966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4886040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49428594112396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54258024692535</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.52553510665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.5297966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52695572376251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405773639679</t>
+    <t xml:space="preserve">1.52695560455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405785560608</t>
   </si>
   <si>
     <t xml:space="preserve">1.51133096218109</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">1.5099104642868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48008179664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49854707717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50706970691681</t>
+    <t xml:space="preserve">1.48008155822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49854695796967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.48292243480682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48434281349182</t>
+    <t xml:space="preserve">1.48434269428253</t>
   </si>
   <si>
     <t xml:space="preserve">1.50564920902252</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">1.53689849376678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61644232273102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62780570983887</t>
+    <t xml:space="preserve">1.61644244194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62780582904816</t>
   </si>
   <si>
     <t xml:space="preserve">1.63206708431244</t>
@@ -1781,91 +1781,91 @@
     <t xml:space="preserve">1.60081768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62496483325958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939742088318</t>
+    <t xml:space="preserve">1.62496471405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939730167389</t>
   </si>
   <si>
     <t xml:space="preserve">1.62070345878601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61502182483673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64627146720886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61218106746674</t>
+    <t xml:space="preserve">1.61502194404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64627122879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61218094825745</t>
   </si>
   <si>
     <t xml:space="preserve">1.51417183876038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50422894954681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4857634305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4630366563797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45877540111542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49286544322968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55678462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57809054851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58661353588104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57382965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63916921615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70450854301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70166766643524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69172465801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69061779975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69356298446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69798123836517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67294597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68325448036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68619990348816</t>
+    <t xml:space="preserve">1.50422883033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576331138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45877516269684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49286532402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5567843914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57809090614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58661341667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57382941246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63916897773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70450866222382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70166754722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69172441959381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6906179189682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69356310367584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69798111915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67294585704803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68325459957123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68619966506958</t>
   </si>
   <si>
     <t xml:space="preserve">1.72890710830688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75099718570709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7627786397934</t>
+    <t xml:space="preserve">1.75099694728851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76277828216553</t>
   </si>
   <si>
     <t xml:space="preserve">1.74510622024536</t>
@@ -1874,118 +1874,118 @@
     <t xml:space="preserve">1.73332524299622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77161431312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77750504016876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812204837799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8010675907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80548572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401313304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8113762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77455961704254</t>
+    <t xml:space="preserve">1.77161419391632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77750492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812216758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80106770992279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80548548698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401289463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81137645244598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77455985546112</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603232860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76719629764557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74216115474701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70239913463593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7392156124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77014172077179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78486835956573</t>
+    <t xml:space="preserve">1.76719641685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7421612739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70239925384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73921573162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7701416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78486824035645</t>
   </si>
   <si>
     <t xml:space="preserve">1.78928625583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79664969444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79517686367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79370450973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78339576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7995947599411</t>
+    <t xml:space="preserve">1.79664981365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79517698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79370427131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78339564800262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79959487915039</t>
   </si>
   <si>
     <t xml:space="preserve">1.80254018306732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77308690547943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192293643951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83493900299072</t>
+    <t xml:space="preserve">1.77308666706085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7819230556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83493888378143</t>
   </si>
   <si>
     <t xml:space="preserve">1.8202121257782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81873965263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82168471813202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84966540336609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84819293022156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82904803752899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76425087451935</t>
+    <t xml:space="preserve">1.81873953342438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82168459892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84966552257538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84819269180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82904815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76425075531006</t>
   </si>
   <si>
     <t xml:space="preserve">1.81432151794434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.809903383255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8319935798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86144697666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91593515872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93655264377594</t>
+    <t xml:space="preserve">1.80990374088287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83199346065521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8614467382431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91593539714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93655288219452</t>
   </si>
   <si>
     <t xml:space="preserve">1.93213474750519</t>
@@ -1997,43 +1997,43 @@
     <t xml:space="preserve">1.97042405605316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9556976556778</t>
+    <t xml:space="preserve">1.95569717884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.94244337081909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94980669021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96158766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98809564113617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99693202972412</t>
+    <t xml:space="preserve">1.94980645179749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96158802509308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98809587955475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99693191051483</t>
   </si>
   <si>
     <t xml:space="preserve">2.00724053382874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98367786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99987733364105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0057680606842</t>
+    <t xml:space="preserve">1.98367762565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99987709522247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00576782226562</t>
   </si>
   <si>
     <t xml:space="preserve">1.98073256015778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9718964099884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97631478309631</t>
+    <t xml:space="preserve">1.97189664840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97631454467773</t>
   </si>
   <si>
     <t xml:space="preserve">1.94391596317291</t>
@@ -2048,25 +2048,25 @@
     <t xml:space="preserve">1.97484183311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01754927635193</t>
+    <t xml:space="preserve">2.01754903793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.04847502708435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02049422264099</t>
+    <t xml:space="preserve">2.02049446105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.04552984237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03374814987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05436587333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02785801887512</t>
+    <t xml:space="preserve">2.03374838829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05436563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02785778045654</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227567672729</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">1.99251401424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02638530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07940101623535</t>
+    <t xml:space="preserve">2.02638506889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07940077781677</t>
   </si>
   <si>
     <t xml:space="preserve">2.06467413902283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07203793525696</t>
+    <t xml:space="preserve">2.0720374584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.06172895431519</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">2.03522086143494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02933073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06614708900452</t>
+    <t xml:space="preserve">2.02933049201965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06614685058594</t>
   </si>
   <si>
     <t xml:space="preserve">2.07645559310913</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">2.08676433563232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02196717262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05731081962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07351016998291</t>
+    <t xml:space="preserve">2.02196741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05731105804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07351040840149</t>
   </si>
   <si>
     <t xml:space="preserve">2.04700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00282263755798</t>
+    <t xml:space="preserve">2.0028223991394</t>
   </si>
   <si>
     <t xml:space="preserve">2.0131311416626</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">2.01460409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04258418083191</t>
+    <t xml:space="preserve">2.04258441925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.11179971694946</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">2.08087372779846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07498288154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11032676696777</t>
+    <t xml:space="preserve">2.0749831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11032700538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.13683485984802</t>
@@ -2159,25 +2159,25 @@
     <t xml:space="preserve">2.10885429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12652659416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17659664154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20457744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19426846504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24581217765808</t>
+    <t xml:space="preserve">2.12652635574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17659711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20457768440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19426870346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2458119392395</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519469261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21341323852539</t>
+    <t xml:space="preserve">2.21341300010681</t>
   </si>
   <si>
     <t xml:space="preserve">2.20899534225464</t>
@@ -2186,64 +2186,64 @@
     <t xml:space="preserve">2.2178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20163178443909</t>
+    <t xml:space="preserve">2.20163202285767</t>
   </si>
   <si>
     <t xml:space="preserve">2.20752263069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17365145683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23255825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21930432319641</t>
+    <t xml:space="preserve">2.17365121841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23255801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21930408477783</t>
   </si>
   <si>
     <t xml:space="preserve">2.21635890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20310473442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24728488922119</t>
+    <t xml:space="preserve">2.20310497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24728465080261</t>
   </si>
   <si>
     <t xml:space="preserve">2.2870466709137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26201128959656</t>
+    <t xml:space="preserve">2.26201105117798</t>
   </si>
   <si>
     <t xml:space="preserve">2.25022983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11474514007568</t>
+    <t xml:space="preserve">2.1147449016571</t>
   </si>
   <si>
     <t xml:space="preserve">2.11621761322021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1530339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13094425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0249125957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08823680877686</t>
+    <t xml:space="preserve">2.15303421020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13094401359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02491235733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08823704719543</t>
   </si>
   <si>
     <t xml:space="preserve">2.10296368598938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83641159534454</t>
+    <t xml:space="preserve">1.98220491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83641147613525</t>
   </si>
   <si>
     <t xml:space="preserve">1.65380120277405</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">1.63318395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3872492313385</t>
+    <t xml:space="preserve">1.38724911212921</t>
   </si>
   <si>
     <t xml:space="preserve">1.42922008037567</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">1.35190522670746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043263435364</t>
+    <t xml:space="preserve">1.35043251514435</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330717563629</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">1.32171559333801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31508874893188</t>
+    <t xml:space="preserve">1.3150886297226</t>
   </si>
   <si>
     <t xml:space="preserve">1.40565729141235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37767672538757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49475359916687</t>
+    <t xml:space="preserve">1.37767684459686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49475347995758</t>
   </si>
   <si>
     <t xml:space="preserve">1.50948011875153</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">1.58311343193054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65674662590027</t>
+    <t xml:space="preserve">1.65674650669098</t>
   </si>
   <si>
     <t xml:space="preserve">1.55071473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5477694272995</t>
+    <t xml:space="preserve">1.54776930809021</t>
   </si>
   <si>
     <t xml:space="preserve">1.5359879732132</t>
@@ -2306,64 +2306,64 @@
     <t xml:space="preserve">1.56249606609344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56102323532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55365991592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54924213886261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54187893867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58164060115814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60225808620453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62434804439545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256659030914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61698484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62287509441376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64643812179565</t>
+    <t xml:space="preserve">1.56102335453033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55366003513336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5492422580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54187881946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58164072036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60225796699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62434816360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256670951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61698460578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62287533283234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64643776416779</t>
   </si>
   <si>
     <t xml:space="preserve">1.65527391433716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67589139938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66705513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64349269866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57574999332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58753132820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5580780506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57427752017975</t>
+    <t xml:space="preserve">1.67589116096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66705501079559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64349257946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60520339012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57575011253357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.587531208992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55807816982269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57427740097046</t>
   </si>
   <si>
     <t xml:space="preserve">1.59047675132751</t>
@@ -2372,40 +2372,40 @@
     <t xml:space="preserve">1.59784007072449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64201998710632</t>
+    <t xml:space="preserve">1.64201986789703</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558253765106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6287659406662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61109399795532</t>
+    <t xml:space="preserve">1.62876582145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61109411716461</t>
   </si>
   <si>
     <t xml:space="preserve">1.6788364648819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71859860420227</t>
+    <t xml:space="preserve">1.71859872341156</t>
   </si>
   <si>
     <t xml:space="preserve">1.76572358608246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75836038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72007131576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7082896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6390745639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821933746338</t>
+    <t xml:space="preserve">1.75836026668549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72007095813751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70828974246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63907468318939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821921825409</t>
   </si>
   <si>
     <t xml:space="preserve">1.70534443855286</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">1.76836574077606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71468603610992</t>
+    <t xml:space="preserve">1.71468591690063</t>
   </si>
   <si>
     <t xml:space="preserve">1.69781517982483</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">1.71161866188049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71621966362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69168031215668</t>
+    <t xml:space="preserve">1.71621954441071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69168043136597</t>
   </si>
   <si>
     <t xml:space="preserve">1.70548367500305</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">1.73462426662445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73769164085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73002314567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68707919120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68554556369781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67327570915222</t>
+    <t xml:space="preserve">1.73769176006317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73002302646637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68707931041718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68554532527924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67327582836151</t>
   </si>
   <si>
     <t xml:space="preserve">1.65793871879578</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">1.68401181697845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70241618156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72235441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7070175409317</t>
+    <t xml:space="preserve">1.70241641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72235453128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70701742172241</t>
   </si>
   <si>
     <t xml:space="preserve">1.66867482662201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64566898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65333771705627</t>
+    <t xml:space="preserve">1.64566910266876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6533374786377</t>
   </si>
   <si>
     <t xml:space="preserve">1.65640509128571</t>
@@ -2495,97 +2495,97 @@
     <t xml:space="preserve">1.63646686077118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64720284938812</t>
+    <t xml:space="preserve">1.64720273017883</t>
   </si>
   <si>
     <t xml:space="preserve">1.67020845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66407358646393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68247818946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7284893989563</t>
+    <t xml:space="preserve">1.66407346725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68247807025909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72848951816559</t>
   </si>
   <si>
     <t xml:space="preserve">1.73615777492523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75609612464905</t>
+    <t xml:space="preserve">1.75609600543976</t>
   </si>
   <si>
     <t xml:space="preserve">1.72695577144623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70088267326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72082078456879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69321393966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094444274902</t>
+    <t xml:space="preserve">1.70088255405426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7208206653595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69321417808533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094432353973</t>
   </si>
   <si>
     <t xml:space="preserve">1.67174220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69934904575348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778769493103</t>
+    <t xml:space="preserve">1.6993488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67787706851959</t>
   </si>
   <si>
     <t xml:space="preserve">1.69014656543732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71008491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68861269950867</t>
+    <t xml:space="preserve">1.71008479595184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68861281871796</t>
   </si>
   <si>
     <t xml:space="preserve">1.6518040895462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64873659610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62573087215424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61959600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59659039974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505665302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58738803863525</t>
+    <t xml:space="preserve">1.64873647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62573075294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61959612369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59659051895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505677223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58738815784454</t>
   </si>
   <si>
     <t xml:space="preserve">1.57971954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57358479499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54904544353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5505793094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49996662139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48156249523163</t>
+    <t xml:space="preserve">1.57358467578888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54904532432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057919025421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49996674060822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48156237602234</t>
   </si>
   <si>
     <t xml:space="preserve">1.4961324930191</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">1.50303423404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51990497112274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54751145839691</t>
+    <t xml:space="preserve">1.51990485191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54751169681549</t>
   </si>
   <si>
     <t xml:space="preserve">1.56438255310059</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">1.53064095973969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60425901412964</t>
+    <t xml:space="preserve">1.60425889492035</t>
   </si>
   <si>
     <t xml:space="preserve">1.59198927879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965789318085</t>
+    <t xml:space="preserve">1.59965777397156</t>
   </si>
   <si>
     <t xml:space="preserve">1.60119152069092</t>
@@ -2627,22 +2627,22 @@
     <t xml:space="preserve">1.57511842250824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6027250289917</t>
+    <t xml:space="preserve">1.60272514820099</t>
   </si>
   <si>
     <t xml:space="preserve">1.66100597381592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7407591342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76069736480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388803958893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69628143310547</t>
+    <t xml:space="preserve">1.74075901508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76069724559784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388815879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69628131389618</t>
   </si>
   <si>
     <t xml:space="preserve">1.63186573982239</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">1.62879836559296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63033187389374</t>
+    <t xml:space="preserve">1.63033199310303</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889219045639</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">1.58585453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6395343542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64260160923004</t>
+    <t xml:space="preserve">1.63953411579132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64260172843933</t>
   </si>
   <si>
     <t xml:space="preserve">1.63493299484253</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">1.66714107990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62266337871552</t>
+    <t xml:space="preserve">1.6226634979248</t>
   </si>
   <si>
     <t xml:space="preserve">1.555180311203</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">1.55671393871307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56131505966187</t>
+    <t xml:space="preserve">1.56131517887115</t>
   </si>
   <si>
     <t xml:space="preserve">1.56898367404938</t>
@@ -2711,34 +2711,34 @@
     <t xml:space="preserve">1.60732626914978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63339960575104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62419724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61192750930786</t>
+    <t xml:space="preserve">1.63339936733246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62419712543488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61192739009857</t>
   </si>
   <si>
     <t xml:space="preserve">1.58432078361511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61806237697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64106798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66560733318329</t>
+    <t xml:space="preserve">1.61806225776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64106810092926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.665607213974</t>
   </si>
   <si>
     <t xml:space="preserve">1.67480945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71775317192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75762987136841</t>
+    <t xml:space="preserve">1.71775341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75762975215912</t>
   </si>
   <si>
     <t xml:space="preserve">1.80517494678497</t>
@@ -2747,16 +2747,16 @@
     <t xml:space="preserve">1.8174444437027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8082423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80670845508575</t>
+    <t xml:space="preserve">1.80824220180511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80670821666718</t>
   </si>
   <si>
     <t xml:space="preserve">1.80364108085632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79903984069824</t>
+    <t xml:space="preserve">1.79903995990753</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290521144867</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">1.82051205635071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78063535690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79443883895874</t>
+    <t xml:space="preserve">1.78063523769379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79443895816803</t>
   </si>
   <si>
     <t xml:space="preserve">1.83278167247772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8097757101059</t>
+    <t xml:space="preserve">1.80977594852448</t>
   </si>
   <si>
     <t xml:space="preserve">1.82971394062042</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">1.85885453224182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83891630172729</t>
+    <t xml:space="preserve">1.83891642093658</t>
   </si>
   <si>
     <t xml:space="preserve">1.82818031311035</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">1.86498939990997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8557870388031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345589160919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84965229034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87112426757812</t>
+    <t xml:space="preserve">1.85578727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8634557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84965240955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8711245059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.89566338062286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90179836750031</t>
+    <t xml:space="preserve">1.90179860591888</t>
   </si>
   <si>
     <t xml:space="preserve">1.91866910457611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90026462078094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91100072860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94627594947815</t>
+    <t xml:space="preserve">1.90026450157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91100060939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94627618789673</t>
   </si>
   <si>
     <t xml:space="preserve">1.95394444465637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9156014919281</t>
+    <t xml:space="preserve">1.91560173034668</t>
   </si>
   <si>
     <t xml:space="preserve">1.92173659801483</t>
@@ -2834,34 +2834,34 @@
     <t xml:space="preserve">1.91713535785675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93553984165192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695004940033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96007943153381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99382054805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96621382236481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00609040260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00762414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01375913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00915789604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95701217651367</t>
+    <t xml:space="preserve">1.93553996086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695028781891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96007919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99382066726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96621406078339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00609064102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00762438774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01375889778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00915765762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95701193809509</t>
   </si>
   <si>
     <t xml:space="preserve">1.95854568481445</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">2.00302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01069188117981</t>
+    <t xml:space="preserve">2.01069164276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.01836037635803</t>
@@ -2885,31 +2885,31 @@
     <t xml:space="preserve">2.02909636497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0336971282959</t>
+    <t xml:space="preserve">2.03369736671448</t>
   </si>
   <si>
     <t xml:space="preserve">2.01682662963867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01631951332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99563097953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97335112094879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97175967693329</t>
+    <t xml:space="preserve">2.01631903648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99563086032867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97335135936737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.971759557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.94470584392548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9224259853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.916060090065</t>
+    <t xml:space="preserve">1.92242586612701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91606020927429</t>
   </si>
   <si>
     <t xml:space="preserve">1.91446888446808</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">1.92401742935181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92719995975494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971677780151</t>
+    <t xml:space="preserve">1.92720007896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971653938293</t>
   </si>
   <si>
     <t xml:space="preserve">1.96061992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95743691921234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96539425849915</t>
+    <t xml:space="preserve">1.95743727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96539413928986</t>
   </si>
   <si>
     <t xml:space="preserve">1.97494268417358</t>
@@ -2942,22 +2942,22 @@
     <t xml:space="preserve">1.98926520347595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96857702732086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91287767887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94788861274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449122905731</t>
+    <t xml:space="preserve">1.96857690811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91287755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478884935379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449099063873</t>
   </si>
   <si>
     <t xml:space="preserve">2.03223347663879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01950216293335</t>
+    <t xml:space="preserve">2.01950240135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.04655623435974</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.06247043609619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724429130554</t>
+    <t xml:space="preserve">2.06724452972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.07997584342957</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">2.13726663589478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14522409439087</t>
+    <t xml:space="preserve">2.14522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.18819189071655</t>
@@ -3002,22 +3002,22 @@
     <t xml:space="preserve">2.20251441001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1706862449646</t>
+    <t xml:space="preserve">2.17068600654602</t>
   </si>
   <si>
     <t xml:space="preserve">2.15158915519714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12453532218933</t>
+    <t xml:space="preserve">2.12453556060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.11816954612732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08315849304199</t>
+    <t xml:space="preserve">2.10066390037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08315873146057</t>
   </si>
   <si>
     <t xml:space="preserve">2.07042741775513</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">2.10862112045288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.089524269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0847499370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0879328250885</t>
+    <t xml:space="preserve">2.08952403068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08474969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.06565308570862</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">2.11180400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14840626716614</t>
+    <t xml:space="preserve">2.14840650558472</t>
   </si>
   <si>
     <t xml:space="preserve">2.12135243415833</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">2.1165783405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11339569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13249230384827</t>
+    <t xml:space="preserve">2.11339545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13249254226685</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612676620483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363241195679</t>
+    <t xml:space="preserve">2.14363217353821</t>
   </si>
   <si>
     <t xml:space="preserve">2.04178190231323</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">2.05928754806519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09589004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02586770057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03064227104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98767364025116</t>
+    <t xml:space="preserve">2.04019045829773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09588980674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02586793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03064203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98767387866974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01154518127441</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">2.15477204322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341755867004</t>
+    <t xml:space="preserve">2.18341779708862</t>
   </si>
   <si>
     <t xml:space="preserve">2.18978333473206</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">2.16113805770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20569753646851</t>
+    <t xml:space="preserve">2.20569729804993</t>
   </si>
   <si>
     <t xml:space="preserve">2.21842861175537</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">2.29163360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27412796020508</t>
+    <t xml:space="preserve">2.27412819862366</t>
   </si>
   <si>
     <t xml:space="preserve">2.2534396648407</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">2.23593425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25025677680969</t>
+    <t xml:space="preserve">2.25025701522827</t>
   </si>
   <si>
     <t xml:space="preserve">2.27571940422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27890229225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22161149978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23115968704224</t>
+    <t xml:space="preserve">2.27890253067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2216112613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23115992546082</t>
   </si>
   <si>
     <t xml:space="preserve">2.200923204422</t>
@@ -3143,10 +3143,10 @@
     <t xml:space="preserve">2.17546057701111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19296622276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19774055480957</t>
+    <t xml:space="preserve">2.19296598434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19774031639099</t>
   </si>
   <si>
     <t xml:space="preserve">2.10384702682495</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">2.15795493125916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17386937141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15954637527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12930989265442</t>
+    <t xml:space="preserve">2.17386913299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15954613685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12930965423584</t>
   </si>
   <si>
     <t xml:space="preserve">2.12771821022034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10702991485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07520174980164</t>
+    <t xml:space="preserve">2.10702967643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07520151138306</t>
   </si>
   <si>
     <t xml:space="preserve">2.07201886177063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08634161949158</t>
+    <t xml:space="preserve">2.086341381073</t>
   </si>
   <si>
     <t xml:space="preserve">2.14204096794128</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">2.09748125076294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09907269477844</t>
+    <t xml:space="preserve">2.09907293319702</t>
   </si>
   <si>
     <t xml:space="preserve">2.09111571311951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06883549690247</t>
+    <t xml:space="preserve">2.06883573532104</t>
   </si>
   <si>
     <t xml:space="preserve">2.01472806930542</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">2.02905058860779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97812533378601</t>
+    <t xml:space="preserve">1.9781254529953</t>
   </si>
   <si>
     <t xml:space="preserve">1.97016847133636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03700733184814</t>
+    <t xml:space="preserve">2.03700757026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.11976099014282</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">2.0354163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98130822181702</t>
+    <t xml:space="preserve">1.98130834102631</t>
   </si>
   <si>
     <t xml:space="preserve">2.02109336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96380281448364</t>
+    <t xml:space="preserve">1.96380257606506</t>
   </si>
   <si>
     <t xml:space="preserve">1.91128599643707</t>
@@ -3230,52 +3230,52 @@
     <t xml:space="preserve">1.89378070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90969467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00677061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00199675559998</t>
+    <t xml:space="preserve">1.90969491004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00677084922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0019965171814</t>
   </si>
   <si>
     <t xml:space="preserve">1.90651178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87945771217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8126186132431</t>
+    <t xml:space="preserve">1.87945795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81261849403381</t>
   </si>
   <si>
     <t xml:space="preserve">1.79193031787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7553277015686</t>
+    <t xml:space="preserve">1.75532782077789</t>
   </si>
   <si>
     <t xml:space="preserve">1.79033875465393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85558676719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8333066701889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84922099113464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83171546459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82534968852997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81102728843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82694137096405</t>
+    <t xml:space="preserve">1.85558664798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83330678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84922087192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83171534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82534980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8110271692276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82694125175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.83012402057648</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">1.85240375995636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88104939460754</t>
+    <t xml:space="preserve">1.88104915618896</t>
   </si>
   <si>
     <t xml:space="preserve">1.92879164218903</t>
@@ -3314,25 +3314,25 @@
     <t xml:space="preserve">2.01313638687134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98289978504181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0035879611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94311416149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93197453022003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95107126235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9542543888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786626815796</t>
+    <t xml:space="preserve">1.98289966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00358819961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9431140422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93197417259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95107138156891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95425415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786650657654</t>
   </si>
   <si>
     <t xml:space="preserve">1.90173780918121</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">1.93834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96221137046814</t>
+    <t xml:space="preserve">1.96221148967743</t>
   </si>
   <si>
     <t xml:space="preserve">1.9526629447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93038308620453</t>
+    <t xml:space="preserve">1.93038332462311</t>
   </si>
   <si>
     <t xml:space="preserve">1.93993151187897</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">1.90014612674713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91765177249908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192430973053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285545349121</t>
+    <t xml:space="preserve">1.91765189170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91924321651459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285533428192</t>
   </si>
   <si>
     <t xml:space="preserve">1.71235942840576</t>
@@ -3374,37 +3374,37 @@
     <t xml:space="preserve">1.61210060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66143441200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65984296798706</t>
+    <t xml:space="preserve">1.66143429279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65984284877777</t>
   </si>
   <si>
     <t xml:space="preserve">1.69007992744446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64711153507233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6168749332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483191490173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65506863594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70758521556854</t>
+    <t xml:space="preserve">1.64711165428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61687481403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483179569244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65506875514984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70758533477783</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964453458786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68053126335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65825176239014</t>
+    <t xml:space="preserve">1.68053138256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65825164318085</t>
   </si>
   <si>
     <t xml:space="preserve">1.68848836421967</t>
@@ -3425,16 +3425,16 @@
     <t xml:space="preserve">1.5850465297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58743381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54128277301788</t>
+    <t xml:space="preserve">1.58743369579315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54128289222717</t>
   </si>
   <si>
     <t xml:space="preserve">1.47842192649841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51025021076202</t>
+    <t xml:space="preserve">1.51025032997131</t>
   </si>
   <si>
     <t xml:space="preserve">1.53383469581604</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">1.54731154441833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51446163654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5026695728302</t>
+    <t xml:space="preserve">1.51446175575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50266945362091</t>
   </si>
   <si>
     <t xml:space="preserve">1.50688099861145</t>
@@ -3482,25 +3482,25 @@
     <t xml:space="preserve">1.46308124065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47403109073639</t>
+    <t xml:space="preserve">1.47403120994568</t>
   </si>
   <si>
     <t xml:space="preserve">1.47150421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48498106002808</t>
+    <t xml:space="preserve">1.48498117923737</t>
   </si>
   <si>
     <t xml:space="preserve">1.51783096790314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49171960353851</t>
+    <t xml:space="preserve">1.49171948432922</t>
   </si>
   <si>
     <t xml:space="preserve">1.46645045280457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45718514919281</t>
+    <t xml:space="preserve">1.4571852684021</t>
   </si>
   <si>
     <t xml:space="preserve">1.41591215133667</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">1.3990660905838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3620046377182</t>
+    <t xml:space="preserve">1.36200475692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.34347414970398</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">1.34178960323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26766681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26177060604095</t>
+    <t xml:space="preserve">1.26766669750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26177072525024</t>
   </si>
   <si>
     <t xml:space="preserve">1.27777445316315</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">1.29798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23144781589508</t>
+    <t xml:space="preserve">1.23144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">1.21291708946228</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">1.20365166664124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20533633232117</t>
+    <t xml:space="preserve">1.20533645153046</t>
   </si>
   <si>
     <t xml:space="preserve">1.175013422966</t>
@@ -3584,22 +3584,22 @@
     <t xml:space="preserve">1.10173296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11942136287689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1059445142746</t>
+    <t xml:space="preserve">1.11942148208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10594439506531</t>
   </si>
   <si>
     <t xml:space="preserve">1.14300584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16911733150482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21965539455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16490578651428</t>
+    <t xml:space="preserve">1.16911721229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21965551376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16490566730499</t>
   </si>
   <si>
     <t xml:space="preserve">1.13710963726044</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">1.11352527141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12700223922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12279057502747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0815178155899</t>
+    <t xml:space="preserve">1.12700212001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12279045581818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08151769638062</t>
   </si>
   <si>
     <t xml:space="preserve">1.10425996780396</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">1.16322124004364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14553272724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18427884578705</t>
+    <t xml:space="preserve">1.14553284645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18427872657776</t>
   </si>
   <si>
     <t xml:space="preserve">1.22470927238464</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.2575591802597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24492454528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25334763526917</t>
+    <t xml:space="preserve">1.24829375743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24492466449738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25334775447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818624019623</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">1.31567811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31652045249939</t>
+    <t xml:space="preserve">1.3165203332901</t>
   </si>
   <si>
     <t xml:space="preserve">1.3299971818924</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">1.38980078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35358166694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32747042179108</t>
+    <t xml:space="preserve">1.3535817861557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32747030258179</t>
   </si>
   <si>
     <t xml:space="preserve">1.34684324264526</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.32662808895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33589339256287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31062436103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29546272754669</t>
+    <t xml:space="preserve">1.33589327335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31062424182892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29546284675598</t>
   </si>
   <si>
     <t xml:space="preserve">1.30135893821716</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.25082075595856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2365015745163</t>
+    <t xml:space="preserve">1.23650169372559</t>
   </si>
   <si>
     <t xml:space="preserve">1.25503218173981</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">1.24660921096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21039032936096</t>
+    <t xml:space="preserve">1.21039021015167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24576687812805</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">1.46139669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4656081199646</t>
+    <t xml:space="preserve">1.46560823917389</t>
   </si>
   <si>
     <t xml:space="preserve">1.4041200876236</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">1.43360066413879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44370830059052</t>
+    <t xml:space="preserve">1.44370818138123</t>
   </si>
   <si>
     <t xml:space="preserve">1.39653921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42265057563782</t>
+    <t xml:space="preserve">1.42265069484711</t>
   </si>
   <si>
     <t xml:space="preserve">1.44623517990112</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">1.43781208992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42770457267761</t>
+    <t xml:space="preserve">1.42770445346832</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148533344269</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">1.38474702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727378845215</t>
+    <t xml:space="preserve">1.38727390766144</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327775478363</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">1.3881162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37716639041901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34431648254395</t>
+    <t xml:space="preserve">1.37716627120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34431636333466</t>
   </si>
   <si>
     <t xml:space="preserve">1.34515881538391</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">1.34094715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31230890750885</t>
+    <t xml:space="preserve">1.31230878829956</t>
   </si>
   <si>
     <t xml:space="preserve">1.41170072555542</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">1.53888845443726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5666846036911</t>
+    <t xml:space="preserve">1.56668448448181</t>
   </si>
   <si>
     <t xml:space="preserve">1.58689975738525</t>
@@ -3911,28 +3911,28 @@
     <t xml:space="preserve">1.60711514949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61132669448853</t>
+    <t xml:space="preserve">1.61132657527924</t>
   </si>
   <si>
     <t xml:space="preserve">1.5641576051712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57426524162292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521521091461</t>
+    <t xml:space="preserve">1.57426536083221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5852153301239</t>
   </si>
   <si>
     <t xml:space="preserve">1.61301124095917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58942663669586</t>
+    <t xml:space="preserve">1.58942675590515</t>
   </si>
   <si>
     <t xml:space="preserve">1.60037672519684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59784960746765</t>
+    <t xml:space="preserve">1.59784972667694</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543048381805</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">1.64754557609558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65007269382477</t>
+    <t xml:space="preserve">1.65007257461548</t>
   </si>
   <si>
     <t xml:space="preserve">1.62396109104156</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">1.62227654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58774220943451</t>
+    <t xml:space="preserve">1.58774209022522</t>
   </si>
   <si>
     <t xml:space="preserve">1.62480342388153</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">1.56752681732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57763457298279</t>
+    <t xml:space="preserve">1.5776344537735</t>
   </si>
   <si>
     <t xml:space="preserve">1.57342302799225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58353066444397</t>
+    <t xml:space="preserve">1.58353054523468</t>
   </si>
   <si>
     <t xml:space="preserve">1.57089602947235</t>
@@ -5328,6 +5328,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.47000002861023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64000010490417</t>
   </si>
 </sst>
 </file>
@@ -22532,7 +22535,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G649" t="s">
-        <v>482</v>
+        <v>356</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22558,7 +22561,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G650" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22584,7 +22587,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G651" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22610,7 +22613,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22636,7 +22639,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G653" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22662,7 +22665,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G654" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22688,7 +22691,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G655" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22714,7 +22717,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G656" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22740,7 +22743,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G657" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22766,7 +22769,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G658" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22792,7 +22795,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G659" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22818,7 +22821,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G660" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22844,7 +22847,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G661" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22870,7 +22873,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G662" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22896,7 +22899,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G663" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22922,7 +22925,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22948,7 +22951,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G665" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22974,7 +22977,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G666" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23000,7 +23003,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G667" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23026,7 +23029,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G668" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23052,7 +23055,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23078,7 +23081,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G670" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23104,7 +23107,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G671" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23130,7 +23133,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G672" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23156,7 +23159,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G673" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23208,7 +23211,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G675" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23234,7 +23237,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G676" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23286,7 +23289,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G678" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23312,7 +23315,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G679" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23338,7 +23341,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G680" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23364,7 +23367,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23390,7 +23393,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G682" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23416,7 +23419,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G683" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23442,7 +23445,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G684" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23468,7 +23471,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G685" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23494,7 +23497,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G686" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23520,7 +23523,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G687" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23572,7 +23575,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23624,7 +23627,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G691" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23728,7 +23731,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G695" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23754,7 +23757,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23780,7 +23783,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G697" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23806,7 +23809,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G698" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23832,7 +23835,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23858,7 +23861,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G700" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23884,7 +23887,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G701" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23910,7 +23913,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G702" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23936,7 +23939,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G703" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23962,7 +23965,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G704" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23988,7 +23991,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -24014,7 +24017,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G706" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -24040,7 +24043,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G707" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24066,7 +24069,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G708" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -24092,7 +24095,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G709" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -24118,7 +24121,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G710" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24144,7 +24147,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G711" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24170,7 +24173,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G712" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24196,7 +24199,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G713" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24222,7 +24225,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G714" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24248,7 +24251,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G715" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24274,7 +24277,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G716" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24300,7 +24303,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G717" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24326,7 +24329,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G718" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24352,7 +24355,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G719" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24378,7 +24381,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G720" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24404,7 +24407,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G721" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24430,7 +24433,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G722" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24456,7 +24459,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G723" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24482,7 +24485,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G724" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24508,7 +24511,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G725" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24534,7 +24537,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G726" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24560,7 +24563,7 @@
         <v>1.97300004959106</v>
       </c>
       <c r="G727" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24586,7 +24589,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G728" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24612,7 +24615,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G729" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24638,7 +24641,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G730" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24664,7 +24667,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v